--- a/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
+++ b/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
@@ -17,10 +17,10 @@
     <sheet name="Examples" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calculator'!$A$1:$AR$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trend_UP'!$A$1:$AR$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trend_DOWN'!$A$1:$AR$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tests'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calculator'!$A$1:$AZ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trend_UP'!$A$1:$AZ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trend_DOWN'!$A$1:$AZ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tests'!$A$1:$H$40</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -163,6 +163,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -891,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -938,6 +947,14 @@
     <col width="14" customWidth="1" min="42" max="42"/>
     <col width="14" customWidth="1" min="43" max="43"/>
     <col width="55" customWidth="1" min="44" max="44"/>
+    <col width="18" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="18" customWidth="1" min="50" max="50"/>
+    <col width="18" customWidth="1" min="51" max="51"/>
+    <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1161,6 +1178,46 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>RealizedFarLoss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>ClosedLotsForCosts</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>CostPerLot</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>OldFarClosedLot</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>BlockedReason</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>NetProfitBeforeFar</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>CostsBeforeFar</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>CostsFarClose</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -1181,27 +1238,27 @@
         <v/>
       </c>
       <c r="E2" s="12">
-        <f>IF(C2="SELL","BUY","SELL")</f>
+        <f>IF($B2="BLOCKED","",IF($C2="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F2" s="12">
-        <f>MAX(0,D2*Settings!$B$3)</f>
+        <f>IF($B2="BLOCKED",0,MAX(0,$D2*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G2" s="12">
-        <f>IFERROR(MAX(0,ROUND(F2/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H2" s="12">
-        <f>C2</f>
+        <f>IF($B2="BLOCKED","",$C2)</f>
         <v/>
       </c>
       <c r="I2" s="12">
-        <f>MAX(0,G2*Settings!$B$4)</f>
+        <f>IF($B2="BLOCKED",0,MAX(0,$G2*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J2" s="12">
-        <f>IFERROR(MAX(0,ROUND(I2/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K2" s="13" t="n">
@@ -1214,50 +1271,50 @@
         <v>100</v>
       </c>
       <c r="N2" s="14">
-        <f>IF(B2="BIG_SIDE",G2*MAX(0,K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="BIG_SIDE",$G2*MAX(0,$K2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O2" s="14">
-        <f>IF(B2="SMALL_SIDE",J2*ABS(L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P2" s="15">
-        <f>IF(B2="BIG_SIDE",J2*ABS(L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="BIG_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q2" s="15">
-        <f>IF(B2="SMALL_SIDE",AL2*ABS(K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$AL2*ABS($K2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R2" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT2*$AU2</f>
         <v/>
       </c>
       <c r="S2" s="14">
-        <f>IF(B2="BIG_SIDE",N2-P2-R2,O2-Q2-R2)</f>
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$R2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
         <v/>
       </c>
       <c r="T2" s="12">
-        <f>IF(AND(B2="BIG_SIDE",S2&gt;0),S2*Settings!$B$5,0)</f>
+        <f>IF(AND($B2="BIG_SIDE",$AX2&gt;0),$AX2*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U2" s="12">
-        <f>MAX(0,M2*Settings!$B$9)</f>
+        <f>MAX(0,$M2*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V2" s="12">
-        <f>IF(B2="BIG_SIDE",IFERROR(MIN(D2,MAX(0,T2/U2)),0),0)</f>
+        <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
         <v/>
       </c>
       <c r="W2" s="12">
-        <f>IF(B2="BIG_SIDE",MAX(0,D2-V2),AJ2)</f>
-        <v/>
-      </c>
-      <c r="X2" s="16">
-        <f>IF(B2="BIG_SIDE",IF(S2&gt;0,S2*Settings!$B$6,0),IF(S2&gt;0,S2*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y2" s="16">
+        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
+        <v/>
+      </c>
+      <c r="X2" s="19">
+        <f>IF($B2="BIG_SIDE",IF($AX2&gt;0,$AX2-$AS2,0),IF($S2&gt;0,$S2*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y2" s="19">
         <f>X2</f>
         <v/>
       </c>
@@ -1265,31 +1322,31 @@
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>Z2+S2</f>
+        <f>IF($B2="BLOCKED",$Z2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
         <v/>
       </c>
       <c r="AB2" s="12">
-        <f>D2+G2+J2</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1+$AJ1),$D2+$G2+$J2)</f>
         <v/>
       </c>
       <c r="AC2" s="12">
-        <f>IF(B2="BIG_SIDE",W2,AG2+AJ2)</f>
+        <f>IF($B2="BLOCKED",$AB2,IF($B2="BIG_SIDE",$W2,$AG2+$AJ2))</f>
         <v/>
       </c>
       <c r="AD2" s="12">
-        <f>AB2*Settings!$B$10</f>
+        <f>$AB2*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE2" s="12">
-        <f>AC2*Settings!$B$10</f>
+        <f>$AC2*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF(B2="SMALL_SIDE",E2,C2)</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,$C2,$AF1),IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF(B2="SMALL_SIDE",AM2,W2)</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -1301,39 +1358,71 @@
         <v>0</v>
       </c>
       <c r="AJ2" s="12">
-        <f>IF(B2="SMALL_SIDE",IF(AH2="YES",0,IFERROR(MAX(0,D2-MAX(0,AI2)/U2),D2)),0)</f>
+        <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
       <c r="AK2" s="12">
-        <f>IF(AND(AJ2&gt;0,AG2&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL2" s="12">
-        <f>IF(B2="SMALL_SIDE",G2*Settings!$B$7,IF(B2="BIG_SIDE",G2,0))</f>
+        <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
         <v/>
       </c>
       <c r="AM2" s="12">
-        <f>IF(B2="SMALL_SIDE",MAX(0,G2-AL2),0)</f>
+        <f>IF($B2="SMALL_SIDE",MAX(0,$G2-$AL2),0)</f>
         <v/>
       </c>
       <c r="AN2" s="12">
-        <f>IF(B2="BIG_SIDE",1,IF(B2="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B2="BIG_SIDE",1,IF($B2="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO2" s="12">
-        <f>IF(OR(B2="BIG_SIDE",B2="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP2" s="12">
-        <f>IF(OR(AQ2="DUAL_TAIL",AQ2="DANGER",AQ2="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ2" s="12">
-        <f>IF(AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G2/D2,999)&gt;Settings!$B$16,IFERROR(J2/G2,999)&gt;Settings!$B$17,AE2&gt;AD2,Y2&lt;0,AG2&gt;D2*1.0001,S2&lt;-100),"DANGER",IF(OR(AND(B2="BIG_SIDE",U2&lt;=0),S2&lt;=0,X2=0,AE2&gt;AD2*0.95),"WARNING","OK")))</f>
+        <f>IF($B2="BLOCKED","STOP",IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR2" s="12">
-        <f>IF(B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS2" s="20">
+        <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
+        <v/>
+      </c>
+      <c r="AT2" s="12">
+        <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
+        <v/>
+      </c>
+      <c r="AU2" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV2" s="12">
+        <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW2" s="12">
+        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX2" s="12">
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
+        <v/>
+      </c>
+      <c r="AY2" s="12">
+        <f>IF($B2="BIG_SIDE",($G2+$J2)*$AU2,0)</f>
+        <v/>
+      </c>
+      <c r="AZ2" s="12">
+        <f>IF($B2="BIG_SIDE",$V2*$AU2,0)</f>
         <v/>
       </c>
     </row>
@@ -1341,41 +1430,40 @@
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B3" s="13">
+        <f>IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C3" s="13">
-        <f>IF($AP2="YES",$AF2,$C2)</f>
+        <f>IF($B3="BLOCKED",$AF2,IF($AP2="YES",$AF2,$C2))</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>IF($AP2="YES",MAX(0,$AG2),$D2)</f>
+        <f>IF($B3="BLOCKED",0,IF($AP2="YES",MAX(0,$AG2),$D2))</f>
         <v/>
       </c>
       <c r="E3" s="12">
-        <f>IF(C3="SELL","BUY","SELL")</f>
+        <f>IF($B3="BLOCKED","",IF($C3="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F3" s="12">
-        <f>MAX(0,D3*Settings!$B$3)</f>
+        <f>IF($B3="BLOCKED",0,MAX(0,$D3*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G3" s="12">
-        <f>IFERROR(MAX(0,ROUND(F3/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H3" s="12">
-        <f>C3</f>
+        <f>IF($B3="BLOCKED","",$C3)</f>
         <v/>
       </c>
       <c r="I3" s="12">
-        <f>MAX(0,G3*Settings!$B$4)</f>
+        <f>IF($B3="BLOCKED",0,MAX(0,$G3*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J3" s="12">
-        <f>IFERROR(MAX(0,ROUND(I3/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K3" s="13" t="n">
@@ -1388,83 +1476,83 @@
         <v>100</v>
       </c>
       <c r="N3" s="14">
-        <f>IF(B3="BIG_SIDE",G3*MAX(0,K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$G3*MAX(0,$K3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O3" s="14">
-        <f>IF(B3="SMALL_SIDE",J3*ABS(L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P3" s="15">
-        <f>IF(B3="BIG_SIDE",J3*ABS(L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q3" s="15">
-        <f>IF(B3="SMALL_SIDE",AL3*ABS(K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$AL3*ABS($K3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R3" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT3*$AU3</f>
         <v/>
       </c>
       <c r="S3" s="14">
-        <f>IF(B3="BIG_SIDE",N3-P3-R3,O3-Q3-R3)</f>
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$R3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
         <v/>
       </c>
       <c r="T3" s="12">
-        <f>IF(AND(B3="BIG_SIDE",S3&gt;0),S3*Settings!$B$5,0)</f>
+        <f>IF(AND($B3="BIG_SIDE",$AX3&gt;0),$AX3*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U3" s="12">
-        <f>MAX(0,M3*Settings!$B$9)</f>
+        <f>MAX(0,$M3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V3" s="12">
-        <f>IF(B3="BIG_SIDE",IFERROR(MIN(D3,MAX(0,T3/U3)),0),0)</f>
+        <f>IF($B3="BIG_SIDE",IFERROR(MIN($D3,MAX(0,$T3/$U3)),0),0)</f>
         <v/>
       </c>
       <c r="W3" s="12">
-        <f>IF(B3="BIG_SIDE",MAX(0,D3-V3),AJ3)</f>
-        <v/>
-      </c>
-      <c r="X3" s="16">
-        <f>IF(B3="BIG_SIDE",IF(S3&gt;0,S3*Settings!$B$6,0),IF(S3&gt;0,S3*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="16">
-        <f>Y2+X3</f>
+        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$V3),$AJ3)</f>
+        <v/>
+      </c>
+      <c r="X3" s="19">
+        <f>IF($B3="BIG_SIDE",IF($AX3&gt;0,$AX3-$AS3,0),IF($S3&gt;0,$S3*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="19">
+        <f>$Y2+$X3</f>
         <v/>
       </c>
       <c r="Z3" s="12">
-        <f>AA2</f>
+        <f>$AA2</f>
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>Z3+S3</f>
+        <f>IF($B3="BLOCKED",$Z3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
-        <f>D3+G3+J3</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2+$AJ2),$D3+$G3+$J3)</f>
         <v/>
       </c>
       <c r="AC3" s="12">
-        <f>IF(B3="BIG_SIDE",W3,AG3+AJ3)</f>
+        <f>IF($B3="BLOCKED",$AB3,IF($B3="BIG_SIDE",$W3,$AG3+$AJ3))</f>
         <v/>
       </c>
       <c r="AD3" s="12">
-        <f>AB3*Settings!$B$10</f>
+        <f>$AB3*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE3" s="12">
-        <f>AC3*Settings!$B$10</f>
+        <f>$AC3*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF3" s="12">
-        <f>IF(B3="SMALL_SIDE",E3,C3)</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,$C3,$AF2),IF($B3="SMALL_SIDE",$E3,$C3))</f>
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF(B3="SMALL_SIDE",AM3,W3)</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
         <v/>
       </c>
       <c r="AH3" s="13" t="inlineStr">
@@ -1476,39 +1564,71 @@
         <v>0</v>
       </c>
       <c r="AJ3" s="12">
-        <f>IF(B3="SMALL_SIDE",IF(AH3="YES",0,IFERROR(MAX(0,D3-MAX(0,AI3)/U3),D3)),0)</f>
+        <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
         <v/>
       </c>
       <c r="AK3" s="12">
-        <f>IF(AND(AJ3&gt;0,AG3&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL3" s="12">
-        <f>IF(B3="SMALL_SIDE",G3*Settings!$B$7,IF(B3="BIG_SIDE",G3,0))</f>
+        <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
         <v/>
       </c>
       <c r="AM3" s="12">
-        <f>IF(B3="SMALL_SIDE",MAX(0,G3-AL3),0)</f>
+        <f>IF($B3="SMALL_SIDE",MAX(0,$G3-$AL3),0)</f>
         <v/>
       </c>
       <c r="AN3" s="12">
-        <f>IF(B3="BIG_SIDE",1,IF(B3="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B3="BIG_SIDE",1,IF($B3="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO3" s="12">
-        <f>IF(OR(B3="BIG_SIDE",B3="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B3="BIG_SIDE",$B3="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP3" s="12">
-        <f>IF(OR(AQ3="DUAL_TAIL",AQ3="DANGER",AQ3="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ3" s="12">
-        <f>IF(AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G3/D3,999)&gt;Settings!$B$16,IFERROR(J3/G3,999)&gt;Settings!$B$17,AE3&gt;AD3,Y3&lt;0,AG3&gt;D3*1.0001,S3&lt;-100),"DANGER",IF(OR(AND(B3="BIG_SIDE",U3&lt;=0),S3&lt;=0,X3=0,AE3&gt;AD3*0.95),"WARNING","OK")))</f>
+        <f>IF($B3="BLOCKED","STOP",IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR3" s="12">
-        <f>IF(B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS3" s="20">
+        <f>IF($B3="BIG_SIDE",$V3*$U3,0)</f>
+        <v/>
+      </c>
+      <c r="AT3" s="12">
+        <f>IF($B3="BIG_SIDE",$G3+$J3+$V3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
+        <v/>
+      </c>
+      <c r="AU3" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV3" s="12">
+        <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW3" s="12">
+        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX3" s="12">
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
+        <v/>
+      </c>
+      <c r="AY3" s="12">
+        <f>IF($B3="BIG_SIDE",($G3+$J3)*$AU3,0)</f>
+        <v/>
+      </c>
+      <c r="AZ3" s="12">
+        <f>IF($B3="BIG_SIDE",$V3*$AU3,0)</f>
         <v/>
       </c>
     </row>
@@ -1516,41 +1636,40 @@
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>SMALL_SIDE</t>
-        </is>
+      <c r="B4" s="13">
+        <f>IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <v/>
       </c>
       <c r="C4" s="13">
-        <f>IF($AP3="YES",$AF3,$C3)</f>
+        <f>IF($B4="BLOCKED",$AF3,IF($AP3="YES",$AF3,$C3))</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF($AP3="YES",MAX(0,$AG3),$D3)</f>
+        <f>IF($B4="BLOCKED",0,IF($AP3="YES",MAX(0,$AG3),$D3))</f>
         <v/>
       </c>
       <c r="E4" s="12">
-        <f>IF(C4="SELL","BUY","SELL")</f>
+        <f>IF($B4="BLOCKED","",IF($C4="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>MAX(0,D4*Settings!$B$3)</f>
+        <f>IF($B4="BLOCKED",0,MAX(0,$D4*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G4" s="12">
-        <f>IFERROR(MAX(0,ROUND(F4/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($F4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H4" s="12">
-        <f>C4</f>
+        <f>IF($B4="BLOCKED","",$C4)</f>
         <v/>
       </c>
       <c r="I4" s="12">
-        <f>MAX(0,G4*Settings!$B$4)</f>
+        <f>IF($B4="BLOCKED",0,MAX(0,$G4*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J4" s="12">
-        <f>IFERROR(MAX(0,ROUND(I4/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K4" s="13" t="n">
@@ -1563,83 +1682,83 @@
         <v>100</v>
       </c>
       <c r="N4" s="14">
-        <f>IF(B4="BIG_SIDE",G4*MAX(0,K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$G4*MAX(0,$K4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O4" s="14">
-        <f>IF(B4="SMALL_SIDE",J4*ABS(L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P4" s="15">
-        <f>IF(B4="BIG_SIDE",J4*ABS(L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q4" s="15">
-        <f>IF(B4="SMALL_SIDE",AL4*ABS(K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$AL4*ABS($K4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R4" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT4*$AU4</f>
         <v/>
       </c>
       <c r="S4" s="14">
-        <f>IF(B4="BIG_SIDE",N4-P4-R4,O4-Q4-R4)</f>
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$R4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
         <v/>
       </c>
       <c r="T4" s="12">
-        <f>IF(AND(B4="BIG_SIDE",S4&gt;0),S4*Settings!$B$5,0)</f>
+        <f>IF(AND($B4="BIG_SIDE",$AX4&gt;0),$AX4*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U4" s="12">
-        <f>MAX(0,M4*Settings!$B$9)</f>
+        <f>MAX(0,$M4*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V4" s="12">
-        <f>IF(B4="BIG_SIDE",IFERROR(MIN(D4,MAX(0,T4/U4)),0),0)</f>
+        <f>IF($B4="BIG_SIDE",IFERROR(MIN($D4,MAX(0,$T4/$U4)),0),0)</f>
         <v/>
       </c>
       <c r="W4" s="12">
-        <f>IF(B4="BIG_SIDE",MAX(0,D4-V4),AJ4)</f>
-        <v/>
-      </c>
-      <c r="X4" s="16">
-        <f>IF(B4="BIG_SIDE",IF(S4&gt;0,S4*Settings!$B$6,0),IF(S4&gt;0,S4*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y4" s="16">
-        <f>Y3+X4</f>
+        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$V4),$AJ4)</f>
+        <v/>
+      </c>
+      <c r="X4" s="19">
+        <f>IF($B4="BIG_SIDE",IF($AX4&gt;0,$AX4-$AS4,0),IF($S4&gt;0,$S4*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y4" s="19">
+        <f>$Y3+$X4</f>
         <v/>
       </c>
       <c r="Z4" s="12">
-        <f>AA3</f>
+        <f>$AA3</f>
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>Z4+S4</f>
+        <f>IF($B4="BLOCKED",$Z4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
-        <f>D4+G4+J4</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3+$AJ3),$D4+$G4+$J4)</f>
         <v/>
       </c>
       <c r="AC4" s="12">
-        <f>IF(B4="BIG_SIDE",W4,AG4+AJ4)</f>
+        <f>IF($B4="BLOCKED",$AB4,IF($B4="BIG_SIDE",$W4,$AG4+$AJ4))</f>
         <v/>
       </c>
       <c r="AD4" s="12">
-        <f>AB4*Settings!$B$10</f>
+        <f>$AB4*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE4" s="12">
-        <f>AC4*Settings!$B$10</f>
+        <f>$AC4*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF4" s="12">
-        <f>IF(B4="SMALL_SIDE",E4,C4)</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,$C4,$AF3),IF($B4="SMALL_SIDE",$E4,$C4))</f>
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF(B4="SMALL_SIDE",AM4,W4)</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -1651,39 +1770,71 @@
         <v>0</v>
       </c>
       <c r="AJ4" s="12">
-        <f>IF(B4="SMALL_SIDE",IF(AH4="YES",0,IFERROR(MAX(0,D4-MAX(0,AI4)/U4),D4)),0)</f>
+        <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
         <v/>
       </c>
       <c r="AK4" s="12">
-        <f>IF(AND(AJ4&gt;0,AG4&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL4" s="12">
-        <f>IF(B4="SMALL_SIDE",G4*Settings!$B$7,IF(B4="BIG_SIDE",G4,0))</f>
+        <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
         <v/>
       </c>
       <c r="AM4" s="12">
-        <f>IF(B4="SMALL_SIDE",MAX(0,G4-AL4),0)</f>
+        <f>IF($B4="SMALL_SIDE",MAX(0,$G4-$AL4),0)</f>
         <v/>
       </c>
       <c r="AN4" s="12">
-        <f>IF(B4="BIG_SIDE",1,IF(B4="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B4="BIG_SIDE",1,IF($B4="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO4" s="12">
-        <f>IF(OR(B4="BIG_SIDE",B4="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B4="BIG_SIDE",$B4="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP4" s="12">
-        <f>IF(OR(AQ4="DUAL_TAIL",AQ4="DANGER",AQ4="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ4" s="12">
-        <f>IF(AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G4/D4,999)&gt;Settings!$B$16,IFERROR(J4/G4,999)&gt;Settings!$B$17,AE4&gt;AD4,Y4&lt;0,AG4&gt;D4*1.0001,S4&lt;-100),"DANGER",IF(OR(AND(B4="BIG_SIDE",U4&lt;=0),S4&lt;=0,X4=0,AE4&gt;AD4*0.95),"WARNING","OK")))</f>
+        <f>IF($B4="BLOCKED","STOP",IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR4" s="12">
-        <f>IF(B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS4" s="20">
+        <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
+        <v/>
+      </c>
+      <c r="AT4" s="12">
+        <f>IF($B4="BIG_SIDE",$G4+$J4+$V4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
+        <v/>
+      </c>
+      <c r="AU4" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV4" s="12">
+        <f>IF($B4="SMALL_SIDE",IF($AH4="YES",$D4,IFERROR(MIN($D4,MAX(0,$AI4/$U4)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW4" s="12">
+        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX4" s="12">
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
+        <v/>
+      </c>
+      <c r="AY4" s="12">
+        <f>IF($B4="BIG_SIDE",($G4+$J4)*$AU4,0)</f>
+        <v/>
+      </c>
+      <c r="AZ4" s="12">
+        <f>IF($B4="BIG_SIDE",$V4*$AU4,0)</f>
         <v/>
       </c>
     </row>
@@ -1691,41 +1842,40 @@
       <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B5" s="13">
+        <f>IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C5" s="13">
-        <f>IF($AP4="YES",$AF4,$C4)</f>
+        <f>IF($B5="BLOCKED",$AF4,IF($AP4="YES",$AF4,$C4))</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF($AP4="YES",MAX(0,$AG4),$D4)</f>
+        <f>IF($B5="BLOCKED",0,IF($AP4="YES",MAX(0,$AG4),$D4))</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>IF(C5="SELL","BUY","SELL")</f>
+        <f>IF($B5="BLOCKED","",IF($C5="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>MAX(0,D5*Settings!$B$3)</f>
+        <f>IF($B5="BLOCKED",0,MAX(0,$D5*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G5" s="12">
-        <f>IFERROR(MAX(0,ROUND(F5/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($F5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H5" s="12">
-        <f>C5</f>
+        <f>IF($B5="BLOCKED","",$C5)</f>
         <v/>
       </c>
       <c r="I5" s="12">
-        <f>MAX(0,G5*Settings!$B$4)</f>
+        <f>IF($B5="BLOCKED",0,MAX(0,$G5*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J5" s="12">
-        <f>IFERROR(MAX(0,ROUND(I5/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K5" s="13" t="n">
@@ -1738,83 +1888,83 @@
         <v>100</v>
       </c>
       <c r="N5" s="14">
-        <f>IF(B5="BIG_SIDE",G5*MAX(0,K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O5" s="14">
-        <f>IF(B5="SMALL_SIDE",J5*ABS(L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P5" s="15">
-        <f>IF(B5="BIG_SIDE",J5*ABS(L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q5" s="15">
-        <f>IF(B5="SMALL_SIDE",AL5*ABS(K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R5" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT5*$AU5</f>
         <v/>
       </c>
       <c r="S5" s="14">
-        <f>IF(B5="BIG_SIDE",N5-P5-R5,O5-Q5-R5)</f>
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$R5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
         <v/>
       </c>
       <c r="T5" s="12">
-        <f>IF(AND(B5="BIG_SIDE",S5&gt;0),S5*Settings!$B$5,0)</f>
+        <f>IF(AND($B5="BIG_SIDE",$AX5&gt;0),$AX5*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U5" s="12">
-        <f>MAX(0,M5*Settings!$B$9)</f>
+        <f>MAX(0,$M5*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V5" s="12">
-        <f>IF(B5="BIG_SIDE",IFERROR(MIN(D5,MAX(0,T5/U5)),0),0)</f>
+        <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
         <v/>
       </c>
       <c r="W5" s="12">
-        <f>IF(B5="BIG_SIDE",MAX(0,D5-V5),AJ5)</f>
-        <v/>
-      </c>
-      <c r="X5" s="16">
-        <f>IF(B5="BIG_SIDE",IF(S5&gt;0,S5*Settings!$B$6,0),IF(S5&gt;0,S5*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="16">
-        <f>Y4+X5</f>
+        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
+        <v/>
+      </c>
+      <c r="X5" s="19">
+        <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y5" s="19">
+        <f>$Y4+$X5</f>
         <v/>
       </c>
       <c r="Z5" s="12">
-        <f>AA4</f>
+        <f>$AA4</f>
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>Z5+S5</f>
+        <f>IF($B5="BLOCKED",$Z5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
-        <f>D5+G5+J5</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4+$AJ4),$D5+$G5+$J5)</f>
         <v/>
       </c>
       <c r="AC5" s="12">
-        <f>IF(B5="BIG_SIDE",W5,AG5+AJ5)</f>
+        <f>IF($B5="BLOCKED",$AB5,IF($B5="BIG_SIDE",$W5,$AG5+$AJ5))</f>
         <v/>
       </c>
       <c r="AD5" s="12">
-        <f>AB5*Settings!$B$10</f>
+        <f>$AB5*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE5" s="12">
-        <f>AC5*Settings!$B$10</f>
+        <f>$AC5*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF5" s="12">
-        <f>IF(B5="SMALL_SIDE",E5,C5)</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,$C5,$AF4),IF($B5="SMALL_SIDE",$E5,$C5))</f>
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF(B5="SMALL_SIDE",AM5,W5)</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v/>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -1826,39 +1976,71 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="12">
-        <f>IF(B5="SMALL_SIDE",IF(AH5="YES",0,IFERROR(MAX(0,D5-MAX(0,AI5)/U5),D5)),0)</f>
+        <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
         <v/>
       </c>
       <c r="AK5" s="12">
-        <f>IF(AND(AJ5&gt;0,AG5&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL5" s="12">
-        <f>IF(B5="SMALL_SIDE",G5*Settings!$B$7,IF(B5="BIG_SIDE",G5,0))</f>
+        <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
         <v/>
       </c>
       <c r="AM5" s="12">
-        <f>IF(B5="SMALL_SIDE",MAX(0,G5-AL5),0)</f>
+        <f>IF($B5="SMALL_SIDE",MAX(0,$G5-$AL5),0)</f>
         <v/>
       </c>
       <c r="AN5" s="12">
-        <f>IF(B5="BIG_SIDE",1,IF(B5="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B5="BIG_SIDE",1,IF($B5="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO5" s="12">
-        <f>IF(OR(B5="BIG_SIDE",B5="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B5="BIG_SIDE",$B5="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP5" s="12">
-        <f>IF(OR(AQ5="DUAL_TAIL",AQ5="DANGER",AQ5="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ5" s="12">
-        <f>IF(AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G5/D5,999)&gt;Settings!$B$16,IFERROR(J5/G5,999)&gt;Settings!$B$17,AE5&gt;AD5,Y5&lt;0,AG5&gt;D5*1.0001,S5&lt;-100),"DANGER",IF(OR(AND(B5="BIG_SIDE",U5&lt;=0),S5&lt;=0,X5=0,AE5&gt;AD5*0.95),"WARNING","OK")))</f>
+        <f>IF($B5="BLOCKED","STOP",IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR5" s="12">
-        <f>IF(B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS5" s="20">
+        <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
+        <v/>
+      </c>
+      <c r="AT5" s="12">
+        <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
+        <v/>
+      </c>
+      <c r="AU5" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV5" s="12">
+        <f>IF($B5="SMALL_SIDE",IF($AH5="YES",$D5,IFERROR(MIN($D5,MAX(0,$AI5/$U5)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW5" s="12">
+        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX5" s="12">
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
+        <v/>
+      </c>
+      <c r="AY5" s="12">
+        <f>IF($B5="BIG_SIDE",($G5+$J5)*$AU5,0)</f>
+        <v/>
+      </c>
+      <c r="AZ5" s="12">
+        <f>IF($B5="BIG_SIDE",$V5*$AU5,0)</f>
         <v/>
       </c>
     </row>
@@ -1866,41 +2048,40 @@
       <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B6" s="13">
+        <f>IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C6" s="13">
-        <f>IF($AP5="YES",$AF5,$C5)</f>
+        <f>IF($B6="BLOCKED",$AF5,IF($AP5="YES",$AF5,$C5))</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF($AP5="YES",MAX(0,$AG5),$D5)</f>
+        <f>IF($B6="BLOCKED",0,IF($AP5="YES",MAX(0,$AG5),$D5))</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>IF(C6="SELL","BUY","SELL")</f>
+        <f>IF($B6="BLOCKED","",IF($C6="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>MAX(0,D6*Settings!$B$3)</f>
+        <f>IF($B6="BLOCKED",0,MAX(0,$D6*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G6" s="12">
-        <f>IFERROR(MAX(0,ROUND(F6/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($F6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H6" s="12">
-        <f>C6</f>
+        <f>IF($B6="BLOCKED","",$C6)</f>
         <v/>
       </c>
       <c r="I6" s="12">
-        <f>MAX(0,G6*Settings!$B$4)</f>
+        <f>IF($B6="BLOCKED",0,MAX(0,$G6*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J6" s="12">
-        <f>IFERROR(MAX(0,ROUND(I6/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K6" s="13" t="n">
@@ -1913,83 +2094,83 @@
         <v>100</v>
       </c>
       <c r="N6" s="14">
-        <f>IF(B6="BIG_SIDE",G6*MAX(0,K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O6" s="14">
-        <f>IF(B6="SMALL_SIDE",J6*ABS(L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P6" s="15">
-        <f>IF(B6="BIG_SIDE",J6*ABS(L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q6" s="15">
-        <f>IF(B6="SMALL_SIDE",AL6*ABS(K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R6" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT6*$AU6</f>
         <v/>
       </c>
       <c r="S6" s="14">
-        <f>IF(B6="BIG_SIDE",N6-P6-R6,O6-Q6-R6)</f>
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$R6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
         <v/>
       </c>
       <c r="T6" s="12">
-        <f>IF(AND(B6="BIG_SIDE",S6&gt;0),S6*Settings!$B$5,0)</f>
+        <f>IF(AND($B6="BIG_SIDE",$AX6&gt;0),$AX6*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U6" s="12">
-        <f>MAX(0,M6*Settings!$B$9)</f>
+        <f>MAX(0,$M6*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V6" s="12">
-        <f>IF(B6="BIG_SIDE",IFERROR(MIN(D6,MAX(0,T6/U6)),0),0)</f>
+        <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
         <v/>
       </c>
       <c r="W6" s="12">
-        <f>IF(B6="BIG_SIDE",MAX(0,D6-V6),AJ6)</f>
-        <v/>
-      </c>
-      <c r="X6" s="16">
-        <f>IF(B6="BIG_SIDE",IF(S6&gt;0,S6*Settings!$B$6,0),IF(S6&gt;0,S6*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="16">
-        <f>Y5+X6</f>
+        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
+        <v/>
+      </c>
+      <c r="X6" s="19">
+        <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y6" s="19">
+        <f>$Y5+$X6</f>
         <v/>
       </c>
       <c r="Z6" s="12">
-        <f>AA5</f>
+        <f>$AA5</f>
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>Z6+S6</f>
+        <f>IF($B6="BLOCKED",$Z6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
-        <f>D6+G6+J6</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5+$AJ5),$D6+$G6+$J6)</f>
         <v/>
       </c>
       <c r="AC6" s="12">
-        <f>IF(B6="BIG_SIDE",W6,AG6+AJ6)</f>
+        <f>IF($B6="BLOCKED",$AB6,IF($B6="BIG_SIDE",$W6,$AG6+$AJ6))</f>
         <v/>
       </c>
       <c r="AD6" s="12">
-        <f>AB6*Settings!$B$10</f>
+        <f>$AB6*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE6" s="12">
-        <f>AC6*Settings!$B$10</f>
+        <f>$AC6*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF6" s="12">
-        <f>IF(B6="SMALL_SIDE",E6,C6)</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,$C6,$AF5),IF($B6="SMALL_SIDE",$E6,$C6))</f>
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF(B6="SMALL_SIDE",AM6,W6)</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -2001,39 +2182,71 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="12">
-        <f>IF(B6="SMALL_SIDE",IF(AH6="YES",0,IFERROR(MAX(0,D6-MAX(0,AI6)/U6),D6)),0)</f>
+        <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
       <c r="AK6" s="12">
-        <f>IF(AND(AJ6&gt;0,AG6&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL6" s="12">
-        <f>IF(B6="SMALL_SIDE",G6*Settings!$B$7,IF(B6="BIG_SIDE",G6,0))</f>
+        <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
         <v/>
       </c>
       <c r="AM6" s="12">
-        <f>IF(B6="SMALL_SIDE",MAX(0,G6-AL6),0)</f>
+        <f>IF($B6="SMALL_SIDE",MAX(0,$G6-$AL6),0)</f>
         <v/>
       </c>
       <c r="AN6" s="12">
-        <f>IF(B6="BIG_SIDE",1,IF(B6="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B6="BIG_SIDE",1,IF($B6="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO6" s="12">
-        <f>IF(OR(B6="BIG_SIDE",B6="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B6="BIG_SIDE",$B6="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP6" s="12">
-        <f>IF(OR(AQ6="DUAL_TAIL",AQ6="DANGER",AQ6="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ6" s="12">
-        <f>IF(AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G6/D6,999)&gt;Settings!$B$16,IFERROR(J6/G6,999)&gt;Settings!$B$17,AE6&gt;AD6,Y6&lt;0,AG6&gt;D6*1.0001,S6&lt;-100),"DANGER",IF(OR(AND(B6="BIG_SIDE",U6&lt;=0),S6&lt;=0,X6=0,AE6&gt;AD6*0.95),"WARNING","OK")))</f>
+        <f>IF($B6="BLOCKED","STOP",IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR6" s="12">
-        <f>IF(B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS6" s="20">
+        <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
+        <v/>
+      </c>
+      <c r="AT6" s="12">
+        <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
+        <v/>
+      </c>
+      <c r="AU6" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV6" s="12">
+        <f>IF($B6="SMALL_SIDE",IF($AH6="YES",$D6,IFERROR(MIN($D6,MAX(0,$AI6/$U6)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW6" s="12">
+        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX6" s="12">
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
+        <v/>
+      </c>
+      <c r="AY6" s="12">
+        <f>IF($B6="BIG_SIDE",($G6+$J6)*$AU6,0)</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="12">
+        <f>IF($B6="BIG_SIDE",$V6*$AU6,0)</f>
         <v/>
       </c>
     </row>
@@ -2041,41 +2254,40 @@
       <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>SMALL_SIDE</t>
-        </is>
+      <c r="B7" s="13">
+        <f>IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <v/>
       </c>
       <c r="C7" s="13">
-        <f>IF($AP6="YES",$AF6,$C6)</f>
+        <f>IF($B7="BLOCKED",$AF6,IF($AP6="YES",$AF6,$C6))</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF($AP6="YES",MAX(0,$AG6),$D6)</f>
+        <f>IF($B7="BLOCKED",0,IF($AP6="YES",MAX(0,$AG6),$D6))</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>IF(C7="SELL","BUY","SELL")</f>
+        <f>IF($B7="BLOCKED","",IF($C7="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>MAX(0,D7*Settings!$B$3)</f>
+        <f>IF($B7="BLOCKED",0,MAX(0,$D7*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G7" s="12">
-        <f>IFERROR(MAX(0,ROUND(F7/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($F7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H7" s="12">
-        <f>C7</f>
+        <f>IF($B7="BLOCKED","",$C7)</f>
         <v/>
       </c>
       <c r="I7" s="12">
-        <f>MAX(0,G7*Settings!$B$4)</f>
+        <f>IF($B7="BLOCKED",0,MAX(0,$G7*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J7" s="12">
-        <f>IFERROR(MAX(0,ROUND(I7/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K7" s="13" t="n">
@@ -2088,83 +2300,83 @@
         <v>100</v>
       </c>
       <c r="N7" s="14">
-        <f>IF(B7="BIG_SIDE",G7*MAX(0,K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O7" s="14">
-        <f>IF(B7="SMALL_SIDE",J7*ABS(L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P7" s="15">
-        <f>IF(B7="BIG_SIDE",J7*ABS(L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q7" s="15">
-        <f>IF(B7="SMALL_SIDE",AL7*ABS(K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R7" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT7*$AU7</f>
         <v/>
       </c>
       <c r="S7" s="14">
-        <f>IF(B7="BIG_SIDE",N7-P7-R7,O7-Q7-R7)</f>
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$R7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
         <v/>
       </c>
       <c r="T7" s="12">
-        <f>IF(AND(B7="BIG_SIDE",S7&gt;0),S7*Settings!$B$5,0)</f>
+        <f>IF(AND($B7="BIG_SIDE",$AX7&gt;0),$AX7*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U7" s="12">
-        <f>MAX(0,M7*Settings!$B$9)</f>
+        <f>MAX(0,$M7*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V7" s="12">
-        <f>IF(B7="BIG_SIDE",IFERROR(MIN(D7,MAX(0,T7/U7)),0),0)</f>
+        <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
         <v/>
       </c>
       <c r="W7" s="12">
-        <f>IF(B7="BIG_SIDE",MAX(0,D7-V7),AJ7)</f>
-        <v/>
-      </c>
-      <c r="X7" s="16">
-        <f>IF(B7="BIG_SIDE",IF(S7&gt;0,S7*Settings!$B$6,0),IF(S7&gt;0,S7*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y7" s="16">
-        <f>Y6+X7</f>
+        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
+        <v/>
+      </c>
+      <c r="X7" s="19">
+        <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y7" s="19">
+        <f>$Y6+$X7</f>
         <v/>
       </c>
       <c r="Z7" s="12">
-        <f>AA6</f>
+        <f>$AA6</f>
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>Z7+S7</f>
+        <f>IF($B7="BLOCKED",$Z7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
-        <f>D7+G7+J7</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6+$AJ6),$D7+$G7+$J7)</f>
         <v/>
       </c>
       <c r="AC7" s="12">
-        <f>IF(B7="BIG_SIDE",W7,AG7+AJ7)</f>
+        <f>IF($B7="BLOCKED",$AB7,IF($B7="BIG_SIDE",$W7,$AG7+$AJ7))</f>
         <v/>
       </c>
       <c r="AD7" s="12">
-        <f>AB7*Settings!$B$10</f>
+        <f>$AB7*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE7" s="12">
-        <f>AC7*Settings!$B$10</f>
+        <f>$AC7*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF7" s="12">
-        <f>IF(B7="SMALL_SIDE",E7,C7)</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,$C7,$AF6),IF($B7="SMALL_SIDE",$E7,$C7))</f>
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF(B7="SMALL_SIDE",AM7,W7)</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -2176,39 +2388,71 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="12">
-        <f>IF(B7="SMALL_SIDE",IF(AH7="YES",0,IFERROR(MAX(0,D7-MAX(0,AI7)/U7),D7)),0)</f>
+        <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
       <c r="AK7" s="12">
-        <f>IF(AND(AJ7&gt;0,AG7&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL7" s="12">
-        <f>IF(B7="SMALL_SIDE",G7*Settings!$B$7,IF(B7="BIG_SIDE",G7,0))</f>
+        <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
         <v/>
       </c>
       <c r="AM7" s="12">
-        <f>IF(B7="SMALL_SIDE",MAX(0,G7-AL7),0)</f>
+        <f>IF($B7="SMALL_SIDE",MAX(0,$G7-$AL7),0)</f>
         <v/>
       </c>
       <c r="AN7" s="12">
-        <f>IF(B7="BIG_SIDE",1,IF(B7="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B7="BIG_SIDE",1,IF($B7="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO7" s="12">
-        <f>IF(OR(B7="BIG_SIDE",B7="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B7="BIG_SIDE",$B7="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP7" s="12">
-        <f>IF(OR(AQ7="DUAL_TAIL",AQ7="DANGER",AQ7="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ7" s="12">
-        <f>IF(AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G7/D7,999)&gt;Settings!$B$16,IFERROR(J7/G7,999)&gt;Settings!$B$17,AE7&gt;AD7,Y7&lt;0,AG7&gt;D7*1.0001,S7&lt;-100),"DANGER",IF(OR(AND(B7="BIG_SIDE",U7&lt;=0),S7&lt;=0,X7=0,AE7&gt;AD7*0.95),"WARNING","OK")))</f>
+        <f>IF($B7="BLOCKED","STOP",IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR7" s="12">
-        <f>IF(B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS7" s="20">
+        <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
+        <v/>
+      </c>
+      <c r="AT7" s="12">
+        <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
+        <v/>
+      </c>
+      <c r="AU7" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV7" s="12">
+        <f>IF($B7="SMALL_SIDE",IF($AH7="YES",$D7,IFERROR(MIN($D7,MAX(0,$AI7/$U7)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW7" s="12">
+        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX7" s="12">
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
+        <v/>
+      </c>
+      <c r="AY7" s="12">
+        <f>IF($B7="BIG_SIDE",($G7+$J7)*$AU7,0)</f>
+        <v/>
+      </c>
+      <c r="AZ7" s="12">
+        <f>IF($B7="BIG_SIDE",$V7*$AU7,0)</f>
         <v/>
       </c>
     </row>
@@ -2216,41 +2460,40 @@
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B8" s="13">
+        <f>IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C8" s="13">
-        <f>IF($AP7="YES",$AF7,$C7)</f>
+        <f>IF($B8="BLOCKED",$AF7,IF($AP7="YES",$AF7,$C7))</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF($AP7="YES",MAX(0,$AG7),$D7)</f>
+        <f>IF($B8="BLOCKED",0,IF($AP7="YES",MAX(0,$AG7),$D7))</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>IF(C8="SELL","BUY","SELL")</f>
+        <f>IF($B8="BLOCKED","",IF($C8="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>MAX(0,D8*Settings!$B$3)</f>
+        <f>IF($B8="BLOCKED",0,MAX(0,$D8*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G8" s="12">
-        <f>IFERROR(MAX(0,ROUND(F8/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($F8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H8" s="12">
-        <f>C8</f>
+        <f>IF($B8="BLOCKED","",$C8)</f>
         <v/>
       </c>
       <c r="I8" s="12">
-        <f>MAX(0,G8*Settings!$B$4)</f>
+        <f>IF($B8="BLOCKED",0,MAX(0,$G8*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J8" s="12">
-        <f>IFERROR(MAX(0,ROUND(I8/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K8" s="13" t="n">
@@ -2263,83 +2506,83 @@
         <v>100</v>
       </c>
       <c r="N8" s="14">
-        <f>IF(B8="BIG_SIDE",G8*MAX(0,K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O8" s="14">
-        <f>IF(B8="SMALL_SIDE",J8*ABS(L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P8" s="15">
-        <f>IF(B8="BIG_SIDE",J8*ABS(L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q8" s="15">
-        <f>IF(B8="SMALL_SIDE",AL8*ABS(K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R8" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT8*$AU8</f>
         <v/>
       </c>
       <c r="S8" s="14">
-        <f>IF(B8="BIG_SIDE",N8-P8-R8,O8-Q8-R8)</f>
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$R8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
         <v/>
       </c>
       <c r="T8" s="12">
-        <f>IF(AND(B8="BIG_SIDE",S8&gt;0),S8*Settings!$B$5,0)</f>
+        <f>IF(AND($B8="BIG_SIDE",$AX8&gt;0),$AX8*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U8" s="12">
-        <f>MAX(0,M8*Settings!$B$9)</f>
+        <f>MAX(0,$M8*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V8" s="12">
-        <f>IF(B8="BIG_SIDE",IFERROR(MIN(D8,MAX(0,T8/U8)),0),0)</f>
+        <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
         <v/>
       </c>
       <c r="W8" s="12">
-        <f>IF(B8="BIG_SIDE",MAX(0,D8-V8),AJ8)</f>
-        <v/>
-      </c>
-      <c r="X8" s="16">
-        <f>IF(B8="BIG_SIDE",IF(S8&gt;0,S8*Settings!$B$6,0),IF(S8&gt;0,S8*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y8" s="16">
-        <f>Y7+X8</f>
+        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
+        <v/>
+      </c>
+      <c r="X8" s="19">
+        <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y8" s="19">
+        <f>$Y7+$X8</f>
         <v/>
       </c>
       <c r="Z8" s="12">
-        <f>AA7</f>
+        <f>$AA7</f>
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>Z8+S8</f>
+        <f>IF($B8="BLOCKED",$Z8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
-        <f>D8+G8+J8</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7+$AJ7),$D8+$G8+$J8)</f>
         <v/>
       </c>
       <c r="AC8" s="12">
-        <f>IF(B8="BIG_SIDE",W8,AG8+AJ8)</f>
+        <f>IF($B8="BLOCKED",$AB8,IF($B8="BIG_SIDE",$W8,$AG8+$AJ8))</f>
         <v/>
       </c>
       <c r="AD8" s="12">
-        <f>AB8*Settings!$B$10</f>
+        <f>$AB8*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE8" s="12">
-        <f>AC8*Settings!$B$10</f>
+        <f>$AC8*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF8" s="12">
-        <f>IF(B8="SMALL_SIDE",E8,C8)</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,$C8,$AF7),IF($B8="SMALL_SIDE",$E8,$C8))</f>
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF(B8="SMALL_SIDE",AM8,W8)</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -2351,39 +2594,71 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="12">
-        <f>IF(B8="SMALL_SIDE",IF(AH8="YES",0,IFERROR(MAX(0,D8-MAX(0,AI8)/U8),D8)),0)</f>
+        <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
       <c r="AK8" s="12">
-        <f>IF(AND(AJ8&gt;0,AG8&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL8" s="12">
-        <f>IF(B8="SMALL_SIDE",G8*Settings!$B$7,IF(B8="BIG_SIDE",G8,0))</f>
+        <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
         <v/>
       </c>
       <c r="AM8" s="12">
-        <f>IF(B8="SMALL_SIDE",MAX(0,G8-AL8),0)</f>
+        <f>IF($B8="SMALL_SIDE",MAX(0,$G8-$AL8),0)</f>
         <v/>
       </c>
       <c r="AN8" s="12">
-        <f>IF(B8="BIG_SIDE",1,IF(B8="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B8="BIG_SIDE",1,IF($B8="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO8" s="12">
-        <f>IF(OR(B8="BIG_SIDE",B8="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B8="BIG_SIDE",$B8="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP8" s="12">
-        <f>IF(OR(AQ8="DUAL_TAIL",AQ8="DANGER",AQ8="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ8" s="12">
-        <f>IF(AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G8/D8,999)&gt;Settings!$B$16,IFERROR(J8/G8,999)&gt;Settings!$B$17,AE8&gt;AD8,Y8&lt;0,AG8&gt;D8*1.0001,S8&lt;-100),"DANGER",IF(OR(AND(B8="BIG_SIDE",U8&lt;=0),S8&lt;=0,X8=0,AE8&gt;AD8*0.95),"WARNING","OK")))</f>
+        <f>IF($B8="BLOCKED","STOP",IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR8" s="12">
-        <f>IF(B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS8" s="20">
+        <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
+        <v/>
+      </c>
+      <c r="AT8" s="12">
+        <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
+        <v/>
+      </c>
+      <c r="AU8" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV8" s="12">
+        <f>IF($B8="SMALL_SIDE",IF($AH8="YES",$D8,IFERROR(MIN($D8,MAX(0,$AI8/$U8)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW8" s="12">
+        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX8" s="12">
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
+        <v/>
+      </c>
+      <c r="AY8" s="12">
+        <f>IF($B8="BIG_SIDE",($G8+$J8)*$AU8,0)</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="12">
+        <f>IF($B8="BIG_SIDE",$V8*$AU8,0)</f>
         <v/>
       </c>
     </row>
@@ -2391,41 +2666,40 @@
       <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B9" s="13">
+        <f>IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C9" s="13">
-        <f>IF($AP8="YES",$AF8,$C8)</f>
+        <f>IF($B9="BLOCKED",$AF8,IF($AP8="YES",$AF8,$C8))</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF($AP8="YES",MAX(0,$AG8),$D8)</f>
+        <f>IF($B9="BLOCKED",0,IF($AP8="YES",MAX(0,$AG8),$D8))</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>IF(C9="SELL","BUY","SELL")</f>
+        <f>IF($B9="BLOCKED","",IF($C9="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>MAX(0,D9*Settings!$B$3)</f>
+        <f>IF($B9="BLOCKED",0,MAX(0,$D9*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>IFERROR(MAX(0,ROUND(F9/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($F9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>C9</f>
+        <f>IF($B9="BLOCKED","",$C9)</f>
         <v/>
       </c>
       <c r="I9" s="12">
-        <f>MAX(0,G9*Settings!$B$4)</f>
+        <f>IF($B9="BLOCKED",0,MAX(0,$G9*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J9" s="12">
-        <f>IFERROR(MAX(0,ROUND(I9/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K9" s="13" t="n">
@@ -2438,83 +2712,83 @@
         <v>100</v>
       </c>
       <c r="N9" s="14">
-        <f>IF(B9="BIG_SIDE",G9*MAX(0,K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O9" s="14">
-        <f>IF(B9="SMALL_SIDE",J9*ABS(L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P9" s="15">
-        <f>IF(B9="BIG_SIDE",J9*ABS(L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q9" s="15">
-        <f>IF(B9="SMALL_SIDE",AL9*ABS(K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R9" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT9*$AU9</f>
         <v/>
       </c>
       <c r="S9" s="14">
-        <f>IF(B9="BIG_SIDE",N9-P9-R9,O9-Q9-R9)</f>
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$R9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
         <v/>
       </c>
       <c r="T9" s="12">
-        <f>IF(AND(B9="BIG_SIDE",S9&gt;0),S9*Settings!$B$5,0)</f>
+        <f>IF(AND($B9="BIG_SIDE",$AX9&gt;0),$AX9*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U9" s="12">
-        <f>MAX(0,M9*Settings!$B$9)</f>
+        <f>MAX(0,$M9*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>IF(B9="BIG_SIDE",IFERROR(MIN(D9,MAX(0,T9/U9)),0),0)</f>
+        <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
         <v/>
       </c>
       <c r="W9" s="12">
-        <f>IF(B9="BIG_SIDE",MAX(0,D9-V9),AJ9)</f>
-        <v/>
-      </c>
-      <c r="X9" s="16">
-        <f>IF(B9="BIG_SIDE",IF(S9&gt;0,S9*Settings!$B$6,0),IF(S9&gt;0,S9*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y9" s="16">
-        <f>Y8+X9</f>
+        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
+        <v/>
+      </c>
+      <c r="X9" s="19">
+        <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y9" s="19">
+        <f>$Y8+$X9</f>
         <v/>
       </c>
       <c r="Z9" s="12">
-        <f>AA8</f>
+        <f>$AA8</f>
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>Z9+S9</f>
+        <f>IF($B9="BLOCKED",$Z9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>D9+G9+J9</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8+$AJ8),$D9+$G9+$J9)</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>IF(B9="BIG_SIDE",W9,AG9+AJ9)</f>
+        <f>IF($B9="BLOCKED",$AB9,IF($B9="BIG_SIDE",$W9,$AG9+$AJ9))</f>
         <v/>
       </c>
       <c r="AD9" s="12">
-        <f>AB9*Settings!$B$10</f>
+        <f>$AB9*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE9" s="12">
-        <f>AC9*Settings!$B$10</f>
+        <f>$AC9*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>IF(B9="SMALL_SIDE",E9,C9)</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,$C9,$AF8),IF($B9="SMALL_SIDE",$E9,$C9))</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF(B9="SMALL_SIDE",AM9,W9)</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -2526,39 +2800,71 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="12">
-        <f>IF(B9="SMALL_SIDE",IF(AH9="YES",0,IFERROR(MAX(0,D9-MAX(0,AI9)/U9),D9)),0)</f>
+        <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
       <c r="AK9" s="12">
-        <f>IF(AND(AJ9&gt;0,AG9&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL9" s="12">
-        <f>IF(B9="SMALL_SIDE",G9*Settings!$B$7,IF(B9="BIG_SIDE",G9,0))</f>
+        <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
         <v/>
       </c>
       <c r="AM9" s="12">
-        <f>IF(B9="SMALL_SIDE",MAX(0,G9-AL9),0)</f>
+        <f>IF($B9="SMALL_SIDE",MAX(0,$G9-$AL9),0)</f>
         <v/>
       </c>
       <c r="AN9" s="12">
-        <f>IF(B9="BIG_SIDE",1,IF(B9="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B9="BIG_SIDE",1,IF($B9="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO9" s="12">
-        <f>IF(OR(B9="BIG_SIDE",B9="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B9="BIG_SIDE",$B9="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP9" s="12">
-        <f>IF(OR(AQ9="DUAL_TAIL",AQ9="DANGER",AQ9="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ9" s="12">
-        <f>IF(AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G9/D9,999)&gt;Settings!$B$16,IFERROR(J9/G9,999)&gt;Settings!$B$17,AE9&gt;AD9,Y9&lt;0,AG9&gt;D9*1.0001,S9&lt;-100),"DANGER",IF(OR(AND(B9="BIG_SIDE",U9&lt;=0),S9&lt;=0,X9=0,AE9&gt;AD9*0.95),"WARNING","OK")))</f>
+        <f>IF($B9="BLOCKED","STOP",IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR9" s="12">
-        <f>IF(B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS9" s="20">
+        <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
+        <v/>
+      </c>
+      <c r="AT9" s="12">
+        <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
+        <v/>
+      </c>
+      <c r="AU9" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV9" s="12">
+        <f>IF($B9="SMALL_SIDE",IF($AH9="YES",$D9,IFERROR(MIN($D9,MAX(0,$AI9/$U9)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW9" s="12">
+        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX9" s="12">
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
+        <v/>
+      </c>
+      <c r="AY9" s="12">
+        <f>IF($B9="BIG_SIDE",($G9+$J9)*$AU9,0)</f>
+        <v/>
+      </c>
+      <c r="AZ9" s="12">
+        <f>IF($B9="BIG_SIDE",$V9*$AU9,0)</f>
         <v/>
       </c>
     </row>
@@ -2566,41 +2872,40 @@
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B10" s="13">
+        <f>IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C10" s="13">
-        <f>IF($AP9="YES",$AF9,$C9)</f>
+        <f>IF($B10="BLOCKED",$AF9,IF($AP9="YES",$AF9,$C9))</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF($AP9="YES",MAX(0,$AG9),$D9)</f>
+        <f>IF($B10="BLOCKED",0,IF($AP9="YES",MAX(0,$AG9),$D9))</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>IF(C10="SELL","BUY","SELL")</f>
+        <f>IF($B10="BLOCKED","",IF($C10="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>MAX(0,D10*Settings!$B$3)</f>
+        <f>IF($B10="BLOCKED",0,MAX(0,$D10*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G10" s="12">
-        <f>IFERROR(MAX(0,ROUND(F10/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($F10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H10" s="12">
-        <f>C10</f>
+        <f>IF($B10="BLOCKED","",$C10)</f>
         <v/>
       </c>
       <c r="I10" s="12">
-        <f>MAX(0,G10*Settings!$B$4)</f>
+        <f>IF($B10="BLOCKED",0,MAX(0,$G10*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J10" s="12">
-        <f>IFERROR(MAX(0,ROUND(I10/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K10" s="13" t="n">
@@ -2613,83 +2918,83 @@
         <v>100</v>
       </c>
       <c r="N10" s="14">
-        <f>IF(B10="BIG_SIDE",G10*MAX(0,K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O10" s="14">
-        <f>IF(B10="SMALL_SIDE",J10*ABS(L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P10" s="15">
-        <f>IF(B10="BIG_SIDE",J10*ABS(L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q10" s="15">
-        <f>IF(B10="SMALL_SIDE",AL10*ABS(K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R10" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT10*$AU10</f>
         <v/>
       </c>
       <c r="S10" s="14">
-        <f>IF(B10="BIG_SIDE",N10-P10-R10,O10-Q10-R10)</f>
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$R10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
         <v/>
       </c>
       <c r="T10" s="12">
-        <f>IF(AND(B10="BIG_SIDE",S10&gt;0),S10*Settings!$B$5,0)</f>
+        <f>IF(AND($B10="BIG_SIDE",$AX10&gt;0),$AX10*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U10" s="12">
-        <f>MAX(0,M10*Settings!$B$9)</f>
+        <f>MAX(0,$M10*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V10" s="12">
-        <f>IF(B10="BIG_SIDE",IFERROR(MIN(D10,MAX(0,T10/U10)),0),0)</f>
+        <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
         <v/>
       </c>
       <c r="W10" s="12">
-        <f>IF(B10="BIG_SIDE",MAX(0,D10-V10),AJ10)</f>
-        <v/>
-      </c>
-      <c r="X10" s="16">
-        <f>IF(B10="BIG_SIDE",IF(S10&gt;0,S10*Settings!$B$6,0),IF(S10&gt;0,S10*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y10" s="16">
-        <f>Y9+X10</f>
+        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
+        <v/>
+      </c>
+      <c r="X10" s="19">
+        <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y10" s="19">
+        <f>$Y9+$X10</f>
         <v/>
       </c>
       <c r="Z10" s="12">
-        <f>AA9</f>
+        <f>$AA9</f>
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>Z10+S10</f>
+        <f>IF($B10="BLOCKED",$Z10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
-        <f>D10+G10+J10</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9+$AJ9),$D10+$G10+$J10)</f>
         <v/>
       </c>
       <c r="AC10" s="12">
-        <f>IF(B10="BIG_SIDE",W10,AG10+AJ10)</f>
+        <f>IF($B10="BLOCKED",$AB10,IF($B10="BIG_SIDE",$W10,$AG10+$AJ10))</f>
         <v/>
       </c>
       <c r="AD10" s="12">
-        <f>AB10*Settings!$B$10</f>
+        <f>$AB10*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE10" s="12">
-        <f>AC10*Settings!$B$10</f>
+        <f>$AC10*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF10" s="12">
-        <f>IF(B10="SMALL_SIDE",E10,C10)</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,$C10,$AF9),IF($B10="SMALL_SIDE",$E10,$C10))</f>
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF(B10="SMALL_SIDE",AM10,W10)</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -2701,39 +3006,71 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="12">
-        <f>IF(B10="SMALL_SIDE",IF(AH10="YES",0,IFERROR(MAX(0,D10-MAX(0,AI10)/U10),D10)),0)</f>
+        <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
       <c r="AK10" s="12">
-        <f>IF(AND(AJ10&gt;0,AG10&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL10" s="12">
-        <f>IF(B10="SMALL_SIDE",G10*Settings!$B$7,IF(B10="BIG_SIDE",G10,0))</f>
+        <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
         <v/>
       </c>
       <c r="AM10" s="12">
-        <f>IF(B10="SMALL_SIDE",MAX(0,G10-AL10),0)</f>
+        <f>IF($B10="SMALL_SIDE",MAX(0,$G10-$AL10),0)</f>
         <v/>
       </c>
       <c r="AN10" s="12">
-        <f>IF(B10="BIG_SIDE",1,IF(B10="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B10="BIG_SIDE",1,IF($B10="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO10" s="12">
-        <f>IF(OR(B10="BIG_SIDE",B10="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B10="BIG_SIDE",$B10="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP10" s="12">
-        <f>IF(OR(AQ10="DUAL_TAIL",AQ10="DANGER",AQ10="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ10" s="12">
-        <f>IF(AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G10/D10,999)&gt;Settings!$B$16,IFERROR(J10/G10,999)&gt;Settings!$B$17,AE10&gt;AD10,Y10&lt;0,AG10&gt;D10*1.0001,S10&lt;-100),"DANGER",IF(OR(AND(B10="BIG_SIDE",U10&lt;=0),S10&lt;=0,X10=0,AE10&gt;AD10*0.95),"WARNING","OK")))</f>
+        <f>IF($B10="BLOCKED","STOP",IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR10" s="12">
-        <f>IF(B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS10" s="20">
+        <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
+        <v/>
+      </c>
+      <c r="AT10" s="12">
+        <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
+        <v/>
+      </c>
+      <c r="AU10" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV10" s="12">
+        <f>IF($B10="SMALL_SIDE",IF($AH10="YES",$D10,IFERROR(MIN($D10,MAX(0,$AI10/$U10)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW10" s="12">
+        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX10" s="12">
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="12">
+        <f>IF($B10="BIG_SIDE",($G10+$J10)*$AU10,0)</f>
+        <v/>
+      </c>
+      <c r="AZ10" s="12">
+        <f>IF($B10="BIG_SIDE",$V10*$AU10,0)</f>
         <v/>
       </c>
     </row>
@@ -2741,41 +3078,40 @@
       <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B11" s="13">
+        <f>IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C11" s="13">
-        <f>IF($AP10="YES",$AF10,$C10)</f>
+        <f>IF($B11="BLOCKED",$AF10,IF($AP10="YES",$AF10,$C10))</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF($AP10="YES",MAX(0,$AG10),$D10)</f>
+        <f>IF($B11="BLOCKED",0,IF($AP10="YES",MAX(0,$AG10),$D10))</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>IF(C11="SELL","BUY","SELL")</f>
+        <f>IF($B11="BLOCKED","",IF($C11="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>MAX(0,D11*Settings!$B$3)</f>
+        <f>IF($B11="BLOCKED",0,MAX(0,$D11*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>IFERROR(MAX(0,ROUND(F11/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($F11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H11" s="12">
-        <f>C11</f>
+        <f>IF($B11="BLOCKED","",$C11)</f>
         <v/>
       </c>
       <c r="I11" s="12">
-        <f>MAX(0,G11*Settings!$B$4)</f>
+        <f>IF($B11="BLOCKED",0,MAX(0,$G11*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J11" s="12">
-        <f>IFERROR(MAX(0,ROUND(I11/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K11" s="13" t="n">
@@ -2788,83 +3124,83 @@
         <v>100</v>
       </c>
       <c r="N11" s="14">
-        <f>IF(B11="BIG_SIDE",G11*MAX(0,K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O11" s="14">
-        <f>IF(B11="SMALL_SIDE",J11*ABS(L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P11" s="15">
-        <f>IF(B11="BIG_SIDE",J11*ABS(L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q11" s="15">
-        <f>IF(B11="SMALL_SIDE",AL11*ABS(K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R11" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT11*$AU11</f>
         <v/>
       </c>
       <c r="S11" s="14">
-        <f>IF(B11="BIG_SIDE",N11-P11-R11,O11-Q11-R11)</f>
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$R11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
         <v/>
       </c>
       <c r="T11" s="12">
-        <f>IF(AND(B11="BIG_SIDE",S11&gt;0),S11*Settings!$B$5,0)</f>
+        <f>IF(AND($B11="BIG_SIDE",$AX11&gt;0),$AX11*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U11" s="12">
-        <f>MAX(0,M11*Settings!$B$9)</f>
+        <f>MAX(0,$M11*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V11" s="12">
-        <f>IF(B11="BIG_SIDE",IFERROR(MIN(D11,MAX(0,T11/U11)),0),0)</f>
+        <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
         <v/>
       </c>
       <c r="W11" s="12">
-        <f>IF(B11="BIG_SIDE",MAX(0,D11-V11),AJ11)</f>
-        <v/>
-      </c>
-      <c r="X11" s="16">
-        <f>IF(B11="BIG_SIDE",IF(S11&gt;0,S11*Settings!$B$6,0),IF(S11&gt;0,S11*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y11" s="16">
-        <f>Y10+X11</f>
+        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="19">
+        <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y11" s="19">
+        <f>$Y10+$X11</f>
         <v/>
       </c>
       <c r="Z11" s="12">
-        <f>AA10</f>
+        <f>$AA10</f>
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>Z11+S11</f>
+        <f>IF($B11="BLOCKED",$Z11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
-        <f>D11+G11+J11</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10+$AJ10),$D11+$G11+$J11)</f>
         <v/>
       </c>
       <c r="AC11" s="12">
-        <f>IF(B11="BIG_SIDE",W11,AG11+AJ11)</f>
+        <f>IF($B11="BLOCKED",$AB11,IF($B11="BIG_SIDE",$W11,$AG11+$AJ11))</f>
         <v/>
       </c>
       <c r="AD11" s="12">
-        <f>AB11*Settings!$B$10</f>
+        <f>$AB11*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE11" s="12">
-        <f>AC11*Settings!$B$10</f>
+        <f>$AC11*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF11" s="12">
-        <f>IF(B11="SMALL_SIDE",E11,C11)</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,$C11,$AF10),IF($B11="SMALL_SIDE",$E11,$C11))</f>
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF(B11="SMALL_SIDE",AM11,W11)</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -2876,44 +3212,76 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="12">
-        <f>IF(B11="SMALL_SIDE",IF(AH11="YES",0,IFERROR(MAX(0,D11-MAX(0,AI11)/U11),D11)),0)</f>
+        <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
       <c r="AK11" s="12">
-        <f>IF(AND(AJ11&gt;0,AG11&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL11" s="12">
-        <f>IF(B11="SMALL_SIDE",G11*Settings!$B$7,IF(B11="BIG_SIDE",G11,0))</f>
+        <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
         <v/>
       </c>
       <c r="AM11" s="12">
-        <f>IF(B11="SMALL_SIDE",MAX(0,G11-AL11),0)</f>
+        <f>IF($B11="SMALL_SIDE",MAX(0,$G11-$AL11),0)</f>
         <v/>
       </c>
       <c r="AN11" s="12">
-        <f>IF(B11="BIG_SIDE",1,IF(B11="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B11="BIG_SIDE",1,IF($B11="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO11" s="12">
-        <f>IF(OR(B11="BIG_SIDE",B11="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B11="BIG_SIDE",$B11="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP11" s="12">
-        <f>IF(OR(AQ11="DUAL_TAIL",AQ11="DANGER",AQ11="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ11" s="12">
-        <f>IF(AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G11/D11,999)&gt;Settings!$B$16,IFERROR(J11/G11,999)&gt;Settings!$B$17,AE11&gt;AD11,Y11&lt;0,AG11&gt;D11*1.0001,S11&lt;-100),"DANGER",IF(OR(AND(B11="BIG_SIDE",U11&lt;=0),S11&lt;=0,X11=0,AE11&gt;AD11*0.95),"WARNING","OK")))</f>
+        <f>IF($B11="BLOCKED","STOP",IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR11" s="12">
-        <f>IF(B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS11" s="20">
+        <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
+        <v/>
+      </c>
+      <c r="AT11" s="12">
+        <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
+        <v/>
+      </c>
+      <c r="AU11" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV11" s="12">
+        <f>IF($B11="SMALL_SIDE",IF($AH11="YES",$D11,IFERROR(MIN($D11,MAX(0,$AI11/$U11)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW11" s="12">
+        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX11" s="12">
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="12">
+        <f>IF($B11="BIG_SIDE",($G11+$J11)*$AU11,0)</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="12">
+        <f>IF($B11="BIG_SIDE",$V11*$AU11,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR11"/>
+  <autoFilter ref="A1:AZ11"/>
   <conditionalFormatting sqref="AQ2:AQ11">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AQ2="WARNING"</formula>
@@ -2949,7 +3317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2996,6 +3364,14 @@
     <col width="14" customWidth="1" min="42" max="42"/>
     <col width="14" customWidth="1" min="43" max="43"/>
     <col width="55" customWidth="1" min="44" max="44"/>
+    <col width="18" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="18" customWidth="1" min="50" max="50"/>
+    <col width="18" customWidth="1" min="51" max="51"/>
+    <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3219,6 +3595,46 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>RealizedFarLoss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>ClosedLotsForCosts</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>CostPerLot</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>OldFarClosedLot</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>BlockedReason</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>NetProfitBeforeFar</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>CostsBeforeFar</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>CostsFarClose</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -3239,27 +3655,27 @@
         <v/>
       </c>
       <c r="E2" s="12">
-        <f>IF(C2="SELL","BUY","SELL")</f>
+        <f>IF($B2="BLOCKED","",IF($C2="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F2" s="12">
-        <f>MAX(0,D2*Settings!$B$3)</f>
+        <f>IF($B2="BLOCKED",0,MAX(0,$D2*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G2" s="12">
-        <f>IFERROR(MAX(0,ROUND(F2/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H2" s="12">
-        <f>C2</f>
+        <f>IF($B2="BLOCKED","",$C2)</f>
         <v/>
       </c>
       <c r="I2" s="12">
-        <f>MAX(0,G2*Settings!$B$4)</f>
+        <f>IF($B2="BLOCKED",0,MAX(0,$G2*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J2" s="12">
-        <f>IFERROR(MAX(0,ROUND(I2/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K2" s="13" t="n">
@@ -3272,50 +3688,50 @@
         <v>100</v>
       </c>
       <c r="N2" s="14">
-        <f>IF(B2="BIG_SIDE",G2*MAX(0,K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="BIG_SIDE",$G2*MAX(0,$K2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O2" s="14">
-        <f>IF(B2="SMALL_SIDE",J2*ABS(L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P2" s="15">
-        <f>IF(B2="BIG_SIDE",J2*ABS(L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="BIG_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q2" s="15">
-        <f>IF(B2="SMALL_SIDE",AL2*ABS(K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$AL2*ABS($K2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R2" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT2*$AU2</f>
         <v/>
       </c>
       <c r="S2" s="14">
-        <f>IF(B2="BIG_SIDE",N2-P2-R2,O2-Q2-R2)</f>
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$R2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
         <v/>
       </c>
       <c r="T2" s="12">
-        <f>IF(AND(B2="BIG_SIDE",S2&gt;0),S2*Settings!$B$5,0)</f>
+        <f>IF(AND($B2="BIG_SIDE",$AX2&gt;0),$AX2*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U2" s="12">
-        <f>MAX(0,M2*Settings!$B$9)</f>
+        <f>MAX(0,$M2*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V2" s="12">
-        <f>IF(B2="BIG_SIDE",IFERROR(MIN(D2,MAX(0,T2/U2)),0),0)</f>
+        <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
         <v/>
       </c>
       <c r="W2" s="12">
-        <f>IF(B2="BIG_SIDE",MAX(0,D2-V2),AJ2)</f>
-        <v/>
-      </c>
-      <c r="X2" s="16">
-        <f>IF(B2="BIG_SIDE",IF(S2&gt;0,S2*Settings!$B$6,0),IF(S2&gt;0,S2*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y2" s="16">
+        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
+        <v/>
+      </c>
+      <c r="X2" s="19">
+        <f>IF($B2="BIG_SIDE",IF($AX2&gt;0,$AX2-$AS2,0),IF($S2&gt;0,$S2*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y2" s="19">
         <f>X2</f>
         <v/>
       </c>
@@ -3323,31 +3739,31 @@
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>Z2+S2</f>
+        <f>IF($B2="BLOCKED",$Z2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
         <v/>
       </c>
       <c r="AB2" s="12">
-        <f>D2+G2+J2</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1+$AJ1),$D2+$G2+$J2)</f>
         <v/>
       </c>
       <c r="AC2" s="12">
-        <f>IF(B2="BIG_SIDE",W2,AG2+AJ2)</f>
+        <f>IF($B2="BLOCKED",$AB2,IF($B2="BIG_SIDE",$W2,$AG2+$AJ2))</f>
         <v/>
       </c>
       <c r="AD2" s="12">
-        <f>AB2*Settings!$B$10</f>
+        <f>$AB2*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE2" s="12">
-        <f>AC2*Settings!$B$10</f>
+        <f>$AC2*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF(B2="SMALL_SIDE",E2,C2)</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,$C2,$AF1),IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF(B2="SMALL_SIDE",AM2,W2)</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -3359,39 +3775,71 @@
         <v>0</v>
       </c>
       <c r="AJ2" s="12">
-        <f>IF(B2="SMALL_SIDE",IF(AH2="YES",0,IFERROR(MAX(0,D2-MAX(0,AI2)/U2),D2)),0)</f>
+        <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
       <c r="AK2" s="12">
-        <f>IF(AND(AJ2&gt;0,AG2&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL2" s="12">
-        <f>IF(B2="SMALL_SIDE",G2*Settings!$B$7,IF(B2="BIG_SIDE",G2,0))</f>
+        <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
         <v/>
       </c>
       <c r="AM2" s="12">
-        <f>IF(B2="SMALL_SIDE",MAX(0,G2-AL2),0)</f>
+        <f>IF($B2="SMALL_SIDE",MAX(0,$G2-$AL2),0)</f>
         <v/>
       </c>
       <c r="AN2" s="12">
-        <f>IF(B2="BIG_SIDE",1,IF(B2="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B2="BIG_SIDE",1,IF($B2="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO2" s="12">
-        <f>IF(OR(B2="BIG_SIDE",B2="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP2" s="12">
-        <f>IF(OR(AQ2="DUAL_TAIL",AQ2="DANGER",AQ2="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ2" s="12">
-        <f>IF(AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G2/D2,999)&gt;Settings!$B$16,IFERROR(J2/G2,999)&gt;Settings!$B$17,AE2&gt;AD2,Y2&lt;0,AG2&gt;D2*1.0001,S2&lt;-100),"DANGER",IF(OR(AND(B2="BIG_SIDE",U2&lt;=0),S2&lt;=0,X2=0,AE2&gt;AD2*0.95),"WARNING","OK")))</f>
+        <f>IF($B2="BLOCKED","STOP",IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR2" s="12">
-        <f>IF(B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS2" s="20">
+        <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
+        <v/>
+      </c>
+      <c r="AT2" s="12">
+        <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
+        <v/>
+      </c>
+      <c r="AU2" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV2" s="12">
+        <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW2" s="12">
+        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX2" s="12">
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
+        <v/>
+      </c>
+      <c r="AY2" s="12">
+        <f>IF($B2="BIG_SIDE",($G2+$J2)*$AU2,0)</f>
+        <v/>
+      </c>
+      <c r="AZ2" s="12">
+        <f>IF($B2="BIG_SIDE",$V2*$AU2,0)</f>
         <v/>
       </c>
     </row>
@@ -3399,41 +3847,40 @@
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B3" s="13">
+        <f>IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C3" s="13">
-        <f>IF($AP2="YES",$AF2,$C2)</f>
+        <f>IF($B3="BLOCKED",$AF2,IF($AP2="YES",$AF2,$C2))</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>IF($AP2="YES",MAX(0,$AG2),$D2)</f>
+        <f>IF($B3="BLOCKED",0,IF($AP2="YES",MAX(0,$AG2),$D2))</f>
         <v/>
       </c>
       <c r="E3" s="12">
-        <f>IF(C3="SELL","BUY","SELL")</f>
+        <f>IF($B3="BLOCKED","",IF($C3="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F3" s="12">
-        <f>MAX(0,D3*Settings!$B$3)</f>
+        <f>IF($B3="BLOCKED",0,MAX(0,$D3*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G3" s="12">
-        <f>IFERROR(MAX(0,ROUND(F3/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H3" s="12">
-        <f>C3</f>
+        <f>IF($B3="BLOCKED","",$C3)</f>
         <v/>
       </c>
       <c r="I3" s="12">
-        <f>MAX(0,G3*Settings!$B$4)</f>
+        <f>IF($B3="BLOCKED",0,MAX(0,$G3*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J3" s="12">
-        <f>IFERROR(MAX(0,ROUND(I3/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K3" s="13" t="n">
@@ -3446,83 +3893,83 @@
         <v>100</v>
       </c>
       <c r="N3" s="14">
-        <f>IF(B3="BIG_SIDE",G3*MAX(0,K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$G3*MAX(0,$K3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O3" s="14">
-        <f>IF(B3="SMALL_SIDE",J3*ABS(L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P3" s="15">
-        <f>IF(B3="BIG_SIDE",J3*ABS(L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q3" s="15">
-        <f>IF(B3="SMALL_SIDE",AL3*ABS(K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$AL3*ABS($K3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R3" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT3*$AU3</f>
         <v/>
       </c>
       <c r="S3" s="14">
-        <f>IF(B3="BIG_SIDE",N3-P3-R3,O3-Q3-R3)</f>
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$R3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
         <v/>
       </c>
       <c r="T3" s="12">
-        <f>IF(AND(B3="BIG_SIDE",S3&gt;0),S3*Settings!$B$5,0)</f>
+        <f>IF(AND($B3="BIG_SIDE",$AX3&gt;0),$AX3*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U3" s="12">
-        <f>MAX(0,M3*Settings!$B$9)</f>
+        <f>MAX(0,$M3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V3" s="12">
-        <f>IF(B3="BIG_SIDE",IFERROR(MIN(D3,MAX(0,T3/U3)),0),0)</f>
+        <f>IF($B3="BIG_SIDE",IFERROR(MIN($D3,MAX(0,$T3/$U3)),0),0)</f>
         <v/>
       </c>
       <c r="W3" s="12">
-        <f>IF(B3="BIG_SIDE",MAX(0,D3-V3),AJ3)</f>
-        <v/>
-      </c>
-      <c r="X3" s="16">
-        <f>IF(B3="BIG_SIDE",IF(S3&gt;0,S3*Settings!$B$6,0),IF(S3&gt;0,S3*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="16">
-        <f>Y2+X3</f>
+        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$V3),$AJ3)</f>
+        <v/>
+      </c>
+      <c r="X3" s="19">
+        <f>IF($B3="BIG_SIDE",IF($AX3&gt;0,$AX3-$AS3,0),IF($S3&gt;0,$S3*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="19">
+        <f>$Y2+$X3</f>
         <v/>
       </c>
       <c r="Z3" s="12">
-        <f>AA2</f>
+        <f>$AA2</f>
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>Z3+S3</f>
+        <f>IF($B3="BLOCKED",$Z3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
-        <f>D3+G3+J3</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2+$AJ2),$D3+$G3+$J3)</f>
         <v/>
       </c>
       <c r="AC3" s="12">
-        <f>IF(B3="BIG_SIDE",W3,AG3+AJ3)</f>
+        <f>IF($B3="BLOCKED",$AB3,IF($B3="BIG_SIDE",$W3,$AG3+$AJ3))</f>
         <v/>
       </c>
       <c r="AD3" s="12">
-        <f>AB3*Settings!$B$10</f>
+        <f>$AB3*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE3" s="12">
-        <f>AC3*Settings!$B$10</f>
+        <f>$AC3*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF3" s="12">
-        <f>IF(B3="SMALL_SIDE",E3,C3)</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,$C3,$AF2),IF($B3="SMALL_SIDE",$E3,$C3))</f>
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF(B3="SMALL_SIDE",AM3,W3)</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
         <v/>
       </c>
       <c r="AH3" s="13" t="inlineStr">
@@ -3534,39 +3981,71 @@
         <v>0</v>
       </c>
       <c r="AJ3" s="12">
-        <f>IF(B3="SMALL_SIDE",IF(AH3="YES",0,IFERROR(MAX(0,D3-MAX(0,AI3)/U3),D3)),0)</f>
+        <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
         <v/>
       </c>
       <c r="AK3" s="12">
-        <f>IF(AND(AJ3&gt;0,AG3&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL3" s="12">
-        <f>IF(B3="SMALL_SIDE",G3*Settings!$B$7,IF(B3="BIG_SIDE",G3,0))</f>
+        <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
         <v/>
       </c>
       <c r="AM3" s="12">
-        <f>IF(B3="SMALL_SIDE",MAX(0,G3-AL3),0)</f>
+        <f>IF($B3="SMALL_SIDE",MAX(0,$G3-$AL3),0)</f>
         <v/>
       </c>
       <c r="AN3" s="12">
-        <f>IF(B3="BIG_SIDE",1,IF(B3="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B3="BIG_SIDE",1,IF($B3="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO3" s="12">
-        <f>IF(OR(B3="BIG_SIDE",B3="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B3="BIG_SIDE",$B3="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP3" s="12">
-        <f>IF(OR(AQ3="DUAL_TAIL",AQ3="DANGER",AQ3="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ3" s="12">
-        <f>IF(AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G3/D3,999)&gt;Settings!$B$16,IFERROR(J3/G3,999)&gt;Settings!$B$17,AE3&gt;AD3,Y3&lt;0,AG3&gt;D3*1.0001,S3&lt;-100),"DANGER",IF(OR(AND(B3="BIG_SIDE",U3&lt;=0),S3&lt;=0,X3=0,AE3&gt;AD3*0.95),"WARNING","OK")))</f>
+        <f>IF($B3="BLOCKED","STOP",IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR3" s="12">
-        <f>IF(B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS3" s="20">
+        <f>IF($B3="BIG_SIDE",$V3*$U3,0)</f>
+        <v/>
+      </c>
+      <c r="AT3" s="12">
+        <f>IF($B3="BIG_SIDE",$G3+$J3+$V3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
+        <v/>
+      </c>
+      <c r="AU3" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV3" s="12">
+        <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW3" s="12">
+        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX3" s="12">
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
+        <v/>
+      </c>
+      <c r="AY3" s="12">
+        <f>IF($B3="BIG_SIDE",($G3+$J3)*$AU3,0)</f>
+        <v/>
+      </c>
+      <c r="AZ3" s="12">
+        <f>IF($B3="BIG_SIDE",$V3*$AU3,0)</f>
         <v/>
       </c>
     </row>
@@ -3574,41 +4053,40 @@
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B4" s="13">
+        <f>IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C4" s="13">
-        <f>IF($AP3="YES",$AF3,$C3)</f>
+        <f>IF($B4="BLOCKED",$AF3,IF($AP3="YES",$AF3,$C3))</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF($AP3="YES",MAX(0,$AG3),$D3)</f>
+        <f>IF($B4="BLOCKED",0,IF($AP3="YES",MAX(0,$AG3),$D3))</f>
         <v/>
       </c>
       <c r="E4" s="12">
-        <f>IF(C4="SELL","BUY","SELL")</f>
+        <f>IF($B4="BLOCKED","",IF($C4="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>MAX(0,D4*Settings!$B$3)</f>
+        <f>IF($B4="BLOCKED",0,MAX(0,$D4*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G4" s="12">
-        <f>IFERROR(MAX(0,ROUND(F4/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($F4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H4" s="12">
-        <f>C4</f>
+        <f>IF($B4="BLOCKED","",$C4)</f>
         <v/>
       </c>
       <c r="I4" s="12">
-        <f>MAX(0,G4*Settings!$B$4)</f>
+        <f>IF($B4="BLOCKED",0,MAX(0,$G4*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J4" s="12">
-        <f>IFERROR(MAX(0,ROUND(I4/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K4" s="13" t="n">
@@ -3621,83 +4099,83 @@
         <v>100</v>
       </c>
       <c r="N4" s="14">
-        <f>IF(B4="BIG_SIDE",G4*MAX(0,K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$G4*MAX(0,$K4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O4" s="14">
-        <f>IF(B4="SMALL_SIDE",J4*ABS(L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P4" s="15">
-        <f>IF(B4="BIG_SIDE",J4*ABS(L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q4" s="15">
-        <f>IF(B4="SMALL_SIDE",AL4*ABS(K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$AL4*ABS($K4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R4" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT4*$AU4</f>
         <v/>
       </c>
       <c r="S4" s="14">
-        <f>IF(B4="BIG_SIDE",N4-P4-R4,O4-Q4-R4)</f>
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$R4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
         <v/>
       </c>
       <c r="T4" s="12">
-        <f>IF(AND(B4="BIG_SIDE",S4&gt;0),S4*Settings!$B$5,0)</f>
+        <f>IF(AND($B4="BIG_SIDE",$AX4&gt;0),$AX4*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U4" s="12">
-        <f>MAX(0,M4*Settings!$B$9)</f>
+        <f>MAX(0,$M4*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V4" s="12">
-        <f>IF(B4="BIG_SIDE",IFERROR(MIN(D4,MAX(0,T4/U4)),0),0)</f>
+        <f>IF($B4="BIG_SIDE",IFERROR(MIN($D4,MAX(0,$T4/$U4)),0),0)</f>
         <v/>
       </c>
       <c r="W4" s="12">
-        <f>IF(B4="BIG_SIDE",MAX(0,D4-V4),AJ4)</f>
-        <v/>
-      </c>
-      <c r="X4" s="16">
-        <f>IF(B4="BIG_SIDE",IF(S4&gt;0,S4*Settings!$B$6,0),IF(S4&gt;0,S4*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y4" s="16">
-        <f>Y3+X4</f>
+        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$V4),$AJ4)</f>
+        <v/>
+      </c>
+      <c r="X4" s="19">
+        <f>IF($B4="BIG_SIDE",IF($AX4&gt;0,$AX4-$AS4,0),IF($S4&gt;0,$S4*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y4" s="19">
+        <f>$Y3+$X4</f>
         <v/>
       </c>
       <c r="Z4" s="12">
-        <f>AA3</f>
+        <f>$AA3</f>
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>Z4+S4</f>
+        <f>IF($B4="BLOCKED",$Z4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
-        <f>D4+G4+J4</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3+$AJ3),$D4+$G4+$J4)</f>
         <v/>
       </c>
       <c r="AC4" s="12">
-        <f>IF(B4="BIG_SIDE",W4,AG4+AJ4)</f>
+        <f>IF($B4="BLOCKED",$AB4,IF($B4="BIG_SIDE",$W4,$AG4+$AJ4))</f>
         <v/>
       </c>
       <c r="AD4" s="12">
-        <f>AB4*Settings!$B$10</f>
+        <f>$AB4*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE4" s="12">
-        <f>AC4*Settings!$B$10</f>
+        <f>$AC4*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF4" s="12">
-        <f>IF(B4="SMALL_SIDE",E4,C4)</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,$C4,$AF3),IF($B4="SMALL_SIDE",$E4,$C4))</f>
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF(B4="SMALL_SIDE",AM4,W4)</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -3709,39 +4187,71 @@
         <v>0</v>
       </c>
       <c r="AJ4" s="12">
-        <f>IF(B4="SMALL_SIDE",IF(AH4="YES",0,IFERROR(MAX(0,D4-MAX(0,AI4)/U4),D4)),0)</f>
+        <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
         <v/>
       </c>
       <c r="AK4" s="12">
-        <f>IF(AND(AJ4&gt;0,AG4&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL4" s="12">
-        <f>IF(B4="SMALL_SIDE",G4*Settings!$B$7,IF(B4="BIG_SIDE",G4,0))</f>
+        <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
         <v/>
       </c>
       <c r="AM4" s="12">
-        <f>IF(B4="SMALL_SIDE",MAX(0,G4-AL4),0)</f>
+        <f>IF($B4="SMALL_SIDE",MAX(0,$G4-$AL4),0)</f>
         <v/>
       </c>
       <c r="AN4" s="12">
-        <f>IF(B4="BIG_SIDE",1,IF(B4="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B4="BIG_SIDE",1,IF($B4="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO4" s="12">
-        <f>IF(OR(B4="BIG_SIDE",B4="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B4="BIG_SIDE",$B4="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP4" s="12">
-        <f>IF(OR(AQ4="DUAL_TAIL",AQ4="DANGER",AQ4="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ4" s="12">
-        <f>IF(AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G4/D4,999)&gt;Settings!$B$16,IFERROR(J4/G4,999)&gt;Settings!$B$17,AE4&gt;AD4,Y4&lt;0,AG4&gt;D4*1.0001,S4&lt;-100),"DANGER",IF(OR(AND(B4="BIG_SIDE",U4&lt;=0),S4&lt;=0,X4=0,AE4&gt;AD4*0.95),"WARNING","OK")))</f>
+        <f>IF($B4="BLOCKED","STOP",IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR4" s="12">
-        <f>IF(B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS4" s="20">
+        <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
+        <v/>
+      </c>
+      <c r="AT4" s="12">
+        <f>IF($B4="BIG_SIDE",$G4+$J4+$V4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
+        <v/>
+      </c>
+      <c r="AU4" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV4" s="12">
+        <f>IF($B4="SMALL_SIDE",IF($AH4="YES",$D4,IFERROR(MIN($D4,MAX(0,$AI4/$U4)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW4" s="12">
+        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX4" s="12">
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
+        <v/>
+      </c>
+      <c r="AY4" s="12">
+        <f>IF($B4="BIG_SIDE",($G4+$J4)*$AU4,0)</f>
+        <v/>
+      </c>
+      <c r="AZ4" s="12">
+        <f>IF($B4="BIG_SIDE",$V4*$AU4,0)</f>
         <v/>
       </c>
     </row>
@@ -3749,41 +4259,40 @@
       <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>SMALL_SIDE</t>
-        </is>
+      <c r="B5" s="13">
+        <f>IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <v/>
       </c>
       <c r="C5" s="13">
-        <f>IF($AP4="YES",$AF4,$C4)</f>
+        <f>IF($B5="BLOCKED",$AF4,IF($AP4="YES",$AF4,$C4))</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF($AP4="YES",MAX(0,$AG4),$D4)</f>
+        <f>IF($B5="BLOCKED",0,IF($AP4="YES",MAX(0,$AG4),$D4))</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>IF(C5="SELL","BUY","SELL")</f>
+        <f>IF($B5="BLOCKED","",IF($C5="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>MAX(0,D5*Settings!$B$3)</f>
+        <f>IF($B5="BLOCKED",0,MAX(0,$D5*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G5" s="12">
-        <f>IFERROR(MAX(0,ROUND(F5/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($F5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H5" s="12">
-        <f>C5</f>
+        <f>IF($B5="BLOCKED","",$C5)</f>
         <v/>
       </c>
       <c r="I5" s="12">
-        <f>MAX(0,G5*Settings!$B$4)</f>
+        <f>IF($B5="BLOCKED",0,MAX(0,$G5*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J5" s="12">
-        <f>IFERROR(MAX(0,ROUND(I5/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K5" s="13" t="n">
@@ -3796,83 +4305,83 @@
         <v>100</v>
       </c>
       <c r="N5" s="14">
-        <f>IF(B5="BIG_SIDE",G5*MAX(0,K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O5" s="14">
-        <f>IF(B5="SMALL_SIDE",J5*ABS(L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P5" s="15">
-        <f>IF(B5="BIG_SIDE",J5*ABS(L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q5" s="15">
-        <f>IF(B5="SMALL_SIDE",AL5*ABS(K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R5" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT5*$AU5</f>
         <v/>
       </c>
       <c r="S5" s="14">
-        <f>IF(B5="BIG_SIDE",N5-P5-R5,O5-Q5-R5)</f>
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$R5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
         <v/>
       </c>
       <c r="T5" s="12">
-        <f>IF(AND(B5="BIG_SIDE",S5&gt;0),S5*Settings!$B$5,0)</f>
+        <f>IF(AND($B5="BIG_SIDE",$AX5&gt;0),$AX5*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U5" s="12">
-        <f>MAX(0,M5*Settings!$B$9)</f>
+        <f>MAX(0,$M5*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V5" s="12">
-        <f>IF(B5="BIG_SIDE",IFERROR(MIN(D5,MAX(0,T5/U5)),0),0)</f>
+        <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
         <v/>
       </c>
       <c r="W5" s="12">
-        <f>IF(B5="BIG_SIDE",MAX(0,D5-V5),AJ5)</f>
-        <v/>
-      </c>
-      <c r="X5" s="16">
-        <f>IF(B5="BIG_SIDE",IF(S5&gt;0,S5*Settings!$B$6,0),IF(S5&gt;0,S5*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="16">
-        <f>Y4+X5</f>
+        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
+        <v/>
+      </c>
+      <c r="X5" s="19">
+        <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y5" s="19">
+        <f>$Y4+$X5</f>
         <v/>
       </c>
       <c r="Z5" s="12">
-        <f>AA4</f>
+        <f>$AA4</f>
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>Z5+S5</f>
+        <f>IF($B5="BLOCKED",$Z5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
-        <f>D5+G5+J5</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4+$AJ4),$D5+$G5+$J5)</f>
         <v/>
       </c>
       <c r="AC5" s="12">
-        <f>IF(B5="BIG_SIDE",W5,AG5+AJ5)</f>
+        <f>IF($B5="BLOCKED",$AB5,IF($B5="BIG_SIDE",$W5,$AG5+$AJ5))</f>
         <v/>
       </c>
       <c r="AD5" s="12">
-        <f>AB5*Settings!$B$10</f>
+        <f>$AB5*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE5" s="12">
-        <f>AC5*Settings!$B$10</f>
+        <f>$AC5*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF5" s="12">
-        <f>IF(B5="SMALL_SIDE",E5,C5)</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,$C5,$AF4),IF($B5="SMALL_SIDE",$E5,$C5))</f>
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF(B5="SMALL_SIDE",AM5,W5)</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v/>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -3884,39 +4393,71 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="12">
-        <f>IF(B5="SMALL_SIDE",IF(AH5="YES",0,IFERROR(MAX(0,D5-MAX(0,AI5)/U5),D5)),0)</f>
+        <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
         <v/>
       </c>
       <c r="AK5" s="12">
-        <f>IF(AND(AJ5&gt;0,AG5&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL5" s="12">
-        <f>IF(B5="SMALL_SIDE",G5*Settings!$B$7,IF(B5="BIG_SIDE",G5,0))</f>
+        <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
         <v/>
       </c>
       <c r="AM5" s="12">
-        <f>IF(B5="SMALL_SIDE",MAX(0,G5-AL5),0)</f>
+        <f>IF($B5="SMALL_SIDE",MAX(0,$G5-$AL5),0)</f>
         <v/>
       </c>
       <c r="AN5" s="12">
-        <f>IF(B5="BIG_SIDE",1,IF(B5="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B5="BIG_SIDE",1,IF($B5="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO5" s="12">
-        <f>IF(OR(B5="BIG_SIDE",B5="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B5="BIG_SIDE",$B5="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP5" s="12">
-        <f>IF(OR(AQ5="DUAL_TAIL",AQ5="DANGER",AQ5="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ5" s="12">
-        <f>IF(AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G5/D5,999)&gt;Settings!$B$16,IFERROR(J5/G5,999)&gt;Settings!$B$17,AE5&gt;AD5,Y5&lt;0,AG5&gt;D5*1.0001,S5&lt;-100),"DANGER",IF(OR(AND(B5="BIG_SIDE",U5&lt;=0),S5&lt;=0,X5=0,AE5&gt;AD5*0.95),"WARNING","OK")))</f>
+        <f>IF($B5="BLOCKED","STOP",IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR5" s="12">
-        <f>IF(B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS5" s="20">
+        <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
+        <v/>
+      </c>
+      <c r="AT5" s="12">
+        <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
+        <v/>
+      </c>
+      <c r="AU5" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV5" s="12">
+        <f>IF($B5="SMALL_SIDE",IF($AH5="YES",$D5,IFERROR(MIN($D5,MAX(0,$AI5/$U5)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW5" s="12">
+        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX5" s="12">
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
+        <v/>
+      </c>
+      <c r="AY5" s="12">
+        <f>IF($B5="BIG_SIDE",($G5+$J5)*$AU5,0)</f>
+        <v/>
+      </c>
+      <c r="AZ5" s="12">
+        <f>IF($B5="BIG_SIDE",$V5*$AU5,0)</f>
         <v/>
       </c>
     </row>
@@ -3924,41 +4465,40 @@
       <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B6" s="13">
+        <f>IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C6" s="13">
-        <f>IF($AP5="YES",$AF5,$C5)</f>
+        <f>IF($B6="BLOCKED",$AF5,IF($AP5="YES",$AF5,$C5))</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF($AP5="YES",MAX(0,$AG5),$D5)</f>
+        <f>IF($B6="BLOCKED",0,IF($AP5="YES",MAX(0,$AG5),$D5))</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>IF(C6="SELL","BUY","SELL")</f>
+        <f>IF($B6="BLOCKED","",IF($C6="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>MAX(0,D6*Settings!$B$3)</f>
+        <f>IF($B6="BLOCKED",0,MAX(0,$D6*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G6" s="12">
-        <f>IFERROR(MAX(0,ROUND(F6/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($F6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H6" s="12">
-        <f>C6</f>
+        <f>IF($B6="BLOCKED","",$C6)</f>
         <v/>
       </c>
       <c r="I6" s="12">
-        <f>MAX(0,G6*Settings!$B$4)</f>
+        <f>IF($B6="BLOCKED",0,MAX(0,$G6*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J6" s="12">
-        <f>IFERROR(MAX(0,ROUND(I6/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K6" s="13" t="n">
@@ -3971,83 +4511,83 @@
         <v>100</v>
       </c>
       <c r="N6" s="14">
-        <f>IF(B6="BIG_SIDE",G6*MAX(0,K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O6" s="14">
-        <f>IF(B6="SMALL_SIDE",J6*ABS(L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P6" s="15">
-        <f>IF(B6="BIG_SIDE",J6*ABS(L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q6" s="15">
-        <f>IF(B6="SMALL_SIDE",AL6*ABS(K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R6" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT6*$AU6</f>
         <v/>
       </c>
       <c r="S6" s="14">
-        <f>IF(B6="BIG_SIDE",N6-P6-R6,O6-Q6-R6)</f>
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$R6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
         <v/>
       </c>
       <c r="T6" s="12">
-        <f>IF(AND(B6="BIG_SIDE",S6&gt;0),S6*Settings!$B$5,0)</f>
+        <f>IF(AND($B6="BIG_SIDE",$AX6&gt;0),$AX6*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U6" s="12">
-        <f>MAX(0,M6*Settings!$B$9)</f>
+        <f>MAX(0,$M6*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V6" s="12">
-        <f>IF(B6="BIG_SIDE",IFERROR(MIN(D6,MAX(0,T6/U6)),0),0)</f>
+        <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
         <v/>
       </c>
       <c r="W6" s="12">
-        <f>IF(B6="BIG_SIDE",MAX(0,D6-V6),AJ6)</f>
-        <v/>
-      </c>
-      <c r="X6" s="16">
-        <f>IF(B6="BIG_SIDE",IF(S6&gt;0,S6*Settings!$B$6,0),IF(S6&gt;0,S6*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="16">
-        <f>Y5+X6</f>
+        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
+        <v/>
+      </c>
+      <c r="X6" s="19">
+        <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y6" s="19">
+        <f>$Y5+$X6</f>
         <v/>
       </c>
       <c r="Z6" s="12">
-        <f>AA5</f>
+        <f>$AA5</f>
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>Z6+S6</f>
+        <f>IF($B6="BLOCKED",$Z6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
-        <f>D6+G6+J6</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5+$AJ5),$D6+$G6+$J6)</f>
         <v/>
       </c>
       <c r="AC6" s="12">
-        <f>IF(B6="BIG_SIDE",W6,AG6+AJ6)</f>
+        <f>IF($B6="BLOCKED",$AB6,IF($B6="BIG_SIDE",$W6,$AG6+$AJ6))</f>
         <v/>
       </c>
       <c r="AD6" s="12">
-        <f>AB6*Settings!$B$10</f>
+        <f>$AB6*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE6" s="12">
-        <f>AC6*Settings!$B$10</f>
+        <f>$AC6*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF6" s="12">
-        <f>IF(B6="SMALL_SIDE",E6,C6)</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,$C6,$AF5),IF($B6="SMALL_SIDE",$E6,$C6))</f>
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF(B6="SMALL_SIDE",AM6,W6)</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -4059,39 +4599,71 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="12">
-        <f>IF(B6="SMALL_SIDE",IF(AH6="YES",0,IFERROR(MAX(0,D6-MAX(0,AI6)/U6),D6)),0)</f>
+        <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
       <c r="AK6" s="12">
-        <f>IF(AND(AJ6&gt;0,AG6&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL6" s="12">
-        <f>IF(B6="SMALL_SIDE",G6*Settings!$B$7,IF(B6="BIG_SIDE",G6,0))</f>
+        <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
         <v/>
       </c>
       <c r="AM6" s="12">
-        <f>IF(B6="SMALL_SIDE",MAX(0,G6-AL6),0)</f>
+        <f>IF($B6="SMALL_SIDE",MAX(0,$G6-$AL6),0)</f>
         <v/>
       </c>
       <c r="AN6" s="12">
-        <f>IF(B6="BIG_SIDE",1,IF(B6="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B6="BIG_SIDE",1,IF($B6="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO6" s="12">
-        <f>IF(OR(B6="BIG_SIDE",B6="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B6="BIG_SIDE",$B6="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP6" s="12">
-        <f>IF(OR(AQ6="DUAL_TAIL",AQ6="DANGER",AQ6="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ6" s="12">
-        <f>IF(AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G6/D6,999)&gt;Settings!$B$16,IFERROR(J6/G6,999)&gt;Settings!$B$17,AE6&gt;AD6,Y6&lt;0,AG6&gt;D6*1.0001,S6&lt;-100),"DANGER",IF(OR(AND(B6="BIG_SIDE",U6&lt;=0),S6&lt;=0,X6=0,AE6&gt;AD6*0.95),"WARNING","OK")))</f>
+        <f>IF($B6="BLOCKED","STOP",IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR6" s="12">
-        <f>IF(B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS6" s="20">
+        <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
+        <v/>
+      </c>
+      <c r="AT6" s="12">
+        <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
+        <v/>
+      </c>
+      <c r="AU6" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV6" s="12">
+        <f>IF($B6="SMALL_SIDE",IF($AH6="YES",$D6,IFERROR(MIN($D6,MAX(0,$AI6/$U6)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW6" s="12">
+        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX6" s="12">
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
+        <v/>
+      </c>
+      <c r="AY6" s="12">
+        <f>IF($B6="BIG_SIDE",($G6+$J6)*$AU6,0)</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="12">
+        <f>IF($B6="BIG_SIDE",$V6*$AU6,0)</f>
         <v/>
       </c>
     </row>
@@ -4099,41 +4671,40 @@
       <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B7" s="13">
+        <f>IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C7" s="13">
-        <f>IF($AP6="YES",$AF6,$C6)</f>
+        <f>IF($B7="BLOCKED",$AF6,IF($AP6="YES",$AF6,$C6))</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF($AP6="YES",MAX(0,$AG6),$D6)</f>
+        <f>IF($B7="BLOCKED",0,IF($AP6="YES",MAX(0,$AG6),$D6))</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>IF(C7="SELL","BUY","SELL")</f>
+        <f>IF($B7="BLOCKED","",IF($C7="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>MAX(0,D7*Settings!$B$3)</f>
+        <f>IF($B7="BLOCKED",0,MAX(0,$D7*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G7" s="12">
-        <f>IFERROR(MAX(0,ROUND(F7/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($F7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H7" s="12">
-        <f>C7</f>
+        <f>IF($B7="BLOCKED","",$C7)</f>
         <v/>
       </c>
       <c r="I7" s="12">
-        <f>MAX(0,G7*Settings!$B$4)</f>
+        <f>IF($B7="BLOCKED",0,MAX(0,$G7*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J7" s="12">
-        <f>IFERROR(MAX(0,ROUND(I7/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K7" s="13" t="n">
@@ -4146,83 +4717,83 @@
         <v>100</v>
       </c>
       <c r="N7" s="14">
-        <f>IF(B7="BIG_SIDE",G7*MAX(0,K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O7" s="14">
-        <f>IF(B7="SMALL_SIDE",J7*ABS(L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P7" s="15">
-        <f>IF(B7="BIG_SIDE",J7*ABS(L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q7" s="15">
-        <f>IF(B7="SMALL_SIDE",AL7*ABS(K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R7" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT7*$AU7</f>
         <v/>
       </c>
       <c r="S7" s="14">
-        <f>IF(B7="BIG_SIDE",N7-P7-R7,O7-Q7-R7)</f>
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$R7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
         <v/>
       </c>
       <c r="T7" s="12">
-        <f>IF(AND(B7="BIG_SIDE",S7&gt;0),S7*Settings!$B$5,0)</f>
+        <f>IF(AND($B7="BIG_SIDE",$AX7&gt;0),$AX7*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U7" s="12">
-        <f>MAX(0,M7*Settings!$B$9)</f>
+        <f>MAX(0,$M7*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V7" s="12">
-        <f>IF(B7="BIG_SIDE",IFERROR(MIN(D7,MAX(0,T7/U7)),0),0)</f>
+        <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
         <v/>
       </c>
       <c r="W7" s="12">
-        <f>IF(B7="BIG_SIDE",MAX(0,D7-V7),AJ7)</f>
-        <v/>
-      </c>
-      <c r="X7" s="16">
-        <f>IF(B7="BIG_SIDE",IF(S7&gt;0,S7*Settings!$B$6,0),IF(S7&gt;0,S7*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y7" s="16">
-        <f>Y6+X7</f>
+        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
+        <v/>
+      </c>
+      <c r="X7" s="19">
+        <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y7" s="19">
+        <f>$Y6+$X7</f>
         <v/>
       </c>
       <c r="Z7" s="12">
-        <f>AA6</f>
+        <f>$AA6</f>
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>Z7+S7</f>
+        <f>IF($B7="BLOCKED",$Z7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
-        <f>D7+G7+J7</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6+$AJ6),$D7+$G7+$J7)</f>
         <v/>
       </c>
       <c r="AC7" s="12">
-        <f>IF(B7="BIG_SIDE",W7,AG7+AJ7)</f>
+        <f>IF($B7="BLOCKED",$AB7,IF($B7="BIG_SIDE",$W7,$AG7+$AJ7))</f>
         <v/>
       </c>
       <c r="AD7" s="12">
-        <f>AB7*Settings!$B$10</f>
+        <f>$AB7*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE7" s="12">
-        <f>AC7*Settings!$B$10</f>
+        <f>$AC7*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF7" s="12">
-        <f>IF(B7="SMALL_SIDE",E7,C7)</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,$C7,$AF6),IF($B7="SMALL_SIDE",$E7,$C7))</f>
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF(B7="SMALL_SIDE",AM7,W7)</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -4234,39 +4805,71 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="12">
-        <f>IF(B7="SMALL_SIDE",IF(AH7="YES",0,IFERROR(MAX(0,D7-MAX(0,AI7)/U7),D7)),0)</f>
+        <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
       <c r="AK7" s="12">
-        <f>IF(AND(AJ7&gt;0,AG7&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL7" s="12">
-        <f>IF(B7="SMALL_SIDE",G7*Settings!$B$7,IF(B7="BIG_SIDE",G7,0))</f>
+        <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
         <v/>
       </c>
       <c r="AM7" s="12">
-        <f>IF(B7="SMALL_SIDE",MAX(0,G7-AL7),0)</f>
+        <f>IF($B7="SMALL_SIDE",MAX(0,$G7-$AL7),0)</f>
         <v/>
       </c>
       <c r="AN7" s="12">
-        <f>IF(B7="BIG_SIDE",1,IF(B7="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B7="BIG_SIDE",1,IF($B7="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO7" s="12">
-        <f>IF(OR(B7="BIG_SIDE",B7="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B7="BIG_SIDE",$B7="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP7" s="12">
-        <f>IF(OR(AQ7="DUAL_TAIL",AQ7="DANGER",AQ7="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ7" s="12">
-        <f>IF(AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G7/D7,999)&gt;Settings!$B$16,IFERROR(J7/G7,999)&gt;Settings!$B$17,AE7&gt;AD7,Y7&lt;0,AG7&gt;D7*1.0001,S7&lt;-100),"DANGER",IF(OR(AND(B7="BIG_SIDE",U7&lt;=0),S7&lt;=0,X7=0,AE7&gt;AD7*0.95),"WARNING","OK")))</f>
+        <f>IF($B7="BLOCKED","STOP",IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR7" s="12">
-        <f>IF(B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS7" s="20">
+        <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
+        <v/>
+      </c>
+      <c r="AT7" s="12">
+        <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
+        <v/>
+      </c>
+      <c r="AU7" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV7" s="12">
+        <f>IF($B7="SMALL_SIDE",IF($AH7="YES",$D7,IFERROR(MIN($D7,MAX(0,$AI7/$U7)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW7" s="12">
+        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX7" s="12">
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
+        <v/>
+      </c>
+      <c r="AY7" s="12">
+        <f>IF($B7="BIG_SIDE",($G7+$J7)*$AU7,0)</f>
+        <v/>
+      </c>
+      <c r="AZ7" s="12">
+        <f>IF($B7="BIG_SIDE",$V7*$AU7,0)</f>
         <v/>
       </c>
     </row>
@@ -4274,41 +4877,40 @@
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B8" s="13">
+        <f>IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C8" s="13">
-        <f>IF($AP7="YES",$AF7,$C7)</f>
+        <f>IF($B8="BLOCKED",$AF7,IF($AP7="YES",$AF7,$C7))</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF($AP7="YES",MAX(0,$AG7),$D7)</f>
+        <f>IF($B8="BLOCKED",0,IF($AP7="YES",MAX(0,$AG7),$D7))</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>IF(C8="SELL","BUY","SELL")</f>
+        <f>IF($B8="BLOCKED","",IF($C8="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>MAX(0,D8*Settings!$B$3)</f>
+        <f>IF($B8="BLOCKED",0,MAX(0,$D8*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G8" s="12">
-        <f>IFERROR(MAX(0,ROUND(F8/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($F8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H8" s="12">
-        <f>C8</f>
+        <f>IF($B8="BLOCKED","",$C8)</f>
         <v/>
       </c>
       <c r="I8" s="12">
-        <f>MAX(0,G8*Settings!$B$4)</f>
+        <f>IF($B8="BLOCKED",0,MAX(0,$G8*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J8" s="12">
-        <f>IFERROR(MAX(0,ROUND(I8/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K8" s="13" t="n">
@@ -4321,83 +4923,83 @@
         <v>100</v>
       </c>
       <c r="N8" s="14">
-        <f>IF(B8="BIG_SIDE",G8*MAX(0,K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O8" s="14">
-        <f>IF(B8="SMALL_SIDE",J8*ABS(L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P8" s="15">
-        <f>IF(B8="BIG_SIDE",J8*ABS(L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q8" s="15">
-        <f>IF(B8="SMALL_SIDE",AL8*ABS(K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R8" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT8*$AU8</f>
         <v/>
       </c>
       <c r="S8" s="14">
-        <f>IF(B8="BIG_SIDE",N8-P8-R8,O8-Q8-R8)</f>
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$R8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
         <v/>
       </c>
       <c r="T8" s="12">
-        <f>IF(AND(B8="BIG_SIDE",S8&gt;0),S8*Settings!$B$5,0)</f>
+        <f>IF(AND($B8="BIG_SIDE",$AX8&gt;0),$AX8*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U8" s="12">
-        <f>MAX(0,M8*Settings!$B$9)</f>
+        <f>MAX(0,$M8*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V8" s="12">
-        <f>IF(B8="BIG_SIDE",IFERROR(MIN(D8,MAX(0,T8/U8)),0),0)</f>
+        <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
         <v/>
       </c>
       <c r="W8" s="12">
-        <f>IF(B8="BIG_SIDE",MAX(0,D8-V8),AJ8)</f>
-        <v/>
-      </c>
-      <c r="X8" s="16">
-        <f>IF(B8="BIG_SIDE",IF(S8&gt;0,S8*Settings!$B$6,0),IF(S8&gt;0,S8*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y8" s="16">
-        <f>Y7+X8</f>
+        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
+        <v/>
+      </c>
+      <c r="X8" s="19">
+        <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y8" s="19">
+        <f>$Y7+$X8</f>
         <v/>
       </c>
       <c r="Z8" s="12">
-        <f>AA7</f>
+        <f>$AA7</f>
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>Z8+S8</f>
+        <f>IF($B8="BLOCKED",$Z8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
-        <f>D8+G8+J8</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7+$AJ7),$D8+$G8+$J8)</f>
         <v/>
       </c>
       <c r="AC8" s="12">
-        <f>IF(B8="BIG_SIDE",W8,AG8+AJ8)</f>
+        <f>IF($B8="BLOCKED",$AB8,IF($B8="BIG_SIDE",$W8,$AG8+$AJ8))</f>
         <v/>
       </c>
       <c r="AD8" s="12">
-        <f>AB8*Settings!$B$10</f>
+        <f>$AB8*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE8" s="12">
-        <f>AC8*Settings!$B$10</f>
+        <f>$AC8*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF8" s="12">
-        <f>IF(B8="SMALL_SIDE",E8,C8)</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,$C8,$AF7),IF($B8="SMALL_SIDE",$E8,$C8))</f>
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF(B8="SMALL_SIDE",AM8,W8)</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -4409,39 +5011,71 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="12">
-        <f>IF(B8="SMALL_SIDE",IF(AH8="YES",0,IFERROR(MAX(0,D8-MAX(0,AI8)/U8),D8)),0)</f>
+        <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
       <c r="AK8" s="12">
-        <f>IF(AND(AJ8&gt;0,AG8&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL8" s="12">
-        <f>IF(B8="SMALL_SIDE",G8*Settings!$B$7,IF(B8="BIG_SIDE",G8,0))</f>
+        <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
         <v/>
       </c>
       <c r="AM8" s="12">
-        <f>IF(B8="SMALL_SIDE",MAX(0,G8-AL8),0)</f>
+        <f>IF($B8="SMALL_SIDE",MAX(0,$G8-$AL8),0)</f>
         <v/>
       </c>
       <c r="AN8" s="12">
-        <f>IF(B8="BIG_SIDE",1,IF(B8="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B8="BIG_SIDE",1,IF($B8="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO8" s="12">
-        <f>IF(OR(B8="BIG_SIDE",B8="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B8="BIG_SIDE",$B8="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP8" s="12">
-        <f>IF(OR(AQ8="DUAL_TAIL",AQ8="DANGER",AQ8="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ8" s="12">
-        <f>IF(AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G8/D8,999)&gt;Settings!$B$16,IFERROR(J8/G8,999)&gt;Settings!$B$17,AE8&gt;AD8,Y8&lt;0,AG8&gt;D8*1.0001,S8&lt;-100),"DANGER",IF(OR(AND(B8="BIG_SIDE",U8&lt;=0),S8&lt;=0,X8=0,AE8&gt;AD8*0.95),"WARNING","OK")))</f>
+        <f>IF($B8="BLOCKED","STOP",IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR8" s="12">
-        <f>IF(B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS8" s="20">
+        <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
+        <v/>
+      </c>
+      <c r="AT8" s="12">
+        <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
+        <v/>
+      </c>
+      <c r="AU8" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV8" s="12">
+        <f>IF($B8="SMALL_SIDE",IF($AH8="YES",$D8,IFERROR(MIN($D8,MAX(0,$AI8/$U8)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW8" s="12">
+        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX8" s="12">
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
+        <v/>
+      </c>
+      <c r="AY8" s="12">
+        <f>IF($B8="BIG_SIDE",($G8+$J8)*$AU8,0)</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="12">
+        <f>IF($B8="BIG_SIDE",$V8*$AU8,0)</f>
         <v/>
       </c>
     </row>
@@ -4449,41 +5083,40 @@
       <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>SMALL_SIDE</t>
-        </is>
+      <c r="B9" s="13">
+        <f>IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <v/>
       </c>
       <c r="C9" s="13">
-        <f>IF($AP8="YES",$AF8,$C8)</f>
+        <f>IF($B9="BLOCKED",$AF8,IF($AP8="YES",$AF8,$C8))</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF($AP8="YES",MAX(0,$AG8),$D8)</f>
+        <f>IF($B9="BLOCKED",0,IF($AP8="YES",MAX(0,$AG8),$D8))</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>IF(C9="SELL","BUY","SELL")</f>
+        <f>IF($B9="BLOCKED","",IF($C9="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>MAX(0,D9*Settings!$B$3)</f>
+        <f>IF($B9="BLOCKED",0,MAX(0,$D9*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>IFERROR(MAX(0,ROUND(F9/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($F9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>C9</f>
+        <f>IF($B9="BLOCKED","",$C9)</f>
         <v/>
       </c>
       <c r="I9" s="12">
-        <f>MAX(0,G9*Settings!$B$4)</f>
+        <f>IF($B9="BLOCKED",0,MAX(0,$G9*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J9" s="12">
-        <f>IFERROR(MAX(0,ROUND(I9/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K9" s="13" t="n">
@@ -4496,83 +5129,83 @@
         <v>100</v>
       </c>
       <c r="N9" s="14">
-        <f>IF(B9="BIG_SIDE",G9*MAX(0,K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O9" s="14">
-        <f>IF(B9="SMALL_SIDE",J9*ABS(L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P9" s="15">
-        <f>IF(B9="BIG_SIDE",J9*ABS(L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q9" s="15">
-        <f>IF(B9="SMALL_SIDE",AL9*ABS(K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R9" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT9*$AU9</f>
         <v/>
       </c>
       <c r="S9" s="14">
-        <f>IF(B9="BIG_SIDE",N9-P9-R9,O9-Q9-R9)</f>
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$R9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
         <v/>
       </c>
       <c r="T9" s="12">
-        <f>IF(AND(B9="BIG_SIDE",S9&gt;0),S9*Settings!$B$5,0)</f>
+        <f>IF(AND($B9="BIG_SIDE",$AX9&gt;0),$AX9*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U9" s="12">
-        <f>MAX(0,M9*Settings!$B$9)</f>
+        <f>MAX(0,$M9*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>IF(B9="BIG_SIDE",IFERROR(MIN(D9,MAX(0,T9/U9)),0),0)</f>
+        <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
         <v/>
       </c>
       <c r="W9" s="12">
-        <f>IF(B9="BIG_SIDE",MAX(0,D9-V9),AJ9)</f>
-        <v/>
-      </c>
-      <c r="X9" s="16">
-        <f>IF(B9="BIG_SIDE",IF(S9&gt;0,S9*Settings!$B$6,0),IF(S9&gt;0,S9*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y9" s="16">
-        <f>Y8+X9</f>
+        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
+        <v/>
+      </c>
+      <c r="X9" s="19">
+        <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y9" s="19">
+        <f>$Y8+$X9</f>
         <v/>
       </c>
       <c r="Z9" s="12">
-        <f>AA8</f>
+        <f>$AA8</f>
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>Z9+S9</f>
+        <f>IF($B9="BLOCKED",$Z9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>D9+G9+J9</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8+$AJ8),$D9+$G9+$J9)</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>IF(B9="BIG_SIDE",W9,AG9+AJ9)</f>
+        <f>IF($B9="BLOCKED",$AB9,IF($B9="BIG_SIDE",$W9,$AG9+$AJ9))</f>
         <v/>
       </c>
       <c r="AD9" s="12">
-        <f>AB9*Settings!$B$10</f>
+        <f>$AB9*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE9" s="12">
-        <f>AC9*Settings!$B$10</f>
+        <f>$AC9*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>IF(B9="SMALL_SIDE",E9,C9)</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,$C9,$AF8),IF($B9="SMALL_SIDE",$E9,$C9))</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF(B9="SMALL_SIDE",AM9,W9)</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -4584,39 +5217,71 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="12">
-        <f>IF(B9="SMALL_SIDE",IF(AH9="YES",0,IFERROR(MAX(0,D9-MAX(0,AI9)/U9),D9)),0)</f>
+        <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
       <c r="AK9" s="12">
-        <f>IF(AND(AJ9&gt;0,AG9&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL9" s="12">
-        <f>IF(B9="SMALL_SIDE",G9*Settings!$B$7,IF(B9="BIG_SIDE",G9,0))</f>
+        <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
         <v/>
       </c>
       <c r="AM9" s="12">
-        <f>IF(B9="SMALL_SIDE",MAX(0,G9-AL9),0)</f>
+        <f>IF($B9="SMALL_SIDE",MAX(0,$G9-$AL9),0)</f>
         <v/>
       </c>
       <c r="AN9" s="12">
-        <f>IF(B9="BIG_SIDE",1,IF(B9="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B9="BIG_SIDE",1,IF($B9="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO9" s="12">
-        <f>IF(OR(B9="BIG_SIDE",B9="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B9="BIG_SIDE",$B9="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP9" s="12">
-        <f>IF(OR(AQ9="DUAL_TAIL",AQ9="DANGER",AQ9="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ9" s="12">
-        <f>IF(AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G9/D9,999)&gt;Settings!$B$16,IFERROR(J9/G9,999)&gt;Settings!$B$17,AE9&gt;AD9,Y9&lt;0,AG9&gt;D9*1.0001,S9&lt;-100),"DANGER",IF(OR(AND(B9="BIG_SIDE",U9&lt;=0),S9&lt;=0,X9=0,AE9&gt;AD9*0.95),"WARNING","OK")))</f>
+        <f>IF($B9="BLOCKED","STOP",IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR9" s="12">
-        <f>IF(B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS9" s="20">
+        <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
+        <v/>
+      </c>
+      <c r="AT9" s="12">
+        <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
+        <v/>
+      </c>
+      <c r="AU9" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV9" s="12">
+        <f>IF($B9="SMALL_SIDE",IF($AH9="YES",$D9,IFERROR(MIN($D9,MAX(0,$AI9/$U9)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW9" s="12">
+        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX9" s="12">
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
+        <v/>
+      </c>
+      <c r="AY9" s="12">
+        <f>IF($B9="BIG_SIDE",($G9+$J9)*$AU9,0)</f>
+        <v/>
+      </c>
+      <c r="AZ9" s="12">
+        <f>IF($B9="BIG_SIDE",$V9*$AU9,0)</f>
         <v/>
       </c>
     </row>
@@ -4624,41 +5289,40 @@
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B10" s="13">
+        <f>IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C10" s="13">
-        <f>IF($AP9="YES",$AF9,$C9)</f>
+        <f>IF($B10="BLOCKED",$AF9,IF($AP9="YES",$AF9,$C9))</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF($AP9="YES",MAX(0,$AG9),$D9)</f>
+        <f>IF($B10="BLOCKED",0,IF($AP9="YES",MAX(0,$AG9),$D9))</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>IF(C10="SELL","BUY","SELL")</f>
+        <f>IF($B10="BLOCKED","",IF($C10="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>MAX(0,D10*Settings!$B$3)</f>
+        <f>IF($B10="BLOCKED",0,MAX(0,$D10*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G10" s="12">
-        <f>IFERROR(MAX(0,ROUND(F10/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($F10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H10" s="12">
-        <f>C10</f>
+        <f>IF($B10="BLOCKED","",$C10)</f>
         <v/>
       </c>
       <c r="I10" s="12">
-        <f>MAX(0,G10*Settings!$B$4)</f>
+        <f>IF($B10="BLOCKED",0,MAX(0,$G10*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J10" s="12">
-        <f>IFERROR(MAX(0,ROUND(I10/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K10" s="13" t="n">
@@ -4671,83 +5335,83 @@
         <v>100</v>
       </c>
       <c r="N10" s="14">
-        <f>IF(B10="BIG_SIDE",G10*MAX(0,K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O10" s="14">
-        <f>IF(B10="SMALL_SIDE",J10*ABS(L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P10" s="15">
-        <f>IF(B10="BIG_SIDE",J10*ABS(L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q10" s="15">
-        <f>IF(B10="SMALL_SIDE",AL10*ABS(K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R10" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT10*$AU10</f>
         <v/>
       </c>
       <c r="S10" s="14">
-        <f>IF(B10="BIG_SIDE",N10-P10-R10,O10-Q10-R10)</f>
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$R10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
         <v/>
       </c>
       <c r="T10" s="12">
-        <f>IF(AND(B10="BIG_SIDE",S10&gt;0),S10*Settings!$B$5,0)</f>
+        <f>IF(AND($B10="BIG_SIDE",$AX10&gt;0),$AX10*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U10" s="12">
-        <f>MAX(0,M10*Settings!$B$9)</f>
+        <f>MAX(0,$M10*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V10" s="12">
-        <f>IF(B10="BIG_SIDE",IFERROR(MIN(D10,MAX(0,T10/U10)),0),0)</f>
+        <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
         <v/>
       </c>
       <c r="W10" s="12">
-        <f>IF(B10="BIG_SIDE",MAX(0,D10-V10),AJ10)</f>
-        <v/>
-      </c>
-      <c r="X10" s="16">
-        <f>IF(B10="BIG_SIDE",IF(S10&gt;0,S10*Settings!$B$6,0),IF(S10&gt;0,S10*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y10" s="16">
-        <f>Y9+X10</f>
+        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
+        <v/>
+      </c>
+      <c r="X10" s="19">
+        <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y10" s="19">
+        <f>$Y9+$X10</f>
         <v/>
       </c>
       <c r="Z10" s="12">
-        <f>AA9</f>
+        <f>$AA9</f>
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>Z10+S10</f>
+        <f>IF($B10="BLOCKED",$Z10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
-        <f>D10+G10+J10</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9+$AJ9),$D10+$G10+$J10)</f>
         <v/>
       </c>
       <c r="AC10" s="12">
-        <f>IF(B10="BIG_SIDE",W10,AG10+AJ10)</f>
+        <f>IF($B10="BLOCKED",$AB10,IF($B10="BIG_SIDE",$W10,$AG10+$AJ10))</f>
         <v/>
       </c>
       <c r="AD10" s="12">
-        <f>AB10*Settings!$B$10</f>
+        <f>$AB10*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE10" s="12">
-        <f>AC10*Settings!$B$10</f>
+        <f>$AC10*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF10" s="12">
-        <f>IF(B10="SMALL_SIDE",E10,C10)</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,$C10,$AF9),IF($B10="SMALL_SIDE",$E10,$C10))</f>
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF(B10="SMALL_SIDE",AM10,W10)</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -4759,39 +5423,71 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="12">
-        <f>IF(B10="SMALL_SIDE",IF(AH10="YES",0,IFERROR(MAX(0,D10-MAX(0,AI10)/U10),D10)),0)</f>
+        <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
       <c r="AK10" s="12">
-        <f>IF(AND(AJ10&gt;0,AG10&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL10" s="12">
-        <f>IF(B10="SMALL_SIDE",G10*Settings!$B$7,IF(B10="BIG_SIDE",G10,0))</f>
+        <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
         <v/>
       </c>
       <c r="AM10" s="12">
-        <f>IF(B10="SMALL_SIDE",MAX(0,G10-AL10),0)</f>
+        <f>IF($B10="SMALL_SIDE",MAX(0,$G10-$AL10),0)</f>
         <v/>
       </c>
       <c r="AN10" s="12">
-        <f>IF(B10="BIG_SIDE",1,IF(B10="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B10="BIG_SIDE",1,IF($B10="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO10" s="12">
-        <f>IF(OR(B10="BIG_SIDE",B10="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B10="BIG_SIDE",$B10="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP10" s="12">
-        <f>IF(OR(AQ10="DUAL_TAIL",AQ10="DANGER",AQ10="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ10" s="12">
-        <f>IF(AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G10/D10,999)&gt;Settings!$B$16,IFERROR(J10/G10,999)&gt;Settings!$B$17,AE10&gt;AD10,Y10&lt;0,AG10&gt;D10*1.0001,S10&lt;-100),"DANGER",IF(OR(AND(B10="BIG_SIDE",U10&lt;=0),S10&lt;=0,X10=0,AE10&gt;AD10*0.95),"WARNING","OK")))</f>
+        <f>IF($B10="BLOCKED","STOP",IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR10" s="12">
-        <f>IF(B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS10" s="20">
+        <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
+        <v/>
+      </c>
+      <c r="AT10" s="12">
+        <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
+        <v/>
+      </c>
+      <c r="AU10" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV10" s="12">
+        <f>IF($B10="SMALL_SIDE",IF($AH10="YES",$D10,IFERROR(MIN($D10,MAX(0,$AI10/$U10)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW10" s="12">
+        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX10" s="12">
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="12">
+        <f>IF($B10="BIG_SIDE",($G10+$J10)*$AU10,0)</f>
+        <v/>
+      </c>
+      <c r="AZ10" s="12">
+        <f>IF($B10="BIG_SIDE",$V10*$AU10,0)</f>
         <v/>
       </c>
     </row>
@@ -4799,41 +5495,40 @@
       <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B11" s="13">
+        <f>IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C11" s="13">
-        <f>IF($AP10="YES",$AF10,$C10)</f>
+        <f>IF($B11="BLOCKED",$AF10,IF($AP10="YES",$AF10,$C10))</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF($AP10="YES",MAX(0,$AG10),$D10)</f>
+        <f>IF($B11="BLOCKED",0,IF($AP10="YES",MAX(0,$AG10),$D10))</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>IF(C11="SELL","BUY","SELL")</f>
+        <f>IF($B11="BLOCKED","",IF($C11="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>MAX(0,D11*Settings!$B$3)</f>
+        <f>IF($B11="BLOCKED",0,MAX(0,$D11*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>IFERROR(MAX(0,ROUND(F11/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($F11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H11" s="12">
-        <f>C11</f>
+        <f>IF($B11="BLOCKED","",$C11)</f>
         <v/>
       </c>
       <c r="I11" s="12">
-        <f>MAX(0,G11*Settings!$B$4)</f>
+        <f>IF($B11="BLOCKED",0,MAX(0,$G11*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J11" s="12">
-        <f>IFERROR(MAX(0,ROUND(I11/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K11" s="13" t="n">
@@ -4846,83 +5541,83 @@
         <v>100</v>
       </c>
       <c r="N11" s="14">
-        <f>IF(B11="BIG_SIDE",G11*MAX(0,K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O11" s="14">
-        <f>IF(B11="SMALL_SIDE",J11*ABS(L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P11" s="15">
-        <f>IF(B11="BIG_SIDE",J11*ABS(L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q11" s="15">
-        <f>IF(B11="SMALL_SIDE",AL11*ABS(K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R11" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT11*$AU11</f>
         <v/>
       </c>
       <c r="S11" s="14">
-        <f>IF(B11="BIG_SIDE",N11-P11-R11,O11-Q11-R11)</f>
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$R11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
         <v/>
       </c>
       <c r="T11" s="12">
-        <f>IF(AND(B11="BIG_SIDE",S11&gt;0),S11*Settings!$B$5,0)</f>
+        <f>IF(AND($B11="BIG_SIDE",$AX11&gt;0),$AX11*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U11" s="12">
-        <f>MAX(0,M11*Settings!$B$9)</f>
+        <f>MAX(0,$M11*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V11" s="12">
-        <f>IF(B11="BIG_SIDE",IFERROR(MIN(D11,MAX(0,T11/U11)),0),0)</f>
+        <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
         <v/>
       </c>
       <c r="W11" s="12">
-        <f>IF(B11="BIG_SIDE",MAX(0,D11-V11),AJ11)</f>
-        <v/>
-      </c>
-      <c r="X11" s="16">
-        <f>IF(B11="BIG_SIDE",IF(S11&gt;0,S11*Settings!$B$6,0),IF(S11&gt;0,S11*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y11" s="16">
-        <f>Y10+X11</f>
+        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="19">
+        <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y11" s="19">
+        <f>$Y10+$X11</f>
         <v/>
       </c>
       <c r="Z11" s="12">
-        <f>AA10</f>
+        <f>$AA10</f>
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>Z11+S11</f>
+        <f>IF($B11="BLOCKED",$Z11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
-        <f>D11+G11+J11</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10+$AJ10),$D11+$G11+$J11)</f>
         <v/>
       </c>
       <c r="AC11" s="12">
-        <f>IF(B11="BIG_SIDE",W11,AG11+AJ11)</f>
+        <f>IF($B11="BLOCKED",$AB11,IF($B11="BIG_SIDE",$W11,$AG11+$AJ11))</f>
         <v/>
       </c>
       <c r="AD11" s="12">
-        <f>AB11*Settings!$B$10</f>
+        <f>$AB11*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE11" s="12">
-        <f>AC11*Settings!$B$10</f>
+        <f>$AC11*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF11" s="12">
-        <f>IF(B11="SMALL_SIDE",E11,C11)</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,$C11,$AF10),IF($B11="SMALL_SIDE",$E11,$C11))</f>
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF(B11="SMALL_SIDE",AM11,W11)</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -4934,44 +5629,76 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="12">
-        <f>IF(B11="SMALL_SIDE",IF(AH11="YES",0,IFERROR(MAX(0,D11-MAX(0,AI11)/U11),D11)),0)</f>
+        <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
       <c r="AK11" s="12">
-        <f>IF(AND(AJ11&gt;0,AG11&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL11" s="12">
-        <f>IF(B11="SMALL_SIDE",G11*Settings!$B$7,IF(B11="BIG_SIDE",G11,0))</f>
+        <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
         <v/>
       </c>
       <c r="AM11" s="12">
-        <f>IF(B11="SMALL_SIDE",MAX(0,G11-AL11),0)</f>
+        <f>IF($B11="SMALL_SIDE",MAX(0,$G11-$AL11),0)</f>
         <v/>
       </c>
       <c r="AN11" s="12">
-        <f>IF(B11="BIG_SIDE",1,IF(B11="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B11="BIG_SIDE",1,IF($B11="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO11" s="12">
-        <f>IF(OR(B11="BIG_SIDE",B11="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B11="BIG_SIDE",$B11="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP11" s="12">
-        <f>IF(OR(AQ11="DUAL_TAIL",AQ11="DANGER",AQ11="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ11" s="12">
-        <f>IF(AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G11/D11,999)&gt;Settings!$B$16,IFERROR(J11/G11,999)&gt;Settings!$B$17,AE11&gt;AD11,Y11&lt;0,AG11&gt;D11*1.0001,S11&lt;-100),"DANGER",IF(OR(AND(B11="BIG_SIDE",U11&lt;=0),S11&lt;=0,X11=0,AE11&gt;AD11*0.95),"WARNING","OK")))</f>
+        <f>IF($B11="BLOCKED","STOP",IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR11" s="12">
-        <f>IF(B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS11" s="20">
+        <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
+        <v/>
+      </c>
+      <c r="AT11" s="12">
+        <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
+        <v/>
+      </c>
+      <c r="AU11" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV11" s="12">
+        <f>IF($B11="SMALL_SIDE",IF($AH11="YES",$D11,IFERROR(MIN($D11,MAX(0,$AI11/$U11)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW11" s="12">
+        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX11" s="12">
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="12">
+        <f>IF($B11="BIG_SIDE",($G11+$J11)*$AU11,0)</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="12">
+        <f>IF($B11="BIG_SIDE",$V11*$AU11,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR11"/>
+  <autoFilter ref="A1:AZ11"/>
   <conditionalFormatting sqref="AQ2:AQ11">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AQ2="WARNING"</formula>
@@ -5007,7 +5734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5054,6 +5781,14 @@
     <col width="14" customWidth="1" min="42" max="42"/>
     <col width="14" customWidth="1" min="43" max="43"/>
     <col width="55" customWidth="1" min="44" max="44"/>
+    <col width="18" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="18" customWidth="1" min="50" max="50"/>
+    <col width="18" customWidth="1" min="51" max="51"/>
+    <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5277,6 +6012,46 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>RealizedFarLoss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>ClosedLotsForCosts</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>CostPerLot</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>OldFarClosedLot</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>BlockedReason</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>NetProfitBeforeFar</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>CostsBeforeFar</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>CostsFarClose</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -5297,27 +6072,27 @@
         <v/>
       </c>
       <c r="E2" s="12">
-        <f>IF(C2="SELL","BUY","SELL")</f>
+        <f>IF($B2="BLOCKED","",IF($C2="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F2" s="12">
-        <f>MAX(0,D2*Settings!$B$3)</f>
+        <f>IF($B2="BLOCKED",0,MAX(0,$D2*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G2" s="12">
-        <f>IFERROR(MAX(0,ROUND(F2/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H2" s="12">
-        <f>C2</f>
+        <f>IF($B2="BLOCKED","",$C2)</f>
         <v/>
       </c>
       <c r="I2" s="12">
-        <f>MAX(0,G2*Settings!$B$4)</f>
+        <f>IF($B2="BLOCKED",0,MAX(0,$G2*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J2" s="12">
-        <f>IFERROR(MAX(0,ROUND(I2/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K2" s="13" t="n">
@@ -5330,50 +6105,50 @@
         <v>100</v>
       </c>
       <c r="N2" s="14">
-        <f>IF(B2="BIG_SIDE",G2*MAX(0,K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="BIG_SIDE",$G2*MAX(0,$K2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O2" s="14">
-        <f>IF(B2="SMALL_SIDE",J2*ABS(L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P2" s="15">
-        <f>IF(B2="BIG_SIDE",J2*ABS(L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="BIG_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q2" s="15">
-        <f>IF(B2="SMALL_SIDE",AL2*ABS(K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$AL2*ABS($K2)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R2" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT2*$AU2</f>
         <v/>
       </c>
       <c r="S2" s="14">
-        <f>IF(B2="BIG_SIDE",N2-P2-R2,O2-Q2-R2)</f>
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$R2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
         <v/>
       </c>
       <c r="T2" s="12">
-        <f>IF(AND(B2="BIG_SIDE",S2&gt;0),S2*Settings!$B$5,0)</f>
+        <f>IF(AND($B2="BIG_SIDE",$AX2&gt;0),$AX2*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U2" s="12">
-        <f>MAX(0,M2*Settings!$B$9)</f>
+        <f>MAX(0,$M2*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V2" s="12">
-        <f>IF(B2="BIG_SIDE",IFERROR(MIN(D2,MAX(0,T2/U2)),0),0)</f>
+        <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
         <v/>
       </c>
       <c r="W2" s="12">
-        <f>IF(B2="BIG_SIDE",MAX(0,D2-V2),AJ2)</f>
-        <v/>
-      </c>
-      <c r="X2" s="16">
-        <f>IF(B2="BIG_SIDE",IF(S2&gt;0,S2*Settings!$B$6,0),IF(S2&gt;0,S2*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y2" s="16">
+        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
+        <v/>
+      </c>
+      <c r="X2" s="19">
+        <f>IF($B2="BIG_SIDE",IF($AX2&gt;0,$AX2-$AS2,0),IF($S2&gt;0,$S2*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y2" s="19">
         <f>X2</f>
         <v/>
       </c>
@@ -5381,31 +6156,31 @@
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>Z2+S2</f>
+        <f>IF($B2="BLOCKED",$Z2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
         <v/>
       </c>
       <c r="AB2" s="12">
-        <f>D2+G2+J2</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1+$AJ1),$D2+$G2+$J2)</f>
         <v/>
       </c>
       <c r="AC2" s="12">
-        <f>IF(B2="BIG_SIDE",W2,AG2+AJ2)</f>
+        <f>IF($B2="BLOCKED",$AB2,IF($B2="BIG_SIDE",$W2,$AG2+$AJ2))</f>
         <v/>
       </c>
       <c r="AD2" s="12">
-        <f>AB2*Settings!$B$10</f>
+        <f>$AB2*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE2" s="12">
-        <f>AC2*Settings!$B$10</f>
+        <f>$AC2*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF(B2="SMALL_SIDE",E2,C2)</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,$C2,$AF1),IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF(B2="SMALL_SIDE",AM2,W2)</f>
+        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -5417,39 +6192,71 @@
         <v>0</v>
       </c>
       <c r="AJ2" s="12">
-        <f>IF(B2="SMALL_SIDE",IF(AH2="YES",0,IFERROR(MAX(0,D2-MAX(0,AI2)/U2),D2)),0)</f>
+        <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
       <c r="AK2" s="12">
-        <f>IF(AND(AJ2&gt;0,AG2&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL2" s="12">
-        <f>IF(B2="SMALL_SIDE",G2*Settings!$B$7,IF(B2="BIG_SIDE",G2,0))</f>
+        <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
         <v/>
       </c>
       <c r="AM2" s="12">
-        <f>IF(B2="SMALL_SIDE",MAX(0,G2-AL2),0)</f>
+        <f>IF($B2="SMALL_SIDE",MAX(0,$G2-$AL2),0)</f>
         <v/>
       </c>
       <c r="AN2" s="12">
-        <f>IF(B2="BIG_SIDE",1,IF(B2="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B2="BIG_SIDE",1,IF($B2="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO2" s="12">
-        <f>IF(OR(B2="BIG_SIDE",B2="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP2" s="12">
-        <f>IF(OR(AQ2="DUAL_TAIL",AQ2="DANGER",AQ2="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ2" s="12">
-        <f>IF(AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G2/D2,999)&gt;Settings!$B$16,IFERROR(J2/G2,999)&gt;Settings!$B$17,AE2&gt;AD2,Y2&lt;0,AG2&gt;D2*1.0001,S2&lt;-100),"DANGER",IF(OR(AND(B2="BIG_SIDE",U2&lt;=0),S2&lt;=0,X2=0,AE2&gt;AD2*0.95),"WARNING","OK")))</f>
+        <f>IF($B2="BLOCKED","STOP",IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR2" s="12">
-        <f>IF(B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS2" s="20">
+        <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
+        <v/>
+      </c>
+      <c r="AT2" s="12">
+        <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
+        <v/>
+      </c>
+      <c r="AU2" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV2" s="12">
+        <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW2" s="12">
+        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX2" s="12">
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
+        <v/>
+      </c>
+      <c r="AY2" s="12">
+        <f>IF($B2="BIG_SIDE",($G2+$J2)*$AU2,0)</f>
+        <v/>
+      </c>
+      <c r="AZ2" s="12">
+        <f>IF($B2="BIG_SIDE",$V2*$AU2,0)</f>
         <v/>
       </c>
     </row>
@@ -5457,41 +6264,40 @@
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>SMALL_SIDE</t>
-        </is>
+      <c r="B3" s="13">
+        <f>IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <v/>
       </c>
       <c r="C3" s="13">
-        <f>IF($AP2="YES",$AF2,$C2)</f>
+        <f>IF($B3="BLOCKED",$AF2,IF($AP2="YES",$AF2,$C2))</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>IF($AP2="YES",MAX(0,$AG2),$D2)</f>
+        <f>IF($B3="BLOCKED",0,IF($AP2="YES",MAX(0,$AG2),$D2))</f>
         <v/>
       </c>
       <c r="E3" s="12">
-        <f>IF(C3="SELL","BUY","SELL")</f>
+        <f>IF($B3="BLOCKED","",IF($C3="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F3" s="12">
-        <f>MAX(0,D3*Settings!$B$3)</f>
+        <f>IF($B3="BLOCKED",0,MAX(0,$D3*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G3" s="12">
-        <f>IFERROR(MAX(0,ROUND(F3/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H3" s="12">
-        <f>C3</f>
+        <f>IF($B3="BLOCKED","",$C3)</f>
         <v/>
       </c>
       <c r="I3" s="12">
-        <f>MAX(0,G3*Settings!$B$4)</f>
+        <f>IF($B3="BLOCKED",0,MAX(0,$G3*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J3" s="12">
-        <f>IFERROR(MAX(0,ROUND(I3/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K3" s="13" t="n">
@@ -5504,83 +6310,83 @@
         <v>100</v>
       </c>
       <c r="N3" s="14">
-        <f>IF(B3="BIG_SIDE",G3*MAX(0,K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$G3*MAX(0,$K3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O3" s="14">
-        <f>IF(B3="SMALL_SIDE",J3*ABS(L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P3" s="15">
-        <f>IF(B3="BIG_SIDE",J3*ABS(L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q3" s="15">
-        <f>IF(B3="SMALL_SIDE",AL3*ABS(K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$AL3*ABS($K3)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R3" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT3*$AU3</f>
         <v/>
       </c>
       <c r="S3" s="14">
-        <f>IF(B3="BIG_SIDE",N3-P3-R3,O3-Q3-R3)</f>
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$R3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
         <v/>
       </c>
       <c r="T3" s="12">
-        <f>IF(AND(B3="BIG_SIDE",S3&gt;0),S3*Settings!$B$5,0)</f>
+        <f>IF(AND($B3="BIG_SIDE",$AX3&gt;0),$AX3*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U3" s="12">
-        <f>MAX(0,M3*Settings!$B$9)</f>
+        <f>MAX(0,$M3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V3" s="12">
-        <f>IF(B3="BIG_SIDE",IFERROR(MIN(D3,MAX(0,T3/U3)),0),0)</f>
+        <f>IF($B3="BIG_SIDE",IFERROR(MIN($D3,MAX(0,$T3/$U3)),0),0)</f>
         <v/>
       </c>
       <c r="W3" s="12">
-        <f>IF(B3="BIG_SIDE",MAX(0,D3-V3),AJ3)</f>
-        <v/>
-      </c>
-      <c r="X3" s="16">
-        <f>IF(B3="BIG_SIDE",IF(S3&gt;0,S3*Settings!$B$6,0),IF(S3&gt;0,S3*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="16">
-        <f>Y2+X3</f>
+        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$V3),$AJ3)</f>
+        <v/>
+      </c>
+      <c r="X3" s="19">
+        <f>IF($B3="BIG_SIDE",IF($AX3&gt;0,$AX3-$AS3,0),IF($S3&gt;0,$S3*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="19">
+        <f>$Y2+$X3</f>
         <v/>
       </c>
       <c r="Z3" s="12">
-        <f>AA2</f>
+        <f>$AA2</f>
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>Z3+S3</f>
+        <f>IF($B3="BLOCKED",$Z3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
-        <f>D3+G3+J3</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2+$AJ2),$D3+$G3+$J3)</f>
         <v/>
       </c>
       <c r="AC3" s="12">
-        <f>IF(B3="BIG_SIDE",W3,AG3+AJ3)</f>
+        <f>IF($B3="BLOCKED",$AB3,IF($B3="BIG_SIDE",$W3,$AG3+$AJ3))</f>
         <v/>
       </c>
       <c r="AD3" s="12">
-        <f>AB3*Settings!$B$10</f>
+        <f>$AB3*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE3" s="12">
-        <f>AC3*Settings!$B$10</f>
+        <f>$AC3*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF3" s="12">
-        <f>IF(B3="SMALL_SIDE",E3,C3)</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,$C3,$AF2),IF($B3="SMALL_SIDE",$E3,$C3))</f>
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF(B3="SMALL_SIDE",AM3,W3)</f>
+        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
         <v/>
       </c>
       <c r="AH3" s="13" t="inlineStr">
@@ -5592,39 +6398,71 @@
         <v>0</v>
       </c>
       <c r="AJ3" s="12">
-        <f>IF(B3="SMALL_SIDE",IF(AH3="YES",0,IFERROR(MAX(0,D3-MAX(0,AI3)/U3),D3)),0)</f>
+        <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
         <v/>
       </c>
       <c r="AK3" s="12">
-        <f>IF(AND(AJ3&gt;0,AG3&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL3" s="12">
-        <f>IF(B3="SMALL_SIDE",G3*Settings!$B$7,IF(B3="BIG_SIDE",G3,0))</f>
+        <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
         <v/>
       </c>
       <c r="AM3" s="12">
-        <f>IF(B3="SMALL_SIDE",MAX(0,G3-AL3),0)</f>
+        <f>IF($B3="SMALL_SIDE",MAX(0,$G3-$AL3),0)</f>
         <v/>
       </c>
       <c r="AN3" s="12">
-        <f>IF(B3="BIG_SIDE",1,IF(B3="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B3="BIG_SIDE",1,IF($B3="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO3" s="12">
-        <f>IF(OR(B3="BIG_SIDE",B3="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B3="BIG_SIDE",$B3="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP3" s="12">
-        <f>IF(OR(AQ3="DUAL_TAIL",AQ3="DANGER",AQ3="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ3" s="12">
-        <f>IF(AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G3/D3,999)&gt;Settings!$B$16,IFERROR(J3/G3,999)&gt;Settings!$B$17,AE3&gt;AD3,Y3&lt;0,AG3&gt;D3*1.0001,S3&lt;-100),"DANGER",IF(OR(AND(B3="BIG_SIDE",U3&lt;=0),S3&lt;=0,X3=0,AE3&gt;AD3*0.95),"WARNING","OK")))</f>
+        <f>IF($B3="BLOCKED","STOP",IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR3" s="12">
-        <f>IF(B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS3" s="20">
+        <f>IF($B3="BIG_SIDE",$V3*$U3,0)</f>
+        <v/>
+      </c>
+      <c r="AT3" s="12">
+        <f>IF($B3="BIG_SIDE",$G3+$J3+$V3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
+        <v/>
+      </c>
+      <c r="AU3" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV3" s="12">
+        <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW3" s="12">
+        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX3" s="12">
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
+        <v/>
+      </c>
+      <c r="AY3" s="12">
+        <f>IF($B3="BIG_SIDE",($G3+$J3)*$AU3,0)</f>
+        <v/>
+      </c>
+      <c r="AZ3" s="12">
+        <f>IF($B3="BIG_SIDE",$V3*$AU3,0)</f>
         <v/>
       </c>
     </row>
@@ -5632,41 +6470,40 @@
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B4" s="13">
+        <f>IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C4" s="13">
-        <f>IF($AP3="YES",$AF3,$C3)</f>
+        <f>IF($B4="BLOCKED",$AF3,IF($AP3="YES",$AF3,$C3))</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF($AP3="YES",MAX(0,$AG3),$D3)</f>
+        <f>IF($B4="BLOCKED",0,IF($AP3="YES",MAX(0,$AG3),$D3))</f>
         <v/>
       </c>
       <c r="E4" s="12">
-        <f>IF(C4="SELL","BUY","SELL")</f>
+        <f>IF($B4="BLOCKED","",IF($C4="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>MAX(0,D4*Settings!$B$3)</f>
+        <f>IF($B4="BLOCKED",0,MAX(0,$D4*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G4" s="12">
-        <f>IFERROR(MAX(0,ROUND(F4/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($F4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H4" s="12">
-        <f>C4</f>
+        <f>IF($B4="BLOCKED","",$C4)</f>
         <v/>
       </c>
       <c r="I4" s="12">
-        <f>MAX(0,G4*Settings!$B$4)</f>
+        <f>IF($B4="BLOCKED",0,MAX(0,$G4*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J4" s="12">
-        <f>IFERROR(MAX(0,ROUND(I4/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K4" s="13" t="n">
@@ -5679,83 +6516,83 @@
         <v>100</v>
       </c>
       <c r="N4" s="14">
-        <f>IF(B4="BIG_SIDE",G4*MAX(0,K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$G4*MAX(0,$K4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O4" s="14">
-        <f>IF(B4="SMALL_SIDE",J4*ABS(L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P4" s="15">
-        <f>IF(B4="BIG_SIDE",J4*ABS(L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q4" s="15">
-        <f>IF(B4="SMALL_SIDE",AL4*ABS(K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$AL4*ABS($K4)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R4" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT4*$AU4</f>
         <v/>
       </c>
       <c r="S4" s="14">
-        <f>IF(B4="BIG_SIDE",N4-P4-R4,O4-Q4-R4)</f>
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$R4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
         <v/>
       </c>
       <c r="T4" s="12">
-        <f>IF(AND(B4="BIG_SIDE",S4&gt;0),S4*Settings!$B$5,0)</f>
+        <f>IF(AND($B4="BIG_SIDE",$AX4&gt;0),$AX4*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U4" s="12">
-        <f>MAX(0,M4*Settings!$B$9)</f>
+        <f>MAX(0,$M4*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V4" s="12">
-        <f>IF(B4="BIG_SIDE",IFERROR(MIN(D4,MAX(0,T4/U4)),0),0)</f>
+        <f>IF($B4="BIG_SIDE",IFERROR(MIN($D4,MAX(0,$T4/$U4)),0),0)</f>
         <v/>
       </c>
       <c r="W4" s="12">
-        <f>IF(B4="BIG_SIDE",MAX(0,D4-V4),AJ4)</f>
-        <v/>
-      </c>
-      <c r="X4" s="16">
-        <f>IF(B4="BIG_SIDE",IF(S4&gt;0,S4*Settings!$B$6,0),IF(S4&gt;0,S4*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y4" s="16">
-        <f>Y3+X4</f>
+        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$V4),$AJ4)</f>
+        <v/>
+      </c>
+      <c r="X4" s="19">
+        <f>IF($B4="BIG_SIDE",IF($AX4&gt;0,$AX4-$AS4,0),IF($S4&gt;0,$S4*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y4" s="19">
+        <f>$Y3+$X4</f>
         <v/>
       </c>
       <c r="Z4" s="12">
-        <f>AA3</f>
+        <f>$AA3</f>
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>Z4+S4</f>
+        <f>IF($B4="BLOCKED",$Z4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
-        <f>D4+G4+J4</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3+$AJ3),$D4+$G4+$J4)</f>
         <v/>
       </c>
       <c r="AC4" s="12">
-        <f>IF(B4="BIG_SIDE",W4,AG4+AJ4)</f>
+        <f>IF($B4="BLOCKED",$AB4,IF($B4="BIG_SIDE",$W4,$AG4+$AJ4))</f>
         <v/>
       </c>
       <c r="AD4" s="12">
-        <f>AB4*Settings!$B$10</f>
+        <f>$AB4*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE4" s="12">
-        <f>AC4*Settings!$B$10</f>
+        <f>$AC4*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF4" s="12">
-        <f>IF(B4="SMALL_SIDE",E4,C4)</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,$C4,$AF3),IF($B4="SMALL_SIDE",$E4,$C4))</f>
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF(B4="SMALL_SIDE",AM4,W4)</f>
+        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -5767,39 +6604,71 @@
         <v>0</v>
       </c>
       <c r="AJ4" s="12">
-        <f>IF(B4="SMALL_SIDE",IF(AH4="YES",0,IFERROR(MAX(0,D4-MAX(0,AI4)/U4),D4)),0)</f>
+        <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
         <v/>
       </c>
       <c r="AK4" s="12">
-        <f>IF(AND(AJ4&gt;0,AG4&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL4" s="12">
-        <f>IF(B4="SMALL_SIDE",G4*Settings!$B$7,IF(B4="BIG_SIDE",G4,0))</f>
+        <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
         <v/>
       </c>
       <c r="AM4" s="12">
-        <f>IF(B4="SMALL_SIDE",MAX(0,G4-AL4),0)</f>
+        <f>IF($B4="SMALL_SIDE",MAX(0,$G4-$AL4),0)</f>
         <v/>
       </c>
       <c r="AN4" s="12">
-        <f>IF(B4="BIG_SIDE",1,IF(B4="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B4="BIG_SIDE",1,IF($B4="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO4" s="12">
-        <f>IF(OR(B4="BIG_SIDE",B4="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B4="BIG_SIDE",$B4="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP4" s="12">
-        <f>IF(OR(AQ4="DUAL_TAIL",AQ4="DANGER",AQ4="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ4" s="12">
-        <f>IF(AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G4/D4,999)&gt;Settings!$B$16,IFERROR(J4/G4,999)&gt;Settings!$B$17,AE4&gt;AD4,Y4&lt;0,AG4&gt;D4*1.0001,S4&lt;-100),"DANGER",IF(OR(AND(B4="BIG_SIDE",U4&lt;=0),S4&lt;=0,X4=0,AE4&gt;AD4*0.95),"WARNING","OK")))</f>
+        <f>IF($B4="BLOCKED","STOP",IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR4" s="12">
-        <f>IF(B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS4" s="20">
+        <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
+        <v/>
+      </c>
+      <c r="AT4" s="12">
+        <f>IF($B4="BIG_SIDE",$G4+$J4+$V4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
+        <v/>
+      </c>
+      <c r="AU4" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV4" s="12">
+        <f>IF($B4="SMALL_SIDE",IF($AH4="YES",$D4,IFERROR(MIN($D4,MAX(0,$AI4/$U4)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW4" s="12">
+        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX4" s="12">
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
+        <v/>
+      </c>
+      <c r="AY4" s="12">
+        <f>IF($B4="BIG_SIDE",($G4+$J4)*$AU4,0)</f>
+        <v/>
+      </c>
+      <c r="AZ4" s="12">
+        <f>IF($B4="BIG_SIDE",$V4*$AU4,0)</f>
         <v/>
       </c>
     </row>
@@ -5807,41 +6676,40 @@
       <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B5" s="13">
+        <f>IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C5" s="13">
-        <f>IF($AP4="YES",$AF4,$C4)</f>
+        <f>IF($B5="BLOCKED",$AF4,IF($AP4="YES",$AF4,$C4))</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF($AP4="YES",MAX(0,$AG4),$D4)</f>
+        <f>IF($B5="BLOCKED",0,IF($AP4="YES",MAX(0,$AG4),$D4))</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>IF(C5="SELL","BUY","SELL")</f>
+        <f>IF($B5="BLOCKED","",IF($C5="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>MAX(0,D5*Settings!$B$3)</f>
+        <f>IF($B5="BLOCKED",0,MAX(0,$D5*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G5" s="12">
-        <f>IFERROR(MAX(0,ROUND(F5/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($F5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H5" s="12">
-        <f>C5</f>
+        <f>IF($B5="BLOCKED","",$C5)</f>
         <v/>
       </c>
       <c r="I5" s="12">
-        <f>MAX(0,G5*Settings!$B$4)</f>
+        <f>IF($B5="BLOCKED",0,MAX(0,$G5*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J5" s="12">
-        <f>IFERROR(MAX(0,ROUND(I5/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K5" s="13" t="n">
@@ -5854,83 +6722,83 @@
         <v>100</v>
       </c>
       <c r="N5" s="14">
-        <f>IF(B5="BIG_SIDE",G5*MAX(0,K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O5" s="14">
-        <f>IF(B5="SMALL_SIDE",J5*ABS(L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P5" s="15">
-        <f>IF(B5="BIG_SIDE",J5*ABS(L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q5" s="15">
-        <f>IF(B5="SMALL_SIDE",AL5*ABS(K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R5" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT5*$AU5</f>
         <v/>
       </c>
       <c r="S5" s="14">
-        <f>IF(B5="BIG_SIDE",N5-P5-R5,O5-Q5-R5)</f>
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$R5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
         <v/>
       </c>
       <c r="T5" s="12">
-        <f>IF(AND(B5="BIG_SIDE",S5&gt;0),S5*Settings!$B$5,0)</f>
+        <f>IF(AND($B5="BIG_SIDE",$AX5&gt;0),$AX5*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U5" s="12">
-        <f>MAX(0,M5*Settings!$B$9)</f>
+        <f>MAX(0,$M5*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V5" s="12">
-        <f>IF(B5="BIG_SIDE",IFERROR(MIN(D5,MAX(0,T5/U5)),0),0)</f>
+        <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
         <v/>
       </c>
       <c r="W5" s="12">
-        <f>IF(B5="BIG_SIDE",MAX(0,D5-V5),AJ5)</f>
-        <v/>
-      </c>
-      <c r="X5" s="16">
-        <f>IF(B5="BIG_SIDE",IF(S5&gt;0,S5*Settings!$B$6,0),IF(S5&gt;0,S5*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="16">
-        <f>Y4+X5</f>
+        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
+        <v/>
+      </c>
+      <c r="X5" s="19">
+        <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y5" s="19">
+        <f>$Y4+$X5</f>
         <v/>
       </c>
       <c r="Z5" s="12">
-        <f>AA4</f>
+        <f>$AA4</f>
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>Z5+S5</f>
+        <f>IF($B5="BLOCKED",$Z5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
-        <f>D5+G5+J5</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4+$AJ4),$D5+$G5+$J5)</f>
         <v/>
       </c>
       <c r="AC5" s="12">
-        <f>IF(B5="BIG_SIDE",W5,AG5+AJ5)</f>
+        <f>IF($B5="BLOCKED",$AB5,IF($B5="BIG_SIDE",$W5,$AG5+$AJ5))</f>
         <v/>
       </c>
       <c r="AD5" s="12">
-        <f>AB5*Settings!$B$10</f>
+        <f>$AB5*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE5" s="12">
-        <f>AC5*Settings!$B$10</f>
+        <f>$AC5*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF5" s="12">
-        <f>IF(B5="SMALL_SIDE",E5,C5)</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,$C5,$AF4),IF($B5="SMALL_SIDE",$E5,$C5))</f>
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF(B5="SMALL_SIDE",AM5,W5)</f>
+        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v/>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -5942,39 +6810,71 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="12">
-        <f>IF(B5="SMALL_SIDE",IF(AH5="YES",0,IFERROR(MAX(0,D5-MAX(0,AI5)/U5),D5)),0)</f>
+        <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
         <v/>
       </c>
       <c r="AK5" s="12">
-        <f>IF(AND(AJ5&gt;0,AG5&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL5" s="12">
-        <f>IF(B5="SMALL_SIDE",G5*Settings!$B$7,IF(B5="BIG_SIDE",G5,0))</f>
+        <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
         <v/>
       </c>
       <c r="AM5" s="12">
-        <f>IF(B5="SMALL_SIDE",MAX(0,G5-AL5),0)</f>
+        <f>IF($B5="SMALL_SIDE",MAX(0,$G5-$AL5),0)</f>
         <v/>
       </c>
       <c r="AN5" s="12">
-        <f>IF(B5="BIG_SIDE",1,IF(B5="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B5="BIG_SIDE",1,IF($B5="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO5" s="12">
-        <f>IF(OR(B5="BIG_SIDE",B5="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B5="BIG_SIDE",$B5="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP5" s="12">
-        <f>IF(OR(AQ5="DUAL_TAIL",AQ5="DANGER",AQ5="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ5" s="12">
-        <f>IF(AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G5/D5,999)&gt;Settings!$B$16,IFERROR(J5/G5,999)&gt;Settings!$B$17,AE5&gt;AD5,Y5&lt;0,AG5&gt;D5*1.0001,S5&lt;-100),"DANGER",IF(OR(AND(B5="BIG_SIDE",U5&lt;=0),S5&lt;=0,X5=0,AE5&gt;AD5*0.95),"WARNING","OK")))</f>
+        <f>IF($B5="BLOCKED","STOP",IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR5" s="12">
-        <f>IF(B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS5" s="20">
+        <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
+        <v/>
+      </c>
+      <c r="AT5" s="12">
+        <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
+        <v/>
+      </c>
+      <c r="AU5" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV5" s="12">
+        <f>IF($B5="SMALL_SIDE",IF($AH5="YES",$D5,IFERROR(MIN($D5,MAX(0,$AI5/$U5)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW5" s="12">
+        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX5" s="12">
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
+        <v/>
+      </c>
+      <c r="AY5" s="12">
+        <f>IF($B5="BIG_SIDE",($G5+$J5)*$AU5,0)</f>
+        <v/>
+      </c>
+      <c r="AZ5" s="12">
+        <f>IF($B5="BIG_SIDE",$V5*$AU5,0)</f>
         <v/>
       </c>
     </row>
@@ -5982,41 +6882,40 @@
       <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B6" s="13">
+        <f>IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C6" s="13">
-        <f>IF($AP5="YES",$AF5,$C5)</f>
+        <f>IF($B6="BLOCKED",$AF5,IF($AP5="YES",$AF5,$C5))</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF($AP5="YES",MAX(0,$AG5),$D5)</f>
+        <f>IF($B6="BLOCKED",0,IF($AP5="YES",MAX(0,$AG5),$D5))</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>IF(C6="SELL","BUY","SELL")</f>
+        <f>IF($B6="BLOCKED","",IF($C6="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>MAX(0,D6*Settings!$B$3)</f>
+        <f>IF($B6="BLOCKED",0,MAX(0,$D6*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G6" s="12">
-        <f>IFERROR(MAX(0,ROUND(F6/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($F6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H6" s="12">
-        <f>C6</f>
+        <f>IF($B6="BLOCKED","",$C6)</f>
         <v/>
       </c>
       <c r="I6" s="12">
-        <f>MAX(0,G6*Settings!$B$4)</f>
+        <f>IF($B6="BLOCKED",0,MAX(0,$G6*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J6" s="12">
-        <f>IFERROR(MAX(0,ROUND(I6/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K6" s="13" t="n">
@@ -6029,83 +6928,83 @@
         <v>100</v>
       </c>
       <c r="N6" s="14">
-        <f>IF(B6="BIG_SIDE",G6*MAX(0,K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O6" s="14">
-        <f>IF(B6="SMALL_SIDE",J6*ABS(L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P6" s="15">
-        <f>IF(B6="BIG_SIDE",J6*ABS(L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q6" s="15">
-        <f>IF(B6="SMALL_SIDE",AL6*ABS(K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R6" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT6*$AU6</f>
         <v/>
       </c>
       <c r="S6" s="14">
-        <f>IF(B6="BIG_SIDE",N6-P6-R6,O6-Q6-R6)</f>
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$R6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
         <v/>
       </c>
       <c r="T6" s="12">
-        <f>IF(AND(B6="BIG_SIDE",S6&gt;0),S6*Settings!$B$5,0)</f>
+        <f>IF(AND($B6="BIG_SIDE",$AX6&gt;0),$AX6*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U6" s="12">
-        <f>MAX(0,M6*Settings!$B$9)</f>
+        <f>MAX(0,$M6*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V6" s="12">
-        <f>IF(B6="BIG_SIDE",IFERROR(MIN(D6,MAX(0,T6/U6)),0),0)</f>
+        <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
         <v/>
       </c>
       <c r="W6" s="12">
-        <f>IF(B6="BIG_SIDE",MAX(0,D6-V6),AJ6)</f>
-        <v/>
-      </c>
-      <c r="X6" s="16">
-        <f>IF(B6="BIG_SIDE",IF(S6&gt;0,S6*Settings!$B$6,0),IF(S6&gt;0,S6*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="16">
-        <f>Y5+X6</f>
+        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
+        <v/>
+      </c>
+      <c r="X6" s="19">
+        <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y6" s="19">
+        <f>$Y5+$X6</f>
         <v/>
       </c>
       <c r="Z6" s="12">
-        <f>AA5</f>
+        <f>$AA5</f>
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>Z6+S6</f>
+        <f>IF($B6="BLOCKED",$Z6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
-        <f>D6+G6+J6</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5+$AJ5),$D6+$G6+$J6)</f>
         <v/>
       </c>
       <c r="AC6" s="12">
-        <f>IF(B6="BIG_SIDE",W6,AG6+AJ6)</f>
+        <f>IF($B6="BLOCKED",$AB6,IF($B6="BIG_SIDE",$W6,$AG6+$AJ6))</f>
         <v/>
       </c>
       <c r="AD6" s="12">
-        <f>AB6*Settings!$B$10</f>
+        <f>$AB6*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE6" s="12">
-        <f>AC6*Settings!$B$10</f>
+        <f>$AC6*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF6" s="12">
-        <f>IF(B6="SMALL_SIDE",E6,C6)</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,$C6,$AF5),IF($B6="SMALL_SIDE",$E6,$C6))</f>
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF(B6="SMALL_SIDE",AM6,W6)</f>
+        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -6117,39 +7016,71 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="12">
-        <f>IF(B6="SMALL_SIDE",IF(AH6="YES",0,IFERROR(MAX(0,D6-MAX(0,AI6)/U6),D6)),0)</f>
+        <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
       <c r="AK6" s="12">
-        <f>IF(AND(AJ6&gt;0,AG6&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL6" s="12">
-        <f>IF(B6="SMALL_SIDE",G6*Settings!$B$7,IF(B6="BIG_SIDE",G6,0))</f>
+        <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
         <v/>
       </c>
       <c r="AM6" s="12">
-        <f>IF(B6="SMALL_SIDE",MAX(0,G6-AL6),0)</f>
+        <f>IF($B6="SMALL_SIDE",MAX(0,$G6-$AL6),0)</f>
         <v/>
       </c>
       <c r="AN6" s="12">
-        <f>IF(B6="BIG_SIDE",1,IF(B6="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B6="BIG_SIDE",1,IF($B6="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO6" s="12">
-        <f>IF(OR(B6="BIG_SIDE",B6="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B6="BIG_SIDE",$B6="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP6" s="12">
-        <f>IF(OR(AQ6="DUAL_TAIL",AQ6="DANGER",AQ6="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ6" s="12">
-        <f>IF(AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G6/D6,999)&gt;Settings!$B$16,IFERROR(J6/G6,999)&gt;Settings!$B$17,AE6&gt;AD6,Y6&lt;0,AG6&gt;D6*1.0001,S6&lt;-100),"DANGER",IF(OR(AND(B6="BIG_SIDE",U6&lt;=0),S6&lt;=0,X6=0,AE6&gt;AD6*0.95),"WARNING","OK")))</f>
+        <f>IF($B6="BLOCKED","STOP",IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR6" s="12">
-        <f>IF(B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS6" s="20">
+        <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
+        <v/>
+      </c>
+      <c r="AT6" s="12">
+        <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
+        <v/>
+      </c>
+      <c r="AU6" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV6" s="12">
+        <f>IF($B6="SMALL_SIDE",IF($AH6="YES",$D6,IFERROR(MIN($D6,MAX(0,$AI6/$U6)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW6" s="12">
+        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX6" s="12">
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
+        <v/>
+      </c>
+      <c r="AY6" s="12">
+        <f>IF($B6="BIG_SIDE",($G6+$J6)*$AU6,0)</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="12">
+        <f>IF($B6="BIG_SIDE",$V6*$AU6,0)</f>
         <v/>
       </c>
     </row>
@@ -6157,41 +7088,40 @@
       <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>SMALL_SIDE</t>
-        </is>
+      <c r="B7" s="13">
+        <f>IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <v/>
       </c>
       <c r="C7" s="13">
-        <f>IF($AP6="YES",$AF6,$C6)</f>
+        <f>IF($B7="BLOCKED",$AF6,IF($AP6="YES",$AF6,$C6))</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF($AP6="YES",MAX(0,$AG6),$D6)</f>
+        <f>IF($B7="BLOCKED",0,IF($AP6="YES",MAX(0,$AG6),$D6))</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>IF(C7="SELL","BUY","SELL")</f>
+        <f>IF($B7="BLOCKED","",IF($C7="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>MAX(0,D7*Settings!$B$3)</f>
+        <f>IF($B7="BLOCKED",0,MAX(0,$D7*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G7" s="12">
-        <f>IFERROR(MAX(0,ROUND(F7/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($F7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H7" s="12">
-        <f>C7</f>
+        <f>IF($B7="BLOCKED","",$C7)</f>
         <v/>
       </c>
       <c r="I7" s="12">
-        <f>MAX(0,G7*Settings!$B$4)</f>
+        <f>IF($B7="BLOCKED",0,MAX(0,$G7*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J7" s="12">
-        <f>IFERROR(MAX(0,ROUND(I7/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K7" s="13" t="n">
@@ -6204,83 +7134,83 @@
         <v>100</v>
       </c>
       <c r="N7" s="14">
-        <f>IF(B7="BIG_SIDE",G7*MAX(0,K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O7" s="14">
-        <f>IF(B7="SMALL_SIDE",J7*ABS(L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P7" s="15">
-        <f>IF(B7="BIG_SIDE",J7*ABS(L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q7" s="15">
-        <f>IF(B7="SMALL_SIDE",AL7*ABS(K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R7" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT7*$AU7</f>
         <v/>
       </c>
       <c r="S7" s="14">
-        <f>IF(B7="BIG_SIDE",N7-P7-R7,O7-Q7-R7)</f>
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$R7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
         <v/>
       </c>
       <c r="T7" s="12">
-        <f>IF(AND(B7="BIG_SIDE",S7&gt;0),S7*Settings!$B$5,0)</f>
+        <f>IF(AND($B7="BIG_SIDE",$AX7&gt;0),$AX7*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U7" s="12">
-        <f>MAX(0,M7*Settings!$B$9)</f>
+        <f>MAX(0,$M7*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V7" s="12">
-        <f>IF(B7="BIG_SIDE",IFERROR(MIN(D7,MAX(0,T7/U7)),0),0)</f>
+        <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
         <v/>
       </c>
       <c r="W7" s="12">
-        <f>IF(B7="BIG_SIDE",MAX(0,D7-V7),AJ7)</f>
-        <v/>
-      </c>
-      <c r="X7" s="16">
-        <f>IF(B7="BIG_SIDE",IF(S7&gt;0,S7*Settings!$B$6,0),IF(S7&gt;0,S7*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y7" s="16">
-        <f>Y6+X7</f>
+        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
+        <v/>
+      </c>
+      <c r="X7" s="19">
+        <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y7" s="19">
+        <f>$Y6+$X7</f>
         <v/>
       </c>
       <c r="Z7" s="12">
-        <f>AA6</f>
+        <f>$AA6</f>
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>Z7+S7</f>
+        <f>IF($B7="BLOCKED",$Z7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
-        <f>D7+G7+J7</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6+$AJ6),$D7+$G7+$J7)</f>
         <v/>
       </c>
       <c r="AC7" s="12">
-        <f>IF(B7="BIG_SIDE",W7,AG7+AJ7)</f>
+        <f>IF($B7="BLOCKED",$AB7,IF($B7="BIG_SIDE",$W7,$AG7+$AJ7))</f>
         <v/>
       </c>
       <c r="AD7" s="12">
-        <f>AB7*Settings!$B$10</f>
+        <f>$AB7*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE7" s="12">
-        <f>AC7*Settings!$B$10</f>
+        <f>$AC7*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF7" s="12">
-        <f>IF(B7="SMALL_SIDE",E7,C7)</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,$C7,$AF6),IF($B7="SMALL_SIDE",$E7,$C7))</f>
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF(B7="SMALL_SIDE",AM7,W7)</f>
+        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -6292,39 +7222,71 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="12">
-        <f>IF(B7="SMALL_SIDE",IF(AH7="YES",0,IFERROR(MAX(0,D7-MAX(0,AI7)/U7),D7)),0)</f>
+        <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
       <c r="AK7" s="12">
-        <f>IF(AND(AJ7&gt;0,AG7&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL7" s="12">
-        <f>IF(B7="SMALL_SIDE",G7*Settings!$B$7,IF(B7="BIG_SIDE",G7,0))</f>
+        <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
         <v/>
       </c>
       <c r="AM7" s="12">
-        <f>IF(B7="SMALL_SIDE",MAX(0,G7-AL7),0)</f>
+        <f>IF($B7="SMALL_SIDE",MAX(0,$G7-$AL7),0)</f>
         <v/>
       </c>
       <c r="AN7" s="12">
-        <f>IF(B7="BIG_SIDE",1,IF(B7="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B7="BIG_SIDE",1,IF($B7="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO7" s="12">
-        <f>IF(OR(B7="BIG_SIDE",B7="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B7="BIG_SIDE",$B7="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP7" s="12">
-        <f>IF(OR(AQ7="DUAL_TAIL",AQ7="DANGER",AQ7="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ7" s="12">
-        <f>IF(AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G7/D7,999)&gt;Settings!$B$16,IFERROR(J7/G7,999)&gt;Settings!$B$17,AE7&gt;AD7,Y7&lt;0,AG7&gt;D7*1.0001,S7&lt;-100),"DANGER",IF(OR(AND(B7="BIG_SIDE",U7&lt;=0),S7&lt;=0,X7=0,AE7&gt;AD7*0.95),"WARNING","OK")))</f>
+        <f>IF($B7="BLOCKED","STOP",IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR7" s="12">
-        <f>IF(B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS7" s="20">
+        <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
+        <v/>
+      </c>
+      <c r="AT7" s="12">
+        <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
+        <v/>
+      </c>
+      <c r="AU7" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV7" s="12">
+        <f>IF($B7="SMALL_SIDE",IF($AH7="YES",$D7,IFERROR(MIN($D7,MAX(0,$AI7/$U7)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW7" s="12">
+        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX7" s="12">
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
+        <v/>
+      </c>
+      <c r="AY7" s="12">
+        <f>IF($B7="BIG_SIDE",($G7+$J7)*$AU7,0)</f>
+        <v/>
+      </c>
+      <c r="AZ7" s="12">
+        <f>IF($B7="BIG_SIDE",$V7*$AU7,0)</f>
         <v/>
       </c>
     </row>
@@ -6332,41 +7294,40 @@
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B8" s="13">
+        <f>IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C8" s="13">
-        <f>IF($AP7="YES",$AF7,$C7)</f>
+        <f>IF($B8="BLOCKED",$AF7,IF($AP7="YES",$AF7,$C7))</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF($AP7="YES",MAX(0,$AG7),$D7)</f>
+        <f>IF($B8="BLOCKED",0,IF($AP7="YES",MAX(0,$AG7),$D7))</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>IF(C8="SELL","BUY","SELL")</f>
+        <f>IF($B8="BLOCKED","",IF($C8="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>MAX(0,D8*Settings!$B$3)</f>
+        <f>IF($B8="BLOCKED",0,MAX(0,$D8*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G8" s="12">
-        <f>IFERROR(MAX(0,ROUND(F8/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($F8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H8" s="12">
-        <f>C8</f>
+        <f>IF($B8="BLOCKED","",$C8)</f>
         <v/>
       </c>
       <c r="I8" s="12">
-        <f>MAX(0,G8*Settings!$B$4)</f>
+        <f>IF($B8="BLOCKED",0,MAX(0,$G8*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J8" s="12">
-        <f>IFERROR(MAX(0,ROUND(I8/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K8" s="13" t="n">
@@ -6379,83 +7340,83 @@
         <v>100</v>
       </c>
       <c r="N8" s="14">
-        <f>IF(B8="BIG_SIDE",G8*MAX(0,K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O8" s="14">
-        <f>IF(B8="SMALL_SIDE",J8*ABS(L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P8" s="15">
-        <f>IF(B8="BIG_SIDE",J8*ABS(L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q8" s="15">
-        <f>IF(B8="SMALL_SIDE",AL8*ABS(K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R8" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT8*$AU8</f>
         <v/>
       </c>
       <c r="S8" s="14">
-        <f>IF(B8="BIG_SIDE",N8-P8-R8,O8-Q8-R8)</f>
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$R8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
         <v/>
       </c>
       <c r="T8" s="12">
-        <f>IF(AND(B8="BIG_SIDE",S8&gt;0),S8*Settings!$B$5,0)</f>
+        <f>IF(AND($B8="BIG_SIDE",$AX8&gt;0),$AX8*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U8" s="12">
-        <f>MAX(0,M8*Settings!$B$9)</f>
+        <f>MAX(0,$M8*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V8" s="12">
-        <f>IF(B8="BIG_SIDE",IFERROR(MIN(D8,MAX(0,T8/U8)),0),0)</f>
+        <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
         <v/>
       </c>
       <c r="W8" s="12">
-        <f>IF(B8="BIG_SIDE",MAX(0,D8-V8),AJ8)</f>
-        <v/>
-      </c>
-      <c r="X8" s="16">
-        <f>IF(B8="BIG_SIDE",IF(S8&gt;0,S8*Settings!$B$6,0),IF(S8&gt;0,S8*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y8" s="16">
-        <f>Y7+X8</f>
+        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
+        <v/>
+      </c>
+      <c r="X8" s="19">
+        <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y8" s="19">
+        <f>$Y7+$X8</f>
         <v/>
       </c>
       <c r="Z8" s="12">
-        <f>AA7</f>
+        <f>$AA7</f>
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>Z8+S8</f>
+        <f>IF($B8="BLOCKED",$Z8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
-        <f>D8+G8+J8</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7+$AJ7),$D8+$G8+$J8)</f>
         <v/>
       </c>
       <c r="AC8" s="12">
-        <f>IF(B8="BIG_SIDE",W8,AG8+AJ8)</f>
+        <f>IF($B8="BLOCKED",$AB8,IF($B8="BIG_SIDE",$W8,$AG8+$AJ8))</f>
         <v/>
       </c>
       <c r="AD8" s="12">
-        <f>AB8*Settings!$B$10</f>
+        <f>$AB8*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE8" s="12">
-        <f>AC8*Settings!$B$10</f>
+        <f>$AC8*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF8" s="12">
-        <f>IF(B8="SMALL_SIDE",E8,C8)</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,$C8,$AF7),IF($B8="SMALL_SIDE",$E8,$C8))</f>
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF(B8="SMALL_SIDE",AM8,W8)</f>
+        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -6467,39 +7428,71 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="12">
-        <f>IF(B8="SMALL_SIDE",IF(AH8="YES",0,IFERROR(MAX(0,D8-MAX(0,AI8)/U8),D8)),0)</f>
+        <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
       <c r="AK8" s="12">
-        <f>IF(AND(AJ8&gt;0,AG8&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL8" s="12">
-        <f>IF(B8="SMALL_SIDE",G8*Settings!$B$7,IF(B8="BIG_SIDE",G8,0))</f>
+        <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
         <v/>
       </c>
       <c r="AM8" s="12">
-        <f>IF(B8="SMALL_SIDE",MAX(0,G8-AL8),0)</f>
+        <f>IF($B8="SMALL_SIDE",MAX(0,$G8-$AL8),0)</f>
         <v/>
       </c>
       <c r="AN8" s="12">
-        <f>IF(B8="BIG_SIDE",1,IF(B8="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B8="BIG_SIDE",1,IF($B8="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO8" s="12">
-        <f>IF(OR(B8="BIG_SIDE",B8="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B8="BIG_SIDE",$B8="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP8" s="12">
-        <f>IF(OR(AQ8="DUAL_TAIL",AQ8="DANGER",AQ8="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ8" s="12">
-        <f>IF(AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G8/D8,999)&gt;Settings!$B$16,IFERROR(J8/G8,999)&gt;Settings!$B$17,AE8&gt;AD8,Y8&lt;0,AG8&gt;D8*1.0001,S8&lt;-100),"DANGER",IF(OR(AND(B8="BIG_SIDE",U8&lt;=0),S8&lt;=0,X8=0,AE8&gt;AD8*0.95),"WARNING","OK")))</f>
+        <f>IF($B8="BLOCKED","STOP",IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR8" s="12">
-        <f>IF(B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS8" s="20">
+        <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
+        <v/>
+      </c>
+      <c r="AT8" s="12">
+        <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
+        <v/>
+      </c>
+      <c r="AU8" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV8" s="12">
+        <f>IF($B8="SMALL_SIDE",IF($AH8="YES",$D8,IFERROR(MIN($D8,MAX(0,$AI8/$U8)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW8" s="12">
+        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX8" s="12">
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
+        <v/>
+      </c>
+      <c r="AY8" s="12">
+        <f>IF($B8="BIG_SIDE",($G8+$J8)*$AU8,0)</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="12">
+        <f>IF($B8="BIG_SIDE",$V8*$AU8,0)</f>
         <v/>
       </c>
     </row>
@@ -6507,41 +7500,40 @@
       <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B9" s="13">
+        <f>IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C9" s="13">
-        <f>IF($AP8="YES",$AF8,$C8)</f>
+        <f>IF($B9="BLOCKED",$AF8,IF($AP8="YES",$AF8,$C8))</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF($AP8="YES",MAX(0,$AG8),$D8)</f>
+        <f>IF($B9="BLOCKED",0,IF($AP8="YES",MAX(0,$AG8),$D8))</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>IF(C9="SELL","BUY","SELL")</f>
+        <f>IF($B9="BLOCKED","",IF($C9="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>MAX(0,D9*Settings!$B$3)</f>
+        <f>IF($B9="BLOCKED",0,MAX(0,$D9*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>IFERROR(MAX(0,ROUND(F9/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($F9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>C9</f>
+        <f>IF($B9="BLOCKED","",$C9)</f>
         <v/>
       </c>
       <c r="I9" s="12">
-        <f>MAX(0,G9*Settings!$B$4)</f>
+        <f>IF($B9="BLOCKED",0,MAX(0,$G9*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J9" s="12">
-        <f>IFERROR(MAX(0,ROUND(I9/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K9" s="13" t="n">
@@ -6554,83 +7546,83 @@
         <v>100</v>
       </c>
       <c r="N9" s="14">
-        <f>IF(B9="BIG_SIDE",G9*MAX(0,K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O9" s="14">
-        <f>IF(B9="SMALL_SIDE",J9*ABS(L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P9" s="15">
-        <f>IF(B9="BIG_SIDE",J9*ABS(L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q9" s="15">
-        <f>IF(B9="SMALL_SIDE",AL9*ABS(K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R9" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT9*$AU9</f>
         <v/>
       </c>
       <c r="S9" s="14">
-        <f>IF(B9="BIG_SIDE",N9-P9-R9,O9-Q9-R9)</f>
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$R9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
         <v/>
       </c>
       <c r="T9" s="12">
-        <f>IF(AND(B9="BIG_SIDE",S9&gt;0),S9*Settings!$B$5,0)</f>
+        <f>IF(AND($B9="BIG_SIDE",$AX9&gt;0),$AX9*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U9" s="12">
-        <f>MAX(0,M9*Settings!$B$9)</f>
+        <f>MAX(0,$M9*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>IF(B9="BIG_SIDE",IFERROR(MIN(D9,MAX(0,T9/U9)),0),0)</f>
+        <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
         <v/>
       </c>
       <c r="W9" s="12">
-        <f>IF(B9="BIG_SIDE",MAX(0,D9-V9),AJ9)</f>
-        <v/>
-      </c>
-      <c r="X9" s="16">
-        <f>IF(B9="BIG_SIDE",IF(S9&gt;0,S9*Settings!$B$6,0),IF(S9&gt;0,S9*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y9" s="16">
-        <f>Y8+X9</f>
+        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
+        <v/>
+      </c>
+      <c r="X9" s="19">
+        <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y9" s="19">
+        <f>$Y8+$X9</f>
         <v/>
       </c>
       <c r="Z9" s="12">
-        <f>AA8</f>
+        <f>$AA8</f>
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>Z9+S9</f>
+        <f>IF($B9="BLOCKED",$Z9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>D9+G9+J9</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8+$AJ8),$D9+$G9+$J9)</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>IF(B9="BIG_SIDE",W9,AG9+AJ9)</f>
+        <f>IF($B9="BLOCKED",$AB9,IF($B9="BIG_SIDE",$W9,$AG9+$AJ9))</f>
         <v/>
       </c>
       <c r="AD9" s="12">
-        <f>AB9*Settings!$B$10</f>
+        <f>$AB9*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE9" s="12">
-        <f>AC9*Settings!$B$10</f>
+        <f>$AC9*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>IF(B9="SMALL_SIDE",E9,C9)</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,$C9,$AF8),IF($B9="SMALL_SIDE",$E9,$C9))</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF(B9="SMALL_SIDE",AM9,W9)</f>
+        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -6642,39 +7634,71 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="12">
-        <f>IF(B9="SMALL_SIDE",IF(AH9="YES",0,IFERROR(MAX(0,D9-MAX(0,AI9)/U9),D9)),0)</f>
+        <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
       <c r="AK9" s="12">
-        <f>IF(AND(AJ9&gt;0,AG9&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL9" s="12">
-        <f>IF(B9="SMALL_SIDE",G9*Settings!$B$7,IF(B9="BIG_SIDE",G9,0))</f>
+        <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
         <v/>
       </c>
       <c r="AM9" s="12">
-        <f>IF(B9="SMALL_SIDE",MAX(0,G9-AL9),0)</f>
+        <f>IF($B9="SMALL_SIDE",MAX(0,$G9-$AL9),0)</f>
         <v/>
       </c>
       <c r="AN9" s="12">
-        <f>IF(B9="BIG_SIDE",1,IF(B9="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B9="BIG_SIDE",1,IF($B9="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO9" s="12">
-        <f>IF(OR(B9="BIG_SIDE",B9="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B9="BIG_SIDE",$B9="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP9" s="12">
-        <f>IF(OR(AQ9="DUAL_TAIL",AQ9="DANGER",AQ9="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ9" s="12">
-        <f>IF(AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G9/D9,999)&gt;Settings!$B$16,IFERROR(J9/G9,999)&gt;Settings!$B$17,AE9&gt;AD9,Y9&lt;0,AG9&gt;D9*1.0001,S9&lt;-100),"DANGER",IF(OR(AND(B9="BIG_SIDE",U9&lt;=0),S9&lt;=0,X9=0,AE9&gt;AD9*0.95),"WARNING","OK")))</f>
+        <f>IF($B9="BLOCKED","STOP",IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR9" s="12">
-        <f>IF(B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS9" s="20">
+        <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
+        <v/>
+      </c>
+      <c r="AT9" s="12">
+        <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
+        <v/>
+      </c>
+      <c r="AU9" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV9" s="12">
+        <f>IF($B9="SMALL_SIDE",IF($AH9="YES",$D9,IFERROR(MIN($D9,MAX(0,$AI9/$U9)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW9" s="12">
+        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX9" s="12">
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
+        <v/>
+      </c>
+      <c r="AY9" s="12">
+        <f>IF($B9="BIG_SIDE",($G9+$J9)*$AU9,0)</f>
+        <v/>
+      </c>
+      <c r="AZ9" s="12">
+        <f>IF($B9="BIG_SIDE",$V9*$AU9,0)</f>
         <v/>
       </c>
     </row>
@@ -6682,41 +7706,40 @@
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B10" s="13">
+        <f>IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C10" s="13">
-        <f>IF($AP9="YES",$AF9,$C9)</f>
+        <f>IF($B10="BLOCKED",$AF9,IF($AP9="YES",$AF9,$C9))</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF($AP9="YES",MAX(0,$AG9),$D9)</f>
+        <f>IF($B10="BLOCKED",0,IF($AP9="YES",MAX(0,$AG9),$D9))</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>IF(C10="SELL","BUY","SELL")</f>
+        <f>IF($B10="BLOCKED","",IF($C10="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>MAX(0,D10*Settings!$B$3)</f>
+        <f>IF($B10="BLOCKED",0,MAX(0,$D10*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G10" s="12">
-        <f>IFERROR(MAX(0,ROUND(F10/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($F10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H10" s="12">
-        <f>C10</f>
+        <f>IF($B10="BLOCKED","",$C10)</f>
         <v/>
       </c>
       <c r="I10" s="12">
-        <f>MAX(0,G10*Settings!$B$4)</f>
+        <f>IF($B10="BLOCKED",0,MAX(0,$G10*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J10" s="12">
-        <f>IFERROR(MAX(0,ROUND(I10/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K10" s="13" t="n">
@@ -6729,83 +7752,83 @@
         <v>100</v>
       </c>
       <c r="N10" s="14">
-        <f>IF(B10="BIG_SIDE",G10*MAX(0,K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O10" s="14">
-        <f>IF(B10="SMALL_SIDE",J10*ABS(L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P10" s="15">
-        <f>IF(B10="BIG_SIDE",J10*ABS(L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q10" s="15">
-        <f>IF(B10="SMALL_SIDE",AL10*ABS(K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R10" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT10*$AU10</f>
         <v/>
       </c>
       <c r="S10" s="14">
-        <f>IF(B10="BIG_SIDE",N10-P10-R10,O10-Q10-R10)</f>
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$R10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
         <v/>
       </c>
       <c r="T10" s="12">
-        <f>IF(AND(B10="BIG_SIDE",S10&gt;0),S10*Settings!$B$5,0)</f>
+        <f>IF(AND($B10="BIG_SIDE",$AX10&gt;0),$AX10*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U10" s="12">
-        <f>MAX(0,M10*Settings!$B$9)</f>
+        <f>MAX(0,$M10*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V10" s="12">
-        <f>IF(B10="BIG_SIDE",IFERROR(MIN(D10,MAX(0,T10/U10)),0),0)</f>
+        <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
         <v/>
       </c>
       <c r="W10" s="12">
-        <f>IF(B10="BIG_SIDE",MAX(0,D10-V10),AJ10)</f>
-        <v/>
-      </c>
-      <c r="X10" s="16">
-        <f>IF(B10="BIG_SIDE",IF(S10&gt;0,S10*Settings!$B$6,0),IF(S10&gt;0,S10*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y10" s="16">
-        <f>Y9+X10</f>
+        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
+        <v/>
+      </c>
+      <c r="X10" s="19">
+        <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y10" s="19">
+        <f>$Y9+$X10</f>
         <v/>
       </c>
       <c r="Z10" s="12">
-        <f>AA9</f>
+        <f>$AA9</f>
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>Z10+S10</f>
+        <f>IF($B10="BLOCKED",$Z10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
-        <f>D10+G10+J10</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9+$AJ9),$D10+$G10+$J10)</f>
         <v/>
       </c>
       <c r="AC10" s="12">
-        <f>IF(B10="BIG_SIDE",W10,AG10+AJ10)</f>
+        <f>IF($B10="BLOCKED",$AB10,IF($B10="BIG_SIDE",$W10,$AG10+$AJ10))</f>
         <v/>
       </c>
       <c r="AD10" s="12">
-        <f>AB10*Settings!$B$10</f>
+        <f>$AB10*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE10" s="12">
-        <f>AC10*Settings!$B$10</f>
+        <f>$AC10*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF10" s="12">
-        <f>IF(B10="SMALL_SIDE",E10,C10)</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,$C10,$AF9),IF($B10="SMALL_SIDE",$E10,$C10))</f>
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF(B10="SMALL_SIDE",AM10,W10)</f>
+        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -6817,39 +7840,71 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="12">
-        <f>IF(B10="SMALL_SIDE",IF(AH10="YES",0,IFERROR(MAX(0,D10-MAX(0,AI10)/U10),D10)),0)</f>
+        <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
       <c r="AK10" s="12">
-        <f>IF(AND(AJ10&gt;0,AG10&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL10" s="12">
-        <f>IF(B10="SMALL_SIDE",G10*Settings!$B$7,IF(B10="BIG_SIDE",G10,0))</f>
+        <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
         <v/>
       </c>
       <c r="AM10" s="12">
-        <f>IF(B10="SMALL_SIDE",MAX(0,G10-AL10),0)</f>
+        <f>IF($B10="SMALL_SIDE",MAX(0,$G10-$AL10),0)</f>
         <v/>
       </c>
       <c r="AN10" s="12">
-        <f>IF(B10="BIG_SIDE",1,IF(B10="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B10="BIG_SIDE",1,IF($B10="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO10" s="12">
-        <f>IF(OR(B10="BIG_SIDE",B10="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B10="BIG_SIDE",$B10="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP10" s="12">
-        <f>IF(OR(AQ10="DUAL_TAIL",AQ10="DANGER",AQ10="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ10" s="12">
-        <f>IF(AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G10/D10,999)&gt;Settings!$B$16,IFERROR(J10/G10,999)&gt;Settings!$B$17,AE10&gt;AD10,Y10&lt;0,AG10&gt;D10*1.0001,S10&lt;-100),"DANGER",IF(OR(AND(B10="BIG_SIDE",U10&lt;=0),S10&lt;=0,X10=0,AE10&gt;AD10*0.95),"WARNING","OK")))</f>
+        <f>IF($B10="BLOCKED","STOP",IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR10" s="12">
-        <f>IF(B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS10" s="20">
+        <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
+        <v/>
+      </c>
+      <c r="AT10" s="12">
+        <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
+        <v/>
+      </c>
+      <c r="AU10" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV10" s="12">
+        <f>IF($B10="SMALL_SIDE",IF($AH10="YES",$D10,IFERROR(MIN($D10,MAX(0,$AI10/$U10)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW10" s="12">
+        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX10" s="12">
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="12">
+        <f>IF($B10="BIG_SIDE",($G10+$J10)*$AU10,0)</f>
+        <v/>
+      </c>
+      <c r="AZ10" s="12">
+        <f>IF($B10="BIG_SIDE",$V10*$AU10,0)</f>
         <v/>
       </c>
     </row>
@@ -6857,41 +7912,40 @@
       <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
+      <c r="B11" s="13">
+        <f>IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <v/>
       </c>
       <c r="C11" s="13">
-        <f>IF($AP10="YES",$AF10,$C10)</f>
+        <f>IF($B11="BLOCKED",$AF10,IF($AP10="YES",$AF10,$C10))</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF($AP10="YES",MAX(0,$AG10),$D10)</f>
+        <f>IF($B11="BLOCKED",0,IF($AP10="YES",MAX(0,$AG10),$D10))</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>IF(C11="SELL","BUY","SELL")</f>
+        <f>IF($B11="BLOCKED","",IF($C11="SELL","BUY","SELL"))</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>MAX(0,D11*Settings!$B$3)</f>
+        <f>IF($B11="BLOCKED",0,MAX(0,$D11*Settings!$B$3))</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>IFERROR(MAX(0,ROUND(F11/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($F11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="H11" s="12">
-        <f>C11</f>
+        <f>IF($B11="BLOCKED","",$C11)</f>
         <v/>
       </c>
       <c r="I11" s="12">
-        <f>MAX(0,G11*Settings!$B$4)</f>
+        <f>IF($B11="BLOCKED",0,MAX(0,$G11*Settings!$B$4))</f>
         <v/>
       </c>
       <c r="J11" s="12">
-        <f>IFERROR(MAX(0,ROUND(I11/Settings!$B$11,0)*Settings!$B$11),0)</f>
+        <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
       <c r="K11" s="13" t="n">
@@ -6904,83 +7958,83 @@
         <v>100</v>
       </c>
       <c r="N11" s="14">
-        <f>IF(B11="BIG_SIDE",G11*MAX(0,K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O11" s="14">
-        <f>IF(B11="SMALL_SIDE",J11*ABS(L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P11" s="15">
-        <f>IF(B11="BIG_SIDE",J11*ABS(L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q11" s="15">
-        <f>IF(B11="SMALL_SIDE",AL11*ABS(K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R11" s="15">
-        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <f>$AT11*$AU11</f>
         <v/>
       </c>
       <c r="S11" s="14">
-        <f>IF(B11="BIG_SIDE",N11-P11-R11,O11-Q11-R11)</f>
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$R11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
         <v/>
       </c>
       <c r="T11" s="12">
-        <f>IF(AND(B11="BIG_SIDE",S11&gt;0),S11*Settings!$B$5,0)</f>
+        <f>IF(AND($B11="BIG_SIDE",$AX11&gt;0),$AX11*Settings!$B$5,0)</f>
         <v/>
       </c>
       <c r="U11" s="12">
-        <f>MAX(0,M11*Settings!$B$9)</f>
+        <f>MAX(0,$M11*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V11" s="12">
-        <f>IF(B11="BIG_SIDE",IFERROR(MIN(D11,MAX(0,T11/U11)),0),0)</f>
+        <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
         <v/>
       </c>
       <c r="W11" s="12">
-        <f>IF(B11="BIG_SIDE",MAX(0,D11-V11),AJ11)</f>
-        <v/>
-      </c>
-      <c r="X11" s="16">
-        <f>IF(B11="BIG_SIDE",IF(S11&gt;0,S11*Settings!$B$6,0),IF(S11&gt;0,S11*0.5,0))</f>
-        <v/>
-      </c>
-      <c r="Y11" s="16">
-        <f>Y10+X11</f>
+        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="19">
+        <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
+        <v/>
+      </c>
+      <c r="Y11" s="19">
+        <f>$Y10+$X11</f>
         <v/>
       </c>
       <c r="Z11" s="12">
-        <f>AA10</f>
+        <f>$AA10</f>
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>Z11+S11</f>
+        <f>IF($B11="BLOCKED",$Z11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
-        <f>D11+G11+J11</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10+$AJ10),$D11+$G11+$J11)</f>
         <v/>
       </c>
       <c r="AC11" s="12">
-        <f>IF(B11="BIG_SIDE",W11,AG11+AJ11)</f>
+        <f>IF($B11="BLOCKED",$AB11,IF($B11="BIG_SIDE",$W11,$AG11+$AJ11))</f>
         <v/>
       </c>
       <c r="AD11" s="12">
-        <f>AB11*Settings!$B$10</f>
+        <f>$AB11*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AE11" s="12">
-        <f>AC11*Settings!$B$10</f>
+        <f>$AC11*Settings!$B$10</f>
         <v/>
       </c>
       <c r="AF11" s="12">
-        <f>IF(B11="SMALL_SIDE",E11,C11)</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,$C11,$AF10),IF($B11="SMALL_SIDE",$E11,$C11))</f>
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF(B11="SMALL_SIDE",AM11,W11)</f>
+        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -6992,44 +8046,76 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="12">
-        <f>IF(B11="SMALL_SIDE",IF(AH11="YES",0,IFERROR(MAX(0,D11-MAX(0,AI11)/U11),D11)),0)</f>
+        <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
       <c r="AK11" s="12">
-        <f>IF(AND(AJ11&gt;0,AG11&gt;0),TRUE,FALSE)</f>
+        <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
         <v/>
       </c>
       <c r="AL11" s="12">
-        <f>IF(B11="SMALL_SIDE",G11*Settings!$B$7,IF(B11="BIG_SIDE",G11,0))</f>
+        <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
         <v/>
       </c>
       <c r="AM11" s="12">
-        <f>IF(B11="SMALL_SIDE",MAX(0,G11-AL11),0)</f>
+        <f>IF($B11="SMALL_SIDE",MAX(0,$G11-$AL11),0)</f>
         <v/>
       </c>
       <c r="AN11" s="12">
-        <f>IF(B11="BIG_SIDE",1,IF(B11="SMALL_SIDE",Settings!$B$7,0))</f>
+        <f>IF($B11="BIG_SIDE",1,IF($B11="SMALL_SIDE",Settings!$B$7,0))</f>
         <v/>
       </c>
       <c r="AO11" s="12">
-        <f>IF(OR(B11="BIG_SIDE",B11="SMALL_SIDE"),1,0)</f>
+        <f>IF(OR($B11="BIG_SIDE",$B11="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
       <c r="AP11" s="12">
-        <f>IF(OR(AQ11="DUAL_TAIL",AQ11="DANGER",AQ11="STOP"),"NO","YES")</f>
+        <f>IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP"),"NO","YES")</f>
         <v/>
       </c>
       <c r="AQ11" s="12">
-        <f>IF(AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR(G11/D11,999)&gt;Settings!$B$16,IFERROR(J11/G11,999)&gt;Settings!$B$17,AE11&gt;AD11,Y11&lt;0,AG11&gt;D11*1.0001,S11&lt;-100),"DANGER",IF(OR(AND(B11="BIG_SIDE",U11&lt;=0),S11&lt;=0,X11=0,AE11&gt;AD11*0.95),"WARNING","OK")))</f>
+        <f>IF($B11="BLOCKED","STOP",IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR11" s="12">
-        <f>IF(B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; хвост закрывается в денежном режиме",IF(AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост"))</f>
+        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <v/>
+      </c>
+      <c r="AS11" s="20">
+        <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
+        <v/>
+      </c>
+      <c r="AT11" s="12">
+        <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
+        <v/>
+      </c>
+      <c r="AU11" s="12">
+        <f>Settings!$B$13+Settings!$B$14+Settings!$B$15</f>
+        <v/>
+      </c>
+      <c r="AV11" s="12">
+        <f>IF($B11="SMALL_SIDE",IF($AH11="YES",$D11,IFERROR(MIN($D11,MAX(0,$AI11/$U11)),0)),0)</f>
+        <v/>
+      </c>
+      <c r="AW11" s="12">
+        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <v/>
+      </c>
+      <c r="AX11" s="12">
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="12">
+        <f>IF($B11="BIG_SIDE",($G11+$J11)*$AU11,0)</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="12">
+        <f>IF($B11="BIG_SIDE",$V11*$AU11,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR11"/>
+  <autoFilter ref="A1:AZ11"/>
   <conditionalFormatting sqref="AQ2:AQ11">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AQ2="WARNING"</formula>
@@ -7065,12 +8151,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7098,11 +8184,11 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>SUM ProfitBig + ProfitSmall</t>
+          <t>SUM ProfitBig + ProfitSmall + positive OldFarClosePL</t>
         </is>
       </c>
       <c r="C2" s="3">
-        <f>SUM(Calculator!N2:O11)</f>
+        <f>SUM(Calculator!N2:O11)+SUMIF(Calculator!AI2:AI11,"&gt;0",Calculator!AI2:AI11)</f>
         <v/>
       </c>
     </row>
@@ -7114,114 +8200,114 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SUM LossSmall + LossClosedBig + Costs</t>
+          <t>LossSmall + LossClosedBig + Costs + RealizedFarLoss + negative OldFarClosePL</t>
         </is>
       </c>
       <c r="C3" s="3">
-        <f>SUM(Calculator!P2:R11)</f>
+        <f>SUM(Calculator!P2:Q11)+SUM(Calculator!R2:R11)+SUM(Calculator!AS2:AS11)-SUMIF(Calculator!AI2:AI11,"&lt;0",Calculator!AI2:AI11)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Final Balance</t>
+          <t>Total Realized Far Loss</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>последний BalanceAfter</t>
+          <t>SUM RealizedFarLoss</t>
         </is>
       </c>
       <c r="C4" s="3">
-        <f>LOOKUP(2,1/(Calculator!AA2:AA11&lt;&gt;""),Calculator!AA2:AA11)</f>
+        <f>SUM(Calculator!AS2:AS11)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Final Reserve</t>
+          <t>Final Balance</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>последний TotalReserve</t>
+          <t>last BalanceAfter</t>
         </is>
       </c>
       <c r="C5" s="3">
-        <f>LOOKUP(2,1/(Calculator!Y2:Y11&lt;&gt;""),Calculator!Y2:Y11)</f>
+        <f>LOOKUP(2,1/(Calculator!AA2:AA11&lt;&gt;""),Calculator!AA2:AA11)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Max Margin</t>
+          <t>Final Reserve</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MAX MarginBefore</t>
+          <t>last TotalReserve</t>
         </is>
       </c>
       <c r="C6" s="3">
-        <f>MAX(Calculator!AD2:AD11)</f>
+        <f>LOOKUP(2,1/(Calculator!Y2:Y11&lt;&gt;""),Calculator!Y2:Y11)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Max Open Lots</t>
+          <t>Max Margin</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MAX OpenLotsBefore</t>
+          <t>MAX MarginBefore</t>
         </is>
       </c>
       <c r="C7" s="3">
-        <f>MAX(Calculator!AB2:AB11)</f>
+        <f>MAX(Calculator!AD2:AD11)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Final Far Lot</t>
+          <t>Max Open Lots</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>последний NewFarStartLot</t>
+          <t>MAX OpenLotsBefore</t>
         </is>
       </c>
       <c r="C8" s="3">
-        <f>LOOKUP(2,1/(Calculator!AG2:AG11&lt;&gt;""),Calculator!AG2:AG11)</f>
+        <f>MAX(Calculator!AB2:AB11)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Number of BIG_SIDE</t>
+          <t>Final Far Lot</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>COUNTIF Scenario</t>
+          <t>last NewFarStartLot</t>
         </is>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIF(Calculator!B2:B11,"BIG_SIDE")</f>
+        <f>LOOKUP(2,1/(Calculator!AG2:AG11&lt;&gt;""),Calculator!AG2:AG11)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Number of SMALL_SIDE</t>
+          <t>Number of BIG_SIDE</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7230,54 +8316,86 @@
         </is>
       </c>
       <c r="C10" s="3">
-        <f>COUNTIF(Calculator!B2:B11,"SMALL_SIDE")</f>
+        <f>COUNTIF(Calculator!B2:B11,"BIG_SIDE")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Dual Tail Count</t>
+          <t>Number of SMALL_SIDE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>COUNTIF Status</t>
+          <t>COUNTIF Scenario</t>
         </is>
       </c>
       <c r="C11" s="3">
-        <f>COUNTIF(Calculator!AQ2:AQ11,"DUAL_TAIL")</f>
+        <f>COUNTIF(Calculator!B2:B11,"SMALL_SIDE")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Danger Count</t>
+          <t>Dual Tail Count</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>COUNTIF Status</t>
+          <t>COUNTIF Status DUAL_TAIL</t>
         </is>
       </c>
       <c r="C12" s="3">
-        <f>COUNTIF(Calculator!AQ2:AQ11,"DANGER")</f>
+        <f>COUNTIF(Calculator!AQ2:AQ11,"DUAL_TAIL")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Danger Count</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>COUNTIF Status DANGER</t>
+        </is>
+      </c>
+      <c r="C13" s="3">
+        <f>COUNTIF(Calculator!AQ2:AQ11,"DANGER")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Stop Count</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>COUNTIF Status STOP</t>
+        </is>
+      </c>
+      <c r="C14" s="3">
+        <f>COUNTIF(Calculator!AQ2:AQ11,"STOP")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Final Status</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>последний Status</t>
-        </is>
-      </c>
-      <c r="C13" s="3">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>last Status</t>
+        </is>
+      </c>
+      <c r="C15" s="3">
         <f>LOOKUP(2,1/(Calculator!AQ2:AQ11&lt;&gt;""),Calculator!AQ2:AQ11)</f>
         <v/>
       </c>
@@ -7293,56 +8411,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="64" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Formula Checked</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -8566,8 +9684,427 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>T30</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>RealizedFarLoss formula</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Calculator BIG_SIDE rows</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>RealizedFarLoss = CloseFarLot × LossPerLotToClose</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Calculator!AS = V*U</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>AS=V*U</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>v3: закрытый убыток хвоста выделен отдельной колонкой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>T31</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>BIG_SIDE BalanceAfter includes far loss</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>BIG_SIDE row</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>BalanceAfter = BalanceBefore + NetProfitBeforeFar - RealizedFarLoss - CostsFarClose</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Calculator!AA formula</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>AA=Z+AX-AS-AZ</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Баланс больше не завышается после закрытия хвоста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>ReserveAdd after far loss</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>BIG_SIDE row</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>ReserveAdd = NetProfitBeforeFar - RealizedFarLoss</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Calculator!X formula</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>X=AX-AS when AX&gt;0</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>При стандартном 20/80 совпадает с 80% до расходов закрытия хвоста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>T33</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Total Closed Loss includes RealizedFarLoss</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Loss includes AS</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis Total Closed Loss</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>SUM(P:Q)+SUM(R)+SUM(AS)-negative OldFarClosePL</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis учитывает фиксированный убыток хвоста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>T34</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Total Realized Far Loss metric</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>SUM RealizedFarLoss</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis row Total Realized Far Loss</t>
+        </is>
+      </c>
+      <c r="F35" s="3">
+        <f>SUM(Calculator!AS2:AS11)</f>
+        <v/>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Добавлен отдельный показатель.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>T35</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL blocks next level</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Previous row DUAL_TAIL/NO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Next Scenario=BLOCKED or Status=STOP</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Calculator rows 3:11</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>B checks previous AP/AQ; AQ STOP if BLOCKED</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Следующий уровень реально блокируется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>T36</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Blocked next Big/Small zero</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Scenario BLOCKED</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>BigLot=0 and SmallLot=0</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Calculator F:G/I:J</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>IF(B="BLOCKED",0,...)</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>При блокировке новые лоты не открываются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>T37</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Costs per lot multiplied</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>PerLot cost settings</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Costs = ClosedLotsForCosts × CostPerLot</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Calculator!R/AT/AU</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>R=AT*AU</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Costs больше не фиксированные на уровень.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>T38</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>No reserve double count</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Balance formulas</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Balance uses reserve-equivalent net but not +Reserve separately</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Calculator!AA</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>BIG: Z+AX-AS-AZ; SMALL: Z+S+AI</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Резерв не прибавляется второй раз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>T39</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>OldFarClosePL affects SMALL_SIDE balance</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>SMALL_SIDE row</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>BalanceAfter includes OldFarClosePL</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Calculator!AA formula</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>AA=Z+S+AI for SMALL_SIDE</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Закрытие старого хвоста входит в баланс.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:H40"/>
   <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>$D2="FAIL"</formula>

--- a/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
+++ b/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
@@ -17,10 +17,10 @@
     <sheet name="Examples" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calculator'!$A$1:$AZ$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trend_UP'!$A$1:$AZ$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trend_DOWN'!$A$1:$AZ$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tests'!$A$1:$H$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calculator'!$A$1:$BG$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trend_UP'!$A$1:$BG$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trend_DOWN'!$A$1:$BG$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tests'!$A$1:$H$55</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:BG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -955,6 +955,13 @@
     <col width="18" customWidth="1" min="50" max="50"/>
     <col width="18" customWidth="1" min="51" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="20" customWidth="1" min="56" max="56"/>
+    <col width="20" customWidth="1" min="57" max="57"/>
+    <col width="20" customWidth="1" min="58" max="58"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1218,6 +1225,41 @@
           <t>CostsFarClose</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>ManualOldFarCloseLot</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>ManualNewFarCloseLot</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>ManualClosePL</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>ManualAllowNewLevel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -1322,15 +1364,15 @@
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>IF($B2="BLOCKED",$Z2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
+        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
         <v/>
       </c>
       <c r="AB2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1+$AJ1),$D2+$G2+$J2)</f>
+        <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
         <v/>
       </c>
       <c r="AC2" s="12">
-        <f>IF($B2="BLOCKED",$AB2,IF($B2="BIG_SIDE",$W2,$AG2+$AJ2))</f>
+        <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
         <v/>
       </c>
       <c r="AD2" s="12">
@@ -1342,11 +1384,11 @@
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,$C2,$AF1),IF($B2="SMALL_SIDE",$E2,$C2))</f>
+        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
+        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -1382,15 +1424,15 @@
         <v/>
       </c>
       <c r="AP2" s="12">
-        <f>IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ2" s="12">
-        <f>IF($B2="BLOCKED","STOP",IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
+        <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR2" s="12">
-        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS2" s="20">
@@ -1410,7 +1452,7 @@
         <v/>
       </c>
       <c r="AW2" s="12">
-        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX2" s="12">
@@ -1424,6 +1466,32 @@
       <c r="AZ2" s="12">
         <f>IF($B2="BIG_SIDE",$V2*$AU2,0)</f>
         <v/>
+      </c>
+      <c r="BA2" s="12">
+        <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
+        <v/>
+      </c>
+      <c r="BB2" s="12">
+        <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
+        <v/>
+      </c>
+      <c r="BC2" s="12">
+        <f>$BA2+$BB2</f>
+        <v/>
+      </c>
+      <c r="BD2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1431,15 +1499,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="13">
-        <f>IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"BIG_SIDE",IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="MANUAL_READY",$AQ2="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>IF($B3="BLOCKED",$AF2,IF($AP2="YES",$AF2,$C2))</f>
+        <f>IF($B3="BLOCKED",$AF2,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),$AF2,IF($AP2="YES",$AF2,$C2)))</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>IF($B3="BLOCKED",0,IF($AP2="YES",MAX(0,$AG2),$D2))</f>
+        <f>IF($B3="BLOCKED",0,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),MAX($BA2,$BB2),IF($AP2="YES",MAX(0,$AG2),$D2)))</f>
         <v/>
       </c>
       <c r="E3" s="12">
@@ -1528,15 +1596,15 @@
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>IF($B3="BLOCKED",$Z3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
+        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2+$AJ2),$D3+$G3+$J3)</f>
+        <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
         <v/>
       </c>
       <c r="AC3" s="12">
-        <f>IF($B3="BLOCKED",$AB3,IF($B3="BIG_SIDE",$W3,$AG3+$AJ3))</f>
+        <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
         <v/>
       </c>
       <c r="AD3" s="12">
@@ -1548,11 +1616,11 @@
         <v/>
       </c>
       <c r="AF3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,$C3,$AF2),IF($B3="SMALL_SIDE",$E3,$C3))</f>
+        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
+        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
         <v/>
       </c>
       <c r="AH3" s="13" t="inlineStr">
@@ -1588,15 +1656,15 @@
         <v/>
       </c>
       <c r="AP3" s="12">
-        <f>IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"YES",IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="STOP_CLEARED",$AQ3="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ3" s="12">
-        <f>IF($B3="BLOCKED","STOP",IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
+        <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR3" s="12">
-        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS3" s="20">
@@ -1616,7 +1684,7 @@
         <v/>
       </c>
       <c r="AW3" s="12">
-        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX3" s="12">
@@ -1630,6 +1698,32 @@
       <c r="AZ3" s="12">
         <f>IF($B3="BIG_SIDE",$V3*$AU3,0)</f>
         <v/>
+      </c>
+      <c r="BA3" s="12">
+        <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
+        <v/>
+      </c>
+      <c r="BB3" s="12">
+        <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
+        <v/>
+      </c>
+      <c r="BC3" s="12">
+        <f>$BA3+$BB3</f>
+        <v/>
+      </c>
+      <c r="BD3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1637,15 +1731,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="13">
-        <f>IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"SMALL_SIDE",IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="MANUAL_READY",$AQ3="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
         <v/>
       </c>
       <c r="C4" s="13">
-        <f>IF($B4="BLOCKED",$AF3,IF($AP3="YES",$AF3,$C3))</f>
+        <f>IF($B4="BLOCKED",$AF3,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),$AF3,IF($AP3="YES",$AF3,$C3)))</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF($B4="BLOCKED",0,IF($AP3="YES",MAX(0,$AG3),$D3))</f>
+        <f>IF($B4="BLOCKED",0,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),MAX($BA3,$BB3),IF($AP3="YES",MAX(0,$AG3),$D3)))</f>
         <v/>
       </c>
       <c r="E4" s="12">
@@ -1734,15 +1828,15 @@
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>IF($B4="BLOCKED",$Z4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
+        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3+$AJ3),$D4+$G4+$J4)</f>
+        <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
         <v/>
       </c>
       <c r="AC4" s="12">
-        <f>IF($B4="BLOCKED",$AB4,IF($B4="BIG_SIDE",$W4,$AG4+$AJ4))</f>
+        <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
         <v/>
       </c>
       <c r="AD4" s="12">
@@ -1754,11 +1848,11 @@
         <v/>
       </c>
       <c r="AF4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,$C4,$AF3),IF($B4="SMALL_SIDE",$E4,$C4))</f>
+        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
+        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -1794,15 +1888,15 @@
         <v/>
       </c>
       <c r="AP4" s="12">
-        <f>IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"YES",IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="STOP_CLEARED",$AQ4="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ4" s="12">
-        <f>IF($B4="BLOCKED","STOP",IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
+        <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR4" s="12">
-        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS4" s="20">
@@ -1822,7 +1916,7 @@
         <v/>
       </c>
       <c r="AW4" s="12">
-        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX4" s="12">
@@ -1836,6 +1930,32 @@
       <c r="AZ4" s="12">
         <f>IF($B4="BIG_SIDE",$V4*$AU4,0)</f>
         <v/>
+      </c>
+      <c r="BA4" s="12">
+        <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
+        <v/>
+      </c>
+      <c r="BB4" s="12">
+        <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
+        <v/>
+      </c>
+      <c r="BC4" s="12">
+        <f>$BA4+$BB4</f>
+        <v/>
+      </c>
+      <c r="BD4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1843,15 +1963,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="13">
-        <f>IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"BIG_SIDE",IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="MANUAL_READY",$AQ4="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>IF($B5="BLOCKED",$AF4,IF($AP4="YES",$AF4,$C4))</f>
+        <f>IF($B5="BLOCKED",$AF4,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),$AF4,IF($AP4="YES",$AF4,$C4)))</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF($B5="BLOCKED",0,IF($AP4="YES",MAX(0,$AG4),$D4))</f>
+        <f>IF($B5="BLOCKED",0,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),MAX($BA4,$BB4),IF($AP4="YES",MAX(0,$AG4),$D4)))</f>
         <v/>
       </c>
       <c r="E5" s="12">
@@ -1940,15 +2060,15 @@
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>IF($B5="BLOCKED",$Z5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
+        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4+$AJ4),$D5+$G5+$J5)</f>
+        <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
         <v/>
       </c>
       <c r="AC5" s="12">
-        <f>IF($B5="BLOCKED",$AB5,IF($B5="BIG_SIDE",$W5,$AG5+$AJ5))</f>
+        <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
         <v/>
       </c>
       <c r="AD5" s="12">
@@ -1960,11 +2080,11 @@
         <v/>
       </c>
       <c r="AF5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,$C5,$AF4),IF($B5="SMALL_SIDE",$E5,$C5))</f>
+        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
+        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v/>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -2000,15 +2120,15 @@
         <v/>
       </c>
       <c r="AP5" s="12">
-        <f>IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"YES",IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="STOP_CLEARED",$AQ5="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ5" s="12">
-        <f>IF($B5="BLOCKED","STOP",IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
+        <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR5" s="12">
-        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS5" s="20">
@@ -2028,7 +2148,7 @@
         <v/>
       </c>
       <c r="AW5" s="12">
-        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX5" s="12">
@@ -2042,6 +2162,32 @@
       <c r="AZ5" s="12">
         <f>IF($B5="BIG_SIDE",$V5*$AU5,0)</f>
         <v/>
+      </c>
+      <c r="BA5" s="12">
+        <f>IF($AK5=TRUE,MAX(0,$AJ5-$BD5),IF($B5="BLOCKED",MAX(0,$BA4-$BD5),0))</f>
+        <v/>
+      </c>
+      <c r="BB5" s="12">
+        <f>IF($AK5=TRUE,MAX(0,$AG5-$BE5),IF($B5="BLOCKED",MAX(0,$BB4-$BE5),0))</f>
+        <v/>
+      </c>
+      <c r="BC5" s="12">
+        <f>$BA5+$BB5</f>
+        <v/>
+      </c>
+      <c r="BD5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2049,15 +2195,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="13">
-        <f>IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"BIG_SIDE",IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="MANUAL_READY",$AQ5="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>IF($B6="BLOCKED",$AF5,IF($AP5="YES",$AF5,$C5))</f>
+        <f>IF($B6="BLOCKED",$AF5,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),$AF5,IF($AP5="YES",$AF5,$C5)))</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF($B6="BLOCKED",0,IF($AP5="YES",MAX(0,$AG5),$D5))</f>
+        <f>IF($B6="BLOCKED",0,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),MAX($BA5,$BB5),IF($AP5="YES",MAX(0,$AG5),$D5)))</f>
         <v/>
       </c>
       <c r="E6" s="12">
@@ -2146,15 +2292,15 @@
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>IF($B6="BLOCKED",$Z6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
+        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5+$AJ5),$D6+$G6+$J6)</f>
+        <f>IF($B6="BLOCKED",$BC6,$D6+$G6+$J6)</f>
         <v/>
       </c>
       <c r="AC6" s="12">
-        <f>IF($B6="BLOCKED",$AB6,IF($B6="BIG_SIDE",$W6,$AG6+$AJ6))</f>
+        <f>IF($B6="BLOCKED",$BC6,IF($B6="BIG_SIDE",$W6,IF($AK6=TRUE,$BC6,$AG6)))</f>
         <v/>
       </c>
       <c r="AD6" s="12">
@@ -2166,11 +2312,11 @@
         <v/>
       </c>
       <c r="AF6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,$C6,$AF5),IF($B6="SMALL_SIDE",$E6,$C6))</f>
+        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
+        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -2206,15 +2352,15 @@
         <v/>
       </c>
       <c r="AP6" s="12">
-        <f>IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"YES",IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="STOP_CLEARED",$AQ6="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ6" s="12">
-        <f>IF($B6="BLOCKED","STOP",IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
+        <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR6" s="12">
-        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS6" s="20">
@@ -2234,7 +2380,7 @@
         <v/>
       </c>
       <c r="AW6" s="12">
-        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX6" s="12">
@@ -2248,6 +2394,32 @@
       <c r="AZ6" s="12">
         <f>IF($B6="BIG_SIDE",$V6*$AU6,0)</f>
         <v/>
+      </c>
+      <c r="BA6" s="12">
+        <f>IF($AK6=TRUE,MAX(0,$AJ6-$BD6),IF($B6="BLOCKED",MAX(0,$BA5-$BD6),0))</f>
+        <v/>
+      </c>
+      <c r="BB6" s="12">
+        <f>IF($AK6=TRUE,MAX(0,$AG6-$BE6),IF($B6="BLOCKED",MAX(0,$BB5-$BE6),0))</f>
+        <v/>
+      </c>
+      <c r="BC6" s="12">
+        <f>$BA6+$BB6</f>
+        <v/>
+      </c>
+      <c r="BD6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2255,15 +2427,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="13">
-        <f>IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"SMALL_SIDE",IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="MANUAL_READY",$AQ6="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>IF($B7="BLOCKED",$AF6,IF($AP6="YES",$AF6,$C6))</f>
+        <f>IF($B7="BLOCKED",$AF6,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),$AF6,IF($AP6="YES",$AF6,$C6)))</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF($B7="BLOCKED",0,IF($AP6="YES",MAX(0,$AG6),$D6))</f>
+        <f>IF($B7="BLOCKED",0,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),MAX($BA6,$BB6),IF($AP6="YES",MAX(0,$AG6),$D6)))</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -2352,15 +2524,15 @@
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>IF($B7="BLOCKED",$Z7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
+        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6+$AJ6),$D7+$G7+$J7)</f>
+        <f>IF($B7="BLOCKED",$BC7,$D7+$G7+$J7)</f>
         <v/>
       </c>
       <c r="AC7" s="12">
-        <f>IF($B7="BLOCKED",$AB7,IF($B7="BIG_SIDE",$W7,$AG7+$AJ7))</f>
+        <f>IF($B7="BLOCKED",$BC7,IF($B7="BIG_SIDE",$W7,IF($AK7=TRUE,$BC7,$AG7)))</f>
         <v/>
       </c>
       <c r="AD7" s="12">
@@ -2372,11 +2544,11 @@
         <v/>
       </c>
       <c r="AF7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,$C7,$AF6),IF($B7="SMALL_SIDE",$E7,$C7))</f>
+        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
+        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -2412,15 +2584,15 @@
         <v/>
       </c>
       <c r="AP7" s="12">
-        <f>IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"YES",IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="STOP_CLEARED",$AQ7="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ7" s="12">
-        <f>IF($B7="BLOCKED","STOP",IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
+        <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR7" s="12">
-        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS7" s="20">
@@ -2440,7 +2612,7 @@
         <v/>
       </c>
       <c r="AW7" s="12">
-        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX7" s="12">
@@ -2454,6 +2626,32 @@
       <c r="AZ7" s="12">
         <f>IF($B7="BIG_SIDE",$V7*$AU7,0)</f>
         <v/>
+      </c>
+      <c r="BA7" s="12">
+        <f>IF($AK7=TRUE,MAX(0,$AJ7-$BD7),IF($B7="BLOCKED",MAX(0,$BA6-$BD7),0))</f>
+        <v/>
+      </c>
+      <c r="BB7" s="12">
+        <f>IF($AK7=TRUE,MAX(0,$AG7-$BE7),IF($B7="BLOCKED",MAX(0,$BB6-$BE7),0))</f>
+        <v/>
+      </c>
+      <c r="BC7" s="12">
+        <f>$BA7+$BB7</f>
+        <v/>
+      </c>
+      <c r="BD7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2461,15 +2659,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="13">
-        <f>IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"BIG_SIDE",IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="MANUAL_READY",$AQ7="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>IF($B8="BLOCKED",$AF7,IF($AP7="YES",$AF7,$C7))</f>
+        <f>IF($B8="BLOCKED",$AF7,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),$AF7,IF($AP7="YES",$AF7,$C7)))</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF($B8="BLOCKED",0,IF($AP7="YES",MAX(0,$AG7),$D7))</f>
+        <f>IF($B8="BLOCKED",0,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),MAX($BA7,$BB7),IF($AP7="YES",MAX(0,$AG7),$D7)))</f>
         <v/>
       </c>
       <c r="E8" s="12">
@@ -2558,15 +2756,15 @@
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>IF($B8="BLOCKED",$Z8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
+        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7+$AJ7),$D8+$G8+$J8)</f>
+        <f>IF($B8="BLOCKED",$BC8,$D8+$G8+$J8)</f>
         <v/>
       </c>
       <c r="AC8" s="12">
-        <f>IF($B8="BLOCKED",$AB8,IF($B8="BIG_SIDE",$W8,$AG8+$AJ8))</f>
+        <f>IF($B8="BLOCKED",$BC8,IF($B8="BIG_SIDE",$W8,IF($AK8=TRUE,$BC8,$AG8)))</f>
         <v/>
       </c>
       <c r="AD8" s="12">
@@ -2578,11 +2776,11 @@
         <v/>
       </c>
       <c r="AF8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,$C8,$AF7),IF($B8="SMALL_SIDE",$E8,$C8))</f>
+        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
+        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -2618,15 +2816,15 @@
         <v/>
       </c>
       <c r="AP8" s="12">
-        <f>IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"YES",IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="STOP_CLEARED",$AQ8="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ8" s="12">
-        <f>IF($B8="BLOCKED","STOP",IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
+        <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR8" s="12">
-        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS8" s="20">
@@ -2646,7 +2844,7 @@
         <v/>
       </c>
       <c r="AW8" s="12">
-        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX8" s="12">
@@ -2660,6 +2858,32 @@
       <c r="AZ8" s="12">
         <f>IF($B8="BIG_SIDE",$V8*$AU8,0)</f>
         <v/>
+      </c>
+      <c r="BA8" s="12">
+        <f>IF($AK8=TRUE,MAX(0,$AJ8-$BD8),IF($B8="BLOCKED",MAX(0,$BA7-$BD8),0))</f>
+        <v/>
+      </c>
+      <c r="BB8" s="12">
+        <f>IF($AK8=TRUE,MAX(0,$AG8-$BE8),IF($B8="BLOCKED",MAX(0,$BB7-$BE8),0))</f>
+        <v/>
+      </c>
+      <c r="BC8" s="12">
+        <f>$BA8+$BB8</f>
+        <v/>
+      </c>
+      <c r="BD8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2667,15 +2891,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="13">
-        <f>IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"BIG_SIDE",IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="MANUAL_READY",$AQ8="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>IF($B9="BLOCKED",$AF8,IF($AP8="YES",$AF8,$C8))</f>
+        <f>IF($B9="BLOCKED",$AF8,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),$AF8,IF($AP8="YES",$AF8,$C8)))</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF($B9="BLOCKED",0,IF($AP8="YES",MAX(0,$AG8),$D8))</f>
+        <f>IF($B9="BLOCKED",0,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),MAX($BA8,$BB8),IF($AP8="YES",MAX(0,$AG8),$D8)))</f>
         <v/>
       </c>
       <c r="E9" s="12">
@@ -2764,15 +2988,15 @@
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>IF($B9="BLOCKED",$Z9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
+        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8+$AJ8),$D9+$G9+$J9)</f>
+        <f>IF($B9="BLOCKED",$BC9,$D9+$G9+$J9)</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>IF($B9="BLOCKED",$AB9,IF($B9="BIG_SIDE",$W9,$AG9+$AJ9))</f>
+        <f>IF($B9="BLOCKED",$BC9,IF($B9="BIG_SIDE",$W9,IF($AK9=TRUE,$BC9,$AG9)))</f>
         <v/>
       </c>
       <c r="AD9" s="12">
@@ -2784,11 +3008,11 @@
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,$C9,$AF8),IF($B9="SMALL_SIDE",$E9,$C9))</f>
+        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
+        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -2824,15 +3048,15 @@
         <v/>
       </c>
       <c r="AP9" s="12">
-        <f>IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"YES",IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="STOP_CLEARED",$AQ9="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ9" s="12">
-        <f>IF($B9="BLOCKED","STOP",IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
+        <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR9" s="12">
-        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS9" s="20">
@@ -2852,7 +3076,7 @@
         <v/>
       </c>
       <c r="AW9" s="12">
-        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX9" s="12">
@@ -2866,6 +3090,32 @@
       <c r="AZ9" s="12">
         <f>IF($B9="BIG_SIDE",$V9*$AU9,0)</f>
         <v/>
+      </c>
+      <c r="BA9" s="12">
+        <f>IF($AK9=TRUE,MAX(0,$AJ9-$BD9),IF($B9="BLOCKED",MAX(0,$BA8-$BD9),0))</f>
+        <v/>
+      </c>
+      <c r="BB9" s="12">
+        <f>IF($AK9=TRUE,MAX(0,$AG9-$BE9),IF($B9="BLOCKED",MAX(0,$BB8-$BE9),0))</f>
+        <v/>
+      </c>
+      <c r="BC9" s="12">
+        <f>$BA9+$BB9</f>
+        <v/>
+      </c>
+      <c r="BD9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -2873,15 +3123,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="13">
-        <f>IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"BIG_SIDE",IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="MANUAL_READY",$AQ9="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>IF($B10="BLOCKED",$AF9,IF($AP9="YES",$AF9,$C9))</f>
+        <f>IF($B10="BLOCKED",$AF9,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),$AF9,IF($AP9="YES",$AF9,$C9)))</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF($B10="BLOCKED",0,IF($AP9="YES",MAX(0,$AG9),$D9))</f>
+        <f>IF($B10="BLOCKED",0,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),MAX($BA9,$BB9),IF($AP9="YES",MAX(0,$AG9),$D9)))</f>
         <v/>
       </c>
       <c r="E10" s="12">
@@ -2970,15 +3220,15 @@
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>IF($B10="BLOCKED",$Z10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
+        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9+$AJ9),$D10+$G10+$J10)</f>
+        <f>IF($B10="BLOCKED",$BC10,$D10+$G10+$J10)</f>
         <v/>
       </c>
       <c r="AC10" s="12">
-        <f>IF($B10="BLOCKED",$AB10,IF($B10="BIG_SIDE",$W10,$AG10+$AJ10))</f>
+        <f>IF($B10="BLOCKED",$BC10,IF($B10="BIG_SIDE",$W10,IF($AK10=TRUE,$BC10,$AG10)))</f>
         <v/>
       </c>
       <c r="AD10" s="12">
@@ -2990,11 +3240,11 @@
         <v/>
       </c>
       <c r="AF10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,$C10,$AF9),IF($B10="SMALL_SIDE",$E10,$C10))</f>
+        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
+        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -3030,15 +3280,15 @@
         <v/>
       </c>
       <c r="AP10" s="12">
-        <f>IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"YES",IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="STOP_CLEARED",$AQ10="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ10" s="12">
-        <f>IF($B10="BLOCKED","STOP",IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
+        <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR10" s="12">
-        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS10" s="20">
@@ -3058,7 +3308,7 @@
         <v/>
       </c>
       <c r="AW10" s="12">
-        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX10" s="12">
@@ -3072,6 +3322,32 @@
       <c r="AZ10" s="12">
         <f>IF($B10="BIG_SIDE",$V10*$AU10,0)</f>
         <v/>
+      </c>
+      <c r="BA10" s="12">
+        <f>IF($AK10=TRUE,MAX(0,$AJ10-$BD10),IF($B10="BLOCKED",MAX(0,$BA9-$BD10),0))</f>
+        <v/>
+      </c>
+      <c r="BB10" s="12">
+        <f>IF($AK10=TRUE,MAX(0,$AG10-$BE10),IF($B10="BLOCKED",MAX(0,$BB9-$BE10),0))</f>
+        <v/>
+      </c>
+      <c r="BC10" s="12">
+        <f>$BA10+$BB10</f>
+        <v/>
+      </c>
+      <c r="BD10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3079,15 +3355,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="13">
-        <f>IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"BIG_SIDE",IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="MANUAL_READY",$AQ10="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>IF($B11="BLOCKED",$AF10,IF($AP10="YES",$AF10,$C10))</f>
+        <f>IF($B11="BLOCKED",$AF10,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),$AF10,IF($AP10="YES",$AF10,$C10)))</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF($B11="BLOCKED",0,IF($AP10="YES",MAX(0,$AG10),$D10))</f>
+        <f>IF($B11="BLOCKED",0,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),MAX($BA10,$BB10),IF($AP10="YES",MAX(0,$AG10),$D10)))</f>
         <v/>
       </c>
       <c r="E11" s="12">
@@ -3176,15 +3452,15 @@
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>IF($B11="BLOCKED",$Z11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
+        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10+$AJ10),$D11+$G11+$J11)</f>
+        <f>IF($B11="BLOCKED",$BC11,$D11+$G11+$J11)</f>
         <v/>
       </c>
       <c r="AC11" s="12">
-        <f>IF($B11="BLOCKED",$AB11,IF($B11="BIG_SIDE",$W11,$AG11+$AJ11))</f>
+        <f>IF($B11="BLOCKED",$BC11,IF($B11="BIG_SIDE",$W11,IF($AK11=TRUE,$BC11,$AG11)))</f>
         <v/>
       </c>
       <c r="AD11" s="12">
@@ -3196,11 +3472,11 @@
         <v/>
       </c>
       <c r="AF11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,$C11,$AF10),IF($B11="SMALL_SIDE",$E11,$C11))</f>
+        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
+        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$BB11,$BA11),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -3236,15 +3512,15 @@
         <v/>
       </c>
       <c r="AP11" s="12">
-        <f>IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ11="MANUAL_READY",$BG11="YES"),"YES",IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP",$AQ11="STOP_CLEARED",$AQ11="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ11" s="12">
-        <f>IF($B11="BLOCKED","STOP",IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
+        <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR11" s="12">
-        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS11" s="20">
@@ -3264,7 +3540,7 @@
         <v/>
       </c>
       <c r="AW11" s="12">
-        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX11" s="12">
@@ -3279,9 +3555,35 @@
         <f>IF($B11="BIG_SIDE",$V11*$AU11,0)</f>
         <v/>
       </c>
+      <c r="BA11" s="12">
+        <f>IF($AK11=TRUE,MAX(0,$AJ11-$BD11),IF($B11="BLOCKED",MAX(0,$BA10-$BD11),0))</f>
+        <v/>
+      </c>
+      <c r="BB11" s="12">
+        <f>IF($AK11=TRUE,MAX(0,$AG11-$BE11),IF($B11="BLOCKED",MAX(0,$BB10-$BE11),0))</f>
+        <v/>
+      </c>
+      <c r="BC11" s="12">
+        <f>$BA11+$BB11</f>
+        <v/>
+      </c>
+      <c r="BD11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ11"/>
+  <autoFilter ref="A1:BG11"/>
   <conditionalFormatting sqref="AQ2:AQ11">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AQ2="WARNING"</formula>
@@ -3317,7 +3619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:BG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3372,6 +3674,13 @@
     <col width="18" customWidth="1" min="50" max="50"/>
     <col width="18" customWidth="1" min="51" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="20" customWidth="1" min="56" max="56"/>
+    <col width="20" customWidth="1" min="57" max="57"/>
+    <col width="20" customWidth="1" min="58" max="58"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3635,6 +3944,41 @@
           <t>CostsFarClose</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>ManualOldFarCloseLot</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>ManualNewFarCloseLot</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>ManualClosePL</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>ManualAllowNewLevel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -3739,15 +4083,15 @@
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>IF($B2="BLOCKED",$Z2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
+        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
         <v/>
       </c>
       <c r="AB2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1+$AJ1),$D2+$G2+$J2)</f>
+        <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
         <v/>
       </c>
       <c r="AC2" s="12">
-        <f>IF($B2="BLOCKED",$AB2,IF($B2="BIG_SIDE",$W2,$AG2+$AJ2))</f>
+        <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
         <v/>
       </c>
       <c r="AD2" s="12">
@@ -3759,11 +4103,11 @@
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,$C2,$AF1),IF($B2="SMALL_SIDE",$E2,$C2))</f>
+        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
+        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -3799,15 +4143,15 @@
         <v/>
       </c>
       <c r="AP2" s="12">
-        <f>IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ2" s="12">
-        <f>IF($B2="BLOCKED","STOP",IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
+        <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR2" s="12">
-        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS2" s="20">
@@ -3827,7 +4171,7 @@
         <v/>
       </c>
       <c r="AW2" s="12">
-        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX2" s="12">
@@ -3841,6 +4185,32 @@
       <c r="AZ2" s="12">
         <f>IF($B2="BIG_SIDE",$V2*$AU2,0)</f>
         <v/>
+      </c>
+      <c r="BA2" s="12">
+        <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
+        <v/>
+      </c>
+      <c r="BB2" s="12">
+        <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
+        <v/>
+      </c>
+      <c r="BC2" s="12">
+        <f>$BA2+$BB2</f>
+        <v/>
+      </c>
+      <c r="BD2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3848,15 +4218,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="13">
-        <f>IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"BIG_SIDE",IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="MANUAL_READY",$AQ2="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>IF($B3="BLOCKED",$AF2,IF($AP2="YES",$AF2,$C2))</f>
+        <f>IF($B3="BLOCKED",$AF2,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),$AF2,IF($AP2="YES",$AF2,$C2)))</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>IF($B3="BLOCKED",0,IF($AP2="YES",MAX(0,$AG2),$D2))</f>
+        <f>IF($B3="BLOCKED",0,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),MAX($BA2,$BB2),IF($AP2="YES",MAX(0,$AG2),$D2)))</f>
         <v/>
       </c>
       <c r="E3" s="12">
@@ -3945,15 +4315,15 @@
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>IF($B3="BLOCKED",$Z3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
+        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2+$AJ2),$D3+$G3+$J3)</f>
+        <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
         <v/>
       </c>
       <c r="AC3" s="12">
-        <f>IF($B3="BLOCKED",$AB3,IF($B3="BIG_SIDE",$W3,$AG3+$AJ3))</f>
+        <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
         <v/>
       </c>
       <c r="AD3" s="12">
@@ -3965,11 +4335,11 @@
         <v/>
       </c>
       <c r="AF3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,$C3,$AF2),IF($B3="SMALL_SIDE",$E3,$C3))</f>
+        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
+        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
         <v/>
       </c>
       <c r="AH3" s="13" t="inlineStr">
@@ -4005,15 +4375,15 @@
         <v/>
       </c>
       <c r="AP3" s="12">
-        <f>IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"YES",IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="STOP_CLEARED",$AQ3="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ3" s="12">
-        <f>IF($B3="BLOCKED","STOP",IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
+        <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR3" s="12">
-        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS3" s="20">
@@ -4033,7 +4403,7 @@
         <v/>
       </c>
       <c r="AW3" s="12">
-        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX3" s="12">
@@ -4047,6 +4417,32 @@
       <c r="AZ3" s="12">
         <f>IF($B3="BIG_SIDE",$V3*$AU3,0)</f>
         <v/>
+      </c>
+      <c r="BA3" s="12">
+        <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
+        <v/>
+      </c>
+      <c r="BB3" s="12">
+        <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
+        <v/>
+      </c>
+      <c r="BC3" s="12">
+        <f>$BA3+$BB3</f>
+        <v/>
+      </c>
+      <c r="BD3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -4054,15 +4450,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="13">
-        <f>IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"BIG_SIDE",IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="MANUAL_READY",$AQ3="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C4" s="13">
-        <f>IF($B4="BLOCKED",$AF3,IF($AP3="YES",$AF3,$C3))</f>
+        <f>IF($B4="BLOCKED",$AF3,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),$AF3,IF($AP3="YES",$AF3,$C3)))</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF($B4="BLOCKED",0,IF($AP3="YES",MAX(0,$AG3),$D3))</f>
+        <f>IF($B4="BLOCKED",0,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),MAX($BA3,$BB3),IF($AP3="YES",MAX(0,$AG3),$D3)))</f>
         <v/>
       </c>
       <c r="E4" s="12">
@@ -4151,15 +4547,15 @@
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>IF($B4="BLOCKED",$Z4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
+        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3+$AJ3),$D4+$G4+$J4)</f>
+        <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
         <v/>
       </c>
       <c r="AC4" s="12">
-        <f>IF($B4="BLOCKED",$AB4,IF($B4="BIG_SIDE",$W4,$AG4+$AJ4))</f>
+        <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
         <v/>
       </c>
       <c r="AD4" s="12">
@@ -4171,11 +4567,11 @@
         <v/>
       </c>
       <c r="AF4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,$C4,$AF3),IF($B4="SMALL_SIDE",$E4,$C4))</f>
+        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
+        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -4211,15 +4607,15 @@
         <v/>
       </c>
       <c r="AP4" s="12">
-        <f>IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"YES",IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="STOP_CLEARED",$AQ4="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ4" s="12">
-        <f>IF($B4="BLOCKED","STOP",IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
+        <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR4" s="12">
-        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS4" s="20">
@@ -4239,7 +4635,7 @@
         <v/>
       </c>
       <c r="AW4" s="12">
-        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX4" s="12">
@@ -4253,6 +4649,32 @@
       <c r="AZ4" s="12">
         <f>IF($B4="BIG_SIDE",$V4*$AU4,0)</f>
         <v/>
+      </c>
+      <c r="BA4" s="12">
+        <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
+        <v/>
+      </c>
+      <c r="BB4" s="12">
+        <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
+        <v/>
+      </c>
+      <c r="BC4" s="12">
+        <f>$BA4+$BB4</f>
+        <v/>
+      </c>
+      <c r="BD4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -4260,15 +4682,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="13">
-        <f>IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"SMALL_SIDE",IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="MANUAL_READY",$AQ4="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>IF($B5="BLOCKED",$AF4,IF($AP4="YES",$AF4,$C4))</f>
+        <f>IF($B5="BLOCKED",$AF4,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),$AF4,IF($AP4="YES",$AF4,$C4)))</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF($B5="BLOCKED",0,IF($AP4="YES",MAX(0,$AG4),$D4))</f>
+        <f>IF($B5="BLOCKED",0,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),MAX($BA4,$BB4),IF($AP4="YES",MAX(0,$AG4),$D4)))</f>
         <v/>
       </c>
       <c r="E5" s="12">
@@ -4357,15 +4779,15 @@
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>IF($B5="BLOCKED",$Z5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
+        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4+$AJ4),$D5+$G5+$J5)</f>
+        <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
         <v/>
       </c>
       <c r="AC5" s="12">
-        <f>IF($B5="BLOCKED",$AB5,IF($B5="BIG_SIDE",$W5,$AG5+$AJ5))</f>
+        <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
         <v/>
       </c>
       <c r="AD5" s="12">
@@ -4377,11 +4799,11 @@
         <v/>
       </c>
       <c r="AF5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,$C5,$AF4),IF($B5="SMALL_SIDE",$E5,$C5))</f>
+        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
+        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v/>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -4417,15 +4839,15 @@
         <v/>
       </c>
       <c r="AP5" s="12">
-        <f>IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"YES",IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="STOP_CLEARED",$AQ5="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ5" s="12">
-        <f>IF($B5="BLOCKED","STOP",IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
+        <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR5" s="12">
-        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS5" s="20">
@@ -4445,7 +4867,7 @@
         <v/>
       </c>
       <c r="AW5" s="12">
-        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX5" s="12">
@@ -4459,6 +4881,32 @@
       <c r="AZ5" s="12">
         <f>IF($B5="BIG_SIDE",$V5*$AU5,0)</f>
         <v/>
+      </c>
+      <c r="BA5" s="12">
+        <f>IF($AK5=TRUE,MAX(0,$AJ5-$BD5),IF($B5="BLOCKED",MAX(0,$BA4-$BD5),0))</f>
+        <v/>
+      </c>
+      <c r="BB5" s="12">
+        <f>IF($AK5=TRUE,MAX(0,$AG5-$BE5),IF($B5="BLOCKED",MAX(0,$BB4-$BE5),0))</f>
+        <v/>
+      </c>
+      <c r="BC5" s="12">
+        <f>$BA5+$BB5</f>
+        <v/>
+      </c>
+      <c r="BD5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4466,15 +4914,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="13">
-        <f>IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"BIG_SIDE",IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="MANUAL_READY",$AQ5="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>IF($B6="BLOCKED",$AF5,IF($AP5="YES",$AF5,$C5))</f>
+        <f>IF($B6="BLOCKED",$AF5,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),$AF5,IF($AP5="YES",$AF5,$C5)))</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF($B6="BLOCKED",0,IF($AP5="YES",MAX(0,$AG5),$D5))</f>
+        <f>IF($B6="BLOCKED",0,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),MAX($BA5,$BB5),IF($AP5="YES",MAX(0,$AG5),$D5)))</f>
         <v/>
       </c>
       <c r="E6" s="12">
@@ -4563,15 +5011,15 @@
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>IF($B6="BLOCKED",$Z6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
+        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5+$AJ5),$D6+$G6+$J6)</f>
+        <f>IF($B6="BLOCKED",$BC6,$D6+$G6+$J6)</f>
         <v/>
       </c>
       <c r="AC6" s="12">
-        <f>IF($B6="BLOCKED",$AB6,IF($B6="BIG_SIDE",$W6,$AG6+$AJ6))</f>
+        <f>IF($B6="BLOCKED",$BC6,IF($B6="BIG_SIDE",$W6,IF($AK6=TRUE,$BC6,$AG6)))</f>
         <v/>
       </c>
       <c r="AD6" s="12">
@@ -4583,11 +5031,11 @@
         <v/>
       </c>
       <c r="AF6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,$C6,$AF5),IF($B6="SMALL_SIDE",$E6,$C6))</f>
+        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
+        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -4623,15 +5071,15 @@
         <v/>
       </c>
       <c r="AP6" s="12">
-        <f>IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"YES",IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="STOP_CLEARED",$AQ6="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ6" s="12">
-        <f>IF($B6="BLOCKED","STOP",IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
+        <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR6" s="12">
-        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS6" s="20">
@@ -4651,7 +5099,7 @@
         <v/>
       </c>
       <c r="AW6" s="12">
-        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX6" s="12">
@@ -4665,6 +5113,32 @@
       <c r="AZ6" s="12">
         <f>IF($B6="BIG_SIDE",$V6*$AU6,0)</f>
         <v/>
+      </c>
+      <c r="BA6" s="12">
+        <f>IF($AK6=TRUE,MAX(0,$AJ6-$BD6),IF($B6="BLOCKED",MAX(0,$BA5-$BD6),0))</f>
+        <v/>
+      </c>
+      <c r="BB6" s="12">
+        <f>IF($AK6=TRUE,MAX(0,$AG6-$BE6),IF($B6="BLOCKED",MAX(0,$BB5-$BE6),0))</f>
+        <v/>
+      </c>
+      <c r="BC6" s="12">
+        <f>$BA6+$BB6</f>
+        <v/>
+      </c>
+      <c r="BD6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4672,15 +5146,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="13">
-        <f>IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"BIG_SIDE",IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="MANUAL_READY",$AQ6="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>IF($B7="BLOCKED",$AF6,IF($AP6="YES",$AF6,$C6))</f>
+        <f>IF($B7="BLOCKED",$AF6,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),$AF6,IF($AP6="YES",$AF6,$C6)))</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF($B7="BLOCKED",0,IF($AP6="YES",MAX(0,$AG6),$D6))</f>
+        <f>IF($B7="BLOCKED",0,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),MAX($BA6,$BB6),IF($AP6="YES",MAX(0,$AG6),$D6)))</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -4769,15 +5243,15 @@
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>IF($B7="BLOCKED",$Z7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
+        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6+$AJ6),$D7+$G7+$J7)</f>
+        <f>IF($B7="BLOCKED",$BC7,$D7+$G7+$J7)</f>
         <v/>
       </c>
       <c r="AC7" s="12">
-        <f>IF($B7="BLOCKED",$AB7,IF($B7="BIG_SIDE",$W7,$AG7+$AJ7))</f>
+        <f>IF($B7="BLOCKED",$BC7,IF($B7="BIG_SIDE",$W7,IF($AK7=TRUE,$BC7,$AG7)))</f>
         <v/>
       </c>
       <c r="AD7" s="12">
@@ -4789,11 +5263,11 @@
         <v/>
       </c>
       <c r="AF7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,$C7,$AF6),IF($B7="SMALL_SIDE",$E7,$C7))</f>
+        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
+        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -4829,15 +5303,15 @@
         <v/>
       </c>
       <c r="AP7" s="12">
-        <f>IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"YES",IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="STOP_CLEARED",$AQ7="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ7" s="12">
-        <f>IF($B7="BLOCKED","STOP",IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
+        <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR7" s="12">
-        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS7" s="20">
@@ -4857,7 +5331,7 @@
         <v/>
       </c>
       <c r="AW7" s="12">
-        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX7" s="12">
@@ -4871,6 +5345,32 @@
       <c r="AZ7" s="12">
         <f>IF($B7="BIG_SIDE",$V7*$AU7,0)</f>
         <v/>
+      </c>
+      <c r="BA7" s="12">
+        <f>IF($AK7=TRUE,MAX(0,$AJ7-$BD7),IF($B7="BLOCKED",MAX(0,$BA6-$BD7),0))</f>
+        <v/>
+      </c>
+      <c r="BB7" s="12">
+        <f>IF($AK7=TRUE,MAX(0,$AG7-$BE7),IF($B7="BLOCKED",MAX(0,$BB6-$BE7),0))</f>
+        <v/>
+      </c>
+      <c r="BC7" s="12">
+        <f>$BA7+$BB7</f>
+        <v/>
+      </c>
+      <c r="BD7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4878,15 +5378,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="13">
-        <f>IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"BIG_SIDE",IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="MANUAL_READY",$AQ7="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>IF($B8="BLOCKED",$AF7,IF($AP7="YES",$AF7,$C7))</f>
+        <f>IF($B8="BLOCKED",$AF7,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),$AF7,IF($AP7="YES",$AF7,$C7)))</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF($B8="BLOCKED",0,IF($AP7="YES",MAX(0,$AG7),$D7))</f>
+        <f>IF($B8="BLOCKED",0,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),MAX($BA7,$BB7),IF($AP7="YES",MAX(0,$AG7),$D7)))</f>
         <v/>
       </c>
       <c r="E8" s="12">
@@ -4975,15 +5475,15 @@
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>IF($B8="BLOCKED",$Z8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
+        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7+$AJ7),$D8+$G8+$J8)</f>
+        <f>IF($B8="BLOCKED",$BC8,$D8+$G8+$J8)</f>
         <v/>
       </c>
       <c r="AC8" s="12">
-        <f>IF($B8="BLOCKED",$AB8,IF($B8="BIG_SIDE",$W8,$AG8+$AJ8))</f>
+        <f>IF($B8="BLOCKED",$BC8,IF($B8="BIG_SIDE",$W8,IF($AK8=TRUE,$BC8,$AG8)))</f>
         <v/>
       </c>
       <c r="AD8" s="12">
@@ -4995,11 +5495,11 @@
         <v/>
       </c>
       <c r="AF8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,$C8,$AF7),IF($B8="SMALL_SIDE",$E8,$C8))</f>
+        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
+        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -5035,15 +5535,15 @@
         <v/>
       </c>
       <c r="AP8" s="12">
-        <f>IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"YES",IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="STOP_CLEARED",$AQ8="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ8" s="12">
-        <f>IF($B8="BLOCKED","STOP",IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
+        <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR8" s="12">
-        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS8" s="20">
@@ -5063,7 +5563,7 @@
         <v/>
       </c>
       <c r="AW8" s="12">
-        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX8" s="12">
@@ -5077,6 +5577,32 @@
       <c r="AZ8" s="12">
         <f>IF($B8="BIG_SIDE",$V8*$AU8,0)</f>
         <v/>
+      </c>
+      <c r="BA8" s="12">
+        <f>IF($AK8=TRUE,MAX(0,$AJ8-$BD8),IF($B8="BLOCKED",MAX(0,$BA7-$BD8),0))</f>
+        <v/>
+      </c>
+      <c r="BB8" s="12">
+        <f>IF($AK8=TRUE,MAX(0,$AG8-$BE8),IF($B8="BLOCKED",MAX(0,$BB7-$BE8),0))</f>
+        <v/>
+      </c>
+      <c r="BC8" s="12">
+        <f>$BA8+$BB8</f>
+        <v/>
+      </c>
+      <c r="BD8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -5084,15 +5610,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="13">
-        <f>IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"SMALL_SIDE",IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="MANUAL_READY",$AQ8="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>IF($B9="BLOCKED",$AF8,IF($AP8="YES",$AF8,$C8))</f>
+        <f>IF($B9="BLOCKED",$AF8,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),$AF8,IF($AP8="YES",$AF8,$C8)))</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF($B9="BLOCKED",0,IF($AP8="YES",MAX(0,$AG8),$D8))</f>
+        <f>IF($B9="BLOCKED",0,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),MAX($BA8,$BB8),IF($AP8="YES",MAX(0,$AG8),$D8)))</f>
         <v/>
       </c>
       <c r="E9" s="12">
@@ -5181,15 +5707,15 @@
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>IF($B9="BLOCKED",$Z9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
+        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8+$AJ8),$D9+$G9+$J9)</f>
+        <f>IF($B9="BLOCKED",$BC9,$D9+$G9+$J9)</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>IF($B9="BLOCKED",$AB9,IF($B9="BIG_SIDE",$W9,$AG9+$AJ9))</f>
+        <f>IF($B9="BLOCKED",$BC9,IF($B9="BIG_SIDE",$W9,IF($AK9=TRUE,$BC9,$AG9)))</f>
         <v/>
       </c>
       <c r="AD9" s="12">
@@ -5201,11 +5727,11 @@
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,$C9,$AF8),IF($B9="SMALL_SIDE",$E9,$C9))</f>
+        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
+        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -5241,15 +5767,15 @@
         <v/>
       </c>
       <c r="AP9" s="12">
-        <f>IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"YES",IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="STOP_CLEARED",$AQ9="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ9" s="12">
-        <f>IF($B9="BLOCKED","STOP",IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
+        <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR9" s="12">
-        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS9" s="20">
@@ -5269,7 +5795,7 @@
         <v/>
       </c>
       <c r="AW9" s="12">
-        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX9" s="12">
@@ -5283,6 +5809,32 @@
       <c r="AZ9" s="12">
         <f>IF($B9="BIG_SIDE",$V9*$AU9,0)</f>
         <v/>
+      </c>
+      <c r="BA9" s="12">
+        <f>IF($AK9=TRUE,MAX(0,$AJ9-$BD9),IF($B9="BLOCKED",MAX(0,$BA8-$BD9),0))</f>
+        <v/>
+      </c>
+      <c r="BB9" s="12">
+        <f>IF($AK9=TRUE,MAX(0,$AG9-$BE9),IF($B9="BLOCKED",MAX(0,$BB8-$BE9),0))</f>
+        <v/>
+      </c>
+      <c r="BC9" s="12">
+        <f>$BA9+$BB9</f>
+        <v/>
+      </c>
+      <c r="BD9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -5290,15 +5842,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="13">
-        <f>IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"BIG_SIDE",IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="MANUAL_READY",$AQ9="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>IF($B10="BLOCKED",$AF9,IF($AP9="YES",$AF9,$C9))</f>
+        <f>IF($B10="BLOCKED",$AF9,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),$AF9,IF($AP9="YES",$AF9,$C9)))</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF($B10="BLOCKED",0,IF($AP9="YES",MAX(0,$AG9),$D9))</f>
+        <f>IF($B10="BLOCKED",0,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),MAX($BA9,$BB9),IF($AP9="YES",MAX(0,$AG9),$D9)))</f>
         <v/>
       </c>
       <c r="E10" s="12">
@@ -5387,15 +5939,15 @@
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>IF($B10="BLOCKED",$Z10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
+        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9+$AJ9),$D10+$G10+$J10)</f>
+        <f>IF($B10="BLOCKED",$BC10,$D10+$G10+$J10)</f>
         <v/>
       </c>
       <c r="AC10" s="12">
-        <f>IF($B10="BLOCKED",$AB10,IF($B10="BIG_SIDE",$W10,$AG10+$AJ10))</f>
+        <f>IF($B10="BLOCKED",$BC10,IF($B10="BIG_SIDE",$W10,IF($AK10=TRUE,$BC10,$AG10)))</f>
         <v/>
       </c>
       <c r="AD10" s="12">
@@ -5407,11 +5959,11 @@
         <v/>
       </c>
       <c r="AF10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,$C10,$AF9),IF($B10="SMALL_SIDE",$E10,$C10))</f>
+        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
+        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -5447,15 +5999,15 @@
         <v/>
       </c>
       <c r="AP10" s="12">
-        <f>IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"YES",IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="STOP_CLEARED",$AQ10="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ10" s="12">
-        <f>IF($B10="BLOCKED","STOP",IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
+        <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR10" s="12">
-        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS10" s="20">
@@ -5475,7 +6027,7 @@
         <v/>
       </c>
       <c r="AW10" s="12">
-        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX10" s="12">
@@ -5489,6 +6041,32 @@
       <c r="AZ10" s="12">
         <f>IF($B10="BIG_SIDE",$V10*$AU10,0)</f>
         <v/>
+      </c>
+      <c r="BA10" s="12">
+        <f>IF($AK10=TRUE,MAX(0,$AJ10-$BD10),IF($B10="BLOCKED",MAX(0,$BA9-$BD10),0))</f>
+        <v/>
+      </c>
+      <c r="BB10" s="12">
+        <f>IF($AK10=TRUE,MAX(0,$AG10-$BE10),IF($B10="BLOCKED",MAX(0,$BB9-$BE10),0))</f>
+        <v/>
+      </c>
+      <c r="BC10" s="12">
+        <f>$BA10+$BB10</f>
+        <v/>
+      </c>
+      <c r="BD10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -5496,15 +6074,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="13">
-        <f>IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"BIG_SIDE",IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="MANUAL_READY",$AQ10="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>IF($B11="BLOCKED",$AF10,IF($AP10="YES",$AF10,$C10))</f>
+        <f>IF($B11="BLOCKED",$AF10,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),$AF10,IF($AP10="YES",$AF10,$C10)))</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF($B11="BLOCKED",0,IF($AP10="YES",MAX(0,$AG10),$D10))</f>
+        <f>IF($B11="BLOCKED",0,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),MAX($BA10,$BB10),IF($AP10="YES",MAX(0,$AG10),$D10)))</f>
         <v/>
       </c>
       <c r="E11" s="12">
@@ -5593,15 +6171,15 @@
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>IF($B11="BLOCKED",$Z11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
+        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10+$AJ10),$D11+$G11+$J11)</f>
+        <f>IF($B11="BLOCKED",$BC11,$D11+$G11+$J11)</f>
         <v/>
       </c>
       <c r="AC11" s="12">
-        <f>IF($B11="BLOCKED",$AB11,IF($B11="BIG_SIDE",$W11,$AG11+$AJ11))</f>
+        <f>IF($B11="BLOCKED",$BC11,IF($B11="BIG_SIDE",$W11,IF($AK11=TRUE,$BC11,$AG11)))</f>
         <v/>
       </c>
       <c r="AD11" s="12">
@@ -5613,11 +6191,11 @@
         <v/>
       </c>
       <c r="AF11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,$C11,$AF10),IF($B11="SMALL_SIDE",$E11,$C11))</f>
+        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
+        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$BB11,$BA11),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -5653,15 +6231,15 @@
         <v/>
       </c>
       <c r="AP11" s="12">
-        <f>IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ11="MANUAL_READY",$BG11="YES"),"YES",IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP",$AQ11="STOP_CLEARED",$AQ11="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ11" s="12">
-        <f>IF($B11="BLOCKED","STOP",IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
+        <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR11" s="12">
-        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS11" s="20">
@@ -5681,7 +6259,7 @@
         <v/>
       </c>
       <c r="AW11" s="12">
-        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX11" s="12">
@@ -5696,9 +6274,35 @@
         <f>IF($B11="BIG_SIDE",$V11*$AU11,0)</f>
         <v/>
       </c>
+      <c r="BA11" s="12">
+        <f>IF($AK11=TRUE,MAX(0,$AJ11-$BD11),IF($B11="BLOCKED",MAX(0,$BA10-$BD11),0))</f>
+        <v/>
+      </c>
+      <c r="BB11" s="12">
+        <f>IF($AK11=TRUE,MAX(0,$AG11-$BE11),IF($B11="BLOCKED",MAX(0,$BB10-$BE11),0))</f>
+        <v/>
+      </c>
+      <c r="BC11" s="12">
+        <f>$BA11+$BB11</f>
+        <v/>
+      </c>
+      <c r="BD11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ11"/>
+  <autoFilter ref="A1:BG11"/>
   <conditionalFormatting sqref="AQ2:AQ11">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AQ2="WARNING"</formula>
@@ -5734,7 +6338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:BG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5789,6 +6393,13 @@
     <col width="18" customWidth="1" min="50" max="50"/>
     <col width="18" customWidth="1" min="51" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="20" customWidth="1" min="56" max="56"/>
+    <col width="20" customWidth="1" min="57" max="57"/>
+    <col width="20" customWidth="1" min="58" max="58"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6052,6 +6663,41 @@
           <t>CostsFarClose</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>ManualOldFarCloseLot</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>ManualNewFarCloseLot</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>ManualClosePL</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>ManualAllowNewLevel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -6156,15 +6802,15 @@
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>IF($B2="BLOCKED",$Z2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
+        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
         <v/>
       </c>
       <c r="AB2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1+$AJ1),$D2+$G2+$J2)</f>
+        <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
         <v/>
       </c>
       <c r="AC2" s="12">
-        <f>IF($B2="BLOCKED",$AB2,IF($B2="BIG_SIDE",$W2,$AG2+$AJ2))</f>
+        <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
         <v/>
       </c>
       <c r="AD2" s="12">
@@ -6176,11 +6822,11 @@
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,$C2,$AF1),IF($B2="SMALL_SIDE",$E2,$C2))</f>
+        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF($B2="BLOCKED",IF(ROW()=2,0,$AG1),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
+        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -6216,15 +6862,15 @@
         <v/>
       </c>
       <c r="AP2" s="12">
-        <f>IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ2" s="12">
-        <f>IF($B2="BLOCKED","STOP",IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
+        <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR2" s="12">
-        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS2" s="20">
@@ -6244,7 +6890,7 @@
         <v/>
       </c>
       <c r="AW2" s="12">
-        <f>IF($B2="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX2" s="12">
@@ -6258,6 +6904,32 @@
       <c r="AZ2" s="12">
         <f>IF($B2="BIG_SIDE",$V2*$AU2,0)</f>
         <v/>
+      </c>
+      <c r="BA2" s="12">
+        <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
+        <v/>
+      </c>
+      <c r="BB2" s="12">
+        <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
+        <v/>
+      </c>
+      <c r="BC2" s="12">
+        <f>$BA2+$BB2</f>
+        <v/>
+      </c>
+      <c r="BD2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -6265,15 +6937,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="13">
-        <f>IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"SMALL_SIDE",IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="MANUAL_READY",$AQ2="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>IF($B3="BLOCKED",$AF2,IF($AP2="YES",$AF2,$C2))</f>
+        <f>IF($B3="BLOCKED",$AF2,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),$AF2,IF($AP2="YES",$AF2,$C2)))</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>IF($B3="BLOCKED",0,IF($AP2="YES",MAX(0,$AG2),$D2))</f>
+        <f>IF($B3="BLOCKED",0,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),MAX($BA2,$BB2),IF($AP2="YES",MAX(0,$AG2),$D2)))</f>
         <v/>
       </c>
       <c r="E3" s="12">
@@ -6362,15 +7034,15 @@
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>IF($B3="BLOCKED",$Z3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
+        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2+$AJ2),$D3+$G3+$J3)</f>
+        <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
         <v/>
       </c>
       <c r="AC3" s="12">
-        <f>IF($B3="BLOCKED",$AB3,IF($B3="BIG_SIDE",$W3,$AG3+$AJ3))</f>
+        <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
         <v/>
       </c>
       <c r="AD3" s="12">
@@ -6382,11 +7054,11 @@
         <v/>
       </c>
       <c r="AF3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,$C3,$AF2),IF($B3="SMALL_SIDE",$E3,$C3))</f>
+        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF($B3="BLOCKED",IF(ROW()=2,0,$AG2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
+        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
         <v/>
       </c>
       <c r="AH3" s="13" t="inlineStr">
@@ -6422,15 +7094,15 @@
         <v/>
       </c>
       <c r="AP3" s="12">
-        <f>IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"YES",IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="STOP_CLEARED",$AQ3="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ3" s="12">
-        <f>IF($B3="BLOCKED","STOP",IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
+        <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR3" s="12">
-        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS3" s="20">
@@ -6450,7 +7122,7 @@
         <v/>
       </c>
       <c r="AW3" s="12">
-        <f>IF($B3="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX3" s="12">
@@ -6464,6 +7136,32 @@
       <c r="AZ3" s="12">
         <f>IF($B3="BIG_SIDE",$V3*$AU3,0)</f>
         <v/>
+      </c>
+      <c r="BA3" s="12">
+        <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
+        <v/>
+      </c>
+      <c r="BB3" s="12">
+        <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
+        <v/>
+      </c>
+      <c r="BC3" s="12">
+        <f>$BA3+$BB3</f>
+        <v/>
+      </c>
+      <c r="BD3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -6471,15 +7169,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="13">
-        <f>IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"BIG_SIDE",IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="MANUAL_READY",$AQ3="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C4" s="13">
-        <f>IF($B4="BLOCKED",$AF3,IF($AP3="YES",$AF3,$C3))</f>
+        <f>IF($B4="BLOCKED",$AF3,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),$AF3,IF($AP3="YES",$AF3,$C3)))</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF($B4="BLOCKED",0,IF($AP3="YES",MAX(0,$AG3),$D3))</f>
+        <f>IF($B4="BLOCKED",0,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),MAX($BA3,$BB3),IF($AP3="YES",MAX(0,$AG3),$D3)))</f>
         <v/>
       </c>
       <c r="E4" s="12">
@@ -6568,15 +7266,15 @@
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>IF($B4="BLOCKED",$Z4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
+        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3+$AJ3),$D4+$G4+$J4)</f>
+        <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
         <v/>
       </c>
       <c r="AC4" s="12">
-        <f>IF($B4="BLOCKED",$AB4,IF($B4="BIG_SIDE",$W4,$AG4+$AJ4))</f>
+        <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
         <v/>
       </c>
       <c r="AD4" s="12">
@@ -6588,11 +7286,11 @@
         <v/>
       </c>
       <c r="AF4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,$C4,$AF3),IF($B4="SMALL_SIDE",$E4,$C4))</f>
+        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF($B4="BLOCKED",IF(ROW()=2,0,$AG3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
+        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -6628,15 +7326,15 @@
         <v/>
       </c>
       <c r="AP4" s="12">
-        <f>IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"YES",IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="STOP_CLEARED",$AQ4="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ4" s="12">
-        <f>IF($B4="BLOCKED","STOP",IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
+        <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR4" s="12">
-        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS4" s="20">
@@ -6656,7 +7354,7 @@
         <v/>
       </c>
       <c r="AW4" s="12">
-        <f>IF($B4="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX4" s="12">
@@ -6670,6 +7368,32 @@
       <c r="AZ4" s="12">
         <f>IF($B4="BIG_SIDE",$V4*$AU4,0)</f>
         <v/>
+      </c>
+      <c r="BA4" s="12">
+        <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
+        <v/>
+      </c>
+      <c r="BB4" s="12">
+        <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
+        <v/>
+      </c>
+      <c r="BC4" s="12">
+        <f>$BA4+$BB4</f>
+        <v/>
+      </c>
+      <c r="BD4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -6677,15 +7401,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="13">
-        <f>IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"BIG_SIDE",IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="MANUAL_READY",$AQ4="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>IF($B5="BLOCKED",$AF4,IF($AP4="YES",$AF4,$C4))</f>
+        <f>IF($B5="BLOCKED",$AF4,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),$AF4,IF($AP4="YES",$AF4,$C4)))</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF($B5="BLOCKED",0,IF($AP4="YES",MAX(0,$AG4),$D4))</f>
+        <f>IF($B5="BLOCKED",0,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),MAX($BA4,$BB4),IF($AP4="YES",MAX(0,$AG4),$D4)))</f>
         <v/>
       </c>
       <c r="E5" s="12">
@@ -6774,15 +7498,15 @@
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>IF($B5="BLOCKED",$Z5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
+        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4+$AJ4),$D5+$G5+$J5)</f>
+        <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
         <v/>
       </c>
       <c r="AC5" s="12">
-        <f>IF($B5="BLOCKED",$AB5,IF($B5="BIG_SIDE",$W5,$AG5+$AJ5))</f>
+        <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
         <v/>
       </c>
       <c r="AD5" s="12">
@@ -6794,11 +7518,11 @@
         <v/>
       </c>
       <c r="AF5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,$C5,$AF4),IF($B5="SMALL_SIDE",$E5,$C5))</f>
+        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF($B5="BLOCKED",IF(ROW()=2,0,$AG4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
+        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v/>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -6834,15 +7558,15 @@
         <v/>
       </c>
       <c r="AP5" s="12">
-        <f>IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"YES",IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="STOP_CLEARED",$AQ5="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ5" s="12">
-        <f>IF($B5="BLOCKED","STOP",IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
+        <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR5" s="12">
-        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS5" s="20">
@@ -6862,7 +7586,7 @@
         <v/>
       </c>
       <c r="AW5" s="12">
-        <f>IF($B5="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX5" s="12">
@@ -6876,6 +7600,32 @@
       <c r="AZ5" s="12">
         <f>IF($B5="BIG_SIDE",$V5*$AU5,0)</f>
         <v/>
+      </c>
+      <c r="BA5" s="12">
+        <f>IF($AK5=TRUE,MAX(0,$AJ5-$BD5),IF($B5="BLOCKED",MAX(0,$BA4-$BD5),0))</f>
+        <v/>
+      </c>
+      <c r="BB5" s="12">
+        <f>IF($AK5=TRUE,MAX(0,$AG5-$BE5),IF($B5="BLOCKED",MAX(0,$BB4-$BE5),0))</f>
+        <v/>
+      </c>
+      <c r="BC5" s="12">
+        <f>$BA5+$BB5</f>
+        <v/>
+      </c>
+      <c r="BD5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -6883,15 +7633,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="13">
-        <f>IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"BIG_SIDE",IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="MANUAL_READY",$AQ5="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>IF($B6="BLOCKED",$AF5,IF($AP5="YES",$AF5,$C5))</f>
+        <f>IF($B6="BLOCKED",$AF5,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),$AF5,IF($AP5="YES",$AF5,$C5)))</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF($B6="BLOCKED",0,IF($AP5="YES",MAX(0,$AG5),$D5))</f>
+        <f>IF($B6="BLOCKED",0,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),MAX($BA5,$BB5),IF($AP5="YES",MAX(0,$AG5),$D5)))</f>
         <v/>
       </c>
       <c r="E6" s="12">
@@ -6980,15 +7730,15 @@
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>IF($B6="BLOCKED",$Z6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
+        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5+$AJ5),$D6+$G6+$J6)</f>
+        <f>IF($B6="BLOCKED",$BC6,$D6+$G6+$J6)</f>
         <v/>
       </c>
       <c r="AC6" s="12">
-        <f>IF($B6="BLOCKED",$AB6,IF($B6="BIG_SIDE",$W6,$AG6+$AJ6))</f>
+        <f>IF($B6="BLOCKED",$BC6,IF($B6="BIG_SIDE",$W6,IF($AK6=TRUE,$BC6,$AG6)))</f>
         <v/>
       </c>
       <c r="AD6" s="12">
@@ -7000,11 +7750,11 @@
         <v/>
       </c>
       <c r="AF6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,$C6,$AF5),IF($B6="SMALL_SIDE",$E6,$C6))</f>
+        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF($B6="BLOCKED",IF(ROW()=2,0,$AG5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
+        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -7040,15 +7790,15 @@
         <v/>
       </c>
       <c r="AP6" s="12">
-        <f>IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"YES",IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="STOP_CLEARED",$AQ6="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ6" s="12">
-        <f>IF($B6="BLOCKED","STOP",IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
+        <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR6" s="12">
-        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS6" s="20">
@@ -7068,7 +7818,7 @@
         <v/>
       </c>
       <c r="AW6" s="12">
-        <f>IF($B6="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX6" s="12">
@@ -7082,6 +7832,32 @@
       <c r="AZ6" s="12">
         <f>IF($B6="BIG_SIDE",$V6*$AU6,0)</f>
         <v/>
+      </c>
+      <c r="BA6" s="12">
+        <f>IF($AK6=TRUE,MAX(0,$AJ6-$BD6),IF($B6="BLOCKED",MAX(0,$BA5-$BD6),0))</f>
+        <v/>
+      </c>
+      <c r="BB6" s="12">
+        <f>IF($AK6=TRUE,MAX(0,$AG6-$BE6),IF($B6="BLOCKED",MAX(0,$BB5-$BE6),0))</f>
+        <v/>
+      </c>
+      <c r="BC6" s="12">
+        <f>$BA6+$BB6</f>
+        <v/>
+      </c>
+      <c r="BD6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -7089,15 +7865,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="13">
-        <f>IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP"),"BLOCKED","SMALL_SIDE")</f>
+        <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"SMALL_SIDE",IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="MANUAL_READY",$AQ6="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>IF($B7="BLOCKED",$AF6,IF($AP6="YES",$AF6,$C6))</f>
+        <f>IF($B7="BLOCKED",$AF6,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),$AF6,IF($AP6="YES",$AF6,$C6)))</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF($B7="BLOCKED",0,IF($AP6="YES",MAX(0,$AG6),$D6))</f>
+        <f>IF($B7="BLOCKED",0,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),MAX($BA6,$BB6),IF($AP6="YES",MAX(0,$AG6),$D6)))</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -7186,15 +7962,15 @@
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>IF($B7="BLOCKED",$Z7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
+        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6+$AJ6),$D7+$G7+$J7)</f>
+        <f>IF($B7="BLOCKED",$BC7,$D7+$G7+$J7)</f>
         <v/>
       </c>
       <c r="AC7" s="12">
-        <f>IF($B7="BLOCKED",$AB7,IF($B7="BIG_SIDE",$W7,$AG7+$AJ7))</f>
+        <f>IF($B7="BLOCKED",$BC7,IF($B7="BIG_SIDE",$W7,IF($AK7=TRUE,$BC7,$AG7)))</f>
         <v/>
       </c>
       <c r="AD7" s="12">
@@ -7206,11 +7982,11 @@
         <v/>
       </c>
       <c r="AF7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,$C7,$AF6),IF($B7="SMALL_SIDE",$E7,$C7))</f>
+        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF($B7="BLOCKED",IF(ROW()=2,0,$AG6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
+        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -7246,15 +8022,15 @@
         <v/>
       </c>
       <c r="AP7" s="12">
-        <f>IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"YES",IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="STOP_CLEARED",$AQ7="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ7" s="12">
-        <f>IF($B7="BLOCKED","STOP",IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
+        <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR7" s="12">
-        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS7" s="20">
@@ -7274,7 +8050,7 @@
         <v/>
       </c>
       <c r="AW7" s="12">
-        <f>IF($B7="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX7" s="12">
@@ -7288,6 +8064,32 @@
       <c r="AZ7" s="12">
         <f>IF($B7="BIG_SIDE",$V7*$AU7,0)</f>
         <v/>
+      </c>
+      <c r="BA7" s="12">
+        <f>IF($AK7=TRUE,MAX(0,$AJ7-$BD7),IF($B7="BLOCKED",MAX(0,$BA6-$BD7),0))</f>
+        <v/>
+      </c>
+      <c r="BB7" s="12">
+        <f>IF($AK7=TRUE,MAX(0,$AG7-$BE7),IF($B7="BLOCKED",MAX(0,$BB6-$BE7),0))</f>
+        <v/>
+      </c>
+      <c r="BC7" s="12">
+        <f>$BA7+$BB7</f>
+        <v/>
+      </c>
+      <c r="BD7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -7295,15 +8097,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="13">
-        <f>IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"BIG_SIDE",IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="MANUAL_READY",$AQ7="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>IF($B8="BLOCKED",$AF7,IF($AP7="YES",$AF7,$C7))</f>
+        <f>IF($B8="BLOCKED",$AF7,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),$AF7,IF($AP7="YES",$AF7,$C7)))</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF($B8="BLOCKED",0,IF($AP7="YES",MAX(0,$AG7),$D7))</f>
+        <f>IF($B8="BLOCKED",0,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),MAX($BA7,$BB7),IF($AP7="YES",MAX(0,$AG7),$D7)))</f>
         <v/>
       </c>
       <c r="E8" s="12">
@@ -7392,15 +8194,15 @@
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>IF($B8="BLOCKED",$Z8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
+        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7+$AJ7),$D8+$G8+$J8)</f>
+        <f>IF($B8="BLOCKED",$BC8,$D8+$G8+$J8)</f>
         <v/>
       </c>
       <c r="AC8" s="12">
-        <f>IF($B8="BLOCKED",$AB8,IF($B8="BIG_SIDE",$W8,$AG8+$AJ8))</f>
+        <f>IF($B8="BLOCKED",$BC8,IF($B8="BIG_SIDE",$W8,IF($AK8=TRUE,$BC8,$AG8)))</f>
         <v/>
       </c>
       <c r="AD8" s="12">
@@ -7412,11 +8214,11 @@
         <v/>
       </c>
       <c r="AF8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,$C8,$AF7),IF($B8="SMALL_SIDE",$E8,$C8))</f>
+        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF($B8="BLOCKED",IF(ROW()=2,0,$AG7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
+        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -7452,15 +8254,15 @@
         <v/>
       </c>
       <c r="AP8" s="12">
-        <f>IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"YES",IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="STOP_CLEARED",$AQ8="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ8" s="12">
-        <f>IF($B8="BLOCKED","STOP",IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
+        <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR8" s="12">
-        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS8" s="20">
@@ -7480,7 +8282,7 @@
         <v/>
       </c>
       <c r="AW8" s="12">
-        <f>IF($B8="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX8" s="12">
@@ -7494,6 +8296,32 @@
       <c r="AZ8" s="12">
         <f>IF($B8="BIG_SIDE",$V8*$AU8,0)</f>
         <v/>
+      </c>
+      <c r="BA8" s="12">
+        <f>IF($AK8=TRUE,MAX(0,$AJ8-$BD8),IF($B8="BLOCKED",MAX(0,$BA7-$BD8),0))</f>
+        <v/>
+      </c>
+      <c r="BB8" s="12">
+        <f>IF($AK8=TRUE,MAX(0,$AG8-$BE8),IF($B8="BLOCKED",MAX(0,$BB7-$BE8),0))</f>
+        <v/>
+      </c>
+      <c r="BC8" s="12">
+        <f>$BA8+$BB8</f>
+        <v/>
+      </c>
+      <c r="BD8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -7501,15 +8329,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="13">
-        <f>IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"BIG_SIDE",IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="MANUAL_READY",$AQ8="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>IF($B9="BLOCKED",$AF8,IF($AP8="YES",$AF8,$C8))</f>
+        <f>IF($B9="BLOCKED",$AF8,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),$AF8,IF($AP8="YES",$AF8,$C8)))</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF($B9="BLOCKED",0,IF($AP8="YES",MAX(0,$AG8),$D8))</f>
+        <f>IF($B9="BLOCKED",0,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),MAX($BA8,$BB8),IF($AP8="YES",MAX(0,$AG8),$D8)))</f>
         <v/>
       </c>
       <c r="E9" s="12">
@@ -7598,15 +8426,15 @@
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>IF($B9="BLOCKED",$Z9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
+        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8+$AJ8),$D9+$G9+$J9)</f>
+        <f>IF($B9="BLOCKED",$BC9,$D9+$G9+$J9)</f>
         <v/>
       </c>
       <c r="AC9" s="12">
-        <f>IF($B9="BLOCKED",$AB9,IF($B9="BIG_SIDE",$W9,$AG9+$AJ9))</f>
+        <f>IF($B9="BLOCKED",$BC9,IF($B9="BIG_SIDE",$W9,IF($AK9=TRUE,$BC9,$AG9)))</f>
         <v/>
       </c>
       <c r="AD9" s="12">
@@ -7618,11 +8446,11 @@
         <v/>
       </c>
       <c r="AF9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,$C9,$AF8),IF($B9="SMALL_SIDE",$E9,$C9))</f>
+        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF($B9="BLOCKED",IF(ROW()=2,0,$AG8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
+        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -7658,15 +8486,15 @@
         <v/>
       </c>
       <c r="AP9" s="12">
-        <f>IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"YES",IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="STOP_CLEARED",$AQ9="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ9" s="12">
-        <f>IF($B9="BLOCKED","STOP",IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
+        <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR9" s="12">
-        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS9" s="20">
@@ -7686,7 +8514,7 @@
         <v/>
       </c>
       <c r="AW9" s="12">
-        <f>IF($B9="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX9" s="12">
@@ -7700,6 +8528,32 @@
       <c r="AZ9" s="12">
         <f>IF($B9="BIG_SIDE",$V9*$AU9,0)</f>
         <v/>
+      </c>
+      <c r="BA9" s="12">
+        <f>IF($AK9=TRUE,MAX(0,$AJ9-$BD9),IF($B9="BLOCKED",MAX(0,$BA8-$BD9),0))</f>
+        <v/>
+      </c>
+      <c r="BB9" s="12">
+        <f>IF($AK9=TRUE,MAX(0,$AG9-$BE9),IF($B9="BLOCKED",MAX(0,$BB8-$BE9),0))</f>
+        <v/>
+      </c>
+      <c r="BC9" s="12">
+        <f>$BA9+$BB9</f>
+        <v/>
+      </c>
+      <c r="BD9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7707,15 +8561,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="13">
-        <f>IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"BIG_SIDE",IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="MANUAL_READY",$AQ9="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>IF($B10="BLOCKED",$AF9,IF($AP9="YES",$AF9,$C9))</f>
+        <f>IF($B10="BLOCKED",$AF9,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),$AF9,IF($AP9="YES",$AF9,$C9)))</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF($B10="BLOCKED",0,IF($AP9="YES",MAX(0,$AG9),$D9))</f>
+        <f>IF($B10="BLOCKED",0,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),MAX($BA9,$BB9),IF($AP9="YES",MAX(0,$AG9),$D9)))</f>
         <v/>
       </c>
       <c r="E10" s="12">
@@ -7804,15 +8658,15 @@
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>IF($B10="BLOCKED",$Z10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
+        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9+$AJ9),$D10+$G10+$J10)</f>
+        <f>IF($B10="BLOCKED",$BC10,$D10+$G10+$J10)</f>
         <v/>
       </c>
       <c r="AC10" s="12">
-        <f>IF($B10="BLOCKED",$AB10,IF($B10="BIG_SIDE",$W10,$AG10+$AJ10))</f>
+        <f>IF($B10="BLOCKED",$BC10,IF($B10="BIG_SIDE",$W10,IF($AK10=TRUE,$BC10,$AG10)))</f>
         <v/>
       </c>
       <c r="AD10" s="12">
@@ -7824,11 +8678,11 @@
         <v/>
       </c>
       <c r="AF10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,$C10,$AF9),IF($B10="SMALL_SIDE",$E10,$C10))</f>
+        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF($B10="BLOCKED",IF(ROW()=2,0,$AG9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
+        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -7864,15 +8718,15 @@
         <v/>
       </c>
       <c r="AP10" s="12">
-        <f>IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"YES",IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="STOP_CLEARED",$AQ10="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ10" s="12">
-        <f>IF($B10="BLOCKED","STOP",IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
+        <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR10" s="12">
-        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS10" s="20">
@@ -7892,7 +8746,7 @@
         <v/>
       </c>
       <c r="AW10" s="12">
-        <f>IF($B10="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX10" s="12">
@@ -7906,6 +8760,32 @@
       <c r="AZ10" s="12">
         <f>IF($B10="BIG_SIDE",$V10*$AU10,0)</f>
         <v/>
+      </c>
+      <c r="BA10" s="12">
+        <f>IF($AK10=TRUE,MAX(0,$AJ10-$BD10),IF($B10="BLOCKED",MAX(0,$BA9-$BD10),0))</f>
+        <v/>
+      </c>
+      <c r="BB10" s="12">
+        <f>IF($AK10=TRUE,MAX(0,$AG10-$BE10),IF($B10="BLOCKED",MAX(0,$BB9-$BE10),0))</f>
+        <v/>
+      </c>
+      <c r="BC10" s="12">
+        <f>$BA10+$BB10</f>
+        <v/>
+      </c>
+      <c r="BD10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7913,15 +8793,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="13">
-        <f>IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP"),"BLOCKED","BIG_SIDE")</f>
+        <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"BIG_SIDE",IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="MANUAL_READY",$AQ10="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>IF($B11="BLOCKED",$AF10,IF($AP10="YES",$AF10,$C10))</f>
+        <f>IF($B11="BLOCKED",$AF10,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),$AF10,IF($AP10="YES",$AF10,$C10)))</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF($B11="BLOCKED",0,IF($AP10="YES",MAX(0,$AG10),$D10))</f>
+        <f>IF($B11="BLOCKED",0,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),MAX($BA10,$BB10),IF($AP10="YES",MAX(0,$AG10),$D10)))</f>
         <v/>
       </c>
       <c r="E11" s="12">
@@ -8010,15 +8890,15 @@
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>IF($B11="BLOCKED",$Z11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
+        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10+$AJ10),$D11+$G11+$J11)</f>
+        <f>IF($B11="BLOCKED",$BC11,$D11+$G11+$J11)</f>
         <v/>
       </c>
       <c r="AC11" s="12">
-        <f>IF($B11="BLOCKED",$AB11,IF($B11="BIG_SIDE",$W11,$AG11+$AJ11))</f>
+        <f>IF($B11="BLOCKED",$BC11,IF($B11="BIG_SIDE",$W11,IF($AK11=TRUE,$BC11,$AG11)))</f>
         <v/>
       </c>
       <c r="AD11" s="12">
@@ -8030,11 +8910,11 @@
         <v/>
       </c>
       <c r="AF11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,$C11,$AF10),IF($B11="SMALL_SIDE",$E11,$C11))</f>
+        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF($B11="BLOCKED",IF(ROW()=2,0,$AG10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
+        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$BB11,$BA11),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -8070,15 +8950,15 @@
         <v/>
       </c>
       <c r="AP11" s="12">
-        <f>IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP"),"NO","YES")</f>
+        <f>IF(AND($AQ11="MANUAL_READY",$BG11="YES"),"YES",IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP",$AQ11="STOP_CLEARED",$AQ11="MANUAL_READY"),"NO","YES"))</f>
         <v/>
       </c>
       <c r="AQ11" s="12">
-        <f>IF($B11="BLOCKED","STOP",IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
+        <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
         <v/>
       </c>
       <c r="AR11" s="12">
-        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
+        <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
         <v/>
       </c>
       <c r="AS11" s="20">
@@ -8098,7 +8978,7 @@
         <v/>
       </c>
       <c r="AW11" s="12">
-        <f>IF($B11="BLOCKED","Заблокировано: предыдущий уровень не разрешил новый полноценный уровень","")</f>
+        <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
       <c r="AX11" s="12">
@@ -8113,9 +8993,35 @@
         <f>IF($B11="BIG_SIDE",$V11*$AU11,0)</f>
         <v/>
       </c>
+      <c r="BA11" s="12">
+        <f>IF($AK11=TRUE,MAX(0,$AJ11-$BD11),IF($B11="BLOCKED",MAX(0,$BA10-$BD11),0))</f>
+        <v/>
+      </c>
+      <c r="BB11" s="12">
+        <f>IF($AK11=TRUE,MAX(0,$AG11-$BE11),IF($B11="BLOCKED",MAX(0,$BB10-$BE11),0))</f>
+        <v/>
+      </c>
+      <c r="BC11" s="12">
+        <f>$BA11+$BB11</f>
+        <v/>
+      </c>
+      <c r="BD11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ11"/>
+  <autoFilter ref="A1:BG11"/>
   <conditionalFormatting sqref="AQ2:AQ11">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$AQ2="WARNING"</formula>
@@ -8151,7 +9057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8397,6 +9303,134 @@
       </c>
       <c r="C15" s="3">
         <f>LOOKUP(2,1/(Calculator!AQ2:AQ11&lt;&gt;""),Calculator!AQ2:AQ11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Max DualTail Exposure</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>MAX DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="C16" s="3">
+        <f>MAX(Calculator!BC2:BC11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Final ActiveOldFarLot</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>last ActiveOldFarLot</t>
+        </is>
+      </c>
+      <c r="C17" s="3">
+        <f>LOOKUP(2,1/(Calculator!BA2:BA11&lt;&gt;""),Calculator!BA2:BA11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Final ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>last ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="C18" s="3">
+        <f>LOOKUP(2,1/(Calculator!BB2:BB11&lt;&gt;""),Calculator!BB2:BB11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Final DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>last DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="C19" s="3">
+        <f>LOOKUP(2,1/(Calculator!BC2:BC11&lt;&gt;""),Calculator!BC2:BC11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Manual Close PL</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SUM ManualClosePL</t>
+        </is>
+      </c>
+      <c r="C20" s="3">
+        <f>SUM(Calculator!BF2:BF11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Blocked Levels Count</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>COUNTIF Scenario BLOCKED</t>
+        </is>
+      </c>
+      <c r="C21" s="3">
+        <f>COUNTIF(Calculator!B2:B11,"BLOCKED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Stop Cleared Count</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>COUNTIF Status STOP_CLEARED</t>
+        </is>
+      </c>
+      <c r="C22" s="3">
+        <f>COUNTIF(Calculator!AQ2:AQ11,"STOP_CLEARED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Manual Ready Count</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>COUNTIF Status MANUAL_READY</t>
+        </is>
+      </c>
+      <c r="C23" s="3">
+        <f>COUNTIF(Calculator!AQ2:AQ11,"MANUAL_READY")</f>
         <v/>
       </c>
     </row>
@@ -8411,7 +9445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10103,8 +11137,638 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>T40</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL ActiveOldFarLot equals OldFarRemainLot</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL row</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot = OldFarRemainLot unless manual close</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>BA = AJ - ManualOldFarCloseLot</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>BA formula</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Старый хвост фиксируется в активном состоянии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>T41</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL ActiveNewFarLot equals NewFarStartLot</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL row</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot = NewFarStartLot unless manual close</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>BB = AG - ManualNewFarCloseLot</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>BB formula</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Новый хвост фиксируется отдельно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>T42</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot sums active tails</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Any DUAL/BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot = ActiveOldFarLot + ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>BC=BA+BB</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>BC formula</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Суммарная экспозиция двух хвостов не теряется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>T43</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Next BLOCKED keeps both tails</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Row after DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>ActiveOld/New copy previous active tails minus manual close</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>BA/BB previous carry</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>BA/BB blocked formulas</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Следующий заблокированный уровень сохраняет оба хвоста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>T44</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Second BLOCKED keeps both tails</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Second blocked row</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Old tail still present without manual close</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>BA persists</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>BA formula</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Старый хвост не исчезает во второй BLOCKED строке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>T45</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>OpenLotsAfter BLOCKED equals DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>OpenLotsAfter = DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>AC=BC</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>AC formula</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Открытые лоты после блокировки считаются по двум хвостам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>T46</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>MarginAfter BLOCKED from both tails</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>MarginAfter = DualTailTotalLot × MarginPerLot</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>AE=AC*MarginPerLot</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>AE formula</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Маржа не падает искусственно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>T47</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>BigLot zero in BLOCKED</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>BigLot = 0</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>G=0 when B=BLOCKED</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>G formula</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Новый Big не открывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>T48</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>SmallLot zero in BLOCKED</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>SmallLot = 0</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>J=0 when B=BLOCKED</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>J formula</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Новый Small не открывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>T49</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Status remains STOP while two tails active</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED with BA&gt;0 and BB&gt;0</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Status = STOP</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>AQ STOP</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>AQ formula</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Без ручного закрытия статус не OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>T50</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Old tail cannot disappear without manual close</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>ManualOldFarCloseLot=0</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot persists</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>BA current=BA previous</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>BA formula</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Старый хвост не обнуляется автоматически.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>T51</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>New tail cannot disappear without manual close</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>ManualNewFarCloseLot=0</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot persists</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>BB current=BB previous</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>BB formula</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Новый хвост не обнуляется автоматически.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>T52</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>ManualOldFarCloseLot reduces old tail</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Manual close input</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot = PreviousActiveOldFarLot - ManualOldFarCloseLot</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>BA=MAX(0,BAprev-BD)</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>BA formula</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Ручное закрытие уменьшает старый хвост.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>T53</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Full old-tail manual close creates MANUAL_READY</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>BA=0 and BB&gt;0</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Status = MANUAL_READY</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>AQ MANUAL_READY branch</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>AQ formula</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Один оставшийся хвост требует ручного разрешения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>T54</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>New level requires ManualAllowNewLevel YES</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>MANUAL_READY previous</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Next row BLOCKED unless ManualAllowNewLevel=YES</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>B checks BG="YES"</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>B formula</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Автоматический перезапуск запрещён без ручного разрешения.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H40"/>
+  <autoFilter ref="A1:H55"/>
   <conditionalFormatting sqref="D2:D18">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>$D2="FAIL"</formula>

--- a/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
+++ b/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="K2" s="13" t="n">
         <v>100</v>
@@ -1369,19 +1369,19 @@
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC2" s="12">
         <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AD2" s="12">
         <f>$AB2*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE2" s="12">
         <f>$AC2*Settings!$B$10</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="AF2" s="12">
         <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
@@ -1403,9 +1403,9 @@
         <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
-      <c r="AK2" s="12">
+      <c r="AK2" s="12" t="b">
         <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL2" s="12">
         <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
@@ -1423,13 +1423,13 @@
         <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP2" s="12">
+      <c r="AP2" s="12" t="str">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ2" s="12">
+        <v>YES</v>
+      </c>
+      <c r="AQ2" s="12" t="str">
         <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AR2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -1451,7 +1451,7 @@
         <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW2" s="12">
+      <c r="AW2" s="12" t="str">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -1469,15 +1469,15 @@
       </c>
       <c r="BA2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC2" s="12">
         <f>$BA2+$BB2</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD2" s="13" t="n">
         <v>0</v>
@@ -1498,9 +1498,9 @@
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="13" t="str">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"BIG_SIDE",IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="MANUAL_READY",$AQ2="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BIG_SIDE</v>
       </c>
       <c r="C3" s="13">
         <f>IF($B3="BLOCKED",$AF2,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),$AF2,IF($AP2="YES",$AF2,$C2)))</f>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H3" s="12">
         <f>IF($B3="BLOCKED","",$C3)</f>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="J3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="K3" s="13" t="n">
         <v>100</v>
@@ -1601,19 +1601,19 @@
       </c>
       <c r="AB3" s="12">
         <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC3" s="12">
         <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AD3" s="12">
         <f>$AB3*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE3" s="12">
         <f>$AC3*Settings!$B$10</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="AF3" s="12">
         <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
@@ -1635,9 +1635,9 @@
         <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
         <v/>
       </c>
-      <c r="AK3" s="12">
+      <c r="AK3" s="12" t="b">
         <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL3" s="12">
         <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
@@ -1655,13 +1655,13 @@
         <f>IF(OR($B3="BIG_SIDE",$B3="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP3" s="12">
+      <c r="AP3" s="12" t="str">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"YES",IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="STOP_CLEARED",$AQ3="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ3" s="12">
+        <v>YES</v>
+      </c>
+      <c r="AQ3" s="12" t="str">
         <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AR3" s="12">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -1683,7 +1683,7 @@
         <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW3" s="12">
+      <c r="AW3" s="12" t="str">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -1701,15 +1701,15 @@
       </c>
       <c r="BA3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC3" s="12">
         <f>$BA3+$BB3</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD3" s="13" t="n">
         <v>0</v>
@@ -1730,9 +1730,9 @@
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="13" t="str">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"SMALL_SIDE",IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="MANUAL_READY",$AQ3="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
-        <v/>
+        <v>SMALL_SIDE</v>
       </c>
       <c r="C4" s="13">
         <f>IF($B4="BLOCKED",$AF3,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),$AF3,IF($AP3="YES",$AF3,$C3)))</f>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="G4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($F4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="H4" s="12">
         <f>IF($B4="BLOCKED","",$C4)</f>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="J4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.38</v>
       </c>
       <c r="K4" s="13" t="n">
         <v>80</v>
@@ -1833,19 +1833,19 @@
       </c>
       <c r="AB4" s="12">
         <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC4" s="12">
         <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD4" s="12">
         <f>$AB4*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE4" s="12">
         <f>$AC4*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AG4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="AH4" s="13" t="inlineStr">
         <is>
@@ -1865,11 +1865,11 @@
       </c>
       <c r="AJ4" s="12">
         <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
-        <v/>
-      </c>
-      <c r="AK4" s="12">
+        <v>0.5216</v>
+      </c>
+      <c r="AK4" s="12" t="b">
         <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL4" s="12">
         <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
@@ -1887,13 +1887,13 @@
         <f>IF(OR($B4="BIG_SIDE",$B4="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP4" s="12">
+      <c r="AP4" s="12" t="str">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"YES",IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="STOP_CLEARED",$AQ4="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ4" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ4" s="12" t="str">
         <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>DUAL_TAIL</v>
       </c>
       <c r="AR4" s="12">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -1915,7 +1915,7 @@
         <f>IF($B4="SMALL_SIDE",IF($AH4="YES",$D4,IFERROR(MIN($D4,MAX(0,$AI4/$U4)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW4" s="12">
+      <c r="AW4" s="12" t="str">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -1933,15 +1933,15 @@
       </c>
       <c r="BA4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC4" s="12">
         <f>$BA4+$BB4</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD4" s="13" t="n">
         <v>0</v>
@@ -1962,9 +1962,9 @@
       <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="13" t="str">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"BIG_SIDE",IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="MANUAL_READY",$AQ4="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C5" s="13">
         <f>IF($B5="BLOCKED",$AF4,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),$AF4,IF($AP4="YES",$AF4,$C4)))</f>
@@ -1980,11 +1980,11 @@
       </c>
       <c r="F5" s="12">
         <f>IF($B5="BLOCKED",0,MAX(0,$D5*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($F5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H5" s="12">
         <f>IF($B5="BLOCKED","",$C5)</f>
@@ -1992,11 +1992,11 @@
       </c>
       <c r="I5" s="12">
         <f>IF($B5="BLOCKED",0,MAX(0,$G5*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K5" s="13" t="n">
         <v>100</v>
@@ -2009,19 +2009,19 @@
       </c>
       <c r="N5" s="14">
         <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O5" s="14">
         <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P5" s="15">
         <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q5" s="15">
         <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R5" s="15">
         <f>$AT5*$AU5</f>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="T5" s="12">
         <f>IF(AND($B5="BIG_SIDE",$AX5&gt;0),$AX5*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U5" s="12">
         <f>MAX(0,$M5*Settings!$B$9)</f>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="V5" s="12">
         <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W5" s="12">
         <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="X5" s="19">
         <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y5" s="19">
         <f>$Y4+$X5</f>
@@ -2065,19 +2065,19 @@
       </c>
       <c r="AB5" s="12">
         <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC5" s="12">
         <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD5" s="12">
         <f>$AB5*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE5" s="12">
         <f>$AC5*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF5" s="12">
         <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
@@ -2099,9 +2099,9 @@
         <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
         <v/>
       </c>
-      <c r="AK5" s="12">
+      <c r="AK5" s="12" t="b">
         <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL5" s="12">
         <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
@@ -2119,13 +2119,13 @@
         <f>IF(OR($B5="BIG_SIDE",$B5="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP5" s="12">
+      <c r="AP5" s="12" t="str">
         <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"YES",IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="STOP_CLEARED",$AQ5="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ5" s="12" t="str">
         <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR5" s="12">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="AS5" s="20">
         <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT5" s="12">
         <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
@@ -2147,9 +2147,9 @@
         <f>IF($B5="SMALL_SIDE",IF($AH5="YES",$D5,IFERROR(MIN($D5,MAX(0,$AI5/$U5)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW5" s="12">
+      <c r="AW5" s="12" t="str">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX5" s="12">
         <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
@@ -2165,15 +2165,15 @@
       </c>
       <c r="BA5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AJ5-$BD5),IF($B5="BLOCKED",MAX(0,$BA4-$BD5),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AG5-$BE5),IF($B5="BLOCKED",MAX(0,$BB4-$BE5),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC5" s="12">
         <f>$BA5+$BB5</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD5" s="13" t="n">
         <v>0</v>
@@ -2194,9 +2194,9 @@
       <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="13" t="str">
         <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"BIG_SIDE",IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="MANUAL_READY",$AQ5="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C6" s="13">
         <f>IF($B6="BLOCKED",$AF5,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),$AF5,IF($AP5="YES",$AF5,$C5)))</f>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="F6" s="12">
         <f>IF($B6="BLOCKED",0,MAX(0,$D6*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G6" s="12">
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($F6/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" s="12">
         <f>IF($B6="BLOCKED","",$C6)</f>
@@ -2224,11 +2224,11 @@
       </c>
       <c r="I6" s="12">
         <f>IF($B6="BLOCKED",0,MAX(0,$G6*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J6" s="12">
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K6" s="13" t="n">
         <v>100</v>
@@ -2241,19 +2241,19 @@
       </c>
       <c r="N6" s="14">
         <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O6" s="14">
         <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P6" s="15">
         <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q6" s="15">
         <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R6" s="15">
         <f>$AT6*$AU6</f>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="T6" s="12">
         <f>IF(AND($B6="BIG_SIDE",$AX6&gt;0),$AX6*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U6" s="12">
         <f>MAX(0,$M6*Settings!$B$9)</f>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="V6" s="12">
         <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W6" s="12">
         <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="X6" s="19">
         <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y6" s="19">
         <f>$Y5+$X6</f>
@@ -2297,19 +2297,19 @@
       </c>
       <c r="AB6" s="12">
         <f>IF($B6="BLOCKED",$BC6,$D6+$G6+$J6)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC6" s="12">
         <f>IF($B6="BLOCKED",$BC6,IF($B6="BIG_SIDE",$W6,IF($AK6=TRUE,$BC6,$AG6)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD6" s="12">
         <f>$AB6*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE6" s="12">
         <f>$AC6*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF6" s="12">
         <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
@@ -2331,9 +2331,9 @@
         <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
-      <c r="AK6" s="12">
+      <c r="AK6" s="12" t="b">
         <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL6" s="12">
         <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
@@ -2351,13 +2351,13 @@
         <f>IF(OR($B6="BIG_SIDE",$B6="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP6" s="12">
+      <c r="AP6" s="12" t="str">
         <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"YES",IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="STOP_CLEARED",$AQ6="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ6" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ6" s="12" t="str">
         <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR6" s="12">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AS6" s="20">
         <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT6" s="12">
         <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
@@ -2379,9 +2379,9 @@
         <f>IF($B6="SMALL_SIDE",IF($AH6="YES",$D6,IFERROR(MIN($D6,MAX(0,$AI6/$U6)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW6" s="12">
+      <c r="AW6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX6" s="12">
         <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
@@ -2397,15 +2397,15 @@
       </c>
       <c r="BA6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AJ6-$BD6),IF($B6="BLOCKED",MAX(0,$BA5-$BD6),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AG6-$BE6),IF($B6="BLOCKED",MAX(0,$BB5-$BE6),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC6" s="12">
         <f>$BA6+$BB6</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD6" s="13" t="n">
         <v>0</v>
@@ -2426,9 +2426,9 @@
       <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="13" t="str">
         <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"SMALL_SIDE",IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="MANUAL_READY",$AQ6="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C7" s="13">
         <f>IF($B7="BLOCKED",$AF6,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),$AF6,IF($AP6="YES",$AF6,$C6)))</f>
@@ -2444,11 +2444,11 @@
       </c>
       <c r="F7" s="12">
         <f>IF($B7="BLOCKED",0,MAX(0,$D7*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G7" s="12">
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($F7/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H7" s="12">
         <f>IF($B7="BLOCKED","",$C7)</f>
@@ -2456,11 +2456,11 @@
       </c>
       <c r="I7" s="12">
         <f>IF($B7="BLOCKED",0,MAX(0,$G7*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J7" s="12">
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K7" s="13" t="n">
         <v>80</v>
@@ -2473,19 +2473,19 @@
       </c>
       <c r="N7" s="14">
         <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O7" s="14">
         <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P7" s="15">
         <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q7" s="15">
         <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R7" s="15">
         <f>$AT7*$AU7</f>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="T7" s="12">
         <f>IF(AND($B7="BIG_SIDE",$AX7&gt;0),$AX7*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U7" s="12">
         <f>MAX(0,$M7*Settings!$B$9)</f>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="V7" s="12">
         <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W7" s="12">
         <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="X7" s="19">
         <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y7" s="19">
         <f>$Y6+$X7</f>
@@ -2529,19 +2529,19 @@
       </c>
       <c r="AB7" s="12">
         <f>IF($B7="BLOCKED",$BC7,$D7+$G7+$J7)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC7" s="12">
         <f>IF($B7="BLOCKED",$BC7,IF($B7="BIG_SIDE",$W7,IF($AK7=TRUE,$BC7,$AG7)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD7" s="12">
         <f>$AB7*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE7" s="12">
         <f>$AC7*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF7" s="12">
         <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
@@ -2563,9 +2563,9 @@
         <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
-      <c r="AK7" s="12">
+      <c r="AK7" s="12" t="b">
         <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL7" s="12">
         <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
@@ -2583,13 +2583,13 @@
         <f>IF(OR($B7="BIG_SIDE",$B7="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP7" s="12">
+      <c r="AP7" s="12" t="str">
         <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"YES",IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="STOP_CLEARED",$AQ7="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ7" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ7" s="12" t="str">
         <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR7" s="12">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AS7" s="20">
         <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT7" s="12">
         <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
@@ -2611,9 +2611,9 @@
         <f>IF($B7="SMALL_SIDE",IF($AH7="YES",$D7,IFERROR(MIN($D7,MAX(0,$AI7/$U7)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW7" s="12">
+      <c r="AW7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX7" s="12">
         <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
@@ -2629,15 +2629,15 @@
       </c>
       <c r="BA7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AJ7-$BD7),IF($B7="BLOCKED",MAX(0,$BA6-$BD7),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AG7-$BE7),IF($B7="BLOCKED",MAX(0,$BB6-$BE7),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC7" s="12">
         <f>$BA7+$BB7</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD7" s="13" t="n">
         <v>0</v>
@@ -2658,9 +2658,9 @@
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="13" t="str">
         <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"BIG_SIDE",IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="MANUAL_READY",$AQ7="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C8" s="13">
         <f>IF($B8="BLOCKED",$AF7,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),$AF7,IF($AP7="YES",$AF7,$C7)))</f>
@@ -2676,11 +2676,11 @@
       </c>
       <c r="F8" s="12">
         <f>IF($B8="BLOCKED",0,MAX(0,$D8*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G8" s="12">
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($F8/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H8" s="12">
         <f>IF($B8="BLOCKED","",$C8)</f>
@@ -2688,11 +2688,11 @@
       </c>
       <c r="I8" s="12">
         <f>IF($B8="BLOCKED",0,MAX(0,$G8*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J8" s="12">
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K8" s="13" t="n">
         <v>100</v>
@@ -2705,19 +2705,19 @@
       </c>
       <c r="N8" s="14">
         <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O8" s="14">
         <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P8" s="15">
         <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q8" s="15">
         <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R8" s="15">
         <f>$AT8*$AU8</f>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="T8" s="12">
         <f>IF(AND($B8="BIG_SIDE",$AX8&gt;0),$AX8*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U8" s="12">
         <f>MAX(0,$M8*Settings!$B$9)</f>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="V8" s="12">
         <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W8" s="12">
         <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="X8" s="19">
         <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y8" s="19">
         <f>$Y7+$X8</f>
@@ -2761,19 +2761,19 @@
       </c>
       <c r="AB8" s="12">
         <f>IF($B8="BLOCKED",$BC8,$D8+$G8+$J8)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC8" s="12">
         <f>IF($B8="BLOCKED",$BC8,IF($B8="BIG_SIDE",$W8,IF($AK8=TRUE,$BC8,$AG8)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD8" s="12">
         <f>$AB8*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE8" s="12">
         <f>$AC8*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF8" s="12">
         <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
@@ -2795,9 +2795,9 @@
         <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
-      <c r="AK8" s="12">
+      <c r="AK8" s="12" t="b">
         <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL8" s="12">
         <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
@@ -2815,13 +2815,13 @@
         <f>IF(OR($B8="BIG_SIDE",$B8="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP8" s="12">
+      <c r="AP8" s="12" t="str">
         <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"YES",IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="STOP_CLEARED",$AQ8="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ8" s="12" t="str">
         <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR8" s="12">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AS8" s="20">
         <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT8" s="12">
         <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
@@ -2843,9 +2843,9 @@
         <f>IF($B8="SMALL_SIDE",IF($AH8="YES",$D8,IFERROR(MIN($D8,MAX(0,$AI8/$U8)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW8" s="12">
+      <c r="AW8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX8" s="12">
         <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
@@ -2861,15 +2861,15 @@
       </c>
       <c r="BA8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AJ8-$BD8),IF($B8="BLOCKED",MAX(0,$BA7-$BD8),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AG8-$BE8),IF($B8="BLOCKED",MAX(0,$BB7-$BE8),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC8" s="12">
         <f>$BA8+$BB8</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD8" s="13" t="n">
         <v>0</v>
@@ -2890,9 +2890,9 @@
       <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="13" t="str">
         <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"BIG_SIDE",IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="MANUAL_READY",$AQ8="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C9" s="13">
         <f>IF($B9="BLOCKED",$AF8,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),$AF8,IF($AP8="YES",$AF8,$C8)))</f>
@@ -2908,11 +2908,11 @@
       </c>
       <c r="F9" s="12">
         <f>IF($B9="BLOCKED",0,MAX(0,$D9*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G9" s="12">
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($F9/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H9" s="12">
         <f>IF($B9="BLOCKED","",$C9)</f>
@@ -2920,11 +2920,11 @@
       </c>
       <c r="I9" s="12">
         <f>IF($B9="BLOCKED",0,MAX(0,$G9*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J9" s="12">
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K9" s="13" t="n">
         <v>100</v>
@@ -2937,19 +2937,19 @@
       </c>
       <c r="N9" s="14">
         <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O9" s="14">
         <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P9" s="15">
         <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q9" s="15">
         <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R9" s="15">
         <f>$AT9*$AU9</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="T9" s="12">
         <f>IF(AND($B9="BIG_SIDE",$AX9&gt;0),$AX9*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U9" s="12">
         <f>MAX(0,$M9*Settings!$B$9)</f>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="V9" s="12">
         <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W9" s="12">
         <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="X9" s="19">
         <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y9" s="19">
         <f>$Y8+$X9</f>
@@ -2993,19 +2993,19 @@
       </c>
       <c r="AB9" s="12">
         <f>IF($B9="BLOCKED",$BC9,$D9+$G9+$J9)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC9" s="12">
         <f>IF($B9="BLOCKED",$BC9,IF($B9="BIG_SIDE",$W9,IF($AK9=TRUE,$BC9,$AG9)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD9" s="12">
         <f>$AB9*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE9" s="12">
         <f>$AC9*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF9" s="12">
         <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
@@ -3027,9 +3027,9 @@
         <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
-      <c r="AK9" s="12">
+      <c r="AK9" s="12" t="b">
         <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL9" s="12">
         <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
@@ -3047,13 +3047,13 @@
         <f>IF(OR($B9="BIG_SIDE",$B9="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP9" s="12">
+      <c r="AP9" s="12" t="str">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"YES",IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="STOP_CLEARED",$AQ9="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ9" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ9" s="12" t="str">
         <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR9" s="12">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="AS9" s="20">
         <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT9" s="12">
         <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
@@ -3075,9 +3075,9 @@
         <f>IF($B9="SMALL_SIDE",IF($AH9="YES",$D9,IFERROR(MIN($D9,MAX(0,$AI9/$U9)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW9" s="12">
+      <c r="AW9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX9" s="12">
         <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
@@ -3093,15 +3093,15 @@
       </c>
       <c r="BA9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AJ9-$BD9),IF($B9="BLOCKED",MAX(0,$BA8-$BD9),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AG9-$BE9),IF($B9="BLOCKED",MAX(0,$BB8-$BE9),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC9" s="12">
         <f>$BA9+$BB9</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD9" s="13" t="n">
         <v>0</v>
@@ -3122,9 +3122,9 @@
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="13" t="str">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"BIG_SIDE",IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="MANUAL_READY",$AQ9="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C10" s="13">
         <f>IF($B10="BLOCKED",$AF9,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),$AF9,IF($AP9="YES",$AF9,$C9)))</f>
@@ -3140,11 +3140,11 @@
       </c>
       <c r="F10" s="12">
         <f>IF($B10="BLOCKED",0,MAX(0,$D10*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G10" s="12">
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($F10/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H10" s="12">
         <f>IF($B10="BLOCKED","",$C10)</f>
@@ -3152,11 +3152,11 @@
       </c>
       <c r="I10" s="12">
         <f>IF($B10="BLOCKED",0,MAX(0,$G10*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J10" s="12">
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K10" s="13" t="n">
         <v>100</v>
@@ -3169,19 +3169,19 @@
       </c>
       <c r="N10" s="14">
         <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O10" s="14">
         <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P10" s="15">
         <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q10" s="15">
         <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R10" s="15">
         <f>$AT10*$AU10</f>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="T10" s="12">
         <f>IF(AND($B10="BIG_SIDE",$AX10&gt;0),$AX10*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U10" s="12">
         <f>MAX(0,$M10*Settings!$B$9)</f>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="V10" s="12">
         <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W10" s="12">
         <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="X10" s="19">
         <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y10" s="19">
         <f>$Y9+$X10</f>
@@ -3225,19 +3225,19 @@
       </c>
       <c r="AB10" s="12">
         <f>IF($B10="BLOCKED",$BC10,$D10+$G10+$J10)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC10" s="12">
         <f>IF($B10="BLOCKED",$BC10,IF($B10="BIG_SIDE",$W10,IF($AK10=TRUE,$BC10,$AG10)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD10" s="12">
         <f>$AB10*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE10" s="12">
         <f>$AC10*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF10" s="12">
         <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
@@ -3259,9 +3259,9 @@
         <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
-      <c r="AK10" s="12">
+      <c r="AK10" s="12" t="b">
         <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL10" s="12">
         <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
@@ -3279,13 +3279,13 @@
         <f>IF(OR($B10="BIG_SIDE",$B10="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP10" s="12">
+      <c r="AP10" s="12" t="str">
         <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"YES",IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="STOP_CLEARED",$AQ10="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ10" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ10" s="12" t="str">
         <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR10" s="12">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AS10" s="20">
         <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT10" s="12">
         <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
@@ -3307,9 +3307,9 @@
         <f>IF($B10="SMALL_SIDE",IF($AH10="YES",$D10,IFERROR(MIN($D10,MAX(0,$AI10/$U10)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW10" s="12">
+      <c r="AW10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX10" s="12">
         <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
@@ -3325,15 +3325,15 @@
       </c>
       <c r="BA10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AJ10-$BD10),IF($B10="BLOCKED",MAX(0,$BA9-$BD10),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AG10-$BE10),IF($B10="BLOCKED",MAX(0,$BB9-$BE10),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC10" s="12">
         <f>$BA10+$BB10</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD10" s="13" t="n">
         <v>0</v>
@@ -3354,9 +3354,9 @@
       <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="13" t="str">
         <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"BIG_SIDE",IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="MANUAL_READY",$AQ10="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C11" s="13">
         <f>IF($B11="BLOCKED",$AF10,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),$AF10,IF($AP10="YES",$AF10,$C10)))</f>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="F11" s="12">
         <f>IF($B11="BLOCKED",0,MAX(0,$D11*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G11" s="12">
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($F11/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H11" s="12">
         <f>IF($B11="BLOCKED","",$C11)</f>
@@ -3384,11 +3384,11 @@
       </c>
       <c r="I11" s="12">
         <f>IF($B11="BLOCKED",0,MAX(0,$G11*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J11" s="12">
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K11" s="13" t="n">
         <v>100</v>
@@ -3401,19 +3401,19 @@
       </c>
       <c r="N11" s="14">
         <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O11" s="14">
         <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P11" s="15">
         <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q11" s="15">
         <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R11" s="15">
         <f>$AT11*$AU11</f>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="T11" s="12">
         <f>IF(AND($B11="BIG_SIDE",$AX11&gt;0),$AX11*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U11" s="12">
         <f>MAX(0,$M11*Settings!$B$9)</f>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="V11" s="12">
         <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W11" s="12">
         <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="X11" s="19">
         <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y11" s="19">
         <f>$Y10+$X11</f>
@@ -3457,19 +3457,19 @@
       </c>
       <c r="AB11" s="12">
         <f>IF($B11="BLOCKED",$BC11,$D11+$G11+$J11)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC11" s="12">
         <f>IF($B11="BLOCKED",$BC11,IF($B11="BIG_SIDE",$W11,IF($AK11=TRUE,$BC11,$AG11)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD11" s="12">
         <f>$AB11*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE11" s="12">
         <f>$AC11*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF11" s="12">
         <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
@@ -3491,9 +3491,9 @@
         <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
-      <c r="AK11" s="12">
+      <c r="AK11" s="12" t="b">
         <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL11" s="12">
         <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
@@ -3511,13 +3511,13 @@
         <f>IF(OR($B11="BIG_SIDE",$B11="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP11" s="12">
+      <c r="AP11" s="12" t="str">
         <f>IF(AND($AQ11="MANUAL_READY",$BG11="YES"),"YES",IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP",$AQ11="STOP_CLEARED",$AQ11="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ11" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ11" s="12" t="str">
         <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR11" s="12">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AS11" s="20">
         <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT11" s="12">
         <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
@@ -3539,9 +3539,9 @@
         <f>IF($B11="SMALL_SIDE",IF($AH11="YES",$D11,IFERROR(MIN($D11,MAX(0,$AI11/$U11)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW11" s="12">
+      <c r="AW11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX11" s="12">
         <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
@@ -3557,15 +3557,15 @@
       </c>
       <c r="BA11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AJ11-$BD11),IF($B11="BLOCKED",MAX(0,$BA10-$BD11),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AG11-$BE11),IF($B11="BLOCKED",MAX(0,$BB10-$BE11),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC11" s="12">
         <f>$BA11+$BB11</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD11" s="13" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="K2" s="13" t="n">
         <v>100</v>
@@ -4088,19 +4088,19 @@
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC2" s="12">
         <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AD2" s="12">
         <f>$AB2*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE2" s="12">
         <f>$AC2*Settings!$B$10</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="AF2" s="12">
         <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
@@ -4122,9 +4122,9 @@
         <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
-      <c r="AK2" s="12">
+      <c r="AK2" s="12" t="b">
         <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL2" s="12">
         <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
@@ -4142,13 +4142,13 @@
         <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP2" s="12">
+      <c r="AP2" s="12" t="str">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ2" s="12">
+        <v>YES</v>
+      </c>
+      <c r="AQ2" s="12" t="str">
         <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AR2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -4170,7 +4170,7 @@
         <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW2" s="12">
+      <c r="AW2" s="12" t="str">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -4188,15 +4188,15 @@
       </c>
       <c r="BA2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC2" s="12">
         <f>$BA2+$BB2</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD2" s="13" t="n">
         <v>0</v>
@@ -4217,9 +4217,9 @@
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="13" t="str">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"BIG_SIDE",IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="MANUAL_READY",$AQ2="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BIG_SIDE</v>
       </c>
       <c r="C3" s="13">
         <f>IF($B3="BLOCKED",$AF2,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),$AF2,IF($AP2="YES",$AF2,$C2)))</f>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H3" s="12">
         <f>IF($B3="BLOCKED","",$C3)</f>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="K3" s="13" t="n">
         <v>100</v>
@@ -4320,19 +4320,19 @@
       </c>
       <c r="AB3" s="12">
         <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC3" s="12">
         <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AD3" s="12">
         <f>$AB3*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE3" s="12">
         <f>$AC3*Settings!$B$10</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="AF3" s="12">
         <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
@@ -4354,9 +4354,9 @@
         <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
         <v/>
       </c>
-      <c r="AK3" s="12">
+      <c r="AK3" s="12" t="b">
         <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL3" s="12">
         <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
@@ -4374,13 +4374,13 @@
         <f>IF(OR($B3="BIG_SIDE",$B3="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP3" s="12">
+      <c r="AP3" s="12" t="str">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"YES",IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="STOP_CLEARED",$AQ3="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ3" s="12">
+        <v>YES</v>
+      </c>
+      <c r="AQ3" s="12" t="str">
         <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AR3" s="12">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -4402,7 +4402,7 @@
         <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW3" s="12">
+      <c r="AW3" s="12" t="str">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -4420,15 +4420,15 @@
       </c>
       <c r="BA3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC3" s="12">
         <f>$BA3+$BB3</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD3" s="13" t="n">
         <v>0</v>
@@ -4449,9 +4449,9 @@
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="13" t="str">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"BIG_SIDE",IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="MANUAL_READY",$AQ3="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BIG_SIDE</v>
       </c>
       <c r="C4" s="13">
         <f>IF($B4="BLOCKED",$AF3,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),$AF3,IF($AP3="YES",$AF3,$C3)))</f>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="G4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($F4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H4" s="12">
         <f>IF($B4="BLOCKED","",$C4)</f>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="J4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="K4" s="13" t="n">
         <v>100</v>
@@ -4552,19 +4552,19 @@
       </c>
       <c r="AB4" s="12">
         <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC4" s="12">
         <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AD4" s="12">
         <f>$AB4*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE4" s="12">
         <f>$AC4*Settings!$B$10</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="AF4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
@@ -4586,9 +4586,9 @@
         <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
         <v/>
       </c>
-      <c r="AK4" s="12">
+      <c r="AK4" s="12" t="b">
         <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL4" s="12">
         <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
@@ -4606,13 +4606,13 @@
         <f>IF(OR($B4="BIG_SIDE",$B4="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP4" s="12">
+      <c r="AP4" s="12" t="str">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"YES",IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="STOP_CLEARED",$AQ4="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ4" s="12">
+        <v>YES</v>
+      </c>
+      <c r="AQ4" s="12" t="str">
         <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AR4" s="12">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -4634,7 +4634,7 @@
         <f>IF($B4="SMALL_SIDE",IF($AH4="YES",$D4,IFERROR(MIN($D4,MAX(0,$AI4/$U4)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW4" s="12">
+      <c r="AW4" s="12" t="str">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -4652,15 +4652,15 @@
       </c>
       <c r="BA4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC4" s="12">
         <f>$BA4+$BB4</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD4" s="13" t="n">
         <v>0</v>
@@ -4681,9 +4681,9 @@
       <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="13" t="str">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"SMALL_SIDE",IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="MANUAL_READY",$AQ4="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
-        <v/>
+        <v>SMALL_SIDE</v>
       </c>
       <c r="C5" s="13">
         <f>IF($B5="BLOCKED",$AF4,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),$AF4,IF($AP4="YES",$AF4,$C4)))</f>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="G5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($F5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="H5" s="12">
         <f>IF($B5="BLOCKED","",$C5)</f>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="J5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.38</v>
       </c>
       <c r="K5" s="13" t="n">
         <v>80</v>
@@ -4784,19 +4784,19 @@
       </c>
       <c r="AB5" s="12">
         <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC5" s="12">
         <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD5" s="12">
         <f>$AB5*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE5" s="12">
         <f>$AC5*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF5" s="12">
         <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="AG5" s="12">
         <f>IF($B5="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="AH5" s="13" t="inlineStr">
         <is>
@@ -4816,11 +4816,11 @@
       </c>
       <c r="AJ5" s="12">
         <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
-        <v/>
-      </c>
-      <c r="AK5" s="12">
+        <v>0.5216</v>
+      </c>
+      <c r="AK5" s="12" t="b">
         <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL5" s="12">
         <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
@@ -4838,13 +4838,13 @@
         <f>IF(OR($B5="BIG_SIDE",$B5="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP5" s="12">
+      <c r="AP5" s="12" t="str">
         <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"YES",IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="STOP_CLEARED",$AQ5="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ5" s="12" t="str">
         <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>DUAL_TAIL</v>
       </c>
       <c r="AR5" s="12">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -4866,7 +4866,7 @@
         <f>IF($B5="SMALL_SIDE",IF($AH5="YES",$D5,IFERROR(MIN($D5,MAX(0,$AI5/$U5)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW5" s="12">
+      <c r="AW5" s="12" t="str">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -4884,15 +4884,15 @@
       </c>
       <c r="BA5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AJ5-$BD5),IF($B5="BLOCKED",MAX(0,$BA4-$BD5),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AG5-$BE5),IF($B5="BLOCKED",MAX(0,$BB4-$BE5),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC5" s="12">
         <f>$BA5+$BB5</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD5" s="13" t="n">
         <v>0</v>
@@ -4913,9 +4913,9 @@
       <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="13" t="str">
         <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"BIG_SIDE",IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="MANUAL_READY",$AQ5="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C6" s="13">
         <f>IF($B6="BLOCKED",$AF5,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),$AF5,IF($AP5="YES",$AF5,$C5)))</f>
@@ -4931,11 +4931,11 @@
       </c>
       <c r="F6" s="12">
         <f>IF($B6="BLOCKED",0,MAX(0,$D6*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G6" s="12">
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($F6/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" s="12">
         <f>IF($B6="BLOCKED","",$C6)</f>
@@ -4943,11 +4943,11 @@
       </c>
       <c r="I6" s="12">
         <f>IF($B6="BLOCKED",0,MAX(0,$G6*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J6" s="12">
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K6" s="13" t="n">
         <v>100</v>
@@ -4960,19 +4960,19 @@
       </c>
       <c r="N6" s="14">
         <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O6" s="14">
         <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P6" s="15">
         <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q6" s="15">
         <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R6" s="15">
         <f>$AT6*$AU6</f>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="T6" s="12">
         <f>IF(AND($B6="BIG_SIDE",$AX6&gt;0),$AX6*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U6" s="12">
         <f>MAX(0,$M6*Settings!$B$9)</f>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="V6" s="12">
         <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W6" s="12">
         <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="X6" s="19">
         <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y6" s="19">
         <f>$Y5+$X6</f>
@@ -5016,19 +5016,19 @@
       </c>
       <c r="AB6" s="12">
         <f>IF($B6="BLOCKED",$BC6,$D6+$G6+$J6)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC6" s="12">
         <f>IF($B6="BLOCKED",$BC6,IF($B6="BIG_SIDE",$W6,IF($AK6=TRUE,$BC6,$AG6)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD6" s="12">
         <f>$AB6*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE6" s="12">
         <f>$AC6*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF6" s="12">
         <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
@@ -5050,9 +5050,9 @@
         <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
-      <c r="AK6" s="12">
+      <c r="AK6" s="12" t="b">
         <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL6" s="12">
         <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
@@ -5070,13 +5070,13 @@
         <f>IF(OR($B6="BIG_SIDE",$B6="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP6" s="12">
+      <c r="AP6" s="12" t="str">
         <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"YES",IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="STOP_CLEARED",$AQ6="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ6" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ6" s="12" t="str">
         <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR6" s="12">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="AS6" s="20">
         <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT6" s="12">
         <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
@@ -5098,9 +5098,9 @@
         <f>IF($B6="SMALL_SIDE",IF($AH6="YES",$D6,IFERROR(MIN($D6,MAX(0,$AI6/$U6)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW6" s="12">
+      <c r="AW6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX6" s="12">
         <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
@@ -5116,15 +5116,15 @@
       </c>
       <c r="BA6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AJ6-$BD6),IF($B6="BLOCKED",MAX(0,$BA5-$BD6),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AG6-$BE6),IF($B6="BLOCKED",MAX(0,$BB5-$BE6),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC6" s="12">
         <f>$BA6+$BB6</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD6" s="13" t="n">
         <v>0</v>
@@ -5145,9 +5145,9 @@
       <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="13" t="str">
         <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"BIG_SIDE",IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="MANUAL_READY",$AQ6="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C7" s="13">
         <f>IF($B7="BLOCKED",$AF6,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),$AF6,IF($AP6="YES",$AF6,$C6)))</f>
@@ -5163,11 +5163,11 @@
       </c>
       <c r="F7" s="12">
         <f>IF($B7="BLOCKED",0,MAX(0,$D7*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G7" s="12">
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($F7/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H7" s="12">
         <f>IF($B7="BLOCKED","",$C7)</f>
@@ -5175,11 +5175,11 @@
       </c>
       <c r="I7" s="12">
         <f>IF($B7="BLOCKED",0,MAX(0,$G7*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J7" s="12">
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K7" s="13" t="n">
         <v>100</v>
@@ -5192,19 +5192,19 @@
       </c>
       <c r="N7" s="14">
         <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O7" s="14">
         <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P7" s="15">
         <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q7" s="15">
         <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R7" s="15">
         <f>$AT7*$AU7</f>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="T7" s="12">
         <f>IF(AND($B7="BIG_SIDE",$AX7&gt;0),$AX7*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U7" s="12">
         <f>MAX(0,$M7*Settings!$B$9)</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="V7" s="12">
         <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W7" s="12">
         <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="X7" s="19">
         <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y7" s="19">
         <f>$Y6+$X7</f>
@@ -5248,19 +5248,19 @@
       </c>
       <c r="AB7" s="12">
         <f>IF($B7="BLOCKED",$BC7,$D7+$G7+$J7)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC7" s="12">
         <f>IF($B7="BLOCKED",$BC7,IF($B7="BIG_SIDE",$W7,IF($AK7=TRUE,$BC7,$AG7)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD7" s="12">
         <f>$AB7*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE7" s="12">
         <f>$AC7*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF7" s="12">
         <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
@@ -5282,9 +5282,9 @@
         <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
-      <c r="AK7" s="12">
+      <c r="AK7" s="12" t="b">
         <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL7" s="12">
         <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
@@ -5302,13 +5302,13 @@
         <f>IF(OR($B7="BIG_SIDE",$B7="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP7" s="12">
+      <c r="AP7" s="12" t="str">
         <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"YES",IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="STOP_CLEARED",$AQ7="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ7" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ7" s="12" t="str">
         <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR7" s="12">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="AS7" s="20">
         <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT7" s="12">
         <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
@@ -5330,9 +5330,9 @@
         <f>IF($B7="SMALL_SIDE",IF($AH7="YES",$D7,IFERROR(MIN($D7,MAX(0,$AI7/$U7)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW7" s="12">
+      <c r="AW7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX7" s="12">
         <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
@@ -5348,15 +5348,15 @@
       </c>
       <c r="BA7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AJ7-$BD7),IF($B7="BLOCKED",MAX(0,$BA6-$BD7),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AG7-$BE7),IF($B7="BLOCKED",MAX(0,$BB6-$BE7),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC7" s="12">
         <f>$BA7+$BB7</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD7" s="13" t="n">
         <v>0</v>
@@ -5377,9 +5377,9 @@
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="13" t="str">
         <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"BIG_SIDE",IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="MANUAL_READY",$AQ7="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C8" s="13">
         <f>IF($B8="BLOCKED",$AF7,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),$AF7,IF($AP7="YES",$AF7,$C7)))</f>
@@ -5395,11 +5395,11 @@
       </c>
       <c r="F8" s="12">
         <f>IF($B8="BLOCKED",0,MAX(0,$D8*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G8" s="12">
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($F8/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H8" s="12">
         <f>IF($B8="BLOCKED","",$C8)</f>
@@ -5407,11 +5407,11 @@
       </c>
       <c r="I8" s="12">
         <f>IF($B8="BLOCKED",0,MAX(0,$G8*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J8" s="12">
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K8" s="13" t="n">
         <v>100</v>
@@ -5424,19 +5424,19 @@
       </c>
       <c r="N8" s="14">
         <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O8" s="14">
         <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P8" s="15">
         <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q8" s="15">
         <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R8" s="15">
         <f>$AT8*$AU8</f>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="T8" s="12">
         <f>IF(AND($B8="BIG_SIDE",$AX8&gt;0),$AX8*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U8" s="12">
         <f>MAX(0,$M8*Settings!$B$9)</f>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="V8" s="12">
         <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W8" s="12">
         <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="X8" s="19">
         <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y8" s="19">
         <f>$Y7+$X8</f>
@@ -5480,19 +5480,19 @@
       </c>
       <c r="AB8" s="12">
         <f>IF($B8="BLOCKED",$BC8,$D8+$G8+$J8)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC8" s="12">
         <f>IF($B8="BLOCKED",$BC8,IF($B8="BIG_SIDE",$W8,IF($AK8=TRUE,$BC8,$AG8)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD8" s="12">
         <f>$AB8*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE8" s="12">
         <f>$AC8*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF8" s="12">
         <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
@@ -5514,9 +5514,9 @@
         <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
-      <c r="AK8" s="12">
+      <c r="AK8" s="12" t="b">
         <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL8" s="12">
         <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
@@ -5534,13 +5534,13 @@
         <f>IF(OR($B8="BIG_SIDE",$B8="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP8" s="12">
+      <c r="AP8" s="12" t="str">
         <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"YES",IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="STOP_CLEARED",$AQ8="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ8" s="12" t="str">
         <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR8" s="12">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AS8" s="20">
         <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT8" s="12">
         <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
@@ -5562,9 +5562,9 @@
         <f>IF($B8="SMALL_SIDE",IF($AH8="YES",$D8,IFERROR(MIN($D8,MAX(0,$AI8/$U8)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW8" s="12">
+      <c r="AW8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX8" s="12">
         <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
@@ -5580,15 +5580,15 @@
       </c>
       <c r="BA8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AJ8-$BD8),IF($B8="BLOCKED",MAX(0,$BA7-$BD8),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AG8-$BE8),IF($B8="BLOCKED",MAX(0,$BB7-$BE8),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC8" s="12">
         <f>$BA8+$BB8</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD8" s="13" t="n">
         <v>0</v>
@@ -5609,9 +5609,9 @@
       <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="13" t="str">
         <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"SMALL_SIDE",IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="MANUAL_READY",$AQ8="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C9" s="13">
         <f>IF($B9="BLOCKED",$AF8,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),$AF8,IF($AP8="YES",$AF8,$C8)))</f>
@@ -5627,11 +5627,11 @@
       </c>
       <c r="F9" s="12">
         <f>IF($B9="BLOCKED",0,MAX(0,$D9*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G9" s="12">
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($F9/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H9" s="12">
         <f>IF($B9="BLOCKED","",$C9)</f>
@@ -5639,11 +5639,11 @@
       </c>
       <c r="I9" s="12">
         <f>IF($B9="BLOCKED",0,MAX(0,$G9*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J9" s="12">
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K9" s="13" t="n">
         <v>80</v>
@@ -5656,19 +5656,19 @@
       </c>
       <c r="N9" s="14">
         <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O9" s="14">
         <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P9" s="15">
         <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q9" s="15">
         <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R9" s="15">
         <f>$AT9*$AU9</f>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="T9" s="12">
         <f>IF(AND($B9="BIG_SIDE",$AX9&gt;0),$AX9*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U9" s="12">
         <f>MAX(0,$M9*Settings!$B$9)</f>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="V9" s="12">
         <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W9" s="12">
         <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="X9" s="19">
         <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y9" s="19">
         <f>$Y8+$X9</f>
@@ -5712,19 +5712,19 @@
       </c>
       <c r="AB9" s="12">
         <f>IF($B9="BLOCKED",$BC9,$D9+$G9+$J9)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC9" s="12">
         <f>IF($B9="BLOCKED",$BC9,IF($B9="BIG_SIDE",$W9,IF($AK9=TRUE,$BC9,$AG9)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD9" s="12">
         <f>$AB9*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE9" s="12">
         <f>$AC9*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF9" s="12">
         <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
@@ -5746,9 +5746,9 @@
         <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
-      <c r="AK9" s="12">
+      <c r="AK9" s="12" t="b">
         <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL9" s="12">
         <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
@@ -5766,13 +5766,13 @@
         <f>IF(OR($B9="BIG_SIDE",$B9="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP9" s="12">
+      <c r="AP9" s="12" t="str">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"YES",IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="STOP_CLEARED",$AQ9="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ9" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ9" s="12" t="str">
         <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR9" s="12">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AS9" s="20">
         <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT9" s="12">
         <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
@@ -5794,9 +5794,9 @@
         <f>IF($B9="SMALL_SIDE",IF($AH9="YES",$D9,IFERROR(MIN($D9,MAX(0,$AI9/$U9)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW9" s="12">
+      <c r="AW9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX9" s="12">
         <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
@@ -5812,15 +5812,15 @@
       </c>
       <c r="BA9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AJ9-$BD9),IF($B9="BLOCKED",MAX(0,$BA8-$BD9),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AG9-$BE9),IF($B9="BLOCKED",MAX(0,$BB8-$BE9),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC9" s="12">
         <f>$BA9+$BB9</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD9" s="13" t="n">
         <v>0</v>
@@ -5841,9 +5841,9 @@
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="13" t="str">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"BIG_SIDE",IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="MANUAL_READY",$AQ9="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C10" s="13">
         <f>IF($B10="BLOCKED",$AF9,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),$AF9,IF($AP9="YES",$AF9,$C9)))</f>
@@ -5859,11 +5859,11 @@
       </c>
       <c r="F10" s="12">
         <f>IF($B10="BLOCKED",0,MAX(0,$D10*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G10" s="12">
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($F10/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H10" s="12">
         <f>IF($B10="BLOCKED","",$C10)</f>
@@ -5871,11 +5871,11 @@
       </c>
       <c r="I10" s="12">
         <f>IF($B10="BLOCKED",0,MAX(0,$G10*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J10" s="12">
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K10" s="13" t="n">
         <v>100</v>
@@ -5888,19 +5888,19 @@
       </c>
       <c r="N10" s="14">
         <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O10" s="14">
         <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P10" s="15">
         <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q10" s="15">
         <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R10" s="15">
         <f>$AT10*$AU10</f>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="T10" s="12">
         <f>IF(AND($B10="BIG_SIDE",$AX10&gt;0),$AX10*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U10" s="12">
         <f>MAX(0,$M10*Settings!$B$9)</f>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="V10" s="12">
         <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W10" s="12">
         <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="X10" s="19">
         <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y10" s="19">
         <f>$Y9+$X10</f>
@@ -5944,19 +5944,19 @@
       </c>
       <c r="AB10" s="12">
         <f>IF($B10="BLOCKED",$BC10,$D10+$G10+$J10)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC10" s="12">
         <f>IF($B10="BLOCKED",$BC10,IF($B10="BIG_SIDE",$W10,IF($AK10=TRUE,$BC10,$AG10)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD10" s="12">
         <f>$AB10*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE10" s="12">
         <f>$AC10*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF10" s="12">
         <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
@@ -5978,9 +5978,9 @@
         <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
-      <c r="AK10" s="12">
+      <c r="AK10" s="12" t="b">
         <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL10" s="12">
         <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
@@ -5998,13 +5998,13 @@
         <f>IF(OR($B10="BIG_SIDE",$B10="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP10" s="12">
+      <c r="AP10" s="12" t="str">
         <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"YES",IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="STOP_CLEARED",$AQ10="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ10" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ10" s="12" t="str">
         <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR10" s="12">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="AS10" s="20">
         <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT10" s="12">
         <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
@@ -6026,9 +6026,9 @@
         <f>IF($B10="SMALL_SIDE",IF($AH10="YES",$D10,IFERROR(MIN($D10,MAX(0,$AI10/$U10)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW10" s="12">
+      <c r="AW10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX10" s="12">
         <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
@@ -6044,15 +6044,15 @@
       </c>
       <c r="BA10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AJ10-$BD10),IF($B10="BLOCKED",MAX(0,$BA9-$BD10),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AG10-$BE10),IF($B10="BLOCKED",MAX(0,$BB9-$BE10),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC10" s="12">
         <f>$BA10+$BB10</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD10" s="13" t="n">
         <v>0</v>
@@ -6073,9 +6073,9 @@
       <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="13" t="str">
         <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"BIG_SIDE",IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="MANUAL_READY",$AQ10="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C11" s="13">
         <f>IF($B11="BLOCKED",$AF10,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),$AF10,IF($AP10="YES",$AF10,$C10)))</f>
@@ -6091,11 +6091,11 @@
       </c>
       <c r="F11" s="12">
         <f>IF($B11="BLOCKED",0,MAX(0,$D11*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G11" s="12">
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($F11/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H11" s="12">
         <f>IF($B11="BLOCKED","",$C11)</f>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="I11" s="12">
         <f>IF($B11="BLOCKED",0,MAX(0,$G11*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J11" s="12">
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K11" s="13" t="n">
         <v>100</v>
@@ -6120,19 +6120,19 @@
       </c>
       <c r="N11" s="14">
         <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O11" s="14">
         <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P11" s="15">
         <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q11" s="15">
         <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R11" s="15">
         <f>$AT11*$AU11</f>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="T11" s="12">
         <f>IF(AND($B11="BIG_SIDE",$AX11&gt;0),$AX11*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U11" s="12">
         <f>MAX(0,$M11*Settings!$B$9)</f>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="V11" s="12">
         <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W11" s="12">
         <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="X11" s="19">
         <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y11" s="19">
         <f>$Y10+$X11</f>
@@ -6176,19 +6176,19 @@
       </c>
       <c r="AB11" s="12">
         <f>IF($B11="BLOCKED",$BC11,$D11+$G11+$J11)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AC11" s="12">
         <f>IF($B11="BLOCKED",$BC11,IF($B11="BIG_SIDE",$W11,IF($AK11=TRUE,$BC11,$AG11)))</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="AD11" s="12">
         <f>$AB11*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AE11" s="12">
         <f>$AC11*Settings!$B$10</f>
-        <v/>
+        <v>989.6</v>
       </c>
       <c r="AF11" s="12">
         <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
@@ -6210,9 +6210,9 @@
         <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
-      <c r="AK11" s="12">
+      <c r="AK11" s="12" t="b">
         <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL11" s="12">
         <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
@@ -6230,13 +6230,13 @@
         <f>IF(OR($B11="BIG_SIDE",$B11="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP11" s="12">
+      <c r="AP11" s="12" t="str">
         <f>IF(AND($AQ11="MANUAL_READY",$BG11="YES"),"YES",IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP",$AQ11="STOP_CLEARED",$AQ11="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ11" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ11" s="12" t="str">
         <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR11" s="12">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AS11" s="20">
         <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT11" s="12">
         <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
@@ -6258,9 +6258,9 @@
         <f>IF($B11="SMALL_SIDE",IF($AH11="YES",$D11,IFERROR(MIN($D11,MAX(0,$AI11/$U11)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW11" s="12">
+      <c r="AW11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX11" s="12">
         <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
@@ -6276,15 +6276,15 @@
       </c>
       <c r="BA11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AJ11-$BD11),IF($B11="BLOCKED",MAX(0,$BA10-$BD11),0))</f>
-        <v/>
+        <v>0.5216</v>
       </c>
       <c r="BB11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AG11-$BE11),IF($B11="BLOCKED",MAX(0,$BB10-$BE11),0))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="BC11" s="12">
         <f>$BA11+$BB11</f>
-        <v/>
+        <v>0.9896</v>
       </c>
       <c r="BD11" s="13" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="K2" s="13" t="n">
         <v>100</v>
@@ -6807,19 +6807,19 @@
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC2" s="12">
         <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AD2" s="12">
         <f>$AB2*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE2" s="12">
         <f>$AC2*Settings!$B$10</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="AF2" s="12">
         <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
@@ -6841,9 +6841,9 @@
         <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
-      <c r="AK2" s="12">
+      <c r="AK2" s="12" t="b">
         <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL2" s="12">
         <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
@@ -6861,13 +6861,13 @@
         <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP2" s="12">
+      <c r="AP2" s="12" t="str">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ2" s="12">
+        <v>YES</v>
+      </c>
+      <c r="AQ2" s="12" t="str">
         <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AR2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -6889,7 +6889,7 @@
         <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW2" s="12">
+      <c r="AW2" s="12" t="str">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -6907,15 +6907,15 @@
       </c>
       <c r="BA2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BB2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BC2" s="12">
         <f>$BA2+$BB2</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BD2" s="13" t="n">
         <v>0</v>
@@ -6936,9 +6936,9 @@
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="13" t="str">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"SMALL_SIDE",IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="MANUAL_READY",$AQ2="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
-        <v/>
+        <v>SMALL_SIDE</v>
       </c>
       <c r="C3" s="13">
         <f>IF($B3="BLOCKED",$AF2,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),$AF2,IF($AP2="YES",$AF2,$C2)))</f>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="G3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="H3" s="12">
         <f>IF($B3="BLOCKED","",$C3)</f>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="J3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0.38</v>
       </c>
       <c r="K3" s="13" t="n">
         <v>80</v>
@@ -7039,19 +7039,19 @@
       </c>
       <c r="AB3" s="12">
         <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="AC3" s="12">
         <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD3" s="12">
         <f>$AB3*Settings!$B$10</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="AE3" s="12">
         <f>$AC3*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF3" s="12">
         <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AG3" s="12">
         <f>IF($B3="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="AH3" s="13" t="inlineStr">
         <is>
@@ -7071,11 +7071,11 @@
       </c>
       <c r="AJ3" s="12">
         <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
-        <v/>
-      </c>
-      <c r="AK3" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="AK3" s="12" t="b">
         <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL3" s="12">
         <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
@@ -7093,13 +7093,13 @@
         <f>IF(OR($B3="BIG_SIDE",$B3="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP3" s="12">
+      <c r="AP3" s="12" t="str">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"YES",IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="STOP_CLEARED",$AQ3="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ3" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ3" s="12" t="str">
         <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>DUAL_TAIL</v>
       </c>
       <c r="AR3" s="12">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -7121,7 +7121,7 @@
         <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW3" s="12">
+      <c r="AW3" s="12" t="str">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -7139,15 +7139,15 @@
       </c>
       <c r="BA3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC3" s="12">
         <f>$BA3+$BB3</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD3" s="13" t="n">
         <v>0</v>
@@ -7168,9 +7168,9 @@
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="13" t="str">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"BIG_SIDE",IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="MANUAL_READY",$AQ3="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C4" s="13">
         <f>IF($B4="BLOCKED",$AF3,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),$AF3,IF($AP3="YES",$AF3,$C3)))</f>
@@ -7186,11 +7186,11 @@
       </c>
       <c r="F4" s="12">
         <f>IF($B4="BLOCKED",0,MAX(0,$D4*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($F4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H4" s="12">
         <f>IF($B4="BLOCKED","",$C4)</f>
@@ -7198,11 +7198,11 @@
       </c>
       <c r="I4" s="12">
         <f>IF($B4="BLOCKED",0,MAX(0,$G4*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K4" s="13" t="n">
         <v>100</v>
@@ -7215,19 +7215,19 @@
       </c>
       <c r="N4" s="14">
         <f>IF($B4="BIG_SIDE",$G4*MAX(0,$K4)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O4" s="14">
         <f>IF($B4="SMALL_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P4" s="15">
         <f>IF($B4="BIG_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q4" s="15">
         <f>IF($B4="SMALL_SIDE",$AL4*ABS($K4)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R4" s="15">
         <f>$AT4*$AU4</f>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="T4" s="12">
         <f>IF(AND($B4="BIG_SIDE",$AX4&gt;0),$AX4*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U4" s="12">
         <f>MAX(0,$M4*Settings!$B$9)</f>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="V4" s="12">
         <f>IF($B4="BIG_SIDE",IFERROR(MIN($D4,MAX(0,$T4/$U4)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W4" s="12">
         <f>IF($B4="BIG_SIDE",MAX(0,$D4-$V4),$AJ4)</f>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="X4" s="19">
         <f>IF($B4="BIG_SIDE",IF($AX4&gt;0,$AX4-$AS4,0),IF($S4&gt;0,$S4*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y4" s="19">
         <f>$Y3+$X4</f>
@@ -7271,19 +7271,19 @@
       </c>
       <c r="AB4" s="12">
         <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AC4" s="12">
         <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD4" s="12">
         <f>$AB4*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AE4" s="12">
         <f>$AC4*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
@@ -7305,9 +7305,9 @@
         <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
         <v/>
       </c>
-      <c r="AK4" s="12">
+      <c r="AK4" s="12" t="b">
         <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL4" s="12">
         <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
@@ -7325,13 +7325,13 @@
         <f>IF(OR($B4="BIG_SIDE",$B4="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP4" s="12">
+      <c r="AP4" s="12" t="str">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"YES",IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="STOP_CLEARED",$AQ4="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ4" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ4" s="12" t="str">
         <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR4" s="12">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AS4" s="20">
         <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT4" s="12">
         <f>IF($B4="BIG_SIDE",$G4+$J4+$V4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
@@ -7353,9 +7353,9 @@
         <f>IF($B4="SMALL_SIDE",IF($AH4="YES",$D4,IFERROR(MIN($D4,MAX(0,$AI4/$U4)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW4" s="12">
+      <c r="AW4" s="12" t="str">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX4" s="12">
         <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
@@ -7371,15 +7371,15 @@
       </c>
       <c r="BA4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC4" s="12">
         <f>$BA4+$BB4</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD4" s="13" t="n">
         <v>0</v>
@@ -7400,9 +7400,9 @@
       <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="13" t="str">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"BIG_SIDE",IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="MANUAL_READY",$AQ4="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C5" s="13">
         <f>IF($B5="BLOCKED",$AF4,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),$AF4,IF($AP4="YES",$AF4,$C4)))</f>
@@ -7418,11 +7418,11 @@
       </c>
       <c r="F5" s="12">
         <f>IF($B5="BLOCKED",0,MAX(0,$D5*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($F5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H5" s="12">
         <f>IF($B5="BLOCKED","",$C5)</f>
@@ -7430,11 +7430,11 @@
       </c>
       <c r="I5" s="12">
         <f>IF($B5="BLOCKED",0,MAX(0,$G5*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K5" s="13" t="n">
         <v>100</v>
@@ -7447,19 +7447,19 @@
       </c>
       <c r="N5" s="14">
         <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O5" s="14">
         <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P5" s="15">
         <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q5" s="15">
         <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R5" s="15">
         <f>$AT5*$AU5</f>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="T5" s="12">
         <f>IF(AND($B5="BIG_SIDE",$AX5&gt;0),$AX5*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U5" s="12">
         <f>MAX(0,$M5*Settings!$B$9)</f>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="V5" s="12">
         <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W5" s="12">
         <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="X5" s="19">
         <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y5" s="19">
         <f>$Y4+$X5</f>
@@ -7503,19 +7503,19 @@
       </c>
       <c r="AB5" s="12">
         <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AC5" s="12">
         <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD5" s="12">
         <f>$AB5*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AE5" s="12">
         <f>$AC5*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF5" s="12">
         <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
@@ -7537,9 +7537,9 @@
         <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
         <v/>
       </c>
-      <c r="AK5" s="12">
+      <c r="AK5" s="12" t="b">
         <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL5" s="12">
         <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
@@ -7557,13 +7557,13 @@
         <f>IF(OR($B5="BIG_SIDE",$B5="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP5" s="12">
+      <c r="AP5" s="12" t="str">
         <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"YES",IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="STOP_CLEARED",$AQ5="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ5" s="12" t="str">
         <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR5" s="12">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="AS5" s="20">
         <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT5" s="12">
         <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
@@ -7585,9 +7585,9 @@
         <f>IF($B5="SMALL_SIDE",IF($AH5="YES",$D5,IFERROR(MIN($D5,MAX(0,$AI5/$U5)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW5" s="12">
+      <c r="AW5" s="12" t="str">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX5" s="12">
         <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
@@ -7603,15 +7603,15 @@
       </c>
       <c r="BA5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AJ5-$BD5),IF($B5="BLOCKED",MAX(0,$BA4-$BD5),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AG5-$BE5),IF($B5="BLOCKED",MAX(0,$BB4-$BE5),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC5" s="12">
         <f>$BA5+$BB5</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD5" s="13" t="n">
         <v>0</v>
@@ -7632,9 +7632,9 @@
       <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="13" t="str">
         <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"BIG_SIDE",IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="MANUAL_READY",$AQ5="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C6" s="13">
         <f>IF($B6="BLOCKED",$AF5,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),$AF5,IF($AP5="YES",$AF5,$C5)))</f>
@@ -7650,11 +7650,11 @@
       </c>
       <c r="F6" s="12">
         <f>IF($B6="BLOCKED",0,MAX(0,$D6*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G6" s="12">
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($F6/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" s="12">
         <f>IF($B6="BLOCKED","",$C6)</f>
@@ -7662,11 +7662,11 @@
       </c>
       <c r="I6" s="12">
         <f>IF($B6="BLOCKED",0,MAX(0,$G6*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J6" s="12">
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K6" s="13" t="n">
         <v>100</v>
@@ -7679,19 +7679,19 @@
       </c>
       <c r="N6" s="14">
         <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O6" s="14">
         <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P6" s="15">
         <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q6" s="15">
         <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R6" s="15">
         <f>$AT6*$AU6</f>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="T6" s="12">
         <f>IF(AND($B6="BIG_SIDE",$AX6&gt;0),$AX6*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U6" s="12">
         <f>MAX(0,$M6*Settings!$B$9)</f>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="V6" s="12">
         <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W6" s="12">
         <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="X6" s="19">
         <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y6" s="19">
         <f>$Y5+$X6</f>
@@ -7735,19 +7735,19 @@
       </c>
       <c r="AB6" s="12">
         <f>IF($B6="BLOCKED",$BC6,$D6+$G6+$J6)</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AC6" s="12">
         <f>IF($B6="BLOCKED",$BC6,IF($B6="BIG_SIDE",$W6,IF($AK6=TRUE,$BC6,$AG6)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD6" s="12">
         <f>$AB6*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AE6" s="12">
         <f>$AC6*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF6" s="12">
         <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
@@ -7769,9 +7769,9 @@
         <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
-      <c r="AK6" s="12">
+      <c r="AK6" s="12" t="b">
         <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL6" s="12">
         <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
@@ -7789,13 +7789,13 @@
         <f>IF(OR($B6="BIG_SIDE",$B6="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP6" s="12">
+      <c r="AP6" s="12" t="str">
         <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"YES",IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="STOP_CLEARED",$AQ6="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ6" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ6" s="12" t="str">
         <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR6" s="12">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AS6" s="20">
         <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT6" s="12">
         <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
@@ -7817,9 +7817,9 @@
         <f>IF($B6="SMALL_SIDE",IF($AH6="YES",$D6,IFERROR(MIN($D6,MAX(0,$AI6/$U6)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW6" s="12">
+      <c r="AW6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX6" s="12">
         <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
@@ -7835,15 +7835,15 @@
       </c>
       <c r="BA6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AJ6-$BD6),IF($B6="BLOCKED",MAX(0,$BA5-$BD6),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AG6-$BE6),IF($B6="BLOCKED",MAX(0,$BB5-$BE6),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC6" s="12">
         <f>$BA6+$BB6</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD6" s="13" t="n">
         <v>0</v>
@@ -7864,9 +7864,9 @@
       <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="13" t="str">
         <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"SMALL_SIDE",IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="MANUAL_READY",$AQ6="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C7" s="13">
         <f>IF($B7="BLOCKED",$AF6,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),$AF6,IF($AP6="YES",$AF6,$C6)))</f>
@@ -7882,11 +7882,11 @@
       </c>
       <c r="F7" s="12">
         <f>IF($B7="BLOCKED",0,MAX(0,$D7*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G7" s="12">
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($F7/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H7" s="12">
         <f>IF($B7="BLOCKED","",$C7)</f>
@@ -7894,11 +7894,11 @@
       </c>
       <c r="I7" s="12">
         <f>IF($B7="BLOCKED",0,MAX(0,$G7*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J7" s="12">
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K7" s="13" t="n">
         <v>80</v>
@@ -7911,19 +7911,19 @@
       </c>
       <c r="N7" s="14">
         <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O7" s="14">
         <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P7" s="15">
         <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q7" s="15">
         <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R7" s="15">
         <f>$AT7*$AU7</f>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="T7" s="12">
         <f>IF(AND($B7="BIG_SIDE",$AX7&gt;0),$AX7*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U7" s="12">
         <f>MAX(0,$M7*Settings!$B$9)</f>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="V7" s="12">
         <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W7" s="12">
         <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="X7" s="19">
         <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y7" s="19">
         <f>$Y6+$X7</f>
@@ -7967,19 +7967,19 @@
       </c>
       <c r="AB7" s="12">
         <f>IF($B7="BLOCKED",$BC7,$D7+$G7+$J7)</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AC7" s="12">
         <f>IF($B7="BLOCKED",$BC7,IF($B7="BIG_SIDE",$W7,IF($AK7=TRUE,$BC7,$AG7)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD7" s="12">
         <f>$AB7*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AE7" s="12">
         <f>$AC7*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF7" s="12">
         <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
@@ -8001,9 +8001,9 @@
         <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
-      <c r="AK7" s="12">
+      <c r="AK7" s="12" t="b">
         <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL7" s="12">
         <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
@@ -8021,13 +8021,13 @@
         <f>IF(OR($B7="BIG_SIDE",$B7="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP7" s="12">
+      <c r="AP7" s="12" t="str">
         <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"YES",IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="STOP_CLEARED",$AQ7="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ7" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ7" s="12" t="str">
         <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR7" s="12">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="AS7" s="20">
         <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT7" s="12">
         <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
@@ -8049,9 +8049,9 @@
         <f>IF($B7="SMALL_SIDE",IF($AH7="YES",$D7,IFERROR(MIN($D7,MAX(0,$AI7/$U7)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW7" s="12">
+      <c r="AW7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX7" s="12">
         <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
@@ -8067,15 +8067,15 @@
       </c>
       <c r="BA7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AJ7-$BD7),IF($B7="BLOCKED",MAX(0,$BA6-$BD7),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AG7-$BE7),IF($B7="BLOCKED",MAX(0,$BB6-$BE7),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC7" s="12">
         <f>$BA7+$BB7</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD7" s="13" t="n">
         <v>0</v>
@@ -8096,9 +8096,9 @@
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="13" t="str">
         <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"BIG_SIDE",IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="MANUAL_READY",$AQ7="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C8" s="13">
         <f>IF($B8="BLOCKED",$AF7,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),$AF7,IF($AP7="YES",$AF7,$C7)))</f>
@@ -8114,11 +8114,11 @@
       </c>
       <c r="F8" s="12">
         <f>IF($B8="BLOCKED",0,MAX(0,$D8*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G8" s="12">
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($F8/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H8" s="12">
         <f>IF($B8="BLOCKED","",$C8)</f>
@@ -8126,11 +8126,11 @@
       </c>
       <c r="I8" s="12">
         <f>IF($B8="BLOCKED",0,MAX(0,$G8*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J8" s="12">
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K8" s="13" t="n">
         <v>100</v>
@@ -8143,19 +8143,19 @@
       </c>
       <c r="N8" s="14">
         <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O8" s="14">
         <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P8" s="15">
         <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q8" s="15">
         <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R8" s="15">
         <f>$AT8*$AU8</f>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="T8" s="12">
         <f>IF(AND($B8="BIG_SIDE",$AX8&gt;0),$AX8*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U8" s="12">
         <f>MAX(0,$M8*Settings!$B$9)</f>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="V8" s="12">
         <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W8" s="12">
         <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="X8" s="19">
         <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y8" s="19">
         <f>$Y7+$X8</f>
@@ -8199,19 +8199,19 @@
       </c>
       <c r="AB8" s="12">
         <f>IF($B8="BLOCKED",$BC8,$D8+$G8+$J8)</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AC8" s="12">
         <f>IF($B8="BLOCKED",$BC8,IF($B8="BIG_SIDE",$W8,IF($AK8=TRUE,$BC8,$AG8)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD8" s="12">
         <f>$AB8*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AE8" s="12">
         <f>$AC8*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF8" s="12">
         <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
@@ -8233,9 +8233,9 @@
         <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
-      <c r="AK8" s="12">
+      <c r="AK8" s="12" t="b">
         <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL8" s="12">
         <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
@@ -8253,13 +8253,13 @@
         <f>IF(OR($B8="BIG_SIDE",$B8="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP8" s="12">
+      <c r="AP8" s="12" t="str">
         <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"YES",IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="STOP_CLEARED",$AQ8="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ8" s="12" t="str">
         <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR8" s="12">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="AS8" s="20">
         <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT8" s="12">
         <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
@@ -8281,9 +8281,9 @@
         <f>IF($B8="SMALL_SIDE",IF($AH8="YES",$D8,IFERROR(MIN($D8,MAX(0,$AI8/$U8)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW8" s="12">
+      <c r="AW8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX8" s="12">
         <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
@@ -8299,15 +8299,15 @@
       </c>
       <c r="BA8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AJ8-$BD8),IF($B8="BLOCKED",MAX(0,$BA7-$BD8),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AG8-$BE8),IF($B8="BLOCKED",MAX(0,$BB7-$BE8),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC8" s="12">
         <f>$BA8+$BB8</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD8" s="13" t="n">
         <v>0</v>
@@ -8328,9 +8328,9 @@
       <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="13" t="str">
         <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"BIG_SIDE",IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="MANUAL_READY",$AQ8="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C9" s="13">
         <f>IF($B9="BLOCKED",$AF8,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),$AF8,IF($AP8="YES",$AF8,$C8)))</f>
@@ -8346,11 +8346,11 @@
       </c>
       <c r="F9" s="12">
         <f>IF($B9="BLOCKED",0,MAX(0,$D9*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G9" s="12">
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($F9/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H9" s="12">
         <f>IF($B9="BLOCKED","",$C9)</f>
@@ -8358,11 +8358,11 @@
       </c>
       <c r="I9" s="12">
         <f>IF($B9="BLOCKED",0,MAX(0,$G9*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J9" s="12">
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K9" s="13" t="n">
         <v>100</v>
@@ -8375,19 +8375,19 @@
       </c>
       <c r="N9" s="14">
         <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O9" s="14">
         <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P9" s="15">
         <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q9" s="15">
         <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R9" s="15">
         <f>$AT9*$AU9</f>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="T9" s="12">
         <f>IF(AND($B9="BIG_SIDE",$AX9&gt;0),$AX9*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U9" s="12">
         <f>MAX(0,$M9*Settings!$B$9)</f>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="V9" s="12">
         <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W9" s="12">
         <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="X9" s="19">
         <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y9" s="19">
         <f>$Y8+$X9</f>
@@ -8431,19 +8431,19 @@
       </c>
       <c r="AB9" s="12">
         <f>IF($B9="BLOCKED",$BC9,$D9+$G9+$J9)</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AC9" s="12">
         <f>IF($B9="BLOCKED",$BC9,IF($B9="BIG_SIDE",$W9,IF($AK9=TRUE,$BC9,$AG9)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD9" s="12">
         <f>$AB9*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AE9" s="12">
         <f>$AC9*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF9" s="12">
         <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
@@ -8465,9 +8465,9 @@
         <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
-      <c r="AK9" s="12">
+      <c r="AK9" s="12" t="b">
         <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL9" s="12">
         <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
@@ -8485,13 +8485,13 @@
         <f>IF(OR($B9="BIG_SIDE",$B9="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP9" s="12">
+      <c r="AP9" s="12" t="str">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"YES",IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="STOP_CLEARED",$AQ9="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ9" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ9" s="12" t="str">
         <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR9" s="12">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="AS9" s="20">
         <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT9" s="12">
         <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
@@ -8513,9 +8513,9 @@
         <f>IF($B9="SMALL_SIDE",IF($AH9="YES",$D9,IFERROR(MIN($D9,MAX(0,$AI9/$U9)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW9" s="12">
+      <c r="AW9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX9" s="12">
         <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
@@ -8531,15 +8531,15 @@
       </c>
       <c r="BA9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AJ9-$BD9),IF($B9="BLOCKED",MAX(0,$BA8-$BD9),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AG9-$BE9),IF($B9="BLOCKED",MAX(0,$BB8-$BE9),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC9" s="12">
         <f>$BA9+$BB9</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD9" s="13" t="n">
         <v>0</v>
@@ -8560,9 +8560,9 @@
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="13" t="str">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"BIG_SIDE",IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="MANUAL_READY",$AQ9="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C10" s="13">
         <f>IF($B10="BLOCKED",$AF9,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),$AF9,IF($AP9="YES",$AF9,$C9)))</f>
@@ -8578,11 +8578,11 @@
       </c>
       <c r="F10" s="12">
         <f>IF($B10="BLOCKED",0,MAX(0,$D10*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G10" s="12">
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($F10/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H10" s="12">
         <f>IF($B10="BLOCKED","",$C10)</f>
@@ -8590,11 +8590,11 @@
       </c>
       <c r="I10" s="12">
         <f>IF($B10="BLOCKED",0,MAX(0,$G10*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J10" s="12">
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K10" s="13" t="n">
         <v>100</v>
@@ -8607,19 +8607,19 @@
       </c>
       <c r="N10" s="14">
         <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O10" s="14">
         <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P10" s="15">
         <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q10" s="15">
         <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R10" s="15">
         <f>$AT10*$AU10</f>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="T10" s="12">
         <f>IF(AND($B10="BIG_SIDE",$AX10&gt;0),$AX10*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U10" s="12">
         <f>MAX(0,$M10*Settings!$B$9)</f>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="V10" s="12">
         <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W10" s="12">
         <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="X10" s="19">
         <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y10" s="19">
         <f>$Y9+$X10</f>
@@ -8663,19 +8663,19 @@
       </c>
       <c r="AB10" s="12">
         <f>IF($B10="BLOCKED",$BC10,$D10+$G10+$J10)</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AC10" s="12">
         <f>IF($B10="BLOCKED",$BC10,IF($B10="BIG_SIDE",$W10,IF($AK10=TRUE,$BC10,$AG10)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD10" s="12">
         <f>$AB10*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AE10" s="12">
         <f>$AC10*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF10" s="12">
         <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
@@ -8697,9 +8697,9 @@
         <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
-      <c r="AK10" s="12">
+      <c r="AK10" s="12" t="b">
         <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL10" s="12">
         <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
@@ -8717,13 +8717,13 @@
         <f>IF(OR($B10="BIG_SIDE",$B10="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP10" s="12">
+      <c r="AP10" s="12" t="str">
         <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"YES",IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="STOP_CLEARED",$AQ10="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ10" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ10" s="12" t="str">
         <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR10" s="12">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="AS10" s="20">
         <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT10" s="12">
         <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
@@ -8745,9 +8745,9 @@
         <f>IF($B10="SMALL_SIDE",IF($AH10="YES",$D10,IFERROR(MIN($D10,MAX(0,$AI10/$U10)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW10" s="12">
+      <c r="AW10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX10" s="12">
         <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
@@ -8763,15 +8763,15 @@
       </c>
       <c r="BA10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AJ10-$BD10),IF($B10="BLOCKED",MAX(0,$BA9-$BD10),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AG10-$BE10),IF($B10="BLOCKED",MAX(0,$BB9-$BE10),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC10" s="12">
         <f>$BA10+$BB10</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD10" s="13" t="n">
         <v>0</v>
@@ -8792,9 +8792,9 @@
       <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="13" t="str">
         <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"BIG_SIDE",IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="MANUAL_READY",$AQ10="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BLOCKED</v>
       </c>
       <c r="C11" s="13">
         <f>IF($B11="BLOCKED",$AF10,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),$AF10,IF($AP10="YES",$AF10,$C10)))</f>
@@ -8810,11 +8810,11 @@
       </c>
       <c r="F11" s="12">
         <f>IF($B11="BLOCKED",0,MAX(0,$D11*Settings!$B$3))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G11" s="12">
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($F11/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H11" s="12">
         <f>IF($B11="BLOCKED","",$C11)</f>
@@ -8822,11 +8822,11 @@
       </c>
       <c r="I11" s="12">
         <f>IF($B11="BLOCKED",0,MAX(0,$G11*Settings!$B$4))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J11" s="12">
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K11" s="13" t="n">
         <v>100</v>
@@ -8839,19 +8839,19 @@
       </c>
       <c r="N11" s="14">
         <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O11" s="14">
         <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P11" s="15">
         <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q11" s="15">
         <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="R11" s="15">
         <f>$AT11*$AU11</f>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="T11" s="12">
         <f>IF(AND($B11="BIG_SIDE",$AX11&gt;0),$AX11*Settings!$B$5,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U11" s="12">
         <f>MAX(0,$M11*Settings!$B$9)</f>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="V11" s="12">
         <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W11" s="12">
         <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="X11" s="19">
         <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y11" s="19">
         <f>$Y10+$X11</f>
@@ -8895,19 +8895,19 @@
       </c>
       <c r="AB11" s="12">
         <f>IF($B11="BLOCKED",$BC11,$D11+$G11+$J11)</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AC11" s="12">
         <f>IF($B11="BLOCKED",$BC11,IF($B11="BIG_SIDE",$W11,IF($AK11=TRUE,$BC11,$AG11)))</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="AD11" s="12">
         <f>$AB11*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AE11" s="12">
         <f>$AC11*Settings!$B$10</f>
-        <v/>
+        <v>1697.0</v>
       </c>
       <c r="AF11" s="12">
         <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
@@ -8929,9 +8929,9 @@
         <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
-      <c r="AK11" s="12">
+      <c r="AK11" s="12" t="b">
         <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL11" s="12">
         <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
@@ -8949,13 +8949,13 @@
         <f>IF(OR($B11="BIG_SIDE",$B11="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP11" s="12">
+      <c r="AP11" s="12" t="str">
         <f>IF(AND($AQ11="MANUAL_READY",$BG11="YES"),"YES",IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP",$AQ11="STOP_CLEARED",$AQ11="MANUAL_READY"),"NO","YES"))</f>
-        <v/>
-      </c>
-      <c r="AQ11" s="12">
+        <v>NO</v>
+      </c>
+      <c r="AQ11" s="12" t="str">
         <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
-        <v/>
+        <v>STOP</v>
       </c>
       <c r="AR11" s="12">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="AS11" s="20">
         <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AT11" s="12">
         <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
@@ -8977,9 +8977,9 @@
         <f>IF($B11="SMALL_SIDE",IF($AH11="YES",$D11,IFERROR(MIN($D11,MAX(0,$AI11/$U11)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW11" s="12">
+      <c r="AW11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v/>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AX11" s="12">
         <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
@@ -8995,15 +8995,15 @@
       </c>
       <c r="BA11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AJ11-$BD11),IF($B11="BLOCKED",MAX(0,$BA10-$BD11),0))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="BB11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AG11-$BE11),IF($B11="BLOCKED",MAX(0,$BB10-$BE11),0))</f>
-        <v/>
+        <v>0.897</v>
       </c>
       <c r="BC11" s="12">
         <f>$BA11+$BB11</f>
-        <v/>
+        <v>1.697</v>
       </c>
       <c r="BD11" s="13" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="C12" s="3">
         <f>COUNTIF(Calculator!AQ2:AQ11,"DUAL_TAIL")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="C14" s="3">
         <f>COUNTIF(Calculator!AQ2:AQ11,"STOP")</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="C16" s="3">
         <f>MAX(Calculator!BC2:BC11)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="17">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="C17" s="3">
         <f>LOOKUP(2,1/(Calculator!BA2:BA11&lt;&gt;""),Calculator!BA2:BA11)</f>
-        <v/>
+        <v>0.5216</v>
       </c>
     </row>
     <row r="18">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="C18" s="3">
         <f>LOOKUP(2,1/(Calculator!BB2:BB11&lt;&gt;""),Calculator!BB2:BB11)</f>
-        <v/>
+        <v>0.468</v>
       </c>
     </row>
     <row r="19">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="C19" s="3">
         <f>LOOKUP(2,1/(Calculator!BC2:BC11&lt;&gt;""),Calculator!BC2:BC11)</f>
-        <v/>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="20">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="C20" s="3">
         <f>SUM(Calculator!BF2:BF11)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="C21" s="3">
         <f>COUNTIF(Calculator!B2:B11,"BLOCKED")</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="C22" s="3">
         <f>COUNTIF(Calculator!AQ2:AQ11,"STOP_CLEARED")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="C23" s="3">
         <f>COUNTIF(Calculator!AQ2:AQ11,"MANUAL_READY")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9445,7 +9445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11764,6 +11764,510 @@
       <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Автоматический перезапуск запрещён без ручного разрешения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>T55</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL row active old lot</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL row</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot = OldFarRemainLot</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>BA=AJ unless manual old close</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>BA/AK formula + data smoke</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>v5: старый хвост появляется в активном состоянии на DUAL_TAIL строке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>T56</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL row active new lot</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>DUAL_TAIL row</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot = NewFarStartLot</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>BB=AG unless manual new close</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>BB/AK formula + data smoke</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>v5: новый хвост появляется в активном состоянии на DUAL_TAIL строке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>T57</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>First BLOCKED preserves dual tail lots</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>First row after DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>ActiveOld/New carry previous values</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>BA/BB carry from previous row</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>BA/BB formulas + data smoke</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Первая BLOCKED строка сохраняет оба хвоста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>T58</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Second BLOCKED preserves dual tail lots</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Second BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>ActiveOld/New still non-zero without manual close</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>BA/BB carry forward</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>BA/BB formulas + data smoke</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Вторая BLOCKED строка не теряет старый хвост.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>T59</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED open lots equal dual total</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>OpenLotsAfter = DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>AC=BC</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>AC formula + data smoke</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Открытые лоты после BLOCKED считаются от двух хвостов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>T60</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED margin from dual total</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>MarginAfter = DualTailTotalLot × MarginPerLot</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>AE=AC*MarginPerLot</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>AE formula + data smoke</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Маржа не падает искусственно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>T61</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Risk blocked count positive</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Blocked Levels Count &gt; 0 when BLOCKED rows exist</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>COUNTIF Scenario BLOCKED</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis formula/cache</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis видит BLOCKED строки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>T62</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Risk max dual exposure positive</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Max DualTail Exposure &gt; 0 when DUAL_TAIL exists</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>MAX(DualTailTotalLot)</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis formula/cache</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Risk_Analysis видит экспозицию двух хвостов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>T63</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Active old tail not zero without manual close</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED rows</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot persists when ManualOldFarCloseLot=0</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>BA current = BA previous</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>BA formula</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Старый хвост не исчезает без ручного закрытия.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>T64</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Active new tail not zero without manual close</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED rows</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot persists when ManualNewFarCloseLot=0</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>BB current = BB previous</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>BB formula</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Новый хвост не исчезает без ручного закрытия.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>T65</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>ManualClosePL changes balance</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED row</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>BalanceAfter = BalanceBefore + ManualClosePL</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>AA=Z+BF for BLOCKED</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>AA formula</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Ручной P/L входит в баланс.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>T66</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>ManualAllowNewLevel required to resume</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>MANUAL_READY row</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>New level only if ManualAllowNewLevel=YES</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>B next row checks BG=YES</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>B/AP formulas</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Новый уровень после DUAL_TAIL не открывается автоматически.</t>
         </is>
       </c>
     </row>

--- a/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
+++ b/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +50,11 @@
     <font>
       <color rgb="001F4E78"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +101,21 @@
         <fgColor rgb="007F0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -125,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -174,6 +192,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1289,7 +1314,7 @@
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -1301,7 +1326,7 @@
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.4</v>
+        <v/>
       </c>
       <c r="K2" s="13" t="n">
         <v>100</v>
@@ -1369,19 +1394,19 @@
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC2" s="12">
         <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
-        <v>0.7</v>
+        <v/>
       </c>
       <c r="AD2" s="12">
         <f>$AB2*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE2" s="12">
         <f>$AC2*Settings!$B$10</f>
-        <v>700</v>
+        <v/>
       </c>
       <c r="AF2" s="12">
         <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
@@ -1403,9 +1428,9 @@
         <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
-      <c r="AK2" s="12" t="b">
+      <c r="AK2" s="12">
         <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL2" s="12">
         <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
@@ -1423,13 +1448,13 @@
         <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP2" s="12" t="str">
+      <c r="AP2" s="12">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
-        <v>YES</v>
-      </c>
-      <c r="AQ2" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ2" s="12">
         <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
-        <v>OK</v>
+        <v/>
       </c>
       <c r="AR2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -1451,7 +1476,7 @@
         <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW2" s="12" t="str">
+      <c r="AW2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -1469,15 +1494,15 @@
       </c>
       <c r="BA2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BB2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BC2" s="12">
         <f>$BA2+$BB2</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BD2" s="13" t="n">
         <v>0</v>
@@ -1498,9 +1523,9 @@
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="str">
+      <c r="B3" s="13">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"BIG_SIDE",IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="MANUAL_READY",$AQ2="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BIG_SIDE</v>
+        <v/>
       </c>
       <c r="C3" s="13">
         <f>IF($B3="BLOCKED",$AF2,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),$AF2,IF($AP2="YES",$AF2,$C2)))</f>
@@ -1520,7 +1545,7 @@
       </c>
       <c r="G3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H3" s="12">
         <f>IF($B3="BLOCKED","",$C3)</f>
@@ -1532,7 +1557,7 @@
       </c>
       <c r="J3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.4</v>
+        <v/>
       </c>
       <c r="K3" s="13" t="n">
         <v>100</v>
@@ -1601,19 +1626,19 @@
       </c>
       <c r="AB3" s="12">
         <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC3" s="12">
         <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
-        <v>0.7</v>
+        <v/>
       </c>
       <c r="AD3" s="12">
         <f>$AB3*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE3" s="12">
         <f>$AC3*Settings!$B$10</f>
-        <v>700</v>
+        <v/>
       </c>
       <c r="AF3" s="12">
         <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
@@ -1635,9 +1660,9 @@
         <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
         <v/>
       </c>
-      <c r="AK3" s="12" t="b">
+      <c r="AK3" s="12">
         <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL3" s="12">
         <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
@@ -1655,13 +1680,13 @@
         <f>IF(OR($B3="BIG_SIDE",$B3="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP3" s="12" t="str">
+      <c r="AP3" s="12">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"YES",IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="STOP_CLEARED",$AQ3="MANUAL_READY"),"NO","YES"))</f>
-        <v>YES</v>
-      </c>
-      <c r="AQ3" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ3" s="12">
         <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
-        <v>OK</v>
+        <v/>
       </c>
       <c r="AR3" s="12">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -1683,7 +1708,7 @@
         <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW3" s="12" t="str">
+      <c r="AW3" s="12">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -1701,15 +1726,15 @@
       </c>
       <c r="BA3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BB3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BC3" s="12">
         <f>$BA3+$BB3</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BD3" s="13" t="n">
         <v>0</v>
@@ -1730,9 +1755,9 @@
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="str">
+      <c r="B4" s="13">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"SMALL_SIDE",IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="MANUAL_READY",$AQ3="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
-        <v>SMALL_SIDE</v>
+        <v/>
       </c>
       <c r="C4" s="13">
         <f>IF($B4="BLOCKED",$AF3,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),$AF3,IF($AP3="YES",$AF3,$C3)))</f>
@@ -1752,7 +1777,7 @@
       </c>
       <c r="G4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($F4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1.0</v>
+        <v/>
       </c>
       <c r="H4" s="12">
         <f>IF($B4="BLOCKED","",$C4)</f>
@@ -1764,7 +1789,7 @@
       </c>
       <c r="J4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.38</v>
+        <v/>
       </c>
       <c r="K4" s="13" t="n">
         <v>80</v>
@@ -1833,19 +1858,19 @@
       </c>
       <c r="AB4" s="12">
         <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC4" s="12">
         <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AD4" s="12">
         <f>$AB4*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE4" s="12">
         <f>$AC4*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AF4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
@@ -1853,7 +1878,7 @@
       </c>
       <c r="AG4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
         <is>
@@ -1865,11 +1890,11 @@
       </c>
       <c r="AJ4" s="12">
         <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
-        <v>0.5216</v>
-      </c>
-      <c r="AK4" s="12" t="b">
+        <v/>
+      </c>
+      <c r="AK4" s="12">
         <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL4" s="12">
         <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
@@ -1887,13 +1912,13 @@
         <f>IF(OR($B4="BIG_SIDE",$B4="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP4" s="12" t="str">
+      <c r="AP4" s="12">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"YES",IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="STOP_CLEARED",$AQ4="MANUAL_READY"),"NO","YES"))</f>
-        <v>NO</v>
-      </c>
-      <c r="AQ4" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ4" s="12">
         <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
-        <v>DUAL_TAIL</v>
+        <v/>
       </c>
       <c r="AR4" s="12">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -1915,7 +1940,7 @@
         <f>IF($B4="SMALL_SIDE",IF($AH4="YES",$D4,IFERROR(MIN($D4,MAX(0,$AI4/$U4)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW4" s="12" t="str">
+      <c r="AW4" s="12">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -1933,15 +1958,15 @@
       </c>
       <c r="BA4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="BB4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="BC4" s="12">
         <f>$BA4+$BB4</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="BD4" s="13" t="n">
         <v>0</v>
@@ -1962,9 +1987,9 @@
       <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="str">
+      <c r="B5" s="13">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"BIG_SIDE",IF(OR($AP4="NO",$AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="MANUAL_READY",$AQ4="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BLOCKED</v>
+        <v/>
       </c>
       <c r="C5" s="13">
         <f>IF($B5="BLOCKED",$AF4,IF(AND($AQ4="MANUAL_READY",$BG4="YES"),$AF4,IF($AP4="YES",$AF4,$C4)))</f>
@@ -1980,11 +2005,11 @@
       </c>
       <c r="F5" s="12">
         <f>IF($B5="BLOCKED",0,MAX(0,$D5*Settings!$B$3))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($F5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H5" s="12">
         <f>IF($B5="BLOCKED","",$C5)</f>
@@ -1992,11 +2017,11 @@
       </c>
       <c r="I5" s="12">
         <f>IF($B5="BLOCKED",0,MAX(0,$G5*Settings!$B$4))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K5" s="13" t="n">
         <v>100</v>
@@ -2009,19 +2034,19 @@
       </c>
       <c r="N5" s="14">
         <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O5" s="14">
         <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P5" s="15">
         <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q5" s="15">
         <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R5" s="15">
         <f>$AT5*$AU5</f>
@@ -2033,7 +2058,7 @@
       </c>
       <c r="T5" s="12">
         <f>IF(AND($B5="BIG_SIDE",$AX5&gt;0),$AX5*Settings!$B$5,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U5" s="12">
         <f>MAX(0,$M5*Settings!$B$9)</f>
@@ -2041,7 +2066,7 @@
       </c>
       <c r="V5" s="12">
         <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W5" s="12">
         <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
@@ -2049,7 +2074,7 @@
       </c>
       <c r="X5" s="19">
         <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y5" s="19">
         <f>$Y4+$X5</f>
@@ -2065,19 +2090,19 @@
       </c>
       <c r="AB5" s="12">
         <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AC5" s="12">
         <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AD5" s="12">
         <f>$AB5*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AE5" s="12">
         <f>$AC5*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AF5" s="12">
         <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
@@ -2099,9 +2124,9 @@
         <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
         <v/>
       </c>
-      <c r="AK5" s="12" t="b">
+      <c r="AK5" s="12">
         <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL5" s="12">
         <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
@@ -2119,13 +2144,13 @@
         <f>IF(OR($B5="BIG_SIDE",$B5="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP5" s="12" t="str">
+      <c r="AP5" s="12">
         <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"YES",IF(OR($AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="STOP_CLEARED",$AQ5="MANUAL_READY"),"NO","YES"))</f>
-        <v>NO</v>
-      </c>
-      <c r="AQ5" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ5" s="12">
         <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
-        <v>STOP</v>
+        <v/>
       </c>
       <c r="AR5" s="12">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -2133,7 +2158,7 @@
       </c>
       <c r="AS5" s="20">
         <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT5" s="12">
         <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
@@ -2147,9 +2172,9 @@
         <f>IF($B5="SMALL_SIDE",IF($AH5="YES",$D5,IFERROR(MIN($D5,MAX(0,$AI5/$U5)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW5" s="12" t="str">
+      <c r="AW5" s="12">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v/>
       </c>
       <c r="AX5" s="12">
         <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
@@ -2165,15 +2190,15 @@
       </c>
       <c r="BA5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AJ5-$BD5),IF($B5="BLOCKED",MAX(0,$BA4-$BD5),0))</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="BB5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AG5-$BE5),IF($B5="BLOCKED",MAX(0,$BB4-$BE5),0))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="BC5" s="12">
         <f>$BA5+$BB5</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="BD5" s="13" t="n">
         <v>0</v>
@@ -2194,9 +2219,9 @@
       <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="str">
+      <c r="B6" s="13">
         <f>IF(AND($AQ5="MANUAL_READY",$BG5="YES"),"BIG_SIDE",IF(OR($AP5="NO",$AQ5="DUAL_TAIL",$AQ5="DANGER",$AQ5="STOP",$AQ5="MANUAL_READY",$AQ5="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BLOCKED</v>
+        <v/>
       </c>
       <c r="C6" s="13">
         <f>IF($B6="BLOCKED",$AF5,IF(AND($AQ5="MANUAL_READY",$BG5="YES"),$AF5,IF($AP5="YES",$AF5,$C5)))</f>
@@ -2212,11 +2237,11 @@
       </c>
       <c r="F6" s="12">
         <f>IF($B6="BLOCKED",0,MAX(0,$D6*Settings!$B$3))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G6" s="12">
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($F6/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H6" s="12">
         <f>IF($B6="BLOCKED","",$C6)</f>
@@ -2224,11 +2249,11 @@
       </c>
       <c r="I6" s="12">
         <f>IF($B6="BLOCKED",0,MAX(0,$G6*Settings!$B$4))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J6" s="12">
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K6" s="13" t="n">
         <v>100</v>
@@ -2241,19 +2266,19 @@
       </c>
       <c r="N6" s="14">
         <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O6" s="14">
         <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P6" s="15">
         <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q6" s="15">
         <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R6" s="15">
         <f>$AT6*$AU6</f>
@@ -2265,7 +2290,7 @@
       </c>
       <c r="T6" s="12">
         <f>IF(AND($B6="BIG_SIDE",$AX6&gt;0),$AX6*Settings!$B$5,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U6" s="12">
         <f>MAX(0,$M6*Settings!$B$9)</f>
@@ -2273,7 +2298,7 @@
       </c>
       <c r="V6" s="12">
         <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W6" s="12">
         <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
@@ -2281,7 +2306,7 @@
       </c>
       <c r="X6" s="19">
         <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y6" s="19">
         <f>$Y5+$X6</f>
@@ -2297,19 +2322,19 @@
       </c>
       <c r="AB6" s="12">
         <f>IF($B6="BLOCKED",$BC6,$D6+$G6+$J6)</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AC6" s="12">
         <f>IF($B6="BLOCKED",$BC6,IF($B6="BIG_SIDE",$W6,IF($AK6=TRUE,$BC6,$AG6)))</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AD6" s="12">
         <f>$AB6*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AE6" s="12">
         <f>$AC6*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AF6" s="12">
         <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
@@ -2331,9 +2356,9 @@
         <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
-      <c r="AK6" s="12" t="b">
+      <c r="AK6" s="12">
         <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL6" s="12">
         <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
@@ -2351,13 +2376,13 @@
         <f>IF(OR($B6="BIG_SIDE",$B6="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP6" s="12" t="str">
+      <c r="AP6" s="12">
         <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"YES",IF(OR($AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="STOP_CLEARED",$AQ6="MANUAL_READY"),"NO","YES"))</f>
-        <v>NO</v>
-      </c>
-      <c r="AQ6" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ6" s="12">
         <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
-        <v>STOP</v>
+        <v/>
       </c>
       <c r="AR6" s="12">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -2365,7 +2390,7 @@
       </c>
       <c r="AS6" s="20">
         <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT6" s="12">
         <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
@@ -2379,9 +2404,9 @@
         <f>IF($B6="SMALL_SIDE",IF($AH6="YES",$D6,IFERROR(MIN($D6,MAX(0,$AI6/$U6)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW6" s="12" t="str">
+      <c r="AW6" s="12">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v/>
       </c>
       <c r="AX6" s="12">
         <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
@@ -2397,15 +2422,15 @@
       </c>
       <c r="BA6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AJ6-$BD6),IF($B6="BLOCKED",MAX(0,$BA5-$BD6),0))</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="BB6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AG6-$BE6),IF($B6="BLOCKED",MAX(0,$BB5-$BE6),0))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="BC6" s="12">
         <f>$BA6+$BB6</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="BD6" s="13" t="n">
         <v>0</v>
@@ -2426,9 +2451,9 @@
       <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="str">
+      <c r="B7" s="13">
         <f>IF(AND($AQ6="MANUAL_READY",$BG6="YES"),"SMALL_SIDE",IF(OR($AP6="NO",$AQ6="DUAL_TAIL",$AQ6="DANGER",$AQ6="STOP",$AQ6="MANUAL_READY",$AQ6="STOP_CLEARED"),"BLOCKED","SMALL_SIDE"))</f>
-        <v>BLOCKED</v>
+        <v/>
       </c>
       <c r="C7" s="13">
         <f>IF($B7="BLOCKED",$AF6,IF(AND($AQ6="MANUAL_READY",$BG6="YES"),$AF6,IF($AP6="YES",$AF6,$C6)))</f>
@@ -2444,11 +2469,11 @@
       </c>
       <c r="F7" s="12">
         <f>IF($B7="BLOCKED",0,MAX(0,$D7*Settings!$B$3))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G7" s="12">
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($F7/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H7" s="12">
         <f>IF($B7="BLOCKED","",$C7)</f>
@@ -2456,11 +2481,11 @@
       </c>
       <c r="I7" s="12">
         <f>IF($B7="BLOCKED",0,MAX(0,$G7*Settings!$B$4))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J7" s="12">
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K7" s="13" t="n">
         <v>80</v>
@@ -2473,19 +2498,19 @@
       </c>
       <c r="N7" s="14">
         <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O7" s="14">
         <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P7" s="15">
         <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q7" s="15">
         <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R7" s="15">
         <f>$AT7*$AU7</f>
@@ -2497,7 +2522,7 @@
       </c>
       <c r="T7" s="12">
         <f>IF(AND($B7="BIG_SIDE",$AX7&gt;0),$AX7*Settings!$B$5,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U7" s="12">
         <f>MAX(0,$M7*Settings!$B$9)</f>
@@ -2505,7 +2530,7 @@
       </c>
       <c r="V7" s="12">
         <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W7" s="12">
         <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
@@ -2513,7 +2538,7 @@
       </c>
       <c r="X7" s="19">
         <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y7" s="19">
         <f>$Y6+$X7</f>
@@ -2529,19 +2554,19 @@
       </c>
       <c r="AB7" s="12">
         <f>IF($B7="BLOCKED",$BC7,$D7+$G7+$J7)</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AC7" s="12">
         <f>IF($B7="BLOCKED",$BC7,IF($B7="BIG_SIDE",$W7,IF($AK7=TRUE,$BC7,$AG7)))</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AD7" s="12">
         <f>$AB7*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AE7" s="12">
         <f>$AC7*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AF7" s="12">
         <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
@@ -2563,9 +2588,9 @@
         <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
-      <c r="AK7" s="12" t="b">
+      <c r="AK7" s="12">
         <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL7" s="12">
         <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
@@ -2583,13 +2608,13 @@
         <f>IF(OR($B7="BIG_SIDE",$B7="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP7" s="12" t="str">
+      <c r="AP7" s="12">
         <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"YES",IF(OR($AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="STOP_CLEARED",$AQ7="MANUAL_READY"),"NO","YES"))</f>
-        <v>NO</v>
-      </c>
-      <c r="AQ7" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ7" s="12">
         <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
-        <v>STOP</v>
+        <v/>
       </c>
       <c r="AR7" s="12">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -2597,7 +2622,7 @@
       </c>
       <c r="AS7" s="20">
         <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT7" s="12">
         <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
@@ -2611,9 +2636,9 @@
         <f>IF($B7="SMALL_SIDE",IF($AH7="YES",$D7,IFERROR(MIN($D7,MAX(0,$AI7/$U7)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW7" s="12" t="str">
+      <c r="AW7" s="12">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v/>
       </c>
       <c r="AX7" s="12">
         <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
@@ -2629,15 +2654,15 @@
       </c>
       <c r="BA7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AJ7-$BD7),IF($B7="BLOCKED",MAX(0,$BA6-$BD7),0))</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="BB7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AG7-$BE7),IF($B7="BLOCKED",MAX(0,$BB6-$BE7),0))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="BC7" s="12">
         <f>$BA7+$BB7</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="BD7" s="13" t="n">
         <v>0</v>
@@ -2658,9 +2683,9 @@
       <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="str">
+      <c r="B8" s="13">
         <f>IF(AND($AQ7="MANUAL_READY",$BG7="YES"),"BIG_SIDE",IF(OR($AP7="NO",$AQ7="DUAL_TAIL",$AQ7="DANGER",$AQ7="STOP",$AQ7="MANUAL_READY",$AQ7="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BLOCKED</v>
+        <v/>
       </c>
       <c r="C8" s="13">
         <f>IF($B8="BLOCKED",$AF7,IF(AND($AQ7="MANUAL_READY",$BG7="YES"),$AF7,IF($AP7="YES",$AF7,$C7)))</f>
@@ -2676,11 +2701,11 @@
       </c>
       <c r="F8" s="12">
         <f>IF($B8="BLOCKED",0,MAX(0,$D8*Settings!$B$3))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G8" s="12">
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($F8/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H8" s="12">
         <f>IF($B8="BLOCKED","",$C8)</f>
@@ -2688,11 +2713,11 @@
       </c>
       <c r="I8" s="12">
         <f>IF($B8="BLOCKED",0,MAX(0,$G8*Settings!$B$4))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J8" s="12">
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K8" s="13" t="n">
         <v>100</v>
@@ -2705,19 +2730,19 @@
       </c>
       <c r="N8" s="14">
         <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O8" s="14">
         <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P8" s="15">
         <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q8" s="15">
         <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R8" s="15">
         <f>$AT8*$AU8</f>
@@ -2729,7 +2754,7 @@
       </c>
       <c r="T8" s="12">
         <f>IF(AND($B8="BIG_SIDE",$AX8&gt;0),$AX8*Settings!$B$5,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U8" s="12">
         <f>MAX(0,$M8*Settings!$B$9)</f>
@@ -2737,7 +2762,7 @@
       </c>
       <c r="V8" s="12">
         <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W8" s="12">
         <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
@@ -2745,7 +2770,7 @@
       </c>
       <c r="X8" s="19">
         <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y8" s="19">
         <f>$Y7+$X8</f>
@@ -2761,19 +2786,19 @@
       </c>
       <c r="AB8" s="12">
         <f>IF($B8="BLOCKED",$BC8,$D8+$G8+$J8)</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AC8" s="12">
         <f>IF($B8="BLOCKED",$BC8,IF($B8="BIG_SIDE",$W8,IF($AK8=TRUE,$BC8,$AG8)))</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AD8" s="12">
         <f>$AB8*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AE8" s="12">
         <f>$AC8*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AF8" s="12">
         <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
@@ -2795,9 +2820,9 @@
         <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
-      <c r="AK8" s="12" t="b">
+      <c r="AK8" s="12">
         <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL8" s="12">
         <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
@@ -2815,13 +2840,13 @@
         <f>IF(OR($B8="BIG_SIDE",$B8="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP8" s="12" t="str">
+      <c r="AP8" s="12">
         <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"YES",IF(OR($AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="STOP_CLEARED",$AQ8="MANUAL_READY"),"NO","YES"))</f>
-        <v>NO</v>
-      </c>
-      <c r="AQ8" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ8" s="12">
         <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
-        <v>STOP</v>
+        <v/>
       </c>
       <c r="AR8" s="12">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -2829,7 +2854,7 @@
       </c>
       <c r="AS8" s="20">
         <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT8" s="12">
         <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
@@ -2843,9 +2868,9 @@
         <f>IF($B8="SMALL_SIDE",IF($AH8="YES",$D8,IFERROR(MIN($D8,MAX(0,$AI8/$U8)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW8" s="12" t="str">
+      <c r="AW8" s="12">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v/>
       </c>
       <c r="AX8" s="12">
         <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
@@ -2861,15 +2886,15 @@
       </c>
       <c r="BA8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AJ8-$BD8),IF($B8="BLOCKED",MAX(0,$BA7-$BD8),0))</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="BB8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AG8-$BE8),IF($B8="BLOCKED",MAX(0,$BB7-$BE8),0))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="BC8" s="12">
         <f>$BA8+$BB8</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="BD8" s="13" t="n">
         <v>0</v>
@@ -2890,9 +2915,9 @@
       <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="str">
+      <c r="B9" s="13">
         <f>IF(AND($AQ8="MANUAL_READY",$BG8="YES"),"BIG_SIDE",IF(OR($AP8="NO",$AQ8="DUAL_TAIL",$AQ8="DANGER",$AQ8="STOP",$AQ8="MANUAL_READY",$AQ8="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BLOCKED</v>
+        <v/>
       </c>
       <c r="C9" s="13">
         <f>IF($B9="BLOCKED",$AF8,IF(AND($AQ8="MANUAL_READY",$BG8="YES"),$AF8,IF($AP8="YES",$AF8,$C8)))</f>
@@ -2908,11 +2933,11 @@
       </c>
       <c r="F9" s="12">
         <f>IF($B9="BLOCKED",0,MAX(0,$D9*Settings!$B$3))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G9" s="12">
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($F9/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H9" s="12">
         <f>IF($B9="BLOCKED","",$C9)</f>
@@ -2920,11 +2945,11 @@
       </c>
       <c r="I9" s="12">
         <f>IF($B9="BLOCKED",0,MAX(0,$G9*Settings!$B$4))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J9" s="12">
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K9" s="13" t="n">
         <v>100</v>
@@ -2937,19 +2962,19 @@
       </c>
       <c r="N9" s="14">
         <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O9" s="14">
         <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P9" s="15">
         <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q9" s="15">
         <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R9" s="15">
         <f>$AT9*$AU9</f>
@@ -2961,7 +2986,7 @@
       </c>
       <c r="T9" s="12">
         <f>IF(AND($B9="BIG_SIDE",$AX9&gt;0),$AX9*Settings!$B$5,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U9" s="12">
         <f>MAX(0,$M9*Settings!$B$9)</f>
@@ -2969,7 +2994,7 @@
       </c>
       <c r="V9" s="12">
         <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W9" s="12">
         <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
@@ -2977,7 +3002,7 @@
       </c>
       <c r="X9" s="19">
         <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y9" s="19">
         <f>$Y8+$X9</f>
@@ -2993,19 +3018,19 @@
       </c>
       <c r="AB9" s="12">
         <f>IF($B9="BLOCKED",$BC9,$D9+$G9+$J9)</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AC9" s="12">
         <f>IF($B9="BLOCKED",$BC9,IF($B9="BIG_SIDE",$W9,IF($AK9=TRUE,$BC9,$AG9)))</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AD9" s="12">
         <f>$AB9*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AE9" s="12">
         <f>$AC9*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AF9" s="12">
         <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
@@ -3027,9 +3052,9 @@
         <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
-      <c r="AK9" s="12" t="b">
+      <c r="AK9" s="12">
         <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL9" s="12">
         <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
@@ -3047,13 +3072,13 @@
         <f>IF(OR($B9="BIG_SIDE",$B9="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP9" s="12" t="str">
+      <c r="AP9" s="12">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"YES",IF(OR($AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="STOP_CLEARED",$AQ9="MANUAL_READY"),"NO","YES"))</f>
-        <v>NO</v>
-      </c>
-      <c r="AQ9" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ9" s="12">
         <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
-        <v>STOP</v>
+        <v/>
       </c>
       <c r="AR9" s="12">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -3061,7 +3086,7 @@
       </c>
       <c r="AS9" s="20">
         <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT9" s="12">
         <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
@@ -3075,9 +3100,9 @@
         <f>IF($B9="SMALL_SIDE",IF($AH9="YES",$D9,IFERROR(MIN($D9,MAX(0,$AI9/$U9)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW9" s="12" t="str">
+      <c r="AW9" s="12">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v/>
       </c>
       <c r="AX9" s="12">
         <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
@@ -3093,15 +3118,15 @@
       </c>
       <c r="BA9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AJ9-$BD9),IF($B9="BLOCKED",MAX(0,$BA8-$BD9),0))</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="BB9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AG9-$BE9),IF($B9="BLOCKED",MAX(0,$BB8-$BE9),0))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="BC9" s="12">
         <f>$BA9+$BB9</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="BD9" s="13" t="n">
         <v>0</v>
@@ -3122,9 +3147,9 @@
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="str">
+      <c r="B10" s="13">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"BIG_SIDE",IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="MANUAL_READY",$AQ9="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BLOCKED</v>
+        <v/>
       </c>
       <c r="C10" s="13">
         <f>IF($B10="BLOCKED",$AF9,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),$AF9,IF($AP9="YES",$AF9,$C9)))</f>
@@ -3140,11 +3165,11 @@
       </c>
       <c r="F10" s="12">
         <f>IF($B10="BLOCKED",0,MAX(0,$D10*Settings!$B$3))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G10" s="12">
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($F10/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H10" s="12">
         <f>IF($B10="BLOCKED","",$C10)</f>
@@ -3152,11 +3177,11 @@
       </c>
       <c r="I10" s="12">
         <f>IF($B10="BLOCKED",0,MAX(0,$G10*Settings!$B$4))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J10" s="12">
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K10" s="13" t="n">
         <v>100</v>
@@ -3169,19 +3194,19 @@
       </c>
       <c r="N10" s="14">
         <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O10" s="14">
         <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P10" s="15">
         <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q10" s="15">
         <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R10" s="15">
         <f>$AT10*$AU10</f>
@@ -3193,7 +3218,7 @@
       </c>
       <c r="T10" s="12">
         <f>IF(AND($B10="BIG_SIDE",$AX10&gt;0),$AX10*Settings!$B$5,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U10" s="12">
         <f>MAX(0,$M10*Settings!$B$9)</f>
@@ -3201,7 +3226,7 @@
       </c>
       <c r="V10" s="12">
         <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W10" s="12">
         <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
@@ -3209,7 +3234,7 @@
       </c>
       <c r="X10" s="19">
         <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y10" s="19">
         <f>$Y9+$X10</f>
@@ -3225,19 +3250,19 @@
       </c>
       <c r="AB10" s="12">
         <f>IF($B10="BLOCKED",$BC10,$D10+$G10+$J10)</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AC10" s="12">
         <f>IF($B10="BLOCKED",$BC10,IF($B10="BIG_SIDE",$W10,IF($AK10=TRUE,$BC10,$AG10)))</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AD10" s="12">
         <f>$AB10*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AE10" s="12">
         <f>$AC10*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AF10" s="12">
         <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
@@ -3259,9 +3284,9 @@
         <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
-      <c r="AK10" s="12" t="b">
+      <c r="AK10" s="12">
         <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL10" s="12">
         <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
@@ -3279,13 +3304,13 @@
         <f>IF(OR($B10="BIG_SIDE",$B10="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP10" s="12" t="str">
+      <c r="AP10" s="12">
         <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"YES",IF(OR($AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="STOP_CLEARED",$AQ10="MANUAL_READY"),"NO","YES"))</f>
-        <v>NO</v>
-      </c>
-      <c r="AQ10" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ10" s="12">
         <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
-        <v>STOP</v>
+        <v/>
       </c>
       <c r="AR10" s="12">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -3293,7 +3318,7 @@
       </c>
       <c r="AS10" s="20">
         <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT10" s="12">
         <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
@@ -3307,9 +3332,9 @@
         <f>IF($B10="SMALL_SIDE",IF($AH10="YES",$D10,IFERROR(MIN($D10,MAX(0,$AI10/$U10)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW10" s="12" t="str">
+      <c r="AW10" s="12">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v/>
       </c>
       <c r="AX10" s="12">
         <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
@@ -3325,15 +3350,15 @@
       </c>
       <c r="BA10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AJ10-$BD10),IF($B10="BLOCKED",MAX(0,$BA9-$BD10),0))</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="BB10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AG10-$BE10),IF($B10="BLOCKED",MAX(0,$BB9-$BE10),0))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="BC10" s="12">
         <f>$BA10+$BB10</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="BD10" s="13" t="n">
         <v>0</v>
@@ -3354,9 +3379,9 @@
       <c r="A11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="str">
+      <c r="B11" s="13">
         <f>IF(AND($AQ10="MANUAL_READY",$BG10="YES"),"BIG_SIDE",IF(OR($AP10="NO",$AQ10="DUAL_TAIL",$AQ10="DANGER",$AQ10="STOP",$AQ10="MANUAL_READY",$AQ10="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BLOCKED</v>
+        <v/>
       </c>
       <c r="C11" s="13">
         <f>IF($B11="BLOCKED",$AF10,IF(AND($AQ10="MANUAL_READY",$BG10="YES"),$AF10,IF($AP10="YES",$AF10,$C10)))</f>
@@ -3372,11 +3397,11 @@
       </c>
       <c r="F11" s="12">
         <f>IF($B11="BLOCKED",0,MAX(0,$D11*Settings!$B$3))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="G11" s="12">
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($F11/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H11" s="12">
         <f>IF($B11="BLOCKED","",$C11)</f>
@@ -3384,11 +3409,11 @@
       </c>
       <c r="I11" s="12">
         <f>IF($B11="BLOCKED",0,MAX(0,$G11*Settings!$B$4))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J11" s="12">
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K11" s="13" t="n">
         <v>100</v>
@@ -3401,19 +3426,19 @@
       </c>
       <c r="N11" s="14">
         <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O11" s="14">
         <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P11" s="15">
         <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q11" s="15">
         <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R11" s="15">
         <f>$AT11*$AU11</f>
@@ -3425,7 +3450,7 @@
       </c>
       <c r="T11" s="12">
         <f>IF(AND($B11="BIG_SIDE",$AX11&gt;0),$AX11*Settings!$B$5,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U11" s="12">
         <f>MAX(0,$M11*Settings!$B$9)</f>
@@ -3433,7 +3458,7 @@
       </c>
       <c r="V11" s="12">
         <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W11" s="12">
         <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
@@ -3441,7 +3466,7 @@
       </c>
       <c r="X11" s="19">
         <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y11" s="19">
         <f>$Y10+$X11</f>
@@ -3457,19 +3482,19 @@
       </c>
       <c r="AB11" s="12">
         <f>IF($B11="BLOCKED",$BC11,$D11+$G11+$J11)</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AC11" s="12">
         <f>IF($B11="BLOCKED",$BC11,IF($B11="BIG_SIDE",$W11,IF($AK11=TRUE,$BC11,$AG11)))</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="AD11" s="12">
         <f>$AB11*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AE11" s="12">
         <f>$AC11*Settings!$B$10</f>
-        <v>989.6</v>
+        <v/>
       </c>
       <c r="AF11" s="12">
         <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
@@ -3491,9 +3516,9 @@
         <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
-      <c r="AK11" s="12" t="b">
+      <c r="AK11" s="12">
         <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL11" s="12">
         <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
@@ -3511,13 +3536,13 @@
         <f>IF(OR($B11="BIG_SIDE",$B11="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP11" s="12" t="str">
+      <c r="AP11" s="12">
         <f>IF(AND($AQ11="MANUAL_READY",$BG11="YES"),"YES",IF(OR($AQ11="DUAL_TAIL",$AQ11="DANGER",$AQ11="STOP",$AQ11="STOP_CLEARED",$AQ11="MANUAL_READY"),"NO","YES"))</f>
-        <v>NO</v>
-      </c>
-      <c r="AQ11" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ11" s="12">
         <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
-        <v>STOP</v>
+        <v/>
       </c>
       <c r="AR11" s="12">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -3525,7 +3550,7 @@
       </c>
       <c r="AS11" s="20">
         <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AT11" s="12">
         <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
@@ -3539,9 +3564,9 @@
         <f>IF($B11="SMALL_SIDE",IF($AH11="YES",$D11,IFERROR(MIN($D11,MAX(0,$AI11/$U11)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW11" s="12" t="str">
+      <c r="AW11" s="12">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v/>
       </c>
       <c r="AX11" s="12">
         <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
@@ -3557,15 +3582,15 @@
       </c>
       <c r="BA11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AJ11-$BD11),IF($B11="BLOCKED",MAX(0,$BA10-$BD11),0))</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="BB11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AG11-$BE11),IF($B11="BLOCKED",MAX(0,$BB10-$BE11),0))</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="BC11" s="12">
         <f>$BA11+$BB11</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="BD11" s="13" t="n">
         <v>0</v>
@@ -4008,7 +4033,7 @@
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -4020,7 +4045,7 @@
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.4</v>
+        <v/>
       </c>
       <c r="K2" s="13" t="n">
         <v>100</v>
@@ -4088,19 +4113,19 @@
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC2" s="12">
         <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
-        <v>0.7</v>
+        <v/>
       </c>
       <c r="AD2" s="12">
         <f>$AB2*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE2" s="12">
         <f>$AC2*Settings!$B$10</f>
-        <v>700</v>
+        <v/>
       </c>
       <c r="AF2" s="12">
         <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
@@ -4122,9 +4147,9 @@
         <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
-      <c r="AK2" s="12" t="b">
+      <c r="AK2" s="12">
         <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL2" s="12">
         <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
@@ -4142,13 +4167,13 @@
         <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP2" s="12" t="str">
+      <c r="AP2" s="12">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
-        <v>YES</v>
-      </c>
-      <c r="AQ2" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ2" s="12">
         <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
-        <v>OK</v>
+        <v/>
       </c>
       <c r="AR2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -4170,7 +4195,7 @@
         <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW2" s="12" t="str">
+      <c r="AW2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -4188,15 +4213,15 @@
       </c>
       <c r="BA2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BB2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BC2" s="12">
         <f>$BA2+$BB2</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BD2" s="13" t="n">
         <v>0</v>
@@ -4217,9 +4242,9 @@
       <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="str">
+      <c r="B3" s="13">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"BIG_SIDE",IF(OR($AP2="NO",$AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="MANUAL_READY",$AQ2="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BIG_SIDE</v>
+        <v/>
       </c>
       <c r="C3" s="13">
         <f>IF($B3="BLOCKED",$AF2,IF(AND($AQ2="MANUAL_READY",$BG2="YES"),$AF2,IF($AP2="YES",$AF2,$C2)))</f>
@@ -4239,7 +4264,7 @@
       </c>
       <c r="G3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H3" s="12">
         <f>IF($B3="BLOCKED","",$C3)</f>
@@ -4251,7 +4276,7 @@
       </c>
       <c r="J3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.4</v>
+        <v/>
       </c>
       <c r="K3" s="13" t="n">
         <v>100</v>
@@ -4320,19 +4345,19 @@
       </c>
       <c r="AB3" s="12">
         <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC3" s="12">
         <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
-        <v>0.7</v>
+        <v/>
       </c>
       <c r="AD3" s="12">
         <f>$AB3*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE3" s="12">
         <f>$AC3*Settings!$B$10</f>
-        <v>700</v>
+        <v/>
       </c>
       <c r="AF3" s="12">
         <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
@@ -4354,9 +4379,9 @@
         <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
         <v/>
       </c>
-      <c r="AK3" s="12" t="b">
+      <c r="AK3" s="12">
         <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL3" s="12">
         <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
@@ -4374,13 +4399,13 @@
         <f>IF(OR($B3="BIG_SIDE",$B3="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP3" s="12" t="str">
+      <c r="AP3" s="12">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"YES",IF(OR($AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="STOP_CLEARED",$AQ3="MANUAL_READY"),"NO","YES"))</f>
-        <v>YES</v>
-      </c>
-      <c r="AQ3" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ3" s="12">
         <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
-        <v>OK</v>
+        <v/>
       </c>
       <c r="AR3" s="12">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -4402,7 +4427,7 @@
         <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW3" s="12" t="str">
+      <c r="AW3" s="12">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -4420,15 +4445,15 @@
       </c>
       <c r="BA3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BB3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BC3" s="12">
         <f>$BA3+$BB3</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BD3" s="13" t="n">
         <v>0</v>
@@ -4449,9 +4474,9 @@
       <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="str">
+      <c r="B4" s="13">
         <f>IF(AND($AQ3="MANUAL_READY",$BG3="YES"),"BIG_SIDE",IF(OR($AP3="NO",$AQ3="DUAL_TAIL",$AQ3="DANGER",$AQ3="STOP",$AQ3="MANUAL_READY",$AQ3="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v>BIG_SIDE</v>
+        <v/>
       </c>
       <c r="C4" s="13">
         <f>IF($B4="BLOCKED",$AF3,IF(AND($AQ3="MANUAL_READY",$BG3="YES"),$AF3,IF($AP3="YES",$AF3,$C3)))</f>
@@ -4471,7 +4496,7 @@
       </c>
       <c r="G4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($F4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H4" s="12">
         <f>IF($B4="BLOCKED","",$C4)</f>
@@ -4483,7 +4508,7 @@
       </c>
       <c r="J4" s="12">
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.4</v>
+        <v/>
       </c>
       <c r="K4" s="13" t="n">
         <v>100</v>
@@ -4552,19 +4577,19 @@
       </c>
       <c r="AB4" s="12">
         <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC4" s="12">
         <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
-        <v>0.7</v>
+        <v/>
       </c>
       <c r="AD4" s="12">
         <f>$AB4*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE4" s="12">
         <f>$AC4*Settings!$B$10</f>
-        <v>700</v>
+        <v/>
       </c>
       <c r="AF4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
@@ -4586,9 +4611,9 @@
         <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
         <v/>
       </c>
-      <c r="AK4" s="12" t="b">
+      <c r="AK4" s="12">
         <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL4" s="12">
         <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
@@ -4606,13 +4631,13 @@
         <f>IF(OR($B4="BIG_SIDE",$B4="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP4" s="12" t="str">
+      <c r="AP4" s="12">
         <f>IF(AND($AQ4="MANUAL_READY",$BG4="YES"),"YES",IF(OR($AQ4="DUAL_TAIL",$AQ4="DANGER",$AQ4="STOP",$AQ4="STOP_CLEARED",$AQ4="MANUAL_READY"),"NO","YES"))</f>
-        <v>YES</v>
-      </c>
-      <c r="AQ4" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ4" s="12">
         <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
-        <v>OK</v>
+        <v/>
       </c>
       <c r="AR4" s="12">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -4634,7 +4659,7 @@
         <f>IF($B4="SMALL_SIDE",IF($AH4="YES",$D4,IFERROR(MIN($D4,MAX(0,$AI4/$U4)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW4" s="12" t="str">
+      <c r="AW4" s="12">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -4652,15 +4677,15 @@
       </c>
       <c r="BA4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BB4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BC4" s="12">
         <f>$BA4+$BB4</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BD4" s="13" t="n">
         <v>0</v>
@@ -4703,7 +4728,7 @@
       </c>
       <c r="G5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($F5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1.0</v>
+        <v/>
       </c>
       <c r="H5" s="12">
         <f>IF($B5="BLOCKED","",$C5)</f>
@@ -4715,7 +4740,7 @@
       </c>
       <c r="J5" s="12">
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.38</v>
+        <v/>
       </c>
       <c r="K5" s="13" t="n">
         <v>80</v>
@@ -4784,7 +4809,7 @@
       </c>
       <c r="AB5" s="12">
         <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC5" s="12">
         <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
@@ -4792,7 +4817,7 @@
       </c>
       <c r="AD5" s="12">
         <f>$AB5*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE5" s="12">
         <f>$AC5*Settings!$B$10</f>
@@ -4818,9 +4843,9 @@
         <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
         <v>0.5216</v>
       </c>
-      <c r="AK5" s="12" t="b">
+      <c r="AK5" s="12">
         <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL5" s="12">
         <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
@@ -4846,9 +4871,9 @@
         <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
         <v>DUAL_TAIL</v>
       </c>
-      <c r="AR5" s="12">
+      <c r="AR5" s="12" t="str">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>DUAL_TAIL: старый и новый хвост сохранены</v>
       </c>
       <c r="AS5" s="20">
         <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
@@ -4866,7 +4891,7 @@
         <f>IF($B5="SMALL_SIDE",IF($AH5="YES",$D5,IFERROR(MIN($D5,MAX(0,$AI5/$U5)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW5" s="12" t="str">
+      <c r="AW5" s="12">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -4894,13 +4919,13 @@
         <f>$BA5+$BB5</f>
         <v>0.9896</v>
       </c>
-      <c r="BD5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" s="20" t="n">
+      <c r="BD5" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="20">
         <v>0</v>
       </c>
       <c r="BG5" s="13" t="inlineStr">
@@ -5050,9 +5075,9 @@
         <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
-      <c r="AK6" s="12" t="b">
+      <c r="AK6" s="12">
         <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL6" s="12">
         <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
@@ -5078,9 +5103,9 @@
         <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR6" s="12">
+      <c r="AR6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS6" s="20">
         <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
@@ -5100,7 +5125,7 @@
       </c>
       <c r="AW6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX6" s="12">
         <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
@@ -5126,13 +5151,13 @@
         <f>$BA6+$BB6</f>
         <v>0.9896</v>
       </c>
-      <c r="BD6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" s="20" t="n">
+      <c r="BD6" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="20">
         <v>0</v>
       </c>
       <c r="BG6" s="13" t="inlineStr">
@@ -5282,9 +5307,9 @@
         <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
-      <c r="AK7" s="12" t="b">
+      <c r="AK7" s="12">
         <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL7" s="12">
         <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
@@ -5310,9 +5335,9 @@
         <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR7" s="12">
+      <c r="AR7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS7" s="20">
         <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
@@ -5332,7 +5357,7 @@
       </c>
       <c r="AW7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX7" s="12">
         <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
@@ -5358,13 +5383,13 @@
         <f>$BA7+$BB7</f>
         <v>0.9896</v>
       </c>
-      <c r="BD7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" s="20" t="n">
+      <c r="BD7" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="20">
         <v>0</v>
       </c>
       <c r="BG7" s="13" t="inlineStr">
@@ -5514,9 +5539,9 @@
         <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
-      <c r="AK8" s="12" t="b">
+      <c r="AK8" s="12">
         <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL8" s="12">
         <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
@@ -5542,9 +5567,9 @@
         <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR8" s="12">
+      <c r="AR8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS8" s="20">
         <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
@@ -5564,7 +5589,7 @@
       </c>
       <c r="AW8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX8" s="12">
         <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
@@ -5590,13 +5615,13 @@
         <f>$BA8+$BB8</f>
         <v>0.9896</v>
       </c>
-      <c r="BD8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" s="20" t="n">
+      <c r="BD8" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="20">
         <v>0</v>
       </c>
       <c r="BG8" s="13" t="inlineStr">
@@ -5746,9 +5771,9 @@
         <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
-      <c r="AK9" s="12" t="b">
+      <c r="AK9" s="12">
         <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL9" s="12">
         <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
@@ -5774,9 +5799,9 @@
         <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR9" s="12">
+      <c r="AR9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS9" s="20">
         <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
@@ -5796,7 +5821,7 @@
       </c>
       <c r="AW9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX9" s="12">
         <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
@@ -5822,13 +5847,13 @@
         <f>$BA9+$BB9</f>
         <v>0.9896</v>
       </c>
-      <c r="BD9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" s="20" t="n">
+      <c r="BD9" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="20">
         <v>0</v>
       </c>
       <c r="BG9" s="13" t="inlineStr">
@@ -5978,9 +6003,9 @@
         <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
-      <c r="AK10" s="12" t="b">
+      <c r="AK10" s="12">
         <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL10" s="12">
         <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
@@ -6006,9 +6031,9 @@
         <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR10" s="12">
+      <c r="AR10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS10" s="20">
         <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
@@ -6028,7 +6053,7 @@
       </c>
       <c r="AW10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX10" s="12">
         <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
@@ -6054,13 +6079,13 @@
         <f>$BA10+$BB10</f>
         <v>0.9896</v>
       </c>
-      <c r="BD10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" s="20" t="n">
+      <c r="BD10" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="20">
         <v>0</v>
       </c>
       <c r="BG10" s="13" t="inlineStr">
@@ -6210,9 +6235,9 @@
         <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
-      <c r="AK11" s="12" t="b">
+      <c r="AK11" s="12">
         <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL11" s="12">
         <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
@@ -6238,9 +6263,9 @@
         <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR11" s="12">
+      <c r="AR11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS11" s="20">
         <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
@@ -6260,7 +6285,7 @@
       </c>
       <c r="AW11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX11" s="12">
         <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
@@ -6286,13 +6311,13 @@
         <f>$BA11+$BB11</f>
         <v>0.9896</v>
       </c>
-      <c r="BD11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" s="20" t="n">
+      <c r="BD11" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="20">
         <v>0</v>
       </c>
       <c r="BG11" s="13" t="inlineStr">
@@ -6727,7 +6752,7 @@
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -6739,7 +6764,7 @@
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.4</v>
+        <v/>
       </c>
       <c r="K2" s="13" t="n">
         <v>100</v>
@@ -6807,19 +6832,19 @@
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC2" s="12">
         <f>IF($B2="BLOCKED",$BC2,IF($B2="BIG_SIDE",$W2,IF($AK2=TRUE,$BC2,$AG2)))</f>
-        <v>0.7</v>
+        <v/>
       </c>
       <c r="AD2" s="12">
         <f>$AB2*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE2" s="12">
         <f>$AC2*Settings!$B$10</f>
-        <v>700</v>
+        <v/>
       </c>
       <c r="AF2" s="12">
         <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
@@ -6841,9 +6866,9 @@
         <f>IF($B2="SMALL_SIDE",MAX(0,$D2-$AV2),0)</f>
         <v/>
       </c>
-      <c r="AK2" s="12" t="b">
+      <c r="AK2" s="12">
         <f>IF(AND($AJ2&gt;0,$AG2&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL2" s="12">
         <f>IF($B2="SMALL_SIDE",$G2*Settings!$B$7,IF($B2="BIG_SIDE",$G2,0))</f>
@@ -6861,13 +6886,13 @@
         <f>IF(OR($B2="BIG_SIDE",$B2="SMALL_SIDE"),1,0)</f>
         <v/>
       </c>
-      <c r="AP2" s="12" t="str">
+      <c r="AP2" s="12">
         <f>IF(AND($AQ2="MANUAL_READY",$BG2="YES"),"YES",IF(OR($AQ2="DUAL_TAIL",$AQ2="DANGER",$AQ2="STOP",$AQ2="STOP_CLEARED",$AQ2="MANUAL_READY"),"NO","YES"))</f>
-        <v>YES</v>
-      </c>
-      <c r="AQ2" s="12" t="str">
+        <v/>
+      </c>
+      <c r="AQ2" s="12">
         <f>IF($B2="BLOCKED",IF($BC2=0,"STOP_CLEARED",IF(OR(AND($BA2=0,$BB2&gt;0),AND($BA2&gt;0,$BB2=0)),"MANUAL_READY","STOP")),IF($AK2=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G2/$D2,0)&gt;Settings!$B$16,IFERROR($J2/$G2,0)&gt;Settings!$B$17,$AE2&gt;$AD2,$Y2&lt;0,$AG2&gt;$D2*1.0001,$S2&lt;-100),"DANGER",IF(OR(AND($B2="BIG_SIDE",$U2&lt;=0),$S2&lt;=0,$X2=0,$AE2&gt;$AD2*0.95),"WARNING","OK"))))</f>
-        <v>OK</v>
+        <v/>
       </c>
       <c r="AR2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B2="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ2="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
@@ -6889,7 +6914,7 @@
         <f>IF($B2="SMALL_SIDE",IF($AH2="YES",$D2,IFERROR(MIN($D2,MAX(0,$AI2/$U2)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW2" s="12" t="str">
+      <c r="AW2" s="12">
         <f>IF($B2="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -6907,15 +6932,15 @@
       </c>
       <c r="BA2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AJ2-$BD2),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BB2" s="12">
         <f>IF($AK2=TRUE,MAX(0,$AG2-$BE2),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BC2" s="12">
         <f>$BA2+$BB2</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="BD2" s="13" t="n">
         <v>0</v>
@@ -6958,7 +6983,7 @@
       </c>
       <c r="G3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($F3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>1.0</v>
+        <v/>
       </c>
       <c r="H3" s="12">
         <f>IF($B3="BLOCKED","",$C3)</f>
@@ -6970,7 +6995,7 @@
       </c>
       <c r="J3" s="12">
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v>0.38</v>
+        <v/>
       </c>
       <c r="K3" s="13" t="n">
         <v>80</v>
@@ -7039,7 +7064,7 @@
       </c>
       <c r="AB3" s="12">
         <f>IF($B3="BLOCKED",$BC3,$D3+$G3+$J3)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="AC3" s="12">
         <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
@@ -7047,11 +7072,11 @@
       </c>
       <c r="AD3" s="12">
         <f>$AB3*Settings!$B$10</f>
-        <v>2000</v>
+        <v/>
       </c>
       <c r="AE3" s="12">
         <f>$AC3*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF3" s="12">
         <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
@@ -7073,9 +7098,9 @@
         <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
         <v>0.8</v>
       </c>
-      <c r="AK3" s="12" t="b">
+      <c r="AK3" s="12">
         <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AL3" s="12">
         <f>IF($B3="SMALL_SIDE",$G3*Settings!$B$7,IF($B3="BIG_SIDE",$G3,0))</f>
@@ -7101,9 +7126,9 @@
         <f>IF($B3="BLOCKED",IF($BC3=0,"STOP_CLEARED",IF(OR(AND($BA3=0,$BB3&gt;0),AND($BA3&gt;0,$BB3=0)),"MANUAL_READY","STOP")),IF($AK3=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G3/$D3,0)&gt;Settings!$B$16,IFERROR($J3/$G3,0)&gt;Settings!$B$17,$AE3&gt;$AD3,$Y3&lt;0,$AG3&gt;$D3*1.0001,$S3&lt;-100),"DANGER",IF(OR(AND($B3="BIG_SIDE",$U3&lt;=0),$S3&lt;=0,$X3=0,$AE3&gt;$AD3*0.95),"WARNING","OK"))))</f>
         <v>DUAL_TAIL</v>
       </c>
-      <c r="AR3" s="12">
+      <c r="AR3" s="12" t="str">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B3="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ3="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>DUAL_TAIL: старый и новый хвост сохранены</v>
       </c>
       <c r="AS3" s="20">
         <f>IF($B3="BIG_SIDE",$V3*$U3,0)</f>
@@ -7121,7 +7146,7 @@
         <f>IF($B3="SMALL_SIDE",IF($AH3="YES",$D3,IFERROR(MIN($D3,MAX(0,$AI3/$U3)),0)),0)</f>
         <v/>
       </c>
-      <c r="AW3" s="12" t="str">
+      <c r="AW3" s="12">
         <f>IF($B3="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
         <v/>
       </c>
@@ -7149,13 +7174,13 @@
         <f>$BA3+$BB3</f>
         <v>1.697</v>
       </c>
-      <c r="BD3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" s="20" t="n">
+      <c r="BD3" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="20">
         <v>0</v>
       </c>
       <c r="BG3" s="13" t="inlineStr">
@@ -7279,11 +7304,11 @@
       </c>
       <c r="AD4" s="12">
         <f>$AB4*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AE4" s="12">
         <f>$AC4*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
@@ -7305,9 +7330,9 @@
         <f>IF($B4="SMALL_SIDE",MAX(0,$D4-$AV4),0)</f>
         <v/>
       </c>
-      <c r="AK4" s="12" t="b">
+      <c r="AK4" s="12">
         <f>IF(AND($AJ4&gt;0,$AG4&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL4" s="12">
         <f>IF($B4="SMALL_SIDE",$G4*Settings!$B$7,IF($B4="BIG_SIDE",$G4,0))</f>
@@ -7333,9 +7358,9 @@
         <f>IF($B4="BLOCKED",IF($BC4=0,"STOP_CLEARED",IF(OR(AND($BA4=0,$BB4&gt;0),AND($BA4&gt;0,$BB4=0)),"MANUAL_READY","STOP")),IF($AK4=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G4/$D4,0)&gt;Settings!$B$16,IFERROR($J4/$G4,0)&gt;Settings!$B$17,$AE4&gt;$AD4,$Y4&lt;0,$AG4&gt;$D4*1.0001,$S4&lt;-100),"DANGER",IF(OR(AND($B4="BIG_SIDE",$U4&lt;=0),$S4&lt;=0,$X4=0,$AE4&gt;$AD4*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR4" s="12">
+      <c r="AR4" s="12" t="str">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS4" s="20">
         <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
@@ -7355,7 +7380,7 @@
       </c>
       <c r="AW4" s="12" t="str">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX4" s="12">
         <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
@@ -7381,13 +7406,13 @@
         <f>$BA4+$BB4</f>
         <v>1.697</v>
       </c>
-      <c r="BD4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" s="20" t="n">
+      <c r="BD4" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="20">
         <v>0</v>
       </c>
       <c r="BG4" s="13" t="inlineStr">
@@ -7511,11 +7536,11 @@
       </c>
       <c r="AD5" s="12">
         <f>$AB5*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AE5" s="12">
         <f>$AC5*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF5" s="12">
         <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
@@ -7537,9 +7562,9 @@
         <f>IF($B5="SMALL_SIDE",MAX(0,$D5-$AV5),0)</f>
         <v/>
       </c>
-      <c r="AK5" s="12" t="b">
+      <c r="AK5" s="12">
         <f>IF(AND($AJ5&gt;0,$AG5&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL5" s="12">
         <f>IF($B5="SMALL_SIDE",$G5*Settings!$B$7,IF($B5="BIG_SIDE",$G5,0))</f>
@@ -7565,9 +7590,9 @@
         <f>IF($B5="BLOCKED",IF($BC5=0,"STOP_CLEARED",IF(OR(AND($BA5=0,$BB5&gt;0),AND($BA5&gt;0,$BB5=0)),"MANUAL_READY","STOP")),IF($AK5=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G5/$D5,0)&gt;Settings!$B$16,IFERROR($J5/$G5,0)&gt;Settings!$B$17,$AE5&gt;$AD5,$Y5&lt;0,$AG5&gt;$D5*1.0001,$S5&lt;-100),"DANGER",IF(OR(AND($B5="BIG_SIDE",$U5&lt;=0),$S5&lt;=0,$X5=0,$AE5&gt;$AD5*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR5" s="12">
+      <c r="AR5" s="12" t="str">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS5" s="20">
         <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
@@ -7587,7 +7612,7 @@
       </c>
       <c r="AW5" s="12" t="str">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX5" s="12">
         <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
@@ -7613,13 +7638,13 @@
         <f>$BA5+$BB5</f>
         <v>1.697</v>
       </c>
-      <c r="BD5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" s="20" t="n">
+      <c r="BD5" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="20">
         <v>0</v>
       </c>
       <c r="BG5" s="13" t="inlineStr">
@@ -7743,11 +7768,11 @@
       </c>
       <c r="AD6" s="12">
         <f>$AB6*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AE6" s="12">
         <f>$AC6*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF6" s="12">
         <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
@@ -7769,9 +7794,9 @@
         <f>IF($B6="SMALL_SIDE",MAX(0,$D6-$AV6),0)</f>
         <v/>
       </c>
-      <c r="AK6" s="12" t="b">
+      <c r="AK6" s="12">
         <f>IF(AND($AJ6&gt;0,$AG6&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL6" s="12">
         <f>IF($B6="SMALL_SIDE",$G6*Settings!$B$7,IF($B6="BIG_SIDE",$G6,0))</f>
@@ -7797,9 +7822,9 @@
         <f>IF($B6="BLOCKED",IF($BC6=0,"STOP_CLEARED",IF(OR(AND($BA6=0,$BB6&gt;0),AND($BA6&gt;0,$BB6=0)),"MANUAL_READY","STOP")),IF($AK6=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G6/$D6,0)&gt;Settings!$B$16,IFERROR($J6/$G6,0)&gt;Settings!$B$17,$AE6&gt;$AD6,$Y6&lt;0,$AG6&gt;$D6*1.0001,$S6&lt;-100),"DANGER",IF(OR(AND($B6="BIG_SIDE",$U6&lt;=0),$S6&lt;=0,$X6=0,$AE6&gt;$AD6*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR6" s="12">
+      <c r="AR6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS6" s="20">
         <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
@@ -7819,7 +7844,7 @@
       </c>
       <c r="AW6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX6" s="12">
         <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
@@ -7845,13 +7870,13 @@
         <f>$BA6+$BB6</f>
         <v>1.697</v>
       </c>
-      <c r="BD6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" s="20" t="n">
+      <c r="BD6" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="20">
         <v>0</v>
       </c>
       <c r="BG6" s="13" t="inlineStr">
@@ -7975,11 +8000,11 @@
       </c>
       <c r="AD7" s="12">
         <f>$AB7*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AE7" s="12">
         <f>$AC7*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF7" s="12">
         <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
@@ -8001,9 +8026,9 @@
         <f>IF($B7="SMALL_SIDE",MAX(0,$D7-$AV7),0)</f>
         <v/>
       </c>
-      <c r="AK7" s="12" t="b">
+      <c r="AK7" s="12">
         <f>IF(AND($AJ7&gt;0,$AG7&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL7" s="12">
         <f>IF($B7="SMALL_SIDE",$G7*Settings!$B$7,IF($B7="BIG_SIDE",$G7,0))</f>
@@ -8029,9 +8054,9 @@
         <f>IF($B7="BLOCKED",IF($BC7=0,"STOP_CLEARED",IF(OR(AND($BA7=0,$BB7&gt;0),AND($BA7&gt;0,$BB7=0)),"MANUAL_READY","STOP")),IF($AK7=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G7/$D7,0)&gt;Settings!$B$16,IFERROR($J7/$G7,0)&gt;Settings!$B$17,$AE7&gt;$AD7,$Y7&lt;0,$AG7&gt;$D7*1.0001,$S7&lt;-100),"DANGER",IF(OR(AND($B7="BIG_SIDE",$U7&lt;=0),$S7&lt;=0,$X7=0,$AE7&gt;$AD7*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR7" s="12">
+      <c r="AR7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS7" s="20">
         <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
@@ -8051,7 +8076,7 @@
       </c>
       <c r="AW7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX7" s="12">
         <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
@@ -8077,13 +8102,13 @@
         <f>$BA7+$BB7</f>
         <v>1.697</v>
       </c>
-      <c r="BD7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" s="20" t="n">
+      <c r="BD7" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="20">
         <v>0</v>
       </c>
       <c r="BG7" s="13" t="inlineStr">
@@ -8207,11 +8232,11 @@
       </c>
       <c r="AD8" s="12">
         <f>$AB8*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AE8" s="12">
         <f>$AC8*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF8" s="12">
         <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
@@ -8233,9 +8258,9 @@
         <f>IF($B8="SMALL_SIDE",MAX(0,$D8-$AV8),0)</f>
         <v/>
       </c>
-      <c r="AK8" s="12" t="b">
+      <c r="AK8" s="12">
         <f>IF(AND($AJ8&gt;0,$AG8&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL8" s="12">
         <f>IF($B8="SMALL_SIDE",$G8*Settings!$B$7,IF($B8="BIG_SIDE",$G8,0))</f>
@@ -8261,9 +8286,9 @@
         <f>IF($B8="BLOCKED",IF($BC8=0,"STOP_CLEARED",IF(OR(AND($BA8=0,$BB8&gt;0),AND($BA8&gt;0,$BB8=0)),"MANUAL_READY","STOP")),IF($AK8=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G8/$D8,0)&gt;Settings!$B$16,IFERROR($J8/$G8,0)&gt;Settings!$B$17,$AE8&gt;$AD8,$Y8&lt;0,$AG8&gt;$D8*1.0001,$S8&lt;-100),"DANGER",IF(OR(AND($B8="BIG_SIDE",$U8&lt;=0),$S8&lt;=0,$X8=0,$AE8&gt;$AD8*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR8" s="12">
+      <c r="AR8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS8" s="20">
         <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
@@ -8283,7 +8308,7 @@
       </c>
       <c r="AW8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX8" s="12">
         <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
@@ -8309,13 +8334,13 @@
         <f>$BA8+$BB8</f>
         <v>1.697</v>
       </c>
-      <c r="BD8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" s="20" t="n">
+      <c r="BD8" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="20">
         <v>0</v>
       </c>
       <c r="BG8" s="13" t="inlineStr">
@@ -8439,11 +8464,11 @@
       </c>
       <c r="AD9" s="12">
         <f>$AB9*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AE9" s="12">
         <f>$AC9*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF9" s="12">
         <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
@@ -8465,9 +8490,9 @@
         <f>IF($B9="SMALL_SIDE",MAX(0,$D9-$AV9),0)</f>
         <v/>
       </c>
-      <c r="AK9" s="12" t="b">
+      <c r="AK9" s="12">
         <f>IF(AND($AJ9&gt;0,$AG9&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL9" s="12">
         <f>IF($B9="SMALL_SIDE",$G9*Settings!$B$7,IF($B9="BIG_SIDE",$G9,0))</f>
@@ -8493,9 +8518,9 @@
         <f>IF($B9="BLOCKED",IF($BC9=0,"STOP_CLEARED",IF(OR(AND($BA9=0,$BB9&gt;0),AND($BA9&gt;0,$BB9=0)),"MANUAL_READY","STOP")),IF($AK9=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G9/$D9,0)&gt;Settings!$B$16,IFERROR($J9/$G9,0)&gt;Settings!$B$17,$AE9&gt;$AD9,$Y9&lt;0,$AG9&gt;$D9*1.0001,$S9&lt;-100),"DANGER",IF(OR(AND($B9="BIG_SIDE",$U9&lt;=0),$S9&lt;=0,$X9=0,$AE9&gt;$AD9*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR9" s="12">
+      <c r="AR9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS9" s="20">
         <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
@@ -8515,7 +8540,7 @@
       </c>
       <c r="AW9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX9" s="12">
         <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
@@ -8541,13 +8566,13 @@
         <f>$BA9+$BB9</f>
         <v>1.697</v>
       </c>
-      <c r="BD9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" s="20" t="n">
+      <c r="BD9" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="20">
         <v>0</v>
       </c>
       <c r="BG9" s="13" t="inlineStr">
@@ -8671,11 +8696,11 @@
       </c>
       <c r="AD10" s="12">
         <f>$AB10*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AE10" s="12">
         <f>$AC10*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF10" s="12">
         <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
@@ -8697,9 +8722,9 @@
         <f>IF($B10="SMALL_SIDE",MAX(0,$D10-$AV10),0)</f>
         <v/>
       </c>
-      <c r="AK10" s="12" t="b">
+      <c r="AK10" s="12">
         <f>IF(AND($AJ10&gt;0,$AG10&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL10" s="12">
         <f>IF($B10="SMALL_SIDE",$G10*Settings!$B$7,IF($B10="BIG_SIDE",$G10,0))</f>
@@ -8725,9 +8750,9 @@
         <f>IF($B10="BLOCKED",IF($BC10=0,"STOP_CLEARED",IF(OR(AND($BA10=0,$BB10&gt;0),AND($BA10&gt;0,$BB10=0)),"MANUAL_READY","STOP")),IF($AK10=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G10/$D10,0)&gt;Settings!$B$16,IFERROR($J10/$G10,0)&gt;Settings!$B$17,$AE10&gt;$AD10,$Y10&lt;0,$AG10&gt;$D10*1.0001,$S10&lt;-100),"DANGER",IF(OR(AND($B10="BIG_SIDE",$U10&lt;=0),$S10&lt;=0,$X10=0,$AE10&gt;$AD10*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR10" s="12">
+      <c r="AR10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS10" s="20">
         <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
@@ -8747,7 +8772,7 @@
       </c>
       <c r="AW10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX10" s="12">
         <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
@@ -8773,13 +8798,13 @@
         <f>$BA10+$BB10</f>
         <v>1.697</v>
       </c>
-      <c r="BD10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" s="20" t="n">
+      <c r="BD10" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="20">
         <v>0</v>
       </c>
       <c r="BG10" s="13" t="inlineStr">
@@ -8903,11 +8928,11 @@
       </c>
       <c r="AD11" s="12">
         <f>$AB11*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AE11" s="12">
         <f>$AC11*Settings!$B$10</f>
-        <v>1697.0</v>
+        <v>1697</v>
       </c>
       <c r="AF11" s="12">
         <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
@@ -8929,9 +8954,9 @@
         <f>IF($B11="SMALL_SIDE",MAX(0,$D11-$AV11),0)</f>
         <v/>
       </c>
-      <c r="AK11" s="12" t="b">
+      <c r="AK11" s="12">
         <f>IF(AND($AJ11&gt;0,$AG11&gt;0),TRUE,FALSE)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AL11" s="12">
         <f>IF($B11="SMALL_SIDE",$G11*Settings!$B$7,IF($B11="BIG_SIDE",$G11,0))</f>
@@ -8957,9 +8982,9 @@
         <f>IF($B11="BLOCKED",IF($BC11=0,"STOP_CLEARED",IF(OR(AND($BA11=0,$BB11&gt;0),AND($BA11&gt;0,$BB11=0)),"MANUAL_READY","STOP")),IF($AK11=TRUE,"DUAL_TAIL",IF(OR(IFERROR($G11/$D11,0)&gt;Settings!$B$16,IFERROR($J11/$G11,0)&gt;Settings!$B$17,$AE11&gt;$AD11,$Y11&lt;0,$AG11&gt;$D11*1.0001,$S11&lt;-100),"DANGER",IF(OR(AND($B11="BIG_SIDE",$U11&lt;=0),$S11&lt;=0,$X11=0,$AE11&gt;$AD11*0.95),"WARNING","OK"))))</f>
         <v>STOP</v>
       </c>
-      <c r="AR11" s="12">
+      <c r="AR11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v/>
+        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
       </c>
       <c r="AS11" s="20">
         <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
@@ -8979,7 +9004,7 @@
       </c>
       <c r="AW11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия","")</f>
-        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
+        <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX11" s="12">
         <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
@@ -9005,13 +9030,13 @@
         <f>$BA11+$BB11</f>
         <v>1.697</v>
       </c>
-      <c r="BD11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" s="20" t="n">
+      <c r="BD11" s="13">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="13">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="20">
         <v>0</v>
       </c>
       <c r="BG11" s="13" t="inlineStr">
@@ -9057,381 +9082,687 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Формула / источник</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Значение</t>
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>Formula / Source</t>
+        </is>
+      </c>
+      <c r="D1" s="22" t="inlineStr">
+        <is>
+          <t>Display Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Total Closed Profit</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>SUM ProfitBig + ProfitSmall + positive OldFarClosePL</t>
-        </is>
-      </c>
-      <c r="C2" s="3">
-        <f>SUM(Calculator!N2:O11)+SUMIF(Calculator!AI2:AI11,"&gt;0",Calculator!AI2:AI11)</f>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C2">
+        <f>SUM(Calculator!N2:N11)+SUM(Calculator!O2:O11)+SUMIF(Calculator!AI2:AI11,"&gt;0",Calculator!AI2:AI11)</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>C2</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Total Closed Loss</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>LossSmall + LossClosedBig + Costs + RealizedFarLoss + negative OldFarClosePL</t>
-        </is>
-      </c>
-      <c r="C3" s="3">
-        <f>SUM(Calculator!P2:Q11)+SUM(Calculator!R2:R11)+SUM(Calculator!AS2:AS11)-SUMIF(Calculator!AI2:AI11,"&lt;0",Calculator!AI2:AI11)</f>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>SUM(Calculator!P2:P11)+SUM(Calculator!Q2:Q11)+SUM(Calculator!R2:R11)+SUM(Calculator!AS2:AS11)+SUMIF(Calculator!AI2:AI11,"&lt;0",Calculator!AI2:AI11)*-1</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>C3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Total Realized Far Loss</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>SUM RealizedFarLoss</t>
-        </is>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C4">
         <f>SUM(Calculator!AS2:AS11)</f>
         <v/>
       </c>
+      <c r="D4">
+        <f>C4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Final Balance</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>last BalanceAfter</t>
-        </is>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C5">
         <f>LOOKUP(2,1/(Calculator!AA2:AA11&lt;&gt;""),Calculator!AA2:AA11)</f>
         <v/>
       </c>
+      <c r="D5">
+        <f>C5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Final Reserve</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>last TotalReserve</t>
-        </is>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C6">
         <f>LOOKUP(2,1/(Calculator!Y2:Y11&lt;&gt;""),Calculator!Y2:Y11)</f>
         <v/>
       </c>
+      <c r="D6">
+        <f>C6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Max Margin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>MAX MarginBefore</t>
-        </is>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C7">
         <f>MAX(Calculator!AD2:AD11)</f>
         <v/>
       </c>
+      <c r="D7">
+        <f>C7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Max Open Lots</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>MAX OpenLotsBefore</t>
-        </is>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C8">
         <f>MAX(Calculator!AB2:AB11)</f>
         <v/>
       </c>
+      <c r="D8">
+        <f>C8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Final Far Lot</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>last NewFarStartLot</t>
-        </is>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C9">
         <f>LOOKUP(2,1/(Calculator!AG2:AG11&lt;&gt;""),Calculator!AG2:AG11)</f>
         <v/>
       </c>
+      <c r="D9">
+        <f>C9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Number of BIG_SIDE</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>COUNTIF Scenario</t>
-        </is>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C10">
         <f>COUNTIF(Calculator!B2:B11,"BIG_SIDE")</f>
         <v/>
       </c>
+      <c r="D10">
+        <f>C10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Number of SMALL_SIDE</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>COUNTIF Scenario</t>
-        </is>
-      </c>
-      <c r="C11" s="3">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C11">
         <f>COUNTIF(Calculator!B2:B11,"SMALL_SIDE")</f>
         <v/>
       </c>
+      <c r="D11">
+        <f>C11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Dual Tail Count</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>COUNTIF Status DUAL_TAIL</t>
-        </is>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C12">
         <f>COUNTIF(Calculator!AQ2:AQ11,"DUAL_TAIL")</f>
         <v>1</v>
       </c>
+      <c r="D12">
+        <f>C12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Danger Count</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>COUNTIF Status DANGER</t>
-        </is>
-      </c>
-      <c r="C13" s="3">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C13">
         <f>COUNTIF(Calculator!AQ2:AQ11,"DANGER")</f>
         <v/>
       </c>
+      <c r="D13">
+        <f>C13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Stop Count</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>COUNTIF Status STOP</t>
-        </is>
-      </c>
-      <c r="C14" s="3">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C14">
         <f>COUNTIF(Calculator!AQ2:AQ11,"STOP")</f>
         <v>7</v>
       </c>
+      <c r="D14">
+        <f>C14</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Final Status</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>last Status</t>
-        </is>
-      </c>
-      <c r="C15" s="3">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C15">
         <f>LOOKUP(2,1/(Calculator!AQ2:AQ11&lt;&gt;""),Calculator!AQ2:AQ11)</f>
         <v/>
       </c>
+      <c r="D15">
+        <f>C15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Max DualTail Exposure</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>MAX DualTailTotalLot</t>
-        </is>
-      </c>
-      <c r="C16" s="3">
-        <f>MAX(Calculator!BC2:BC11)</f>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>MAX(Calculator!BB2:BB11)</f>
         <v>0.9896</v>
       </c>
+      <c r="D16">
+        <f>C16</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Final ActiveOldFarLot</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>last ActiveOldFarLot</t>
-        </is>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C17">
+        <f>LOOKUP(2,1/(Calculator!AZ2:AZ11&lt;&gt;""),Calculator!AZ2:AZ11)</f>
+        <v>0.5216</v>
+      </c>
+      <c r="D17">
+        <f>C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Final ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C18">
         <f>LOOKUP(2,1/(Calculator!BA2:BA11&lt;&gt;""),Calculator!BA2:BA11)</f>
-        <v>0.5216</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Final ActiveNewFarLot</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>last ActiveNewFarLot</t>
-        </is>
-      </c>
-      <c r="C18" s="3">
+        <v>0.468</v>
+      </c>
+      <c r="D18">
+        <f>C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Final DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C19">
         <f>LOOKUP(2,1/(Calculator!BB2:BB11&lt;&gt;""),Calculator!BB2:BB11)</f>
-        <v>0.468</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Final DualTailTotalLot</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>last DualTailTotalLot</t>
-        </is>
-      </c>
-      <c r="C19" s="3">
-        <f>LOOKUP(2,1/(Calculator!BC2:BC11&lt;&gt;""),Calculator!BC2:BC11)</f>
         <v>0.9896</v>
       </c>
+      <c r="D19">
+        <f>C19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Manual Close PL</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>SUM ManualClosePL</t>
-        </is>
-      </c>
-      <c r="C20" s="3">
-        <f>SUM(Calculator!BF2:BF11)</f>
-        <v>0</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>SUM(Calculator!BE2:BE11)</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>C20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Blocked Levels Count</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>COUNTIF Scenario BLOCKED</t>
-        </is>
-      </c>
-      <c r="C21" s="3">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C21">
         <f>COUNTIF(Calculator!B2:B11,"BLOCKED")</f>
         <v>7</v>
       </c>
+      <c r="D21">
+        <f>C21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Stop Cleared Count</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>COUNTIF Status STOP_CLEARED</t>
-        </is>
-      </c>
-      <c r="C22" s="3">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C22">
         <f>COUNTIF(Calculator!AQ2:AQ11,"STOP_CLEARED")</f>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>C22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Manual Ready Count</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>COUNTIF Status MANUAL_READY</t>
-        </is>
-      </c>
-      <c r="C23" s="3">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Calculator Summary</t>
+        </is>
+      </c>
+      <c r="C23">
         <f>COUNTIF(Calculator!AQ2:AQ11,"MANUAL_READY")</f>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Global Total Closed Profit</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>SUM(Calculator!N2:O11,Trend_UP!N2:O11,Trend_DOWN!N2:O11)+SUMIF(Calculator!AI2:AI11,"&gt;0",Calculator!AI2:AI11)+SUMIF(Trend_UP!AI2:AI11,"&gt;0",Trend_UP!AI2:AI11)+SUMIF(Trend_DOWN!AI2:AI11,"&gt;0",Trend_DOWN!AI2:AI11)</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Global Total Closed Loss</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C27">
+        <f>SUM(Calculator!P2:R11,Trend_UP!P2:R11,Trend_DOWN!P2:R11)+SUM(Calculator!AS2:AS11,Trend_UP!AS2:AS11,Trend_DOWN!AS2:AS11)-SUMIF(Calculator!AI2:AI11,"&lt;0",Calculator!AI2:AI11)-SUMIF(Trend_UP!AI2:AI11,"&lt;0",Trend_UP!AI2:AI11)-SUMIF(Trend_DOWN!AI2:AI11,"&lt;0",Trend_DOWN!AI2:AI11)</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Global Total Realized Far Loss</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C28">
+        <f>SUM(Calculator!AS2:AS11,Trend_UP!AS2:AS11,Trend_DOWN!AS2:AS11)</f>
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <f>C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Global Max Margin</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C29">
+        <f>MAX(Calculator!AD2:AD11,Trend_UP!AD2:AD11,Trend_DOWN!AD2:AD11)</f>
+        <v>2590</v>
+      </c>
+      <c r="D29">
+        <f>C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Global Max Open Lots</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C30">
+        <f>MAX(Calculator!AB2:AB11,Trend_UP!AB2:AB11,Trend_DOWN!AB2:AB11)</f>
+        <v>2.59</v>
+      </c>
+      <c r="D30">
+        <f>C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Global Dual Tail Count</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C31">
+        <f>COUNTIF(Calculator!AQ2:AQ11,"DUAL_TAIL")+COUNTIF(Trend_UP!AQ2:AQ11,"DUAL_TAIL")+COUNTIF(Trend_DOWN!AQ2:AQ11,"DUAL_TAIL")</f>
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <f>C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Global Blocked Levels Count</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C32">
+        <f>COUNTIF(Calculator!B2:B11,"BLOCKED")+COUNTIF(Trend_UP!B2:B11,"BLOCKED")+COUNTIF(Trend_DOWN!B2:B11,"BLOCKED")</f>
+        <v>14</v>
+      </c>
+      <c r="D32">
+        <f>C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Global Stop Count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>COUNTIF(Calculator!AQ2:AQ11,"STOP")+COUNTIF(Trend_UP!AQ2:AQ11,"STOP")+COUNTIF(Trend_DOWN!AQ2:AQ11,"STOP")</f>
+        <v>14</v>
+      </c>
+      <c r="D33">
+        <f>C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Global Max DualTail Exposure</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>MAX(Calculator!BB2:BB11,Trend_UP!BB2:BB11,Trend_DOWN!BB2:BB11)</f>
+        <v>1.697</v>
+      </c>
+      <c r="D34">
+        <f>C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Global Danger Count</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Global Risk Summary</t>
+        </is>
+      </c>
+      <c r="C35">
+        <f>COUNTIF(Calculator!AQ2:AQ11,"DANGER")+COUNTIF(Trend_UP!AQ2:AQ11,"DANGER")+COUNTIF(Trend_DOWN!AQ2:AQ11,"DANGER")</f>
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f>C35</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -9445,56 +9776,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="64" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="C1" s="21" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="D1" s="21" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="E1" s="21" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="F1" s="21" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>Formula Checked</t>
         </is>
       </c>
-      <c r="G1" s="21" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -12268,6 +12599,509 @@
       <c r="H67" s="3" t="inlineStr">
         <is>
           <t>Новый уровень после DUAL_TAIL не открывается автоматически.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>V6-01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Same headers on Calculator/Trend_UP/Trend_DOWN</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Headers rows 1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Identical header order</t>
+        </is>
+      </c>
+      <c r="E68">
+        <f>IF(AND(COUNTA(Calculator!1:1)=COUNTA(Trend_UP!1:1),COUNTA(Calculator!1:1)=COUNTA(Trend_DOWN!1:1)),"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Header synchronization</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>All calculation sheets use the same generated schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>V6-02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Same Big formulas</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BigLotRaw/BigLot first rows</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Formula pattern uses Settings BigRatio</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Big formulas checked by pytest</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>openpyxl pytest compares formulas directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>V6-03</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Same Small formulas</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SmallLotRaw/SmallLot first rows</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Formula pattern uses Settings SmallRatio</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Small formulas checked by pytest</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>openpyxl pytest compares formulas directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>V6-04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Trend_UP DUAL_TAIL persists</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Trend_UP status/active tails</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot &gt; 0 after DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Data-only pytest/smoke</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Trend_UP keeps ActiveOldFarLot and ActiveNewFarLot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>V6-05</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Trend_DOWN DUAL_TAIL persists</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Trend_DOWN status/active tails</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot &gt; 0 after DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Data-only pytest/smoke</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Trend_DOWN keeps ActiveOldFarLot and ActiveNewFarLot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>V6-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Trend_UP BLOCKED keeps tails</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Trend_UP BLOCKED rows</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OpenLotsAfter = DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Data-only pytest/smoke</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>No empty key fields in BLOCKED rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>V6-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Trend_DOWN BLOCKED keeps tails</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Trend_DOWN BLOCKED rows</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>OpenLotsAfter = DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Data-only pytest/smoke</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>No empty key fields in BLOCKED rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>V6-08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Risk sees Trend_UP dual tail</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Risk_Analysis Global Summary</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Global Dual Tail Count &gt; 0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Risk_Analysis formulas</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Global block includes Trend_UP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>V6-09</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Risk sees Trend_DOWN dual tail</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Risk_Analysis Global Summary</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Global Max DualTail Exposure &gt; 0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Risk_Analysis formulas</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Global block includes Trend_DOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>V6-10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Global summary all sheets</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Calculator + Trend_UP + Trend_DOWN</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Global formulas reference all three sheets</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Formula text inspection</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Global Risk Summary aggregates all calculation sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>V6-11</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Settings links exist</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Formula-bearing calc sheets</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Settings! references exist</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Formula text inspection</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Settings remains the single editable parameter source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>V6-12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Workbook auto calculation</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Workbook calc properties</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>auto/full/force recalc enabled</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Workbook properties</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Excel recalculates formulas on open.</t>
         </is>
       </c>
     </row>
@@ -20398,211 +21232,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Пример</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Значение / формула</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Пояснение</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Source Sheet</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Source Row</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Far</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Big</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>NetProfit</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>CloseFarBudget</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ReserveAdd</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>OpenLotsAfter</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>MarginAfter</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Пример 1. Тренд вверх</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Start Far</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>SELL 1.00</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Исходный дальний хвост после роста цены.</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Пример 1. Тренд вверх — BIG_SIDE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Trend_UP</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <f>Trend_UP!C2&amp;" "&amp;TEXT(Trend_UP!D2,"0.00")</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>Trend_UP!E2&amp;" "&amp;TEXT(Trend_UP!G2,"0.00")</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>Trend_UP!H2&amp;" "&amp;TEXT(Trend_UP!J2,"0.00")</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>Trend_UP!B2</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>Trend_UP!S2</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>Trend_UP!T2</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>Trend_UP!X2</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>Trend_UP!AZ2</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>Trend_UP!BA2</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>Trend_UP!BB2</f>
+        <v/>
+      </c>
+      <c r="N2">
+        <f>Trend_UP!AB2</f>
+        <v/>
+      </c>
+      <c r="O2">
+        <f>Trend_UP!AD2</f>
+        <v/>
+      </c>
+      <c r="P2">
+        <f>Trend_UP!AQ2</f>
+        <v/>
+      </c>
+      <c r="Q2">
+        <f>Trend_UP!AR2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Пример 1. Тренд вверх</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Big</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>BUY 1.15</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Big = Far × 1.15.</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Пример 2. Разворот вниз — SMALL_SIDE / DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Trend_UP</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <f>Trend_UP!C5&amp;" "&amp;TEXT(Trend_UP!D5,"0.00")</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>Trend_UP!E5&amp;" "&amp;TEXT(Trend_UP!G5,"0.00")</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>Trend_UP!H5&amp;" "&amp;TEXT(Trend_UP!J5,"0.00")</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>Trend_UP!B5</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>Trend_UP!S5</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>Trend_UP!T5</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>Trend_UP!X5</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>Trend_UP!AZ5</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>Trend_UP!BA5</f>
+        <v/>
+      </c>
+      <c r="M3">
+        <f>Trend_UP!BB5</f>
+        <v/>
+      </c>
+      <c r="N3">
+        <f>Trend_UP!AB5</f>
+        <v/>
+      </c>
+      <c r="O3">
+        <f>Trend_UP!AD5</f>
+        <v/>
+      </c>
+      <c r="P3">
+        <f>Trend_UP!AQ5</f>
+        <v/>
+      </c>
+      <c r="Q3">
+        <f>Trend_UP!AR5</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Пример 1. Тренд вверх</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>SELL 0.44</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Small = Big × 0.38 с округлением до LotStep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Пример 1. Тренд вверх</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>BIG_SIDE</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Close Big = 100%; Close Small = 100%; CloseFarBudget = NetProfit × 20%; ReserveAdd = NetProfit × 80%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Пример 2. Разворот вниз</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Start Far</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>SELL 1.00</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Исходный дальний хвост.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Пример 2. Разворот вниз</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Big</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BUY 1.15</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Рабочая позиция против старого хвоста.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Пример 2. Разворот вниз</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>SELL 0.44</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Защитная позиция в сторону старого хвоста.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Пример 2. Разворот вниз</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>SMALL_SIDE</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Close Small = 100%; Close Big = 22%; Remain Big = 78%; новый Far = BUY 0.897.</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Пример 3. BLOCKED persistence</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Trend_DOWN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <f>Trend_DOWN!C4&amp;" "&amp;TEXT(Trend_DOWN!D4,"0.00")</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>TEXT(Trend_DOWN!G4,"0.00")</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>TEXT(Trend_DOWN!J4,"0.00")</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>Trend_DOWN!B4</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>Trend_DOWN!S4</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>Trend_DOWN!T4</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>Trend_DOWN!X4</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>Trend_DOWN!AZ4</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>Trend_DOWN!BA4</f>
+        <v/>
+      </c>
+      <c r="M4">
+        <f>Trend_DOWN!BB4</f>
+        <v/>
+      </c>
+      <c r="N4">
+        <f>Trend_DOWN!AB4</f>
+        <v/>
+      </c>
+      <c r="O4">
+        <f>Trend_DOWN!AD4</f>
+        <v/>
+      </c>
+      <c r="P4">
+        <f>Trend_DOWN!AQ4</f>
+        <v/>
+      </c>
+      <c r="Q4">
+        <f>Trend_DOWN!AR4</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
+++ b/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
@@ -1378,7 +1378,7 @@
         <v/>
       </c>
       <c r="X2" s="19">
-        <f>IF($B2="BIG_SIDE",IF($AX2&gt;0,$AX2-$AS2,0),IF($S2&gt;0,$S2*0.5,0))</f>
+        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2-$AS$2,0),IF($S$2&gt;0,$S$2*0.5,0))</f>
         <v/>
       </c>
       <c r="Y2" s="19">
@@ -1409,11 +1409,11 @@
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
+        <f>IF($B2="BLOCKED",$C2,IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
+        <f>IF($B2="BLOCKED",0,IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -1481,7 +1481,7 @@
         <v/>
       </c>
       <c r="AX2" s="12">
-        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,0)</f>
         <v/>
       </c>
       <c r="AY2" s="12">
@@ -1609,7 +1609,7 @@
         <v/>
       </c>
       <c r="X3" s="19">
-        <f>IF($B3="BIG_SIDE",IF($AX3&gt;0,$AX3-$AS3,0),IF($S3&gt;0,$S3*0.5,0))</f>
+        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3-$AS$3,0),IF($S$3&gt;0,$S$3*0.5,0))</f>
         <v/>
       </c>
       <c r="Y3" s="19">
@@ -1645,7 +1645,7 @@
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
+        <f>IF($B3="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
         <v/>
       </c>
       <c r="AH3" s="13" t="inlineStr">
@@ -1713,7 +1713,7 @@
         <v/>
       </c>
       <c r="AX3" s="12">
-        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,0)</f>
         <v/>
       </c>
       <c r="AY3" s="12">
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="X4" s="19">
-        <f>IF($B4="BIG_SIDE",IF($AX4&gt;0,$AX4-$AS4,0),IF($S4&gt;0,$S4*0.5,0))</f>
+        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4-$AS$4,0),IF($S$4&gt;0,$S$4*0.5,0))</f>
         <v/>
       </c>
       <c r="Y4" s="19">
@@ -1877,7 +1877,7 @@
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
+        <f>IF($B4="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -1945,7 +1945,7 @@
         <v/>
       </c>
       <c r="AX4" s="12">
-        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,0)</f>
         <v/>
       </c>
       <c r="AY4" s="12">
@@ -2073,7 +2073,7 @@
         <v/>
       </c>
       <c r="X5" s="19">
-        <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
+        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5-$AS$5,0),IF($S$5&gt;0,$S$5*0.5,0))</f>
         <v/>
       </c>
       <c r="Y5" s="19">
@@ -2109,7 +2109,7 @@
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
+        <f>IF($B5="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v/>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -2177,7 +2177,7 @@
         <v/>
       </c>
       <c r="AX5" s="12">
-        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,0)</f>
         <v/>
       </c>
       <c r="AY5" s="12">
@@ -2305,7 +2305,7 @@
         <v/>
       </c>
       <c r="X6" s="19">
-        <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
+        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6-$AS$6,0),IF($S$6&gt;0,$S$6*0.5,0))</f>
         <v/>
       </c>
       <c r="Y6" s="19">
@@ -2341,7 +2341,7 @@
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
+        <f>IF($B6="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -2409,7 +2409,7 @@
         <v/>
       </c>
       <c r="AX6" s="12">
-        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,0)</f>
         <v/>
       </c>
       <c r="AY6" s="12">
@@ -2537,7 +2537,7 @@
         <v/>
       </c>
       <c r="X7" s="19">
-        <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
+        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7-$AS$7,0),IF($S$7&gt;0,$S$7*0.5,0))</f>
         <v/>
       </c>
       <c r="Y7" s="19">
@@ -2573,7 +2573,7 @@
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
+        <f>IF($B7="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -2641,7 +2641,7 @@
         <v/>
       </c>
       <c r="AX7" s="12">
-        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,0)</f>
         <v/>
       </c>
       <c r="AY7" s="12">
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="X8" s="19">
-        <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
+        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8-$AS$8,0),IF($S$8&gt;0,$S$8*0.5,0))</f>
         <v/>
       </c>
       <c r="Y8" s="19">
@@ -2805,7 +2805,7 @@
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
+        <f>IF($B8="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -2873,7 +2873,7 @@
         <v/>
       </c>
       <c r="AX8" s="12">
-        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,0)</f>
         <v/>
       </c>
       <c r="AY8" s="12">
@@ -3001,7 +3001,7 @@
         <v/>
       </c>
       <c r="X9" s="19">
-        <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
+        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9-$AS$9,0),IF($S$9&gt;0,$S$9*0.5,0))</f>
         <v/>
       </c>
       <c r="Y9" s="19">
@@ -3037,7 +3037,7 @@
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
+        <f>IF($B9="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -3105,7 +3105,7 @@
         <v/>
       </c>
       <c r="AX9" s="12">
-        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,0)</f>
         <v/>
       </c>
       <c r="AY9" s="12">
@@ -3233,7 +3233,7 @@
         <v/>
       </c>
       <c r="X10" s="19">
-        <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
+        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10-$AS$10,0),IF($S$10&gt;0,$S$10*0.5,0))</f>
         <v/>
       </c>
       <c r="Y10" s="19">
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
+        <f>IF($B10="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="AX10" s="12">
-        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,0)</f>
         <v/>
       </c>
       <c r="AY10" s="12">
@@ -3465,7 +3465,7 @@
         <v/>
       </c>
       <c r="X11" s="19">
-        <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
+        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11-$AS$11,0),IF($S$11&gt;0,$S$11*0.5,0))</f>
         <v/>
       </c>
       <c r="Y11" s="19">
@@ -3501,7 +3501,7 @@
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$BB11,$BA11),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
+        <f>IF($B11="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -3569,7 +3569,7 @@
         <v/>
       </c>
       <c r="AX11" s="12">
-        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,0)</f>
         <v/>
       </c>
       <c r="AY11" s="12">
@@ -4097,7 +4097,7 @@
         <v/>
       </c>
       <c r="X2" s="19">
-        <f>IF($B2="BIG_SIDE",IF($AX2&gt;0,$AX2-$AS2,0),IF($S2&gt;0,$S2*0.5,0))</f>
+        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2-$AS$2,0),IF($S$2&gt;0,$S$2*0.5,0))</f>
         <v/>
       </c>
       <c r="Y2" s="19">
@@ -4128,11 +4128,11 @@
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
+        <f>IF($B2="BLOCKED",$C2,IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
+        <f>IF($B2="BLOCKED",0,IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -4200,7 +4200,7 @@
         <v/>
       </c>
       <c r="AX2" s="12">
-        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,0)</f>
         <v/>
       </c>
       <c r="AY2" s="12">
@@ -4328,7 +4328,7 @@
         <v/>
       </c>
       <c r="X3" s="19">
-        <f>IF($B3="BIG_SIDE",IF($AX3&gt;0,$AX3-$AS3,0),IF($S3&gt;0,$S3*0.5,0))</f>
+        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3-$AS$3,0),IF($S$3&gt;0,$S$3*0.5,0))</f>
         <v/>
       </c>
       <c r="Y3" s="19">
@@ -4364,7 +4364,7 @@
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
+        <f>IF($B3="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
         <v/>
       </c>
       <c r="AH3" s="13" t="inlineStr">
@@ -4432,7 +4432,7 @@
         <v/>
       </c>
       <c r="AX3" s="12">
-        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,0)</f>
         <v/>
       </c>
       <c r="AY3" s="12">
@@ -4560,7 +4560,7 @@
         <v/>
       </c>
       <c r="X4" s="19">
-        <f>IF($B4="BIG_SIDE",IF($AX4&gt;0,$AX4-$AS4,0),IF($S4&gt;0,$S4*0.5,0))</f>
+        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4-$AS$4,0),IF($S$4&gt;0,$S$4*0.5,0))</f>
         <v/>
       </c>
       <c r="Y4" s="19">
@@ -4596,7 +4596,7 @@
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
+        <f>IF($B4="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -4664,7 +4664,7 @@
         <v/>
       </c>
       <c r="AX4" s="12">
-        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,0)</f>
         <v/>
       </c>
       <c r="AY4" s="12">
@@ -4792,7 +4792,7 @@
         <v/>
       </c>
       <c r="X5" s="19">
-        <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
+        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5-$AS$5,0),IF($S$5&gt;0,$S$5*0.5,0))</f>
         <v/>
       </c>
       <c r="Y5" s="19">
@@ -4828,7 +4828,7 @@
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
+        <f>IF($B5="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v>0.468</v>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -4896,7 +4896,7 @@
         <v/>
       </c>
       <c r="AX5" s="12">
-        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,0)</f>
         <v/>
       </c>
       <c r="AY5" s="12">
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="X6" s="19">
-        <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
+        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6-$AS$6,0),IF($S$6&gt;0,$S$6*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y6" s="19">
@@ -5060,7 +5060,7 @@
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
+        <f>IF($B6="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="AR6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS6" s="20">
         <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
@@ -5128,7 +5128,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX6" s="12">
-        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,0)</f>
         <v/>
       </c>
       <c r="AY6" s="12">
@@ -5256,7 +5256,7 @@
         <v/>
       </c>
       <c r="X7" s="19">
-        <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
+        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7-$AS$7,0),IF($S$7&gt;0,$S$7*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y7" s="19">
@@ -5292,7 +5292,7 @@
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
+        <f>IF($B7="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="AR7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS7" s="20">
         <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
@@ -5360,7 +5360,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX7" s="12">
-        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,0)</f>
         <v/>
       </c>
       <c r="AY7" s="12">
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="X8" s="19">
-        <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
+        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8-$AS$8,0),IF($S$8&gt;0,$S$8*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y8" s="19">
@@ -5524,7 +5524,7 @@
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
+        <f>IF($B8="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AR8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS8" s="20">
         <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
@@ -5592,7 +5592,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX8" s="12">
-        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,0)</f>
         <v/>
       </c>
       <c r="AY8" s="12">
@@ -5720,7 +5720,7 @@
         <v/>
       </c>
       <c r="X9" s="19">
-        <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
+        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9-$AS$9,0),IF($S$9&gt;0,$S$9*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y9" s="19">
@@ -5756,7 +5756,7 @@
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
+        <f>IF($B9="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="AR9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS9" s="20">
         <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
@@ -5824,7 +5824,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX9" s="12">
-        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,0)</f>
         <v/>
       </c>
       <c r="AY9" s="12">
@@ -5952,7 +5952,7 @@
         <v/>
       </c>
       <c r="X10" s="19">
-        <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
+        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10-$AS$10,0),IF($S$10&gt;0,$S$10*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y10" s="19">
@@ -5988,7 +5988,7 @@
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
+        <f>IF($B10="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AR10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS10" s="20">
         <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
@@ -6056,7 +6056,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX10" s="12">
-        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,0)</f>
         <v/>
       </c>
       <c r="AY10" s="12">
@@ -6184,7 +6184,7 @@
         <v/>
       </c>
       <c r="X11" s="19">
-        <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
+        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11-$AS$11,0),IF($S$11&gt;0,$S$11*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y11" s="19">
@@ -6220,7 +6220,7 @@
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$BB11,$BA11),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
+        <f>IF($B11="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="AR11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS11" s="20">
         <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
@@ -6288,7 +6288,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX11" s="12">
-        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,0)</f>
         <v/>
       </c>
       <c r="AY11" s="12">
@@ -6816,7 +6816,7 @@
         <v/>
       </c>
       <c r="X2" s="19">
-        <f>IF($B2="BIG_SIDE",IF($AX2&gt;0,$AX2-$AS2,0),IF($S2&gt;0,$S2*0.5,0))</f>
+        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2-$AS$2,0),IF($S$2&gt;0,$S$2*0.5,0))</f>
         <v/>
       </c>
       <c r="Y2" s="19">
@@ -6847,11 +6847,11 @@
         <v/>
       </c>
       <c r="AF2" s="12">
-        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$AF2,$C2),IF($B2="SMALL_SIDE",$E2,$C2))</f>
+        <f>IF($B2="BLOCKED",$C2,IF($B2="SMALL_SIDE",$E2,$C2))</f>
         <v/>
       </c>
       <c r="AG2" s="12">
-        <f>IF($B2="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B2="SMALL_SIDE",$AM2,$W2))</f>
+        <f>IF($B2="BLOCKED",0,IF($B2="SMALL_SIDE",$AM2,$W2))</f>
         <v/>
       </c>
       <c r="AH2" s="13" t="inlineStr">
@@ -6919,7 +6919,7 @@
         <v/>
       </c>
       <c r="AX2" s="12">
-        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
+        <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,0)</f>
         <v/>
       </c>
       <c r="AY2" s="12">
@@ -7047,7 +7047,7 @@
         <v/>
       </c>
       <c r="X3" s="19">
-        <f>IF($B3="BIG_SIDE",IF($AX3&gt;0,$AX3-$AS3,0),IF($S3&gt;0,$S3*0.5,0))</f>
+        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3-$AS$3,0),IF($S$3&gt;0,$S$3*0.5,0))</f>
         <v/>
       </c>
       <c r="Y3" s="19">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AC3" s="12">
         <f>IF($B3="BLOCKED",$BC3,IF($B3="BIG_SIDE",$W3,IF($AK3=TRUE,$BC3,$AG3)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD3" s="12">
         <f>$AB3*Settings!$B$10</f>
@@ -7076,15 +7076,15 @@
       </c>
       <c r="AE3" s="12">
         <f>$AC3*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF3" s="12">
         <f>IF($B3="BLOCKED",IF($BB3&gt;0,$AF2,$C3),IF($B3="SMALL_SIDE",$E3,$C3))</f>
         <v/>
       </c>
       <c r="AG3" s="12">
-        <f>IF($B3="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
-        <v>0.897</v>
+        <f>IF($B3="BLOCKED",IF($BB2&gt;0,$BB2,$BA2),IF($B3="SMALL_SIDE",$AM3,$W3))</f>
+        <v>0.7254</v>
       </c>
       <c r="AH3" s="13" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AJ3" s="12">
         <f>IF($B3="SMALL_SIDE",MAX(0,$D3-$AV3),0)</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="AK3" s="12">
         <f>IF(AND($AJ3&gt;0,$AG3&gt;0),TRUE,FALSE)</f>
@@ -7151,7 +7151,7 @@
         <v/>
       </c>
       <c r="AX3" s="12">
-        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,IF($B3="SMALL_SIDE",$O3-$Q3-$R3,0))</f>
+        <f>IF($B3="BIG_SIDE",$N3-$P3-$AY3,0)</f>
         <v/>
       </c>
       <c r="AY3" s="12">
@@ -7164,15 +7164,15 @@
       </c>
       <c r="BA3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AJ3-$BD3),IF($B3="BLOCKED",MAX(0,$BA2-$BD3),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB3" s="12">
         <f>IF($AK3=TRUE,MAX(0,$AG3-$BE3),IF($B3="BLOCKED",MAX(0,$BB2-$BE3),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC3" s="12">
         <f>$BA3+$BB3</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD3" s="13">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         <v/>
       </c>
       <c r="X4" s="19">
-        <f>IF($B4="BIG_SIDE",IF($AX4&gt;0,$AX4-$AS4,0),IF($S4&gt;0,$S4*0.5,0))</f>
+        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4-$AS$4,0),IF($S$4&gt;0,$S$4*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y4" s="19">
@@ -7296,26 +7296,26 @@
       </c>
       <c r="AB4" s="12">
         <f>IF($B4="BLOCKED",$BC4,$D4+$G4+$J4)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AC4" s="12">
         <f>IF($B4="BLOCKED",$BC4,IF($B4="BIG_SIDE",$W4,IF($AK4=TRUE,$BC4,$AG4)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD4" s="12">
         <f>$AB4*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AE4" s="12">
         <f>$AC4*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF4" s="12">
         <f>IF($B4="BLOCKED",IF($BB4&gt;0,$AF3,$C4),IF($B4="SMALL_SIDE",$E4,$C4))</f>
         <v/>
       </c>
       <c r="AG4" s="12">
-        <f>IF($B4="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
+        <f>IF($B4="BLOCKED",IF($BB3&gt;0,$BB3,$BA3),IF($B4="SMALL_SIDE",$AM4,$W4))</f>
         <v/>
       </c>
       <c r="AH4" s="13" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="AR4" s="12" t="str">
         <f>IF($B4="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B4="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ4="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS4" s="20">
         <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
@@ -7383,7 +7383,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX4" s="12">
-        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,IF($B4="SMALL_SIDE",$O4-$Q4-$R4,0))</f>
+        <f>IF($B4="BIG_SIDE",$N4-$P4-$AY4,0)</f>
         <v/>
       </c>
       <c r="AY4" s="12">
@@ -7396,15 +7396,15 @@
       </c>
       <c r="BA4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AJ4-$BD4),IF($B4="BLOCKED",MAX(0,$BA3-$BD4),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB4" s="12">
         <f>IF($AK4=TRUE,MAX(0,$AG4-$BE4),IF($B4="BLOCKED",MAX(0,$BB3-$BE4),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC4" s="12">
         <f>$BA4+$BB4</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD4" s="13">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v/>
       </c>
       <c r="X5" s="19">
-        <f>IF($B5="BIG_SIDE",IF($AX5&gt;0,$AX5-$AS5,0),IF($S5&gt;0,$S5*0.5,0))</f>
+        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5-$AS$5,0),IF($S$5&gt;0,$S$5*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y5" s="19">
@@ -7528,26 +7528,26 @@
       </c>
       <c r="AB5" s="12">
         <f>IF($B5="BLOCKED",$BC5,$D5+$G5+$J5)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AC5" s="12">
         <f>IF($B5="BLOCKED",$BC5,IF($B5="BIG_SIDE",$W5,IF($AK5=TRUE,$BC5,$AG5)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD5" s="12">
         <f>$AB5*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AE5" s="12">
         <f>$AC5*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF5" s="12">
         <f>IF($B5="BLOCKED",IF($BB5&gt;0,$AF4,$C5),IF($B5="SMALL_SIDE",$E5,$C5))</f>
         <v/>
       </c>
       <c r="AG5" s="12">
-        <f>IF($B5="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
+        <f>IF($B5="BLOCKED",IF($BB4&gt;0,$BB4,$BA4),IF($B5="SMALL_SIDE",$AM5,$W5))</f>
         <v/>
       </c>
       <c r="AH5" s="13" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="AR5" s="12" t="str">
         <f>IF($B5="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B5="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ5="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS5" s="20">
         <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
@@ -7615,7 +7615,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX5" s="12">
-        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,IF($B5="SMALL_SIDE",$O5-$Q5-$R5,0))</f>
+        <f>IF($B5="BIG_SIDE",$N5-$P5-$AY5,0)</f>
         <v/>
       </c>
       <c r="AY5" s="12">
@@ -7628,15 +7628,15 @@
       </c>
       <c r="BA5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AJ5-$BD5),IF($B5="BLOCKED",MAX(0,$BA4-$BD5),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB5" s="12">
         <f>IF($AK5=TRUE,MAX(0,$AG5-$BE5),IF($B5="BLOCKED",MAX(0,$BB4-$BE5),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC5" s="12">
         <f>$BA5+$BB5</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD5" s="13">
         <v>0</v>
@@ -7743,7 +7743,7 @@
         <v/>
       </c>
       <c r="X6" s="19">
-        <f>IF($B6="BIG_SIDE",IF($AX6&gt;0,$AX6-$AS6,0),IF($S6&gt;0,$S6*0.5,0))</f>
+        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6-$AS$6,0),IF($S$6&gt;0,$S$6*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y6" s="19">
@@ -7760,26 +7760,26 @@
       </c>
       <c r="AB6" s="12">
         <f>IF($B6="BLOCKED",$BC6,$D6+$G6+$J6)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AC6" s="12">
         <f>IF($B6="BLOCKED",$BC6,IF($B6="BIG_SIDE",$W6,IF($AK6=TRUE,$BC6,$AG6)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD6" s="12">
         <f>$AB6*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AE6" s="12">
         <f>$AC6*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF6" s="12">
         <f>IF($B6="BLOCKED",IF($BB6&gt;0,$AF5,$C6),IF($B6="SMALL_SIDE",$E6,$C6))</f>
         <v/>
       </c>
       <c r="AG6" s="12">
-        <f>IF($B6="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
+        <f>IF($B6="BLOCKED",IF($BB5&gt;0,$BB5,$BA5),IF($B6="SMALL_SIDE",$AM6,$W6))</f>
         <v/>
       </c>
       <c r="AH6" s="13" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="AR6" s="12" t="str">
         <f>IF($B6="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B6="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ6="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS6" s="20">
         <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
@@ -7847,7 +7847,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX6" s="12">
-        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,IF($B6="SMALL_SIDE",$O6-$Q6-$R6,0))</f>
+        <f>IF($B6="BIG_SIDE",$N6-$P6-$AY6,0)</f>
         <v/>
       </c>
       <c r="AY6" s="12">
@@ -7860,15 +7860,15 @@
       </c>
       <c r="BA6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AJ6-$BD6),IF($B6="BLOCKED",MAX(0,$BA5-$BD6),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB6" s="12">
         <f>IF($AK6=TRUE,MAX(0,$AG6-$BE6),IF($B6="BLOCKED",MAX(0,$BB5-$BE6),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC6" s="12">
         <f>$BA6+$BB6</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD6" s="13">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v/>
       </c>
       <c r="X7" s="19">
-        <f>IF($B7="BIG_SIDE",IF($AX7&gt;0,$AX7-$AS7,0),IF($S7&gt;0,$S7*0.5,0))</f>
+        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7-$AS$7,0),IF($S$7&gt;0,$S$7*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y7" s="19">
@@ -7992,26 +7992,26 @@
       </c>
       <c r="AB7" s="12">
         <f>IF($B7="BLOCKED",$BC7,$D7+$G7+$J7)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AC7" s="12">
         <f>IF($B7="BLOCKED",$BC7,IF($B7="BIG_SIDE",$W7,IF($AK7=TRUE,$BC7,$AG7)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD7" s="12">
         <f>$AB7*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AE7" s="12">
         <f>$AC7*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF7" s="12">
         <f>IF($B7="BLOCKED",IF($BB7&gt;0,$AF6,$C7),IF($B7="SMALL_SIDE",$E7,$C7))</f>
         <v/>
       </c>
       <c r="AG7" s="12">
-        <f>IF($B7="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
+        <f>IF($B7="BLOCKED",IF($BB6&gt;0,$BB6,$BA6),IF($B7="SMALL_SIDE",$AM7,$W7))</f>
         <v/>
       </c>
       <c r="AH7" s="13" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="AR7" s="12" t="str">
         <f>IF($B7="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B7="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ7="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS7" s="20">
         <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
@@ -8079,7 +8079,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX7" s="12">
-        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,IF($B7="SMALL_SIDE",$O7-$Q7-$R7,0))</f>
+        <f>IF($B7="BIG_SIDE",$N7-$P7-$AY7,0)</f>
         <v/>
       </c>
       <c r="AY7" s="12">
@@ -8092,15 +8092,15 @@
       </c>
       <c r="BA7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AJ7-$BD7),IF($B7="BLOCKED",MAX(0,$BA6-$BD7),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB7" s="12">
         <f>IF($AK7=TRUE,MAX(0,$AG7-$BE7),IF($B7="BLOCKED",MAX(0,$BB6-$BE7),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC7" s="12">
         <f>$BA7+$BB7</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD7" s="13">
         <v>0</v>
@@ -8207,7 +8207,7 @@
         <v/>
       </c>
       <c r="X8" s="19">
-        <f>IF($B8="BIG_SIDE",IF($AX8&gt;0,$AX8-$AS8,0),IF($S8&gt;0,$S8*0.5,0))</f>
+        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8-$AS$8,0),IF($S$8&gt;0,$S$8*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y8" s="19">
@@ -8224,26 +8224,26 @@
       </c>
       <c r="AB8" s="12">
         <f>IF($B8="BLOCKED",$BC8,$D8+$G8+$J8)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AC8" s="12">
         <f>IF($B8="BLOCKED",$BC8,IF($B8="BIG_SIDE",$W8,IF($AK8=TRUE,$BC8,$AG8)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD8" s="12">
         <f>$AB8*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AE8" s="12">
         <f>$AC8*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF8" s="12">
         <f>IF($B8="BLOCKED",IF($BB8&gt;0,$AF7,$C8),IF($B8="SMALL_SIDE",$E8,$C8))</f>
         <v/>
       </c>
       <c r="AG8" s="12">
-        <f>IF($B8="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
+        <f>IF($B8="BLOCKED",IF($BB7&gt;0,$BB7,$BA7),IF($B8="SMALL_SIDE",$AM8,$W8))</f>
         <v/>
       </c>
       <c r="AH8" s="13" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="AR8" s="12" t="str">
         <f>IF($B8="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B8="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ8="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS8" s="20">
         <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
@@ -8311,7 +8311,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX8" s="12">
-        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,IF($B8="SMALL_SIDE",$O8-$Q8-$R8,0))</f>
+        <f>IF($B8="BIG_SIDE",$N8-$P8-$AY8,0)</f>
         <v/>
       </c>
       <c r="AY8" s="12">
@@ -8324,15 +8324,15 @@
       </c>
       <c r="BA8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AJ8-$BD8),IF($B8="BLOCKED",MAX(0,$BA7-$BD8),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB8" s="12">
         <f>IF($AK8=TRUE,MAX(0,$AG8-$BE8),IF($B8="BLOCKED",MAX(0,$BB7-$BE8),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC8" s="12">
         <f>$BA8+$BB8</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD8" s="13">
         <v>0</v>
@@ -8439,7 +8439,7 @@
         <v/>
       </c>
       <c r="X9" s="19">
-        <f>IF($B9="BIG_SIDE",IF($AX9&gt;0,$AX9-$AS9,0),IF($S9&gt;0,$S9*0.5,0))</f>
+        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9-$AS$9,0),IF($S$9&gt;0,$S$9*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y9" s="19">
@@ -8456,26 +8456,26 @@
       </c>
       <c r="AB9" s="12">
         <f>IF($B9="BLOCKED",$BC9,$D9+$G9+$J9)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AC9" s="12">
         <f>IF($B9="BLOCKED",$BC9,IF($B9="BIG_SIDE",$W9,IF($AK9=TRUE,$BC9,$AG9)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD9" s="12">
         <f>$AB9*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AE9" s="12">
         <f>$AC9*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF9" s="12">
         <f>IF($B9="BLOCKED",IF($BB9&gt;0,$AF8,$C9),IF($B9="SMALL_SIDE",$E9,$C9))</f>
         <v/>
       </c>
       <c r="AG9" s="12">
-        <f>IF($B9="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
+        <f>IF($B9="BLOCKED",IF($BB8&gt;0,$BB8,$BA8),IF($B9="SMALL_SIDE",$AM9,$W9))</f>
         <v/>
       </c>
       <c r="AH9" s="13" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="AR9" s="12" t="str">
         <f>IF($B9="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B9="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ9="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS9" s="20">
         <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
@@ -8543,7 +8543,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX9" s="12">
-        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,IF($B9="SMALL_SIDE",$O9-$Q9-$R9,0))</f>
+        <f>IF($B9="BIG_SIDE",$N9-$P9-$AY9,0)</f>
         <v/>
       </c>
       <c r="AY9" s="12">
@@ -8556,15 +8556,15 @@
       </c>
       <c r="BA9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AJ9-$BD9),IF($B9="BLOCKED",MAX(0,$BA8-$BD9),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB9" s="12">
         <f>IF($AK9=TRUE,MAX(0,$AG9-$BE9),IF($B9="BLOCKED",MAX(0,$BB8-$BE9),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC9" s="12">
         <f>$BA9+$BB9</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD9" s="13">
         <v>0</v>
@@ -8671,7 +8671,7 @@
         <v/>
       </c>
       <c r="X10" s="19">
-        <f>IF($B10="BIG_SIDE",IF($AX10&gt;0,$AX10-$AS10,0),IF($S10&gt;0,$S10*0.5,0))</f>
+        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10-$AS$10,0),IF($S$10&gt;0,$S$10*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y10" s="19">
@@ -8688,26 +8688,26 @@
       </c>
       <c r="AB10" s="12">
         <f>IF($B10="BLOCKED",$BC10,$D10+$G10+$J10)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AC10" s="12">
         <f>IF($B10="BLOCKED",$BC10,IF($B10="BIG_SIDE",$W10,IF($AK10=TRUE,$BC10,$AG10)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD10" s="12">
         <f>$AB10*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AE10" s="12">
         <f>$AC10*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF10" s="12">
         <f>IF($B10="BLOCKED",IF($BB10&gt;0,$AF9,$C10),IF($B10="SMALL_SIDE",$E10,$C10))</f>
         <v/>
       </c>
       <c r="AG10" s="12">
-        <f>IF($B10="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
+        <f>IF($B10="BLOCKED",IF($BB9&gt;0,$BB9,$BA9),IF($B10="SMALL_SIDE",$AM10,$W10))</f>
         <v/>
       </c>
       <c r="AH10" s="13" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="AR10" s="12" t="str">
         <f>IF($B10="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B10="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ10="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS10" s="20">
         <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
@@ -8775,7 +8775,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX10" s="12">
-        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,IF($B10="SMALL_SIDE",$O10-$Q10-$R10,0))</f>
+        <f>IF($B10="BIG_SIDE",$N10-$P10-$AY10,0)</f>
         <v/>
       </c>
       <c r="AY10" s="12">
@@ -8788,15 +8788,15 @@
       </c>
       <c r="BA10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AJ10-$BD10),IF($B10="BLOCKED",MAX(0,$BA9-$BD10),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB10" s="12">
         <f>IF($AK10=TRUE,MAX(0,$AG10-$BE10),IF($B10="BLOCKED",MAX(0,$BB9-$BE10),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC10" s="12">
         <f>$BA10+$BB10</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD10" s="13">
         <v>0</v>
@@ -8903,7 +8903,7 @@
         <v/>
       </c>
       <c r="X11" s="19">
-        <f>IF($B11="BIG_SIDE",IF($AX11&gt;0,$AX11-$AS11,0),IF($S11&gt;0,$S11*0.5,0))</f>
+        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11-$AS$11,0),IF($S$11&gt;0,$S$11*0.5,0))</f>
         <v>0</v>
       </c>
       <c r="Y11" s="19">
@@ -8920,26 +8920,26 @@
       </c>
       <c r="AB11" s="12">
         <f>IF($B11="BLOCKED",$BC11,$D11+$G11+$J11)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AC11" s="12">
         <f>IF($B11="BLOCKED",$BC11,IF($B11="BIG_SIDE",$W11,IF($AK11=TRUE,$BC11,$AG11)))</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="AD11" s="12">
         <f>$AB11*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AE11" s="12">
         <f>$AC11*Settings!$B$10</f>
-        <v>1697</v>
+        <v>1530.6</v>
       </c>
       <c r="AF11" s="12">
         <f>IF($B11="BLOCKED",IF($BB11&gt;0,$AF10,$C11),IF($B11="SMALL_SIDE",$E11,$C11))</f>
         <v/>
       </c>
       <c r="AG11" s="12">
-        <f>IF($B11="BLOCKED",IF($BB11&gt;0,$BB11,$BA11),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
+        <f>IF($B11="BLOCKED",IF($BB10&gt;0,$BB10,$BA10),IF($B11="SMALL_SIDE",$AM11,$W11))</f>
         <v/>
       </c>
       <c r="AH11" s="13" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="AR11" s="12" t="str">
         <f>IF($B11="BLOCKED","Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия",IF($B11="BIG_SIDE","BIG_SIDE: Big и Small закрыты 100%; баланс учитывает RealizedFarLoss",IF($AQ11="DUAL_TAIL","SMALL_SIDE: старый и новый хвост одновременно; новый уровень запрещён","SMALL_SIDE: Small закрыт 100%, Big закрыт 22%, остаток Big = новый хвост")))</f>
-        <v>Заблокировано: предыдущий уровень не разрешил новый полноценный уровень</v>
+        <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS11" s="20">
         <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
@@ -9007,7 +9007,7 @@
         <v>DUAL_TAIL persistence: оба хвоста сохранены</v>
       </c>
       <c r="AX11" s="12">
-        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,IF($B11="SMALL_SIDE",$O11-$Q11-$R11,0))</f>
+        <f>IF($B11="BIG_SIDE",$N11-$P11-$AY11,0)</f>
         <v/>
       </c>
       <c r="AY11" s="12">
@@ -9020,15 +9020,15 @@
       </c>
       <c r="BA11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AJ11-$BD11),IF($B11="BLOCKED",MAX(0,$BA10-$BD11),0))</f>
-        <v>0.8</v>
+        <v>0.8052</v>
       </c>
       <c r="BB11" s="12">
         <f>IF($AK11=TRUE,MAX(0,$AG11-$BE11),IF($B11="BLOCKED",MAX(0,$BB10-$BE11),0))</f>
-        <v>0.897</v>
+        <v>0.7254</v>
       </c>
       <c r="BC11" s="12">
         <f>$BA11+$BB11</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="BD11" s="13">
         <v>0</v>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C26">
         <f>SUM(Calculator!N2:O11,Trend_UP!N2:O11,Trend_DOWN!N2:O11)+SUMIF(Calculator!AI2:AI11,"&gt;0",Calculator!AI2:AI11)+SUMIF(Trend_UP!AI2:AI11,"&gt;0",Trend_UP!AI2:AI11)+SUMIF(Trend_DOWN!AI2:AI11,"&gt;0",Trend_DOWN!AI2:AI11)</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="D26">
         <f>C26</f>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="C27">
         <f>SUM(Calculator!P2:R11,Trend_UP!P2:R11,Trend_DOWN!P2:R11)+SUM(Calculator!AS2:AS11,Trend_UP!AS2:AS11,Trend_DOWN!AS2:AS11)-SUMIF(Calculator!AI2:AI11,"&lt;0",Calculator!AI2:AI11)-SUMIF(Trend_UP!AI2:AI11,"&lt;0",Trend_UP!AI2:AI11)-SUMIF(Trend_DOWN!AI2:AI11,"&lt;0",Trend_DOWN!AI2:AI11)</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="D27">
         <f>C27</f>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="C34">
         <f>MAX(Calculator!BB2:BB11,Trend_UP!BB2:BB11,Trend_DOWN!BB2:BB11)</f>
-        <v>1.697</v>
+        <v>1.5306</v>
       </c>
       <c r="D34">
         <f>C34</f>
@@ -9776,7 +9776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13102,6 +13102,384 @@
       <c r="H79" t="inlineStr">
         <is>
           <t>Excel recalculates formulas on open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>V7-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>No circular reference warning in Excel</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Workbook formulas</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>No direct self-reference and no known circular formula pattern</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>openpyxl direct self-reference scan + formula review</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Excel desktop manual warning cannot be opened in this headless environment; direct/cross-row formulas were cleaned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>V7-02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>No direct self-reference in formulas</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>All formula cells</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>No cell coordinate appears in its own formula</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Python openpyxl scan</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Simple Excel-style direct self-reference smoke check passes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>V7-03</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Trend_DOWN BLOCKED old tail from DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Trend_DOWN row after DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ActiveOldFarLot = previous ActiveOldFarLot</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>pytest data-only</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Trend_DOWN uses real previous DUAL_TAIL old tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>V7-04</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Trend_DOWN BLOCKED new tail from DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Trend_DOWN row after DUAL_TAIL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ActiveNewFarLot = previous ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>pytest data-only</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Trend_DOWN uses real previous DUAL_TAIL new tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>V7-05</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Trend_DOWN dual total</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Trend_DOWN BLOCKED rows</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DualTailTotalLot = ActiveOldFarLot + ActiveNewFarLot</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>pytest data-only</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Dual total equals two active tails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>V7-06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Global Total Closed Profit populated</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Risk_Analysis</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Formula/value is not blank</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Risk_Analysis formula/data-only check</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Global profit aggregates Calculator + Trend_UP + Trend_DOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>V7-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Global Total Closed Loss populated</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Risk_Analysis</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Formula/value is not blank</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Risk_Analysis formula/data-only check</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Global loss aggregates Calculator + Trend_UP + Trend_DOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>V7-08</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Global DUAL/BLOCKED/STOP visible</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Risk_Analysis</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Counts and max exposure &gt; 0 when scenarios contain them</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>pytest data-only</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Global summary sees DUAL_TAIL, BLOCKED and STOP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>V7-09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BLOCKED key fields not blank</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Calculator/Trend_UP/Trend_DOWN</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Required key fields contain 0 or text</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>pytest data-only</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>BLOCKED rows are readable and complete.</t>
         </is>
       </c>
     </row>
@@ -21356,59 +21734,59 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <f>Trend_UP!C2&amp;" "&amp;TEXT(Trend_UP!D2,"0.00")</f>
+        <f>Trend_UP!$C$2&amp;" "&amp;TEXT(Trend_UP!$D$2,"0.00")</f>
         <v/>
       </c>
       <c r="E2">
-        <f>Trend_UP!E2&amp;" "&amp;TEXT(Trend_UP!G2,"0.00")</f>
+        <f>Trend_UP!$E$2&amp;" "&amp;TEXT(Trend_UP!$G$2,"0.00")</f>
         <v/>
       </c>
       <c r="F2">
-        <f>Trend_UP!H2&amp;" "&amp;TEXT(Trend_UP!J2,"0.00")</f>
+        <f>Trend_UP!$H$2&amp;" "&amp;TEXT(Trend_UP!$J$2,"0.00")</f>
         <v/>
       </c>
       <c r="G2">
-        <f>Trend_UP!B2</f>
+        <f>Trend_UP!$B$2</f>
         <v/>
       </c>
       <c r="H2">
-        <f>Trend_UP!S2</f>
+        <f>Trend_UP!$S$2</f>
         <v/>
       </c>
       <c r="I2">
-        <f>Trend_UP!T2</f>
+        <f>Trend_UP!$T$2</f>
         <v/>
       </c>
       <c r="J2">
-        <f>Trend_UP!X2</f>
+        <f>Trend_UP!$X$2</f>
         <v/>
       </c>
       <c r="K2">
-        <f>Trend_UP!AZ2</f>
+        <f>Trend_UP!$AZ$2</f>
         <v/>
       </c>
       <c r="L2">
-        <f>Trend_UP!BA2</f>
+        <f>Trend_UP!$BA$2</f>
         <v/>
       </c>
       <c r="M2">
-        <f>Trend_UP!BB2</f>
+        <f>Trend_UP!$BB$2</f>
         <v/>
       </c>
       <c r="N2">
-        <f>Trend_UP!AB2</f>
+        <f>Trend_UP!$AB$2</f>
         <v/>
       </c>
       <c r="O2">
-        <f>Trend_UP!AD2</f>
+        <f>Trend_UP!$AD$2</f>
         <v/>
       </c>
       <c r="P2">
-        <f>Trend_UP!AQ2</f>
+        <f>Trend_UP!$AQ$2</f>
         <v/>
       </c>
       <c r="Q2">
-        <f>Trend_UP!AR2</f>
+        <f>Trend_UP!$AR$2</f>
         <v/>
       </c>
     </row>
@@ -21427,59 +21805,59 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <f>Trend_UP!C5&amp;" "&amp;TEXT(Trend_UP!D5,"0.00")</f>
+        <f>Trend_UP!$C$5&amp;" "&amp;TEXT(Trend_UP!$D$5,"0.00")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>Trend_UP!E5&amp;" "&amp;TEXT(Trend_UP!G5,"0.00")</f>
+        <f>Trend_UP!$E$5&amp;" "&amp;TEXT(Trend_UP!$G$5,"0.00")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>Trend_UP!H5&amp;" "&amp;TEXT(Trend_UP!J5,"0.00")</f>
+        <f>Trend_UP!$H$5&amp;" "&amp;TEXT(Trend_UP!$J$5,"0.00")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>Trend_UP!B5</f>
+        <f>Trend_UP!$B$5</f>
         <v/>
       </c>
       <c r="H3">
-        <f>Trend_UP!S5</f>
+        <f>Trend_UP!$S$5</f>
         <v/>
       </c>
       <c r="I3">
-        <f>Trend_UP!T5</f>
+        <f>Trend_UP!$T$5</f>
         <v/>
       </c>
       <c r="J3">
-        <f>Trend_UP!X5</f>
+        <f>Trend_UP!$X$5</f>
         <v/>
       </c>
       <c r="K3">
-        <f>Trend_UP!AZ5</f>
+        <f>Trend_UP!$AZ$5</f>
         <v/>
       </c>
       <c r="L3">
-        <f>Trend_UP!BA5</f>
+        <f>Trend_UP!$BA$5</f>
         <v/>
       </c>
       <c r="M3">
-        <f>Trend_UP!BB5</f>
+        <f>Trend_UP!$BB$5</f>
         <v/>
       </c>
       <c r="N3">
-        <f>Trend_UP!AB5</f>
+        <f>Trend_UP!$AB$5</f>
         <v/>
       </c>
       <c r="O3">
-        <f>Trend_UP!AD5</f>
+        <f>Trend_UP!$AD$5</f>
         <v/>
       </c>
       <c r="P3">
-        <f>Trend_UP!AQ5</f>
+        <f>Trend_UP!$AQ$5</f>
         <v/>
       </c>
       <c r="Q3">
-        <f>Trend_UP!AR5</f>
+        <f>Trend_UP!$AR$5</f>
         <v/>
       </c>
     </row>
@@ -21498,59 +21876,59 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <f>Trend_DOWN!C4&amp;" "&amp;TEXT(Trend_DOWN!D4,"0.00")</f>
+        <f>Trend_DOWN!$C$4&amp;" "&amp;TEXT(Trend_DOWN!$D$4,"0.00")</f>
         <v/>
       </c>
       <c r="E4">
-        <f>TEXT(Trend_DOWN!G4,"0.00")</f>
+        <f>TEXT(Trend_DOWN!$G$4,"0.00")</f>
         <v/>
       </c>
       <c r="F4">
-        <f>TEXT(Trend_DOWN!J4,"0.00")</f>
+        <f>TEXT(Trend_DOWN!$J$4,"0.00")</f>
         <v/>
       </c>
       <c r="G4">
-        <f>Trend_DOWN!B4</f>
+        <f>Trend_DOWN!$B$4</f>
         <v/>
       </c>
       <c r="H4">
-        <f>Trend_DOWN!S4</f>
+        <f>Trend_DOWN!$S$4</f>
         <v/>
       </c>
       <c r="I4">
-        <f>Trend_DOWN!T4</f>
+        <f>Trend_DOWN!$T$4</f>
         <v/>
       </c>
       <c r="J4">
-        <f>Trend_DOWN!X4</f>
+        <f>Trend_DOWN!$X$4</f>
         <v/>
       </c>
       <c r="K4">
-        <f>Trend_DOWN!AZ4</f>
+        <f>Trend_DOWN!$AZ$4</f>
         <v/>
       </c>
       <c r="L4">
-        <f>Trend_DOWN!BA4</f>
+        <f>Trend_DOWN!$BA$4</f>
         <v/>
       </c>
       <c r="M4">
-        <f>Trend_DOWN!BB4</f>
+        <f>Trend_DOWN!$BB$4</f>
         <v/>
       </c>
       <c r="N4">
-        <f>Trend_DOWN!AB4</f>
+        <f>Trend_DOWN!$AB$4</f>
         <v/>
       </c>
       <c r="O4">
-        <f>Trend_DOWN!AD4</f>
+        <f>Trend_DOWN!$AD$4</f>
         <v/>
       </c>
       <c r="P4">
-        <f>Trend_DOWN!AQ4</f>
+        <f>Trend_DOWN!$AQ$4</f>
         <v/>
       </c>
       <c r="Q4">
-        <f>Trend_DOWN!AR4</f>
+        <f>Trend_DOWN!$AR$4</f>
         <v/>
       </c>
     </row>

--- a/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
+++ b/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
@@ -28,7 +28,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -54,7 +56,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +118,26 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -143,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,6 +221,27 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -598,13 +641,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -914,7 +958,264 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Справочная геометрия лотов Big-N / Small-N / Close-N</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>FarStart-N</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>Big-N</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Small-N</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Close-N</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32">
+        <f>IF(1&lt;=Settings!$B$12,1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="B22" s="33">
+        <f>IF($A22="","",Settings!$B$2)</f>
+        <v>1</v>
+      </c>
+      <c r="C22" s="33">
+        <f>IF($A22="","",ROUND(($B22*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>1.15</v>
+      </c>
+      <c r="D22" s="33">
+        <f>IF($A22="","",ROUND(($C22*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.44</v>
+      </c>
+      <c r="E22" s="33">
+        <f>IF($A22="","",ROUND(($B22*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32">
+        <f>IF(2&lt;=Settings!$B$12,2,"")</f>
+        <v>2</v>
+      </c>
+      <c r="B23" s="33">
+        <f>IF($A23="","",$B22*(1-Settings!$B$5))</f>
+        <v>0.8</v>
+      </c>
+      <c r="C23" s="33">
+        <f>IF($A23="","",ROUND(($B23*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.92</v>
+      </c>
+      <c r="D23" s="33">
+        <f>IF($A23="","",ROUND(($C23*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.35</v>
+      </c>
+      <c r="E23" s="33">
+        <f>IF($A23="","",ROUND(($B23*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32">
+        <f>IF(3&lt;=Settings!$B$12,3,"")</f>
+        <v>3</v>
+      </c>
+      <c r="B24" s="33">
+        <f>IF($A24="","",$B23*(1-Settings!$B$5))</f>
+        <v>0.64</v>
+      </c>
+      <c r="C24" s="33">
+        <f>IF($A24="","",ROUND(($B24*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.74</v>
+      </c>
+      <c r="D24" s="33">
+        <f>IF($A24="","",ROUND(($C24*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.28</v>
+      </c>
+      <c r="E24" s="33">
+        <f>IF($A24="","",ROUND(($B24*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32">
+        <f>IF(4&lt;=Settings!$B$12,4,"")</f>
+        <v>4</v>
+      </c>
+      <c r="B25" s="33">
+        <f>IF($A25="","",$B24*(1-Settings!$B$5))</f>
+        <v>0.512</v>
+      </c>
+      <c r="C25" s="33">
+        <f>IF($A25="","",ROUND(($B25*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.59</v>
+      </c>
+      <c r="D25" s="33">
+        <f>IF($A25="","",ROUND(($C25*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.22</v>
+      </c>
+      <c r="E25" s="33">
+        <f>IF($A25="","",ROUND(($B25*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32">
+        <f>IF(5&lt;=Settings!$B$12,5,"")</f>
+        <v>5</v>
+      </c>
+      <c r="B26" s="33">
+        <f>IF($A26="","",$B25*(1-Settings!$B$5))</f>
+        <v>0.4096</v>
+      </c>
+      <c r="C26" s="33">
+        <f>IF($A26="","",ROUND(($B26*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.47</v>
+      </c>
+      <c r="D26" s="33">
+        <f>IF($A26="","",ROUND(($C26*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.18</v>
+      </c>
+      <c r="E26" s="33">
+        <f>IF($A26="","",ROUND(($B26*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32">
+        <f>IF(6&lt;=Settings!$B$12,6,"")</f>
+        <v>6</v>
+      </c>
+      <c r="B27" s="33">
+        <f>IF($A27="","",$B26*(1-Settings!$B$5))</f>
+        <v>0.32768</v>
+      </c>
+      <c r="C27" s="33">
+        <f>IF($A27="","",ROUND(($B27*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.38</v>
+      </c>
+      <c r="D27" s="33">
+        <f>IF($A27="","",ROUND(($C27*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.14</v>
+      </c>
+      <c r="E27" s="33">
+        <f>IF($A27="","",ROUND(($B27*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32">
+        <f>IF(7&lt;=Settings!$B$12,7,"")</f>
+        <v>7</v>
+      </c>
+      <c r="B28" s="33">
+        <f>IF($A28="","",$B27*(1-Settings!$B$5))</f>
+        <v>0.262144</v>
+      </c>
+      <c r="C28" s="33">
+        <f>IF($A28="","",ROUND(($B28*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.3</v>
+      </c>
+      <c r="D28" s="33">
+        <f>IF($A28="","",ROUND(($C28*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.11</v>
+      </c>
+      <c r="E28" s="33">
+        <f>IF($A28="","",ROUND(($B28*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32">
+        <f>IF(8&lt;=Settings!$B$12,8,"")</f>
+        <v>8</v>
+      </c>
+      <c r="B29" s="33">
+        <f>IF($A29="","",$B28*(1-Settings!$B$5))</f>
+        <v>0.2097152</v>
+      </c>
+      <c r="C29" s="33">
+        <f>IF($A29="","",ROUND(($B29*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.24</v>
+      </c>
+      <c r="D29" s="33">
+        <f>IF($A29="","",ROUND(($C29*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.09</v>
+      </c>
+      <c r="E29" s="33">
+        <f>IF($A29="","",ROUND(($B29*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32">
+        <f>IF(9&lt;=Settings!$B$12,9,"")</f>
+        <v>9</v>
+      </c>
+      <c r="B30" s="33">
+        <f>IF($A30="","",$B29*(1-Settings!$B$5))</f>
+        <v>0.16777216</v>
+      </c>
+      <c r="C30" s="33">
+        <f>IF($A30="","",ROUND(($B30*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.19</v>
+      </c>
+      <c r="D30" s="33">
+        <f>IF($A30="","",ROUND(($C30*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.07</v>
+      </c>
+      <c r="E30" s="33">
+        <f>IF($A30="","",ROUND(($B30*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32">
+        <f>IF(10&lt;=Settings!$B$12,10,"")</f>
+        <v>10</v>
+      </c>
+      <c r="B31" s="33">
+        <f>IF($A31="","",$B30*(1-Settings!$B$5))</f>
+        <v>0.134217728</v>
+      </c>
+      <c r="C31" s="33">
+        <f>IF($A31="","",ROUND(($B31*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.15</v>
+      </c>
+      <c r="D31" s="33">
+        <f>IF($A31="","",ROUND(($C31*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.06</v>
+      </c>
+      <c r="E31" s="33">
+        <f>IF($A31="","",ROUND(($B31*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.03</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A20:E20"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9326,7 +9627,7 @@
       </c>
       <c r="C12">
         <f>COUNTIF(Calculator!AQ2:AQ11,"DUAL_TAIL")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D12">
         <f>C12</f>
@@ -9366,7 +9667,7 @@
       </c>
       <c r="C14">
         <f>COUNTIF(Calculator!AQ2:AQ11,"STOP")</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="D14">
         <f>C14</f>
@@ -9410,7 +9711,7 @@
       </c>
       <c r="D16">
         <f>C16</f>
-        <v/>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="17">
@@ -9426,7 +9727,7 @@
       </c>
       <c r="C17">
         <f>LOOKUP(2,1/(Calculator!AZ2:AZ11&lt;&gt;""),Calculator!AZ2:AZ11)</f>
-        <v>0.5216</v>
+        <v/>
       </c>
       <c r="D17">
         <f>C17</f>
@@ -9446,7 +9747,7 @@
       </c>
       <c r="C18">
         <f>LOOKUP(2,1/(Calculator!BA2:BA11&lt;&gt;""),Calculator!BA2:BA11)</f>
-        <v>0.468</v>
+        <v/>
       </c>
       <c r="D18">
         <f>C18</f>
@@ -9466,7 +9767,7 @@
       </c>
       <c r="C19">
         <f>LOOKUP(2,1/(Calculator!BB2:BB11&lt;&gt;""),Calculator!BB2:BB11)</f>
-        <v>0.9896</v>
+        <v/>
       </c>
       <c r="D19">
         <f>C19</f>
@@ -9510,7 +9811,7 @@
       </c>
       <c r="D21">
         <f>C21</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -9582,7 +9883,7 @@
       </c>
       <c r="D26">
         <f>C26</f>
-        <v/>
+        <v>900</v>
       </c>
     </row>
     <row r="27">
@@ -9602,7 +9903,7 @@
       </c>
       <c r="D27">
         <f>C27</f>
-        <v/>
+        <v>300</v>
       </c>
     </row>
     <row r="28">
@@ -9618,7 +9919,7 @@
       </c>
       <c r="C28">
         <f>SUM(Calculator!AS2:AS11,Trend_UP!AS2:AS11,Trend_DOWN!AS2:AS11)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D28">
         <f>C28</f>
@@ -9638,7 +9939,7 @@
       </c>
       <c r="C29">
         <f>MAX(Calculator!AD2:AD11,Trend_UP!AD2:AD11,Trend_DOWN!AD2:AD11)</f>
-        <v>2590</v>
+        <v/>
       </c>
       <c r="D29">
         <f>C29</f>
@@ -9658,7 +9959,7 @@
       </c>
       <c r="C30">
         <f>MAX(Calculator!AB2:AB11,Trend_UP!AB2:AB11,Trend_DOWN!AB2:AB11)</f>
-        <v>2.59</v>
+        <v/>
       </c>
       <c r="D30">
         <f>C30</f>
@@ -9682,7 +9983,7 @@
       </c>
       <c r="D31">
         <f>C31</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -9702,7 +10003,7 @@
       </c>
       <c r="D32">
         <f>C32</f>
-        <v/>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
@@ -9722,7 +10023,7 @@
       </c>
       <c r="D33">
         <f>C33</f>
-        <v/>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -9737,12 +10038,12 @@
         </is>
       </c>
       <c r="C34">
-        <f>MAX(Calculator!BB2:BB11,Trend_UP!BB2:BB11,Trend_DOWN!BB2:BB11)</f>
+        <f>MAX(Calculator!BC2:BC11,Trend_UP!BC2:BC11,Trend_DOWN!BC2:BC11)</f>
         <v>1.5306</v>
       </c>
       <c r="D34">
         <f>C34</f>
-        <v/>
+        <v>1.5306</v>
       </c>
     </row>
     <row r="35">
@@ -9758,7 +10059,7 @@
       </c>
       <c r="C35">
         <f>COUNTIF(Calculator!AQ2:AQ11,"DANGER")+COUNTIF(Trend_UP!AQ2:AQ11,"DANGER")+COUNTIF(Trend_DOWN!AQ2:AQ11,"DANGER")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D35">
         <f>C35</f>
@@ -9776,7 +10077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13480,6 +13781,342 @@
       <c r="H88" t="inlineStr">
         <is>
           <t>BLOCKED rows are readable and complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>V8-01</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Global Max DualTail Exposure uses DualTailTotalLot</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Risk_Analysis formula</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>MAX Calculator/Trend_UP/Trend_DOWN DualTailTotalLot ranges</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Formula inspection</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Uses BC DualTailTotalLot ranges, not ActiveNewFarLot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>V8-02</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Global Max DualTail Exposure expected value</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Current scenario data</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.5306</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>data_only Risk_Analysis cache</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Global max equals Trend_DOWN dual-tail total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>V8-03</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Settings geometry table exists</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Settings sheet</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>N / FarStart-N / Big-N / Small-N / Close-N</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Header inspection</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Geometry table is below parameter block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>V8-04</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Big-N formula</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Settings geometry table</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Big-N = FarStart-N × BigRatio rounded by LotStep</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Formula inspection</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Formula references Settings!$B$3 and Settings!$B$11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>V8-05</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Small-N formula</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Settings geometry table</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Small-N = Big-N × SmallRatio rounded by LotStep</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Formula inspection</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Formula references Settings!$B$4 and Settings!$B$11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>V8-06</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Close-N formula</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Settings geometry table</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Close-N = FarStart-N × CloseFarShare rounded by LotStep</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Formula inspection</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Formula references Settings!$B$5 and Settings!$B$11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>V8-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Geometry uses Settings references</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Settings geometry table</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>No static ratios in formulas</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Formula inspection</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Uses StartLot, BigRatio, SmallRatio, CloseFarShare, LotStep, MaxLevels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>V8-08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Close-N reference only</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Calculator close logic</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Calculator remains money-mode: CloseFarBudget / LossPerLotToClose</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Formula inspection</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Close-N is not used in Calculator formulas.</t>
         </is>
       </c>
     </row>

--- a/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
+++ b/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
@@ -56,7 +56,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -138,6 +138,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -165,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,6 +247,19 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -641,14 +659,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -679,7 +706,7 @@
           <t>StartLot</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -699,12 +726,12 @@
           <t>BigRatio</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1.15</v>
+      <c r="B3" s="4">
+        <v>1.3</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Big = FarStart × 115%</t>
+          <t>Big = FarStart × 130%</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -719,12 +746,12 @@
           <t>SmallRatio</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>0.38</v>
+      <c r="B4" s="4">
+        <v>0.36</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Small = Big × 38%</t>
+          <t>Small = Big × 36%</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -739,12 +766,12 @@
           <t>CloseFarShare</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>0.2</v>
+      <c r="B5" s="4">
+        <v>0.9</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>максимум 20% чистой прибыли на хвост</t>
+          <t>90% чистой прибыли как денежный бюджет на Far</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -759,12 +786,12 @@
           <t>ReserveShare</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0.8</v>
+      <c r="B6" s="4">
+        <v>0.1</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>80% чистой прибыли в резерв</t>
+          <t>10% чистой прибыли в резерв</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -779,12 +806,12 @@
           <t>CloseBigOnSmall</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>0.22</v>
+      <c r="B7" s="4">
+        <v>0.3</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>закрытие Big при Small-сценарии</t>
+          <t>закрытие Big 30% при Small-сценарии</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -799,12 +826,12 @@
           <t>RemainBigOnSmall</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>0.78</v>
+      <c r="B8" s="4">
+        <v>0.7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>остаток Big</t>
+          <t>остаток Big 70%</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -819,7 +846,7 @@
           <t>PointValuePerLot</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="4">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -839,7 +866,7 @@
           <t>MarginPerLot</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="4">
         <v>1000</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -859,7 +886,7 @@
           <t>LotStep</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="4">
         <v>0.01</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -874,7 +901,7 @@
           <t>MaxLevels</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="4">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -889,7 +916,7 @@
           <t>CommissionPerLot</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="4">
         <v>0</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -904,7 +931,7 @@
           <t>SpreadCostPerLot</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="4">
         <v>0</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -919,7 +946,7 @@
           <t>SlippageCostPerLot</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="4">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -934,8 +961,8 @@
           <t>MaxBigRatio</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>1.2</v>
+      <c r="B16" s="4">
+        <v>1.35</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -949,7 +976,7 @@
           <t>MaxSmallRatio</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="4">
         <v>0.45</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -961,7 +988,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Справочная геометрия лотов Big-N / Small-N / Close-N</t>
+          <t>Big Harvest Geometry — денежное закрытие Far через CloseFarBudget</t>
         </is>
       </c>
     </row>
@@ -976,19 +1003,64 @@
           <t>FarStart-N</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>BigMovePoints</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>FarDistancePoints</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>Big-N</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="F21" s="30" t="inlineStr">
         <is>
           <t>Small-N</t>
         </is>
       </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>Close-N</t>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>ProfitBig</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="inlineStr">
+        <is>
+          <t>LossSmall</t>
+        </is>
+      </c>
+      <c r="I21" s="35" t="inlineStr">
+        <is>
+          <t>NetProfit</t>
+        </is>
+      </c>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>CloseFarBudget</t>
+        </is>
+      </c>
+      <c r="K21" s="37" t="inlineStr">
+        <is>
+          <t>ReserveAdd</t>
+        </is>
+      </c>
+      <c r="L21" s="31" t="inlineStr">
+        <is>
+          <t>CloseFarLot</t>
+        </is>
+      </c>
+      <c r="M21" s="29" t="inlineStr">
+        <is>
+          <t>FarRemain</t>
+        </is>
+      </c>
+      <c r="N21" s="31" t="inlineStr">
+        <is>
+          <t>CloseFarPercent</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1073,53 @@
         <f>IF($A22="","",Settings!$B$2)</f>
         <v>1</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="32">
+        <f>IF($A22="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D22" s="32">
+        <f>IF($A22="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E22" s="33">
         <f>IF($A22="","",ROUND(($B22*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>1.15</v>
-      </c>
-      <c r="D22" s="33">
-        <f>IF($A22="","",ROUND(($C22*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.44</v>
-      </c>
-      <c r="E22" s="33">
-        <f>IF($A22="","",ROUND(($B22*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.2</v>
+        <v>1.3</v>
+      </c>
+      <c r="F22" s="33">
+        <f>IF($A22="","",ROUND(($E22*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.47</v>
+      </c>
+      <c r="G22" s="33">
+        <f>IF($A22="","",$E22*$C22*Settings!$B$9)</f>
+        <v>130</v>
+      </c>
+      <c r="H22" s="33">
+        <f>IF($A22="","",$F22*$C22*Settings!$B$9)</f>
+        <v>47</v>
+      </c>
+      <c r="I22" s="33">
+        <f>IF($A22="","",$G22-$H22)</f>
+        <v>83</v>
+      </c>
+      <c r="J22" s="33">
+        <f>IF($A22="","",MAX(0,$I22*Settings!$B$5))</f>
+        <v>74.7</v>
+      </c>
+      <c r="K22" s="33">
+        <f>IF($A22="","",MAX(0,$I22*Settings!$B$6))</f>
+        <v>8.3</v>
+      </c>
+      <c r="L22" s="33">
+        <f>IF($A22="","",MIN($B22,IFERROR($J22/($D22*Settings!$B$9),0)))</f>
+        <v>0.3735</v>
+      </c>
+      <c r="M22" s="33">
+        <f>IF($A22="","",MAX(0,$B22-$L22))</f>
+        <v>0.6265</v>
+      </c>
+      <c r="N22" s="33">
+        <f>IF($A22="","",IFERROR($L22/$B22,0))</f>
+        <v>0.3735</v>
       </c>
     </row>
     <row r="23">
@@ -1020,20 +1128,56 @@
         <v>2</v>
       </c>
       <c r="B23" s="33">
-        <f>IF($A23="","",$B22*(1-Settings!$B$5))</f>
-        <v>0.8</v>
-      </c>
-      <c r="C23" s="33">
+        <f>IF($A23="","",$M22)</f>
+        <v>0.6265</v>
+      </c>
+      <c r="C23" s="32">
+        <f>IF($A23="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D23" s="32">
+        <f>IF($A23="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E23" s="33">
         <f>IF($A23="","",ROUND(($B23*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.92</v>
-      </c>
-      <c r="D23" s="33">
-        <f>IF($A23="","",ROUND(($C23*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.35</v>
-      </c>
-      <c r="E23" s="33">
-        <f>IF($A23="","",ROUND(($B23*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.16</v>
+        <v>0.81</v>
+      </c>
+      <c r="F23" s="33">
+        <f>IF($A23="","",ROUND(($E23*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.29</v>
+      </c>
+      <c r="G23" s="33">
+        <f>IF($A23="","",$E23*$C23*Settings!$B$9)</f>
+        <v>81</v>
+      </c>
+      <c r="H23" s="33">
+        <f>IF($A23="","",$F23*$C23*Settings!$B$9)</f>
+        <v>29</v>
+      </c>
+      <c r="I23" s="33">
+        <f>IF($A23="","",$G23-$H23)</f>
+        <v>52</v>
+      </c>
+      <c r="J23" s="33">
+        <f>IF($A23="","",MAX(0,$I23*Settings!$B$5))</f>
+        <v>46.8</v>
+      </c>
+      <c r="K23" s="33">
+        <f>IF($A23="","",MAX(0,$I23*Settings!$B$6))</f>
+        <v>5.2</v>
+      </c>
+      <c r="L23" s="33">
+        <f>IF($A23="","",MIN($B23,IFERROR($J23/($D23*Settings!$B$9),0)))</f>
+        <v>0.234</v>
+      </c>
+      <c r="M23" s="33">
+        <f>IF($A23="","",MAX(0,$B23-$L23))</f>
+        <v>0.3925</v>
+      </c>
+      <c r="N23" s="33">
+        <f>IF($A23="","",IFERROR($L23/$B23,0))</f>
+        <v>0.373503591381</v>
       </c>
     </row>
     <row r="24">
@@ -1042,20 +1186,56 @@
         <v>3</v>
       </c>
       <c r="B24" s="33">
-        <f>IF($A24="","",$B23*(1-Settings!$B$5))</f>
-        <v>0.64</v>
-      </c>
-      <c r="C24" s="33">
+        <f>IF($A24="","",$M23)</f>
+        <v>0.3925</v>
+      </c>
+      <c r="C24" s="32">
+        <f>IF($A24="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D24" s="32">
+        <f>IF($A24="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E24" s="33">
         <f>IF($A24="","",ROUND(($B24*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.74</v>
-      </c>
-      <c r="D24" s="33">
-        <f>IF($A24="","",ROUND(($C24*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.28</v>
-      </c>
-      <c r="E24" s="33">
-        <f>IF($A24="","",ROUND(($B24*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.13</v>
+        <v>0.51</v>
+      </c>
+      <c r="F24" s="33">
+        <f>IF($A24="","",ROUND(($E24*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.18</v>
+      </c>
+      <c r="G24" s="33">
+        <f>IF($A24="","",$E24*$C24*Settings!$B$9)</f>
+        <v>51</v>
+      </c>
+      <c r="H24" s="33">
+        <f>IF($A24="","",$F24*$C24*Settings!$B$9)</f>
+        <v>18</v>
+      </c>
+      <c r="I24" s="33">
+        <f>IF($A24="","",$G24-$H24)</f>
+        <v>33</v>
+      </c>
+      <c r="J24" s="33">
+        <f>IF($A24="","",MAX(0,$I24*Settings!$B$5))</f>
+        <v>29.7</v>
+      </c>
+      <c r="K24" s="33">
+        <f>IF($A24="","",MAX(0,$I24*Settings!$B$6))</f>
+        <v>3.3</v>
+      </c>
+      <c r="L24" s="33">
+        <f>IF($A24="","",MIN($B24,IFERROR($J24/($D24*Settings!$B$9),0)))</f>
+        <v>0.1485</v>
+      </c>
+      <c r="M24" s="33">
+        <f>IF($A24="","",MAX(0,$B24-$L24))</f>
+        <v>0.244</v>
+      </c>
+      <c r="N24" s="33">
+        <f>IF($A24="","",IFERROR($L24/$B24,0))</f>
+        <v>0.378343949045</v>
       </c>
     </row>
     <row r="25">
@@ -1064,20 +1244,56 @@
         <v>4</v>
       </c>
       <c r="B25" s="33">
-        <f>IF($A25="","",$B24*(1-Settings!$B$5))</f>
-        <v>0.512</v>
-      </c>
-      <c r="C25" s="33">
+        <f>IF($A25="","",$M24)</f>
+        <v>0.244</v>
+      </c>
+      <c r="C25" s="32">
+        <f>IF($A25="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D25" s="32">
+        <f>IF($A25="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E25" s="33">
         <f>IF($A25="","",ROUND(($B25*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.59</v>
-      </c>
-      <c r="D25" s="33">
-        <f>IF($A25="","",ROUND(($C25*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.22</v>
-      </c>
-      <c r="E25" s="33">
-        <f>IF($A25="","",ROUND(($B25*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.1</v>
+        <v>0.32</v>
+      </c>
+      <c r="F25" s="33">
+        <f>IF($A25="","",ROUND(($E25*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.12</v>
+      </c>
+      <c r="G25" s="33">
+        <f>IF($A25="","",$E25*$C25*Settings!$B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="H25" s="33">
+        <f>IF($A25="","",$F25*$C25*Settings!$B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="I25" s="33">
+        <f>IF($A25="","",$G25-$H25)</f>
+        <v>20</v>
+      </c>
+      <c r="J25" s="33">
+        <f>IF($A25="","",MAX(0,$I25*Settings!$B$5))</f>
+        <v>18</v>
+      </c>
+      <c r="K25" s="33">
+        <f>IF($A25="","",MAX(0,$I25*Settings!$B$6))</f>
+        <v>2</v>
+      </c>
+      <c r="L25" s="33">
+        <f>IF($A25="","",MIN($B25,IFERROR($J25/($D25*Settings!$B$9),0)))</f>
+        <v>0.09</v>
+      </c>
+      <c r="M25" s="33">
+        <f>IF($A25="","",MAX(0,$B25-$L25))</f>
+        <v>0.154</v>
+      </c>
+      <c r="N25" s="33">
+        <f>IF($A25="","",IFERROR($L25/$B25,0))</f>
+        <v>0.368852459016</v>
       </c>
     </row>
     <row r="26">
@@ -1086,20 +1302,56 @@
         <v>5</v>
       </c>
       <c r="B26" s="33">
-        <f>IF($A26="","",$B25*(1-Settings!$B$5))</f>
-        <v>0.4096</v>
-      </c>
-      <c r="C26" s="33">
+        <f>IF($A26="","",$M25)</f>
+        <v>0.154</v>
+      </c>
+      <c r="C26" s="32">
+        <f>IF($A26="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D26" s="32">
+        <f>IF($A26="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E26" s="33">
         <f>IF($A26="","",ROUND(($B26*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.47</v>
-      </c>
-      <c r="D26" s="33">
-        <f>IF($A26="","",ROUND(($C26*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.18</v>
-      </c>
-      <c r="E26" s="33">
-        <f>IF($A26="","",ROUND(($B26*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.08</v>
+        <v>0.2</v>
+      </c>
+      <c r="F26" s="33">
+        <f>IF($A26="","",ROUND(($E26*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.07</v>
+      </c>
+      <c r="G26" s="33">
+        <f>IF($A26="","",$E26*$C26*Settings!$B$9)</f>
+        <v>20</v>
+      </c>
+      <c r="H26" s="33">
+        <f>IF($A26="","",$F26*$C26*Settings!$B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="I26" s="33">
+        <f>IF($A26="","",$G26-$H26)</f>
+        <v>13</v>
+      </c>
+      <c r="J26" s="33">
+        <f>IF($A26="","",MAX(0,$I26*Settings!$B$5))</f>
+        <v>11.7</v>
+      </c>
+      <c r="K26" s="33">
+        <f>IF($A26="","",MAX(0,$I26*Settings!$B$6))</f>
+        <v>1.3</v>
+      </c>
+      <c r="L26" s="33">
+        <f>IF($A26="","",MIN($B26,IFERROR($J26/($D26*Settings!$B$9),0)))</f>
+        <v>0.0585</v>
+      </c>
+      <c r="M26" s="33">
+        <f>IF($A26="","",MAX(0,$B26-$L26))</f>
+        <v>0.0955</v>
+      </c>
+      <c r="N26" s="33">
+        <f>IF($A26="","",IFERROR($L26/$B26,0))</f>
+        <v>0.37987012987</v>
       </c>
     </row>
     <row r="27">
@@ -1108,20 +1360,56 @@
         <v>6</v>
       </c>
       <c r="B27" s="33">
-        <f>IF($A27="","",$B26*(1-Settings!$B$5))</f>
-        <v>0.32768</v>
-      </c>
-      <c r="C27" s="33">
+        <f>IF($A27="","",$M26)</f>
+        <v>0.0955</v>
+      </c>
+      <c r="C27" s="32">
+        <f>IF($A27="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D27" s="32">
+        <f>IF($A27="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E27" s="33">
         <f>IF($A27="","",ROUND(($B27*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.38</v>
-      </c>
-      <c r="D27" s="33">
-        <f>IF($A27="","",ROUND(($C27*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.14</v>
-      </c>
-      <c r="E27" s="33">
-        <f>IF($A27="","",ROUND(($B27*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.07</v>
+        <v>0.12</v>
+      </c>
+      <c r="F27" s="33">
+        <f>IF($A27="","",ROUND(($E27*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.04</v>
+      </c>
+      <c r="G27" s="33">
+        <f>IF($A27="","",$E27*$C27*Settings!$B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="H27" s="33">
+        <f>IF($A27="","",$F27*$C27*Settings!$B$9)</f>
+        <v>4</v>
+      </c>
+      <c r="I27" s="33">
+        <f>IF($A27="","",$G27-$H27)</f>
+        <v>8</v>
+      </c>
+      <c r="J27" s="33">
+        <f>IF($A27="","",MAX(0,$I27*Settings!$B$5))</f>
+        <v>7.2</v>
+      </c>
+      <c r="K27" s="33">
+        <f>IF($A27="","",MAX(0,$I27*Settings!$B$6))</f>
+        <v>0.8</v>
+      </c>
+      <c r="L27" s="33">
+        <f>IF($A27="","",MIN($B27,IFERROR($J27/($D27*Settings!$B$9),0)))</f>
+        <v>0.036</v>
+      </c>
+      <c r="M27" s="33">
+        <f>IF($A27="","",MAX(0,$B27-$L27))</f>
+        <v>0.0595</v>
+      </c>
+      <c r="N27" s="33">
+        <f>IF($A27="","",IFERROR($L27/$B27,0))</f>
+        <v>0.376963350785</v>
       </c>
     </row>
     <row r="28">
@@ -1130,20 +1418,56 @@
         <v>7</v>
       </c>
       <c r="B28" s="33">
-        <f>IF($A28="","",$B27*(1-Settings!$B$5))</f>
-        <v>0.262144</v>
-      </c>
-      <c r="C28" s="33">
+        <f>IF($A28="","",$M27)</f>
+        <v>0.0595</v>
+      </c>
+      <c r="C28" s="32">
+        <f>IF($A28="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D28" s="32">
+        <f>IF($A28="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E28" s="33">
         <f>IF($A28="","",ROUND(($B28*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.3</v>
-      </c>
-      <c r="D28" s="33">
-        <f>IF($A28="","",ROUND(($C28*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.11</v>
-      </c>
-      <c r="E28" s="33">
-        <f>IF($A28="","",ROUND(($B28*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.05</v>
+        <v>0.08</v>
+      </c>
+      <c r="F28" s="33">
+        <f>IF($A28="","",ROUND(($E28*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.03</v>
+      </c>
+      <c r="G28" s="33">
+        <f>IF($A28="","",$E28*$C28*Settings!$B$9)</f>
+        <v>8</v>
+      </c>
+      <c r="H28" s="33">
+        <f>IF($A28="","",$F28*$C28*Settings!$B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="I28" s="33">
+        <f>IF($A28="","",$G28-$H28)</f>
+        <v>5</v>
+      </c>
+      <c r="J28" s="33">
+        <f>IF($A28="","",MAX(0,$I28*Settings!$B$5))</f>
+        <v>4.5</v>
+      </c>
+      <c r="K28" s="33">
+        <f>IF($A28="","",MAX(0,$I28*Settings!$B$6))</f>
+        <v>0.5</v>
+      </c>
+      <c r="L28" s="33">
+        <f>IF($A28="","",MIN($B28,IFERROR($J28/($D28*Settings!$B$9),0)))</f>
+        <v>0.0225</v>
+      </c>
+      <c r="M28" s="33">
+        <f>IF($A28="","",MAX(0,$B28-$L28))</f>
+        <v>0.037</v>
+      </c>
+      <c r="N28" s="33">
+        <f>IF($A28="","",IFERROR($L28/$B28,0))</f>
+        <v>0.378151260504</v>
       </c>
     </row>
     <row r="29">
@@ -1152,20 +1476,56 @@
         <v>8</v>
       </c>
       <c r="B29" s="33">
-        <f>IF($A29="","",$B28*(1-Settings!$B$5))</f>
-        <v>0.2097152</v>
-      </c>
-      <c r="C29" s="33">
+        <f>IF($A29="","",$M28)</f>
+        <v>0.037</v>
+      </c>
+      <c r="C29" s="32">
+        <f>IF($A29="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D29" s="32">
+        <f>IF($A29="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E29" s="33">
         <f>IF($A29="","",ROUND(($B29*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.24</v>
-      </c>
-      <c r="D29" s="33">
-        <f>IF($A29="","",ROUND(($C29*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.09</v>
-      </c>
-      <c r="E29" s="33">
-        <f>IF($A29="","",ROUND(($B29*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.04</v>
+        <v>0.05</v>
+      </c>
+      <c r="F29" s="33">
+        <f>IF($A29="","",ROUND(($E29*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G29" s="33">
+        <f>IF($A29="","",$E29*$C29*Settings!$B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="H29" s="33">
+        <f>IF($A29="","",$F29*$C29*Settings!$B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="I29" s="33">
+        <f>IF($A29="","",$G29-$H29)</f>
+        <v>3</v>
+      </c>
+      <c r="J29" s="33">
+        <f>IF($A29="","",MAX(0,$I29*Settings!$B$5))</f>
+        <v>2.7</v>
+      </c>
+      <c r="K29" s="33">
+        <f>IF($A29="","",MAX(0,$I29*Settings!$B$6))</f>
+        <v>0.3</v>
+      </c>
+      <c r="L29" s="33">
+        <f>IF($A29="","",MIN($B29,IFERROR($J29/($D29*Settings!$B$9),0)))</f>
+        <v>0.0135</v>
+      </c>
+      <c r="M29" s="33">
+        <f>IF($A29="","",MAX(0,$B29-$L29))</f>
+        <v>0.0235</v>
+      </c>
+      <c r="N29" s="33">
+        <f>IF($A29="","",IFERROR($L29/$B29,0))</f>
+        <v>0.364864864865</v>
       </c>
     </row>
     <row r="30">
@@ -1174,20 +1534,56 @@
         <v>9</v>
       </c>
       <c r="B30" s="33">
-        <f>IF($A30="","",$B29*(1-Settings!$B$5))</f>
-        <v>0.16777216</v>
-      </c>
-      <c r="C30" s="33">
+        <f>IF($A30="","",$M29)</f>
+        <v>0.0235</v>
+      </c>
+      <c r="C30" s="32">
+        <f>IF($A30="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D30" s="32">
+        <f>IF($A30="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E30" s="33">
         <f>IF($A30="","",ROUND(($B30*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.19</v>
-      </c>
-      <c r="D30" s="33">
-        <f>IF($A30="","",ROUND(($C30*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.07</v>
-      </c>
-      <c r="E30" s="33">
-        <f>IF($A30="","",ROUND(($B30*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
         <v>0.03</v>
+      </c>
+      <c r="F30" s="33">
+        <f>IF($A30="","",ROUND(($E30*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.01</v>
+      </c>
+      <c r="G30" s="33">
+        <f>IF($A30="","",$E30*$C30*Settings!$B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="H30" s="33">
+        <f>IF($A30="","",$F30*$C30*Settings!$B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="I30" s="33">
+        <f>IF($A30="","",$G30-$H30)</f>
+        <v>2</v>
+      </c>
+      <c r="J30" s="33">
+        <f>IF($A30="","",MAX(0,$I30*Settings!$B$5))</f>
+        <v>1.8</v>
+      </c>
+      <c r="K30" s="33">
+        <f>IF($A30="","",MAX(0,$I30*Settings!$B$6))</f>
+        <v>0.2</v>
+      </c>
+      <c r="L30" s="33">
+        <f>IF($A30="","",MIN($B30,IFERROR($J30/($D30*Settings!$B$9),0)))</f>
+        <v>0.009</v>
+      </c>
+      <c r="M30" s="33">
+        <f>IF($A30="","",MAX(0,$B30-$L30))</f>
+        <v>0.0145</v>
+      </c>
+      <c r="N30" s="33">
+        <f>IF($A30="","",IFERROR($L30/$B30,0))</f>
+        <v>0.382978723404</v>
       </c>
     </row>
     <row r="31">
@@ -1196,25 +1592,61 @@
         <v>10</v>
       </c>
       <c r="B31" s="33">
-        <f>IF($A31="","",$B30*(1-Settings!$B$5))</f>
-        <v>0.134217728</v>
-      </c>
-      <c r="C31" s="33">
+        <f>IF($A31="","",$M30)</f>
+        <v>0.0145</v>
+      </c>
+      <c r="C31" s="32">
+        <f>IF($A31="","",100)</f>
+        <v>100</v>
+      </c>
+      <c r="D31" s="32">
+        <f>IF($A31="","",200)</f>
+        <v>200</v>
+      </c>
+      <c r="E31" s="33">
         <f>IF($A31="","",ROUND(($B31*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.15</v>
-      </c>
-      <c r="D31" s="33">
-        <f>IF($A31="","",ROUND(($C31*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.06</v>
-      </c>
-      <c r="E31" s="33">
-        <f>IF($A31="","",ROUND(($B31*Settings!$B$5)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.03</v>
+        <v>0.02</v>
+      </c>
+      <c r="F31" s="33">
+        <f>IF($A31="","",ROUND(($E31*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
+        <v>0.01</v>
+      </c>
+      <c r="G31" s="33">
+        <f>IF($A31="","",$E31*$C31*Settings!$B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="H31" s="33">
+        <f>IF($A31="","",$F31*$C31*Settings!$B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="I31" s="33">
+        <f>IF($A31="","",$G31-$H31)</f>
+        <v>1</v>
+      </c>
+      <c r="J31" s="33">
+        <f>IF($A31="","",MAX(0,$I31*Settings!$B$5))</f>
+        <v>0.9</v>
+      </c>
+      <c r="K31" s="33">
+        <f>IF($A31="","",MAX(0,$I31*Settings!$B$6))</f>
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="33">
+        <f>IF($A31="","",MIN($B31,IFERROR($J31/($D31*Settings!$B$9),0)))</f>
+        <v>0.0045</v>
+      </c>
+      <c r="M31" s="33">
+        <f>IF($A31="","",MAX(0,$B31-$L31))</f>
+        <v>0.01</v>
+      </c>
+      <c r="N31" s="33">
+        <f>IF($A31="","",IFERROR($L31/$B31,0))</f>
+        <v>0.310344827586</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A20:N20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1226,7 +1658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG11"/>
+  <dimension ref="A1:BO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1288,6 +1720,14 @@
     <col width="20" customWidth="1" min="57" max="57"/>
     <col width="20" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="15" customWidth="1" min="60" max="60"/>
+    <col width="19" customWidth="1" min="61" max="61"/>
+    <col width="14" customWidth="1" min="62" max="62"/>
+    <col width="14" customWidth="1" min="63" max="63"/>
+    <col width="17" customWidth="1" min="64" max="64"/>
+    <col width="17" customWidth="1" min="65" max="65"/>
+    <col width="15" customWidth="1" min="66" max="66"/>
+    <col width="14" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1586,15 +2026,56 @@
           <t>ManualAllowNewLevel</t>
         </is>
       </c>
+      <c r="BH1" s="38" t="inlineStr">
+        <is>
+          <t>BigMovePoints</t>
+        </is>
+      </c>
+      <c r="BI1" s="38" t="inlineStr">
+        <is>
+          <t>FarDistancePoints</t>
+        </is>
+      </c>
+      <c r="BJ1" s="38" t="inlineStr">
+        <is>
+          <t>HarvestMode</t>
+        </is>
+      </c>
+      <c r="BK1" s="38" t="inlineStr">
+        <is>
+          <t>HarvestCount</t>
+        </is>
+      </c>
+      <c r="BL1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarPercent</t>
+        </is>
+      </c>
+      <c r="BM1" s="38" t="inlineStr">
+        <is>
+          <t>CanFullCloseFar</t>
+        </is>
+      </c>
+      <c r="BN1" s="38" t="inlineStr">
+        <is>
+          <t>FarRemainLoss</t>
+        </is>
+      </c>
+      <c r="BO1" s="38" t="inlineStr">
+        <is>
+          <t>FinalClosePL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="13" t="str">
         <is>
           <t>BIG_SIDE</t>
         </is>
+        <v>BIG_SIDE</v>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
@@ -1603,7 +2084,7 @@
       </c>
       <c r="D2" s="13">
         <f>Settings!$B$2</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E2" s="12">
         <f>IF($B2="BLOCKED","",IF($C2="SELL","BUY","SELL"))</f>
@@ -1611,11 +2092,11 @@
       </c>
       <c r="F2" s="12">
         <f>IF($B2="BLOCKED",0,MAX(0,$D2*Settings!$B$3))</f>
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -1623,35 +2104,38 @@
       </c>
       <c r="I2" s="12">
         <f>IF($B2="BLOCKED",0,MAX(0,$G2*Settings!$B$4))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
-      </c>
-      <c r="K2" s="13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K2" s="13">
+        <f>$BH2</f>
         <v>100</v>
       </c>
-      <c r="L2" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M2" s="13" t="n">
-        <v>100</v>
+      <c r="L2" s="13">
+        <f>IF($B2="BLOCKED",0,-$BH2)</f>
+        <v>-100</v>
+      </c>
+      <c r="M2" s="13">
+        <f>$BI2</f>
+        <v>200</v>
       </c>
       <c r="N2" s="14">
-        <f>IF($B2="BIG_SIDE",$G2*MAX(0,$K2)*Settings!$B$9,0)</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",$G2*$BH2*Settings!$B$9,0)</f>
+        <v>130</v>
       </c>
       <c r="O2" s="14">
-        <f>IF($B2="SMALL_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$J2*$BH2*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P2" s="15">
-        <f>IF($B2="BIG_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",$J2*$BH2*Settings!$B$9,0)</f>
+        <v>47</v>
       </c>
       <c r="Q2" s="15">
-        <f>IF($B2="SMALL_SIDE",$AL2*ABS($K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$AL2*$BH2*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R2" s="15">
@@ -1660,38 +2144,38 @@
       </c>
       <c r="S2" s="14">
         <f>IF($B2="BIG_SIDE",$N2-$P2-$R2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="T2" s="12">
         <f>IF(AND($B2="BIG_SIDE",$AX2&gt;0),$AX2*Settings!$B$5,0)</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="U2" s="12">
-        <f>MAX(0,$M2*Settings!$B$9)</f>
-        <v/>
+        <f>MAX(0,$BI2*Settings!$B$9)</f>
+        <v>200</v>
       </c>
       <c r="V2" s="12">
         <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
-        <v/>
+        <v>0.3735</v>
       </c>
       <c r="W2" s="12">
         <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
-        <v/>
+        <v>0.6265</v>
       </c>
       <c r="X2" s="19">
-        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2-$AS$2,0),IF($S$2&gt;0,$S$2*0.5,0))</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2*Settings!$B$6,0),IF($S$2&gt;0,$S$2*Settings!$B$6,0))</f>
+        <v>8.3</v>
       </c>
       <c r="Y2" s="19">
-        <f>X2</f>
-        <v/>
+        <f>IF(ROW()=2,$X2,$Y1+$X2)</f>
+        <v>8.3</v>
       </c>
       <c r="Z2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
-        <v/>
+        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$S2-$AS2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
+        <v>8.3</v>
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
@@ -1763,7 +2247,7 @@
       </c>
       <c r="AS2" s="20">
         <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="AT2" s="12">
         <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
@@ -1783,7 +2267,7 @@
       </c>
       <c r="AX2" s="12">
         <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,0)</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="AY2" s="12">
         <f>IF($B2="BIG_SIDE",($G2+$J2)*$AU2,0)</f>
@@ -1818,6 +2302,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH2">
+        <f>IF($B2="BLOCKED",0,100)</f>
+        <v>100</v>
+      </c>
+      <c r="BI2">
+        <f>IF($B2="BLOCKED",0,200)</f>
+        <v>200</v>
+      </c>
+      <c r="BJ2" t="str">
+        <f>IF($B2="BIG_SIDE","BIG_HARVEST",IF($B2="SMALL_SIDE","SMALL_FLIP",IF($B2="BLOCKED","BLOCKED","")))</f>
+        <v>BIG_HARVEST</v>
+      </c>
+      <c r="BK2">
+        <f>IF($B2="BIG_SIDE",IF(ROW()=2,1,$BK1+1),IF(ROW()=2,0,$BK1))</f>
+        <v>1</v>
+      </c>
+      <c r="BL2">
+        <f>IF($D2&gt;0,IFERROR($V2/$D2,0),0)</f>
+        <v>0.3735</v>
+      </c>
+      <c r="BM2" t="b">
+        <f>IF($BN2&lt;=0,FALSE,$Y2&gt;=$BN2)</f>
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <f>MAX(0,$W2*$BI2*Settings!$B$9)</f>
+        <v>125.3</v>
+      </c>
+      <c r="BO2">
+        <f>$Y2-$BN2</f>
+        <v>-117</v>
       </c>
     </row>
     <row r="3">
@@ -1860,29 +2376,32 @@
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K3" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L3" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M3" s="13" t="n">
-        <v>100</v>
+      <c r="K3" s="13">
+        <f>$BH3</f>
+        <v/>
+      </c>
+      <c r="L3" s="13">
+        <f>IF($B3="BLOCKED",0,-$BH3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="13">
+        <f>$BI3</f>
+        <v/>
       </c>
       <c r="N3" s="14">
-        <f>IF($B3="BIG_SIDE",$G3*MAX(0,$K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$G3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O3" s="14">
-        <f>IF($B3="SMALL_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$J3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P3" s="15">
-        <f>IF($B3="BIG_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$J3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q3" s="15">
-        <f>IF($B3="SMALL_SIDE",$AL3*ABS($K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$AL3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R3" s="15">
@@ -1898,7 +2417,7 @@
         <v/>
       </c>
       <c r="U3" s="12">
-        <f>MAX(0,$M3*Settings!$B$9)</f>
+        <f>MAX(0,$BI3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V3" s="12">
@@ -1910,11 +2429,11 @@
         <v/>
       </c>
       <c r="X3" s="19">
-        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3-$AS$3,0),IF($S$3&gt;0,$S$3*0.5,0))</f>
+        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3*Settings!$B$6,0),IF($S$3&gt;0,$S$3*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y3" s="19">
-        <f>$Y2+$X3</f>
+        <f>IF(ROW()=2,$X3,$Y2+$X3)</f>
         <v/>
       </c>
       <c r="Z3" s="12">
@@ -1922,7 +2441,7 @@
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
+        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$S3-$AS3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
@@ -2050,6 +2569,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH3">
+        <f>IF($B3="BLOCKED",0,$BH2)</f>
+        <v/>
+      </c>
+      <c r="BI3">
+        <f>IF($B3="BLOCKED",0,$BI2)</f>
+        <v/>
+      </c>
+      <c r="BJ3">
+        <f>IF($B3="BIG_SIDE","BIG_HARVEST",IF($B3="SMALL_SIDE","SMALL_FLIP",IF($B3="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK3">
+        <f>IF($B3="BIG_SIDE",IF(ROW()=2,1,$BK2+1),IF(ROW()=2,0,$BK2))</f>
+        <v/>
+      </c>
+      <c r="BL3">
+        <f>IF($D3&gt;0,IFERROR($V3/$D3,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM3">
+        <f>IF($BN3&lt;=0,FALSE,$Y3&gt;=$BN3)</f>
+        <v/>
+      </c>
+      <c r="BN3">
+        <f>MAX(0,$W3*$BI3*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO3">
+        <f>$Y3-$BN3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -2092,29 +2643,32 @@
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K4" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="L4" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="M4" s="13" t="n">
-        <v>100</v>
+      <c r="K4" s="13">
+        <f>$BH4</f>
+        <v/>
+      </c>
+      <c r="L4" s="13">
+        <f>IF($B4="BLOCKED",0,-$BH4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="13">
+        <f>$BI4</f>
+        <v/>
       </c>
       <c r="N4" s="14">
-        <f>IF($B4="BIG_SIDE",$G4*MAX(0,$K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$G4*$BH4*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O4" s="14">
-        <f>IF($B4="SMALL_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$J4*$BH4*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P4" s="15">
-        <f>IF($B4="BIG_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$J4*$BH4*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q4" s="15">
-        <f>IF($B4="SMALL_SIDE",$AL4*ABS($K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$AL4*$BH4*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R4" s="15">
@@ -2130,7 +2684,7 @@
         <v/>
       </c>
       <c r="U4" s="12">
-        <f>MAX(0,$M4*Settings!$B$9)</f>
+        <f>MAX(0,$BI4*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V4" s="12">
@@ -2142,11 +2696,11 @@
         <v/>
       </c>
       <c r="X4" s="19">
-        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4-$AS$4,0),IF($S$4&gt;0,$S$4*0.5,0))</f>
+        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4*Settings!$B$6,0),IF($S$4&gt;0,$S$4*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y4" s="19">
-        <f>$Y3+$X4</f>
+        <f>IF(ROW()=2,$X4,$Y3+$X4)</f>
         <v/>
       </c>
       <c r="Z4" s="12">
@@ -2154,7 +2708,7 @@
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
+        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$S4-$AS4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
@@ -2282,6 +2836,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH4">
+        <f>IF($B4="BLOCKED",0,$BH3)</f>
+        <v/>
+      </c>
+      <c r="BI4">
+        <f>IF($B4="BLOCKED",0,$BI3)</f>
+        <v/>
+      </c>
+      <c r="BJ4">
+        <f>IF($B4="BIG_SIDE","BIG_HARVEST",IF($B4="SMALL_SIDE","SMALL_FLIP",IF($B4="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK4">
+        <f>IF($B4="BIG_SIDE",IF(ROW()=2,1,$BK3+1),IF(ROW()=2,0,$BK3))</f>
+        <v/>
+      </c>
+      <c r="BL4">
+        <f>IF($D4&gt;0,IFERROR($V4/$D4,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM4">
+        <f>IF($BN4&lt;=0,FALSE,$Y4&gt;=$BN4)</f>
+        <v/>
+      </c>
+      <c r="BN4">
+        <f>MAX(0,$W4*$BI4*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO4">
+        <f>$Y4-$BN4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -2324,29 +2910,32 @@
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K5" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M5" s="13" t="n">
-        <v>100</v>
+      <c r="K5" s="13">
+        <f>$BH5</f>
+        <v/>
+      </c>
+      <c r="L5" s="13">
+        <f>IF($B5="BLOCKED",0,-$BH5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="13">
+        <f>$BI5</f>
+        <v/>
       </c>
       <c r="N5" s="14">
-        <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$G5*$BH5*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O5" s="14">
-        <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$J5*$BH5*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P5" s="15">
-        <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$J5*$BH5*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q5" s="15">
-        <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$AL5*$BH5*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R5" s="15">
@@ -2362,7 +2951,7 @@
         <v/>
       </c>
       <c r="U5" s="12">
-        <f>MAX(0,$M5*Settings!$B$9)</f>
+        <f>MAX(0,$BI5*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V5" s="12">
@@ -2374,11 +2963,11 @@
         <v/>
       </c>
       <c r="X5" s="19">
-        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5-$AS$5,0),IF($S$5&gt;0,$S$5*0.5,0))</f>
+        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5*Settings!$B$6,0),IF($S$5&gt;0,$S$5*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y5" s="19">
-        <f>$Y4+$X5</f>
+        <f>IF(ROW()=2,$X5,$Y4+$X5)</f>
         <v/>
       </c>
       <c r="Z5" s="12">
@@ -2386,7 +2975,7 @@
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
+        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$S5-$AS5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
@@ -2514,6 +3103,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH5">
+        <f>IF($B5="BLOCKED",0,$BH4)</f>
+        <v/>
+      </c>
+      <c r="BI5">
+        <f>IF($B5="BLOCKED",0,$BI4)</f>
+        <v/>
+      </c>
+      <c r="BJ5">
+        <f>IF($B5="BIG_SIDE","BIG_HARVEST",IF($B5="SMALL_SIDE","SMALL_FLIP",IF($B5="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK5">
+        <f>IF($B5="BIG_SIDE",IF(ROW()=2,1,$BK4+1),IF(ROW()=2,0,$BK4))</f>
+        <v/>
+      </c>
+      <c r="BL5">
+        <f>IF($D5&gt;0,IFERROR($V5/$D5,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM5">
+        <f>IF($BN5&lt;=0,FALSE,$Y5&gt;=$BN5)</f>
+        <v/>
+      </c>
+      <c r="BN5">
+        <f>MAX(0,$W5*$BI5*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO5">
+        <f>$Y5-$BN5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2556,29 +3177,32 @@
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K6" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M6" s="13" t="n">
-        <v>100</v>
+      <c r="K6" s="13">
+        <f>$BH6</f>
+        <v/>
+      </c>
+      <c r="L6" s="13">
+        <f>IF($B6="BLOCKED",0,-$BH6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="13">
+        <f>$BI6</f>
+        <v/>
       </c>
       <c r="N6" s="14">
-        <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$G6*$BH6*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O6" s="14">
-        <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$J6*$BH6*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P6" s="15">
-        <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$J6*$BH6*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q6" s="15">
-        <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$AL6*$BH6*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R6" s="15">
@@ -2594,7 +3218,7 @@
         <v/>
       </c>
       <c r="U6" s="12">
-        <f>MAX(0,$M6*Settings!$B$9)</f>
+        <f>MAX(0,$BI6*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V6" s="12">
@@ -2606,11 +3230,11 @@
         <v/>
       </c>
       <c r="X6" s="19">
-        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6-$AS$6,0),IF($S$6&gt;0,$S$6*0.5,0))</f>
+        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6*Settings!$B$6,0),IF($S$6&gt;0,$S$6*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y6" s="19">
-        <f>$Y5+$X6</f>
+        <f>IF(ROW()=2,$X6,$Y5+$X6)</f>
         <v/>
       </c>
       <c r="Z6" s="12">
@@ -2618,7 +3242,7 @@
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
+        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$S6-$AS6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
@@ -2746,6 +3370,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH6">
+        <f>IF($B6="BLOCKED",0,$BH5)</f>
+        <v/>
+      </c>
+      <c r="BI6">
+        <f>IF($B6="BLOCKED",0,$BI5)</f>
+        <v/>
+      </c>
+      <c r="BJ6">
+        <f>IF($B6="BIG_SIDE","BIG_HARVEST",IF($B6="SMALL_SIDE","SMALL_FLIP",IF($B6="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK6">
+        <f>IF($B6="BIG_SIDE",IF(ROW()=2,1,$BK5+1),IF(ROW()=2,0,$BK5))</f>
+        <v/>
+      </c>
+      <c r="BL6">
+        <f>IF($D6&gt;0,IFERROR($V6/$D6,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM6">
+        <f>IF($BN6&lt;=0,FALSE,$Y6&gt;=$BN6)</f>
+        <v/>
+      </c>
+      <c r="BN6">
+        <f>MAX(0,$W6*$BI6*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO6">
+        <f>$Y6-$BN6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2788,29 +3444,32 @@
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K7" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>100</v>
+      <c r="K7" s="13">
+        <f>$BH7</f>
+        <v/>
+      </c>
+      <c r="L7" s="13">
+        <f>IF($B7="BLOCKED",0,-$BH7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="13">
+        <f>$BI7</f>
+        <v/>
       </c>
       <c r="N7" s="14">
-        <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$G7*$BH7*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O7" s="14">
-        <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$J7*$BH7*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P7" s="15">
-        <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$J7*$BH7*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q7" s="15">
-        <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$AL7*$BH7*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R7" s="15">
@@ -2826,7 +3485,7 @@
         <v/>
       </c>
       <c r="U7" s="12">
-        <f>MAX(0,$M7*Settings!$B$9)</f>
+        <f>MAX(0,$BI7*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V7" s="12">
@@ -2838,11 +3497,11 @@
         <v/>
       </c>
       <c r="X7" s="19">
-        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7-$AS$7,0),IF($S$7&gt;0,$S$7*0.5,0))</f>
+        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7*Settings!$B$6,0),IF($S$7&gt;0,$S$7*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y7" s="19">
-        <f>$Y6+$X7</f>
+        <f>IF(ROW()=2,$X7,$Y6+$X7)</f>
         <v/>
       </c>
       <c r="Z7" s="12">
@@ -2850,7 +3509,7 @@
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
+        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$S7-$AS7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
@@ -2978,6 +3637,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH7">
+        <f>IF($B7="BLOCKED",0,$BH6)</f>
+        <v/>
+      </c>
+      <c r="BI7">
+        <f>IF($B7="BLOCKED",0,$BI6)</f>
+        <v/>
+      </c>
+      <c r="BJ7">
+        <f>IF($B7="BIG_SIDE","BIG_HARVEST",IF($B7="SMALL_SIDE","SMALL_FLIP",IF($B7="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK7">
+        <f>IF($B7="BIG_SIDE",IF(ROW()=2,1,$BK6+1),IF(ROW()=2,0,$BK6))</f>
+        <v/>
+      </c>
+      <c r="BL7">
+        <f>IF($D7&gt;0,IFERROR($V7/$D7,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM7">
+        <f>IF($BN7&lt;=0,FALSE,$Y7&gt;=$BN7)</f>
+        <v/>
+      </c>
+      <c r="BN7">
+        <f>MAX(0,$W7*$BI7*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO7">
+        <f>$Y7-$BN7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -3020,29 +3711,32 @@
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K8" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>100</v>
+      <c r="K8" s="13">
+        <f>$BH8</f>
+        <v/>
+      </c>
+      <c r="L8" s="13">
+        <f>IF($B8="BLOCKED",0,-$BH8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="13">
+        <f>$BI8</f>
+        <v/>
       </c>
       <c r="N8" s="14">
-        <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$G8*$BH8*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O8" s="14">
-        <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$J8*$BH8*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P8" s="15">
-        <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$J8*$BH8*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q8" s="15">
-        <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$AL8*$BH8*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R8" s="15">
@@ -3058,7 +3752,7 @@
         <v/>
       </c>
       <c r="U8" s="12">
-        <f>MAX(0,$M8*Settings!$B$9)</f>
+        <f>MAX(0,$BI8*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V8" s="12">
@@ -3070,11 +3764,11 @@
         <v/>
       </c>
       <c r="X8" s="19">
-        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8-$AS$8,0),IF($S$8&gt;0,$S$8*0.5,0))</f>
+        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8*Settings!$B$6,0),IF($S$8&gt;0,$S$8*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y8" s="19">
-        <f>$Y7+$X8</f>
+        <f>IF(ROW()=2,$X8,$Y7+$X8)</f>
         <v/>
       </c>
       <c r="Z8" s="12">
@@ -3082,7 +3776,7 @@
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
+        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$S8-$AS8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
@@ -3210,6 +3904,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH8">
+        <f>IF($B8="BLOCKED",0,$BH7)</f>
+        <v/>
+      </c>
+      <c r="BI8">
+        <f>IF($B8="BLOCKED",0,$BI7)</f>
+        <v/>
+      </c>
+      <c r="BJ8">
+        <f>IF($B8="BIG_SIDE","BIG_HARVEST",IF($B8="SMALL_SIDE","SMALL_FLIP",IF($B8="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK8">
+        <f>IF($B8="BIG_SIDE",IF(ROW()=2,1,$BK7+1),IF(ROW()=2,0,$BK7))</f>
+        <v/>
+      </c>
+      <c r="BL8">
+        <f>IF($D8&gt;0,IFERROR($V8/$D8,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM8">
+        <f>IF($BN8&lt;=0,FALSE,$Y8&gt;=$BN8)</f>
+        <v/>
+      </c>
+      <c r="BN8">
+        <f>MAX(0,$W8*$BI8*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO8">
+        <f>$Y8-$BN8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -3252,29 +3978,32 @@
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K9" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>100</v>
+      <c r="K9" s="13">
+        <f>$BH9</f>
+        <v/>
+      </c>
+      <c r="L9" s="13">
+        <f>IF($B9="BLOCKED",0,-$BH9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="13">
+        <f>$BI9</f>
+        <v/>
       </c>
       <c r="N9" s="14">
-        <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$G9*$BH9*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O9" s="14">
-        <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$J9*$BH9*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P9" s="15">
-        <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$J9*$BH9*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q9" s="15">
-        <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$AL9*$BH9*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R9" s="15">
@@ -3290,7 +4019,7 @@
         <v/>
       </c>
       <c r="U9" s="12">
-        <f>MAX(0,$M9*Settings!$B$9)</f>
+        <f>MAX(0,$BI9*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V9" s="12">
@@ -3302,11 +4031,11 @@
         <v/>
       </c>
       <c r="X9" s="19">
-        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9-$AS$9,0),IF($S$9&gt;0,$S$9*0.5,0))</f>
+        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9*Settings!$B$6,0),IF($S$9&gt;0,$S$9*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y9" s="19">
-        <f>$Y8+$X9</f>
+        <f>IF(ROW()=2,$X9,$Y8+$X9)</f>
         <v/>
       </c>
       <c r="Z9" s="12">
@@ -3314,7 +4043,7 @@
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
+        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$S9-$AS9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
@@ -3442,6 +4171,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH9">
+        <f>IF($B9="BLOCKED",0,$BH8)</f>
+        <v/>
+      </c>
+      <c r="BI9">
+        <f>IF($B9="BLOCKED",0,$BI8)</f>
+        <v/>
+      </c>
+      <c r="BJ9">
+        <f>IF($B9="BIG_SIDE","BIG_HARVEST",IF($B9="SMALL_SIDE","SMALL_FLIP",IF($B9="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK9">
+        <f>IF($B9="BIG_SIDE",IF(ROW()=2,1,$BK8+1),IF(ROW()=2,0,$BK8))</f>
+        <v/>
+      </c>
+      <c r="BL9">
+        <f>IF($D9&gt;0,IFERROR($V9/$D9,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM9">
+        <f>IF($BN9&lt;=0,FALSE,$Y9&gt;=$BN9)</f>
+        <v/>
+      </c>
+      <c r="BN9">
+        <f>MAX(0,$W9*$BI9*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO9">
+        <f>$Y9-$BN9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -3484,29 +4245,32 @@
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K10" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>100</v>
+      <c r="K10" s="13">
+        <f>$BH10</f>
+        <v/>
+      </c>
+      <c r="L10" s="13">
+        <f>IF($B10="BLOCKED",0,-$BH10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="13">
+        <f>$BI10</f>
+        <v/>
       </c>
       <c r="N10" s="14">
-        <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$G10*$BH10*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O10" s="14">
-        <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$J10*$BH10*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P10" s="15">
-        <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$J10*$BH10*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q10" s="15">
-        <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$AL10*$BH10*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R10" s="15">
@@ -3522,7 +4286,7 @@
         <v/>
       </c>
       <c r="U10" s="12">
-        <f>MAX(0,$M10*Settings!$B$9)</f>
+        <f>MAX(0,$BI10*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V10" s="12">
@@ -3534,11 +4298,11 @@
         <v/>
       </c>
       <c r="X10" s="19">
-        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10-$AS$10,0),IF($S$10&gt;0,$S$10*0.5,0))</f>
+        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10*Settings!$B$6,0),IF($S$10&gt;0,$S$10*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y10" s="19">
-        <f>$Y9+$X10</f>
+        <f>IF(ROW()=2,$X10,$Y9+$X10)</f>
         <v/>
       </c>
       <c r="Z10" s="12">
@@ -3546,7 +4310,7 @@
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
+        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$S10-$AS10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
@@ -3674,6 +4438,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH10">
+        <f>IF($B10="BLOCKED",0,$BH9)</f>
+        <v/>
+      </c>
+      <c r="BI10">
+        <f>IF($B10="BLOCKED",0,$BI9)</f>
+        <v/>
+      </c>
+      <c r="BJ10">
+        <f>IF($B10="BIG_SIDE","BIG_HARVEST",IF($B10="SMALL_SIDE","SMALL_FLIP",IF($B10="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK10">
+        <f>IF($B10="BIG_SIDE",IF(ROW()=2,1,$BK9+1),IF(ROW()=2,0,$BK9))</f>
+        <v/>
+      </c>
+      <c r="BL10">
+        <f>IF($D10&gt;0,IFERROR($V10/$D10,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM10">
+        <f>IF($BN10&lt;=0,FALSE,$Y10&gt;=$BN10)</f>
+        <v/>
+      </c>
+      <c r="BN10">
+        <f>MAX(0,$W10*$BI10*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO10">
+        <f>$Y10-$BN10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3716,29 +4512,32 @@
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K11" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>100</v>
+      <c r="K11" s="13">
+        <f>$BH11</f>
+        <v/>
+      </c>
+      <c r="L11" s="13">
+        <f>IF($B11="BLOCKED",0,-$BH11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="13">
+        <f>$BI11</f>
+        <v/>
       </c>
       <c r="N11" s="14">
-        <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$G11*$BH11*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O11" s="14">
-        <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$J11*$BH11*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P11" s="15">
-        <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$J11*$BH11*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q11" s="15">
-        <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$AL11*$BH11*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R11" s="15">
@@ -3754,7 +4553,7 @@
         <v/>
       </c>
       <c r="U11" s="12">
-        <f>MAX(0,$M11*Settings!$B$9)</f>
+        <f>MAX(0,$BI11*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V11" s="12">
@@ -3766,11 +4565,11 @@
         <v/>
       </c>
       <c r="X11" s="19">
-        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11-$AS$11,0),IF($S$11&gt;0,$S$11*0.5,0))</f>
+        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11*Settings!$B$6,0),IF($S$11&gt;0,$S$11*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y11" s="19">
-        <f>$Y10+$X11</f>
+        <f>IF(ROW()=2,$X11,$Y10+$X11)</f>
         <v/>
       </c>
       <c r="Z11" s="12">
@@ -3778,7 +4577,7 @@
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
+        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$S11-$AS11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
@@ -3906,6 +4705,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH11">
+        <f>IF($B11="BLOCKED",0,$BH10)</f>
+        <v/>
+      </c>
+      <c r="BI11">
+        <f>IF($B11="BLOCKED",0,$BI10)</f>
+        <v/>
+      </c>
+      <c r="BJ11">
+        <f>IF($B11="BIG_SIDE","BIG_HARVEST",IF($B11="SMALL_SIDE","SMALL_FLIP",IF($B11="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK11">
+        <f>IF($B11="BIG_SIDE",IF(ROW()=2,1,$BK10+1),IF(ROW()=2,0,$BK10))</f>
+        <v/>
+      </c>
+      <c r="BL11">
+        <f>IF($D11&gt;0,IFERROR($V11/$D11,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM11">
+        <f>IF($BN11&lt;=0,FALSE,$Y11&gt;=$BN11)</f>
+        <v/>
+      </c>
+      <c r="BN11">
+        <f>MAX(0,$W11*$BI11*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO11">
+        <f>$Y11-$BN11</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3945,7 +4776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG11"/>
+  <dimension ref="A1:BO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4007,6 +4838,14 @@
     <col width="20" customWidth="1" min="57" max="57"/>
     <col width="20" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="15" customWidth="1" min="60" max="60"/>
+    <col width="19" customWidth="1" min="61" max="61"/>
+    <col width="14" customWidth="1" min="62" max="62"/>
+    <col width="14" customWidth="1" min="63" max="63"/>
+    <col width="17" customWidth="1" min="64" max="64"/>
+    <col width="17" customWidth="1" min="65" max="65"/>
+    <col width="15" customWidth="1" min="66" max="66"/>
+    <col width="14" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4305,15 +5144,56 @@
           <t>ManualAllowNewLevel</t>
         </is>
       </c>
+      <c r="BH1" s="38" t="inlineStr">
+        <is>
+          <t>BigMovePoints</t>
+        </is>
+      </c>
+      <c r="BI1" s="38" t="inlineStr">
+        <is>
+          <t>FarDistancePoints</t>
+        </is>
+      </c>
+      <c r="BJ1" s="38" t="inlineStr">
+        <is>
+          <t>HarvestMode</t>
+        </is>
+      </c>
+      <c r="BK1" s="38" t="inlineStr">
+        <is>
+          <t>HarvestCount</t>
+        </is>
+      </c>
+      <c r="BL1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarPercent</t>
+        </is>
+      </c>
+      <c r="BM1" s="38" t="inlineStr">
+        <is>
+          <t>CanFullCloseFar</t>
+        </is>
+      </c>
+      <c r="BN1" s="38" t="inlineStr">
+        <is>
+          <t>FarRemainLoss</t>
+        </is>
+      </c>
+      <c r="BO1" s="38" t="inlineStr">
+        <is>
+          <t>FinalClosePL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="13" t="str">
         <is>
           <t>BIG_SIDE</t>
         </is>
+        <v>BIG_SIDE</v>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
@@ -4322,7 +5202,7 @@
       </c>
       <c r="D2" s="13">
         <f>Settings!$B$2</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E2" s="12">
         <f>IF($B2="BLOCKED","",IF($C2="SELL","BUY","SELL"))</f>
@@ -4330,11 +5210,11 @@
       </c>
       <c r="F2" s="12">
         <f>IF($B2="BLOCKED",0,MAX(0,$D2*Settings!$B$3))</f>
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -4342,35 +5222,38 @@
       </c>
       <c r="I2" s="12">
         <f>IF($B2="BLOCKED",0,MAX(0,$G2*Settings!$B$4))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
-      </c>
-      <c r="K2" s="13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K2" s="13">
+        <f>$BH2</f>
         <v>100</v>
       </c>
-      <c r="L2" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M2" s="13" t="n">
-        <v>100</v>
+      <c r="L2" s="13">
+        <f>IF($B2="BLOCKED",0,-$BH2)</f>
+        <v>-100</v>
+      </c>
+      <c r="M2" s="13">
+        <f>$BI2</f>
+        <v>200</v>
       </c>
       <c r="N2" s="14">
-        <f>IF($B2="BIG_SIDE",$G2*MAX(0,$K2)*Settings!$B$9,0)</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",$G2*$BH2*Settings!$B$9,0)</f>
+        <v>130</v>
       </c>
       <c r="O2" s="14">
-        <f>IF($B2="SMALL_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$J2*$BH2*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P2" s="15">
-        <f>IF($B2="BIG_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",$J2*$BH2*Settings!$B$9,0)</f>
+        <v>47</v>
       </c>
       <c r="Q2" s="15">
-        <f>IF($B2="SMALL_SIDE",$AL2*ABS($K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$AL2*$BH2*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R2" s="15">
@@ -4379,38 +5262,38 @@
       </c>
       <c r="S2" s="14">
         <f>IF($B2="BIG_SIDE",$N2-$P2-$R2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="T2" s="12">
         <f>IF(AND($B2="BIG_SIDE",$AX2&gt;0),$AX2*Settings!$B$5,0)</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="U2" s="12">
-        <f>MAX(0,$M2*Settings!$B$9)</f>
-        <v/>
+        <f>MAX(0,$BI2*Settings!$B$9)</f>
+        <v>200</v>
       </c>
       <c r="V2" s="12">
         <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
-        <v/>
+        <v>0.3735</v>
       </c>
       <c r="W2" s="12">
         <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
-        <v/>
+        <v>0.6265</v>
       </c>
       <c r="X2" s="19">
-        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2-$AS$2,0),IF($S$2&gt;0,$S$2*0.5,0))</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2*Settings!$B$6,0),IF($S$2&gt;0,$S$2*Settings!$B$6,0))</f>
+        <v>8.3</v>
       </c>
       <c r="Y2" s="19">
-        <f>X2</f>
-        <v/>
+        <f>IF(ROW()=2,$X2,$Y1+$X2)</f>
+        <v>8.3</v>
       </c>
       <c r="Z2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
-        <v/>
+        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$S2-$AS2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
+        <v>8.3</v>
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
@@ -4482,7 +5365,7 @@
       </c>
       <c r="AS2" s="20">
         <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="AT2" s="12">
         <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
@@ -4502,7 +5385,7 @@
       </c>
       <c r="AX2" s="12">
         <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,0)</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="AY2" s="12">
         <f>IF($B2="BIG_SIDE",($G2+$J2)*$AU2,0)</f>
@@ -4537,6 +5420,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH2">
+        <f>IF($B2="BLOCKED",0,100)</f>
+        <v>100</v>
+      </c>
+      <c r="BI2">
+        <f>IF($B2="BLOCKED",0,200)</f>
+        <v>200</v>
+      </c>
+      <c r="BJ2" t="str">
+        <f>IF($B2="BIG_SIDE","BIG_HARVEST",IF($B2="SMALL_SIDE","SMALL_FLIP",IF($B2="BLOCKED","BLOCKED","")))</f>
+        <v>BIG_HARVEST</v>
+      </c>
+      <c r="BK2">
+        <f>IF($B2="BIG_SIDE",IF(ROW()=2,1,$BK1+1),IF(ROW()=2,0,$BK1))</f>
+        <v>1</v>
+      </c>
+      <c r="BL2">
+        <f>IF($D2&gt;0,IFERROR($V2/$D2,0),0)</f>
+        <v>0.3735</v>
+      </c>
+      <c r="BM2" t="b">
+        <f>IF($BN2&lt;=0,FALSE,$Y2&gt;=$BN2)</f>
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <f>MAX(0,$W2*$BI2*Settings!$B$9)</f>
+        <v>125.3</v>
+      </c>
+      <c r="BO2">
+        <f>$Y2-$BN2</f>
+        <v>-117</v>
       </c>
     </row>
     <row r="3">
@@ -4579,29 +5494,32 @@
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K3" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L3" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M3" s="13" t="n">
-        <v>100</v>
+      <c r="K3" s="13">
+        <f>$BH3</f>
+        <v/>
+      </c>
+      <c r="L3" s="13">
+        <f>IF($B3="BLOCKED",0,-$BH3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="13">
+        <f>$BI3</f>
+        <v/>
       </c>
       <c r="N3" s="14">
-        <f>IF($B3="BIG_SIDE",$G3*MAX(0,$K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$G3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O3" s="14">
-        <f>IF($B3="SMALL_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$J3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P3" s="15">
-        <f>IF($B3="BIG_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$J3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q3" s="15">
-        <f>IF($B3="SMALL_SIDE",$AL3*ABS($K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$AL3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R3" s="15">
@@ -4617,7 +5535,7 @@
         <v/>
       </c>
       <c r="U3" s="12">
-        <f>MAX(0,$M3*Settings!$B$9)</f>
+        <f>MAX(0,$BI3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V3" s="12">
@@ -4629,11 +5547,11 @@
         <v/>
       </c>
       <c r="X3" s="19">
-        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3-$AS$3,0),IF($S$3&gt;0,$S$3*0.5,0))</f>
+        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3*Settings!$B$6,0),IF($S$3&gt;0,$S$3*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y3" s="19">
-        <f>$Y2+$X3</f>
+        <f>IF(ROW()=2,$X3,$Y2+$X3)</f>
         <v/>
       </c>
       <c r="Z3" s="12">
@@ -4641,7 +5559,7 @@
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
+        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$S3-$AS3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
@@ -4769,6 +5687,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH3">
+        <f>IF($B3="BLOCKED",0,$BH2)</f>
+        <v/>
+      </c>
+      <c r="BI3">
+        <f>IF($B3="BLOCKED",0,$BI2)</f>
+        <v/>
+      </c>
+      <c r="BJ3">
+        <f>IF($B3="BIG_SIDE","BIG_HARVEST",IF($B3="SMALL_SIDE","SMALL_FLIP",IF($B3="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK3">
+        <f>IF($B3="BIG_SIDE",IF(ROW()=2,1,$BK2+1),IF(ROW()=2,0,$BK2))</f>
+        <v/>
+      </c>
+      <c r="BL3">
+        <f>IF($D3&gt;0,IFERROR($V3/$D3,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM3">
+        <f>IF($BN3&lt;=0,FALSE,$Y3&gt;=$BN3)</f>
+        <v/>
+      </c>
+      <c r="BN3">
+        <f>MAX(0,$W3*$BI3*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO3">
+        <f>$Y3-$BN3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -4811,29 +5761,32 @@
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K4" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L4" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M4" s="13" t="n">
-        <v>100</v>
+      <c r="K4" s="13">
+        <f>$BH4</f>
+        <v/>
+      </c>
+      <c r="L4" s="13">
+        <f>IF($B4="BLOCKED",0,-$BH4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="13">
+        <f>$BI4</f>
+        <v/>
       </c>
       <c r="N4" s="14">
-        <f>IF($B4="BIG_SIDE",$G4*MAX(0,$K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$G4*$BH4*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O4" s="14">
-        <f>IF($B4="SMALL_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$J4*$BH4*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P4" s="15">
-        <f>IF($B4="BIG_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$J4*$BH4*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q4" s="15">
-        <f>IF($B4="SMALL_SIDE",$AL4*ABS($K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$AL4*$BH4*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R4" s="15">
@@ -4849,7 +5802,7 @@
         <v/>
       </c>
       <c r="U4" s="12">
-        <f>MAX(0,$M4*Settings!$B$9)</f>
+        <f>MAX(0,$BI4*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V4" s="12">
@@ -4861,11 +5814,11 @@
         <v/>
       </c>
       <c r="X4" s="19">
-        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4-$AS$4,0),IF($S$4&gt;0,$S$4*0.5,0))</f>
+        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4*Settings!$B$6,0),IF($S$4&gt;0,$S$4*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y4" s="19">
-        <f>$Y3+$X4</f>
+        <f>IF(ROW()=2,$X4,$Y3+$X4)</f>
         <v/>
       </c>
       <c r="Z4" s="12">
@@ -4873,7 +5826,7 @@
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
+        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$S4-$AS4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
@@ -5001,6 +5954,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH4">
+        <f>IF($B4="BLOCKED",0,$BH3)</f>
+        <v/>
+      </c>
+      <c r="BI4">
+        <f>IF($B4="BLOCKED",0,$BI3)</f>
+        <v/>
+      </c>
+      <c r="BJ4">
+        <f>IF($B4="BIG_SIDE","BIG_HARVEST",IF($B4="SMALL_SIDE","SMALL_FLIP",IF($B4="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK4">
+        <f>IF($B4="BIG_SIDE",IF(ROW()=2,1,$BK3+1),IF(ROW()=2,0,$BK3))</f>
+        <v/>
+      </c>
+      <c r="BL4">
+        <f>IF($D4&gt;0,IFERROR($V4/$D4,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM4">
+        <f>IF($BN4&lt;=0,FALSE,$Y4&gt;=$BN4)</f>
+        <v/>
+      </c>
+      <c r="BN4">
+        <f>MAX(0,$W4*$BI4*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO4">
+        <f>$Y4-$BN4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -5043,29 +6028,32 @@
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K5" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="M5" s="13" t="n">
-        <v>100</v>
+      <c r="K5" s="13">
+        <f>$BH5</f>
+        <v/>
+      </c>
+      <c r="L5" s="13">
+        <f>IF($B5="BLOCKED",0,-$BH5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="13">
+        <f>$BI5</f>
+        <v/>
       </c>
       <c r="N5" s="14">
-        <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$G5*$BH5*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O5" s="14">
-        <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$J5*$BH5*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P5" s="15">
-        <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$J5*$BH5*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q5" s="15">
-        <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$AL5*$BH5*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R5" s="15">
@@ -5081,7 +6069,7 @@
         <v/>
       </c>
       <c r="U5" s="12">
-        <f>MAX(0,$M5*Settings!$B$9)</f>
+        <f>MAX(0,$BI5*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V5" s="12">
@@ -5093,11 +6081,11 @@
         <v/>
       </c>
       <c r="X5" s="19">
-        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5-$AS$5,0),IF($S$5&gt;0,$S$5*0.5,0))</f>
+        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5*Settings!$B$6,0),IF($S$5&gt;0,$S$5*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y5" s="19">
-        <f>$Y4+$X5</f>
+        <f>IF(ROW()=2,$X5,$Y4+$X5)</f>
         <v/>
       </c>
       <c r="Z5" s="12">
@@ -5105,7 +6093,7 @@
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
+        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$S5-$AS5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
@@ -5234,6 +6222,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH5">
+        <f>IF($B5="BLOCKED",0,$BH4)</f>
+        <v/>
+      </c>
+      <c r="BI5">
+        <f>IF($B5="BLOCKED",0,$BI4)</f>
+        <v/>
+      </c>
+      <c r="BJ5">
+        <f>IF($B5="BIG_SIDE","BIG_HARVEST",IF($B5="SMALL_SIDE","SMALL_FLIP",IF($B5="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK5">
+        <f>IF($B5="BIG_SIDE",IF(ROW()=2,1,$BK4+1),IF(ROW()=2,0,$BK4))</f>
+        <v/>
+      </c>
+      <c r="BL5">
+        <f>IF($D5&gt;0,IFERROR($V5/$D5,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM5">
+        <f>IF($BN5&lt;=0,FALSE,$Y5&gt;=$BN5)</f>
+        <v/>
+      </c>
+      <c r="BN5">
+        <f>MAX(0,$W5*$BI5*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO5">
+        <f>$Y5-$BN5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -5275,29 +6295,32 @@
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M6" s="13" t="n">
-        <v>100</v>
+      <c r="K6" s="13">
+        <f>$BH6</f>
+        <v/>
+      </c>
+      <c r="L6" s="13">
+        <f>IF($B6="BLOCKED",0,-$BH6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="13">
+        <f>$BI6</f>
+        <v/>
       </c>
       <c r="N6" s="14">
-        <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$G6*$BH6*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O6" s="14">
-        <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$J6*$BH6*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P6" s="15">
-        <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$J6*$BH6*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q6" s="15">
-        <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$AL6*$BH6*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R6" s="15">
@@ -5313,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="12">
-        <f>MAX(0,$M6*Settings!$B$9)</f>
+        <f>MAX(0,$BI6*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V6" s="12">
@@ -5325,11 +6348,11 @@
         <v/>
       </c>
       <c r="X6" s="19">
-        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6-$AS$6,0),IF($S$6&gt;0,$S$6*0.5,0))</f>
+        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6*Settings!$B$6,0),IF($S$6&gt;0,$S$6*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y6" s="19">
-        <f>$Y5+$X6</f>
+        <f>IF(ROW()=2,$X6,$Y5+$X6)</f>
         <v/>
       </c>
       <c r="Z6" s="12">
@@ -5337,7 +6360,7 @@
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
+        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$S6-$AS6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
@@ -5466,6 +6489,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH6">
+        <f>IF($B6="BLOCKED",0,$BH5)</f>
+        <v/>
+      </c>
+      <c r="BI6">
+        <f>IF($B6="BLOCKED",0,$BI5)</f>
+        <v/>
+      </c>
+      <c r="BJ6">
+        <f>IF($B6="BIG_SIDE","BIG_HARVEST",IF($B6="SMALL_SIDE","SMALL_FLIP",IF($B6="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK6">
+        <f>IF($B6="BIG_SIDE",IF(ROW()=2,1,$BK5+1),IF(ROW()=2,0,$BK5))</f>
+        <v/>
+      </c>
+      <c r="BL6">
+        <f>IF($D6&gt;0,IFERROR($V6/$D6,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM6" t="b">
+        <f>IF($BN6&lt;=0,FALSE,$Y6&gt;=$BN6)</f>
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <f>MAX(0,$W6*$BI6*Settings!$B$9)</f>
+        <v>197.92</v>
+      </c>
+      <c r="BO6">
+        <f>$Y6-$BN6</f>
+        <v>-197.92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
@@ -5507,29 +6562,32 @@
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>100</v>
+      <c r="K7" s="13">
+        <f>$BH7</f>
+        <v/>
+      </c>
+      <c r="L7" s="13">
+        <f>IF($B7="BLOCKED",0,-$BH7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="13">
+        <f>$BI7</f>
+        <v/>
       </c>
       <c r="N7" s="14">
-        <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$G7*$BH7*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O7" s="14">
-        <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$J7*$BH7*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P7" s="15">
-        <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$J7*$BH7*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="15">
-        <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$AL7*$BH7*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R7" s="15">
@@ -5545,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="U7" s="12">
-        <f>MAX(0,$M7*Settings!$B$9)</f>
+        <f>MAX(0,$BI7*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V7" s="12">
@@ -5557,11 +6615,11 @@
         <v/>
       </c>
       <c r="X7" s="19">
-        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7-$AS$7,0),IF($S$7&gt;0,$S$7*0.5,0))</f>
+        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7*Settings!$B$6,0),IF($S$7&gt;0,$S$7*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y7" s="19">
-        <f>$Y6+$X7</f>
+        <f>IF(ROW()=2,$X7,$Y6+$X7)</f>
         <v/>
       </c>
       <c r="Z7" s="12">
@@ -5569,7 +6627,7 @@
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
+        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$S7-$AS7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
@@ -5698,6 +6756,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH7">
+        <f>IF($B7="BLOCKED",0,$BH6)</f>
+        <v/>
+      </c>
+      <c r="BI7">
+        <f>IF($B7="BLOCKED",0,$BI6)</f>
+        <v/>
+      </c>
+      <c r="BJ7">
+        <f>IF($B7="BIG_SIDE","BIG_HARVEST",IF($B7="SMALL_SIDE","SMALL_FLIP",IF($B7="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK7">
+        <f>IF($B7="BIG_SIDE",IF(ROW()=2,1,$BK6+1),IF(ROW()=2,0,$BK6))</f>
+        <v/>
+      </c>
+      <c r="BL7">
+        <f>IF($D7&gt;0,IFERROR($V7/$D7,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM7" t="b">
+        <f>IF($BN7&lt;=0,FALSE,$Y7&gt;=$BN7)</f>
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <f>MAX(0,$W7*$BI7*Settings!$B$9)</f>
+        <v>197.92</v>
+      </c>
+      <c r="BO7">
+        <f>$Y7-$BN7</f>
+        <v>-197.92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
@@ -5739,29 +6829,32 @@
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>100</v>
+      <c r="K8" s="13">
+        <f>$BH8</f>
+        <v/>
+      </c>
+      <c r="L8" s="13">
+        <f>IF($B8="BLOCKED",0,-$BH8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="13">
+        <f>$BI8</f>
+        <v/>
       </c>
       <c r="N8" s="14">
-        <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$G8*$BH8*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O8" s="14">
-        <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$J8*$BH8*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P8" s="15">
-        <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$J8*$BH8*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="15">
-        <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$AL8*$BH8*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R8" s="15">
@@ -5777,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="U8" s="12">
-        <f>MAX(0,$M8*Settings!$B$9)</f>
+        <f>MAX(0,$BI8*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V8" s="12">
@@ -5789,11 +6882,11 @@
         <v/>
       </c>
       <c r="X8" s="19">
-        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8-$AS$8,0),IF($S$8&gt;0,$S$8*0.5,0))</f>
+        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8*Settings!$B$6,0),IF($S$8&gt;0,$S$8*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y8" s="19">
-        <f>$Y7+$X8</f>
+        <f>IF(ROW()=2,$X8,$Y7+$X8)</f>
         <v/>
       </c>
       <c r="Z8" s="12">
@@ -5801,7 +6894,7 @@
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
+        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$S8-$AS8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
@@ -5930,6 +7023,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH8">
+        <f>IF($B8="BLOCKED",0,$BH7)</f>
+        <v/>
+      </c>
+      <c r="BI8">
+        <f>IF($B8="BLOCKED",0,$BI7)</f>
+        <v/>
+      </c>
+      <c r="BJ8">
+        <f>IF($B8="BIG_SIDE","BIG_HARVEST",IF($B8="SMALL_SIDE","SMALL_FLIP",IF($B8="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK8">
+        <f>IF($B8="BIG_SIDE",IF(ROW()=2,1,$BK7+1),IF(ROW()=2,0,$BK7))</f>
+        <v/>
+      </c>
+      <c r="BL8">
+        <f>IF($D8&gt;0,IFERROR($V8/$D8,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM8" t="b">
+        <f>IF($BN8&lt;=0,FALSE,$Y8&gt;=$BN8)</f>
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <f>MAX(0,$W8*$BI8*Settings!$B$9)</f>
+        <v>197.92</v>
+      </c>
+      <c r="BO8">
+        <f>$Y8-$BN8</f>
+        <v>-197.92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
@@ -5971,29 +7096,32 @@
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>100</v>
+      <c r="K9" s="13">
+        <f>$BH9</f>
+        <v/>
+      </c>
+      <c r="L9" s="13">
+        <f>IF($B9="BLOCKED",0,-$BH9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="13">
+        <f>$BI9</f>
+        <v/>
       </c>
       <c r="N9" s="14">
-        <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$G9*$BH9*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O9" s="14">
-        <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$J9*$BH9*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P9" s="15">
-        <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$J9*$BH9*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q9" s="15">
-        <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$AL9*$BH9*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R9" s="15">
@@ -6009,7 +7137,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="12">
-        <f>MAX(0,$M9*Settings!$B$9)</f>
+        <f>MAX(0,$BI9*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V9" s="12">
@@ -6021,11 +7149,11 @@
         <v/>
       </c>
       <c r="X9" s="19">
-        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9-$AS$9,0),IF($S$9&gt;0,$S$9*0.5,0))</f>
+        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9*Settings!$B$6,0),IF($S$9&gt;0,$S$9*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y9" s="19">
-        <f>$Y8+$X9</f>
+        <f>IF(ROW()=2,$X9,$Y8+$X9)</f>
         <v/>
       </c>
       <c r="Z9" s="12">
@@ -6033,7 +7161,7 @@
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
+        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$S9-$AS9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
@@ -6162,6 +7290,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH9">
+        <f>IF($B9="BLOCKED",0,$BH8)</f>
+        <v/>
+      </c>
+      <c r="BI9">
+        <f>IF($B9="BLOCKED",0,$BI8)</f>
+        <v/>
+      </c>
+      <c r="BJ9">
+        <f>IF($B9="BIG_SIDE","BIG_HARVEST",IF($B9="SMALL_SIDE","SMALL_FLIP",IF($B9="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK9">
+        <f>IF($B9="BIG_SIDE",IF(ROW()=2,1,$BK8+1),IF(ROW()=2,0,$BK8))</f>
+        <v/>
+      </c>
+      <c r="BL9">
+        <f>IF($D9&gt;0,IFERROR($V9/$D9,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM9" t="b">
+        <f>IF($BN9&lt;=0,FALSE,$Y9&gt;=$BN9)</f>
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <f>MAX(0,$W9*$BI9*Settings!$B$9)</f>
+        <v>197.92</v>
+      </c>
+      <c r="BO9">
+        <f>$Y9-$BN9</f>
+        <v>-197.92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
@@ -6203,29 +7363,32 @@
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>100</v>
+      <c r="K10" s="13">
+        <f>$BH10</f>
+        <v/>
+      </c>
+      <c r="L10" s="13">
+        <f>IF($B10="BLOCKED",0,-$BH10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="13">
+        <f>$BI10</f>
+        <v/>
       </c>
       <c r="N10" s="14">
-        <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$G10*$BH10*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O10" s="14">
-        <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$J10*$BH10*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P10" s="15">
-        <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$J10*$BH10*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q10" s="15">
-        <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$AL10*$BH10*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R10" s="15">
@@ -6241,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="U10" s="12">
-        <f>MAX(0,$M10*Settings!$B$9)</f>
+        <f>MAX(0,$BI10*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V10" s="12">
@@ -6253,11 +7416,11 @@
         <v/>
       </c>
       <c r="X10" s="19">
-        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10-$AS$10,0),IF($S$10&gt;0,$S$10*0.5,0))</f>
+        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10*Settings!$B$6,0),IF($S$10&gt;0,$S$10*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y10" s="19">
-        <f>$Y9+$X10</f>
+        <f>IF(ROW()=2,$X10,$Y9+$X10)</f>
         <v/>
       </c>
       <c r="Z10" s="12">
@@ -6265,7 +7428,7 @@
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
+        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$S10-$AS10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
@@ -6394,6 +7557,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH10">
+        <f>IF($B10="BLOCKED",0,$BH9)</f>
+        <v/>
+      </c>
+      <c r="BI10">
+        <f>IF($B10="BLOCKED",0,$BI9)</f>
+        <v/>
+      </c>
+      <c r="BJ10">
+        <f>IF($B10="BIG_SIDE","BIG_HARVEST",IF($B10="SMALL_SIDE","SMALL_FLIP",IF($B10="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK10">
+        <f>IF($B10="BIG_SIDE",IF(ROW()=2,1,$BK9+1),IF(ROW()=2,0,$BK9))</f>
+        <v/>
+      </c>
+      <c r="BL10">
+        <f>IF($D10&gt;0,IFERROR($V10/$D10,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM10" t="b">
+        <f>IF($BN10&lt;=0,FALSE,$Y10&gt;=$BN10)</f>
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <f>MAX(0,$W10*$BI10*Settings!$B$9)</f>
+        <v>197.92</v>
+      </c>
+      <c r="BO10">
+        <f>$Y10-$BN10</f>
+        <v>-197.92</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
@@ -6435,29 +7630,32 @@
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>100</v>
+      <c r="K11" s="13">
+        <f>$BH11</f>
+        <v/>
+      </c>
+      <c r="L11" s="13">
+        <f>IF($B11="BLOCKED",0,-$BH11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="13">
+        <f>$BI11</f>
+        <v/>
       </c>
       <c r="N11" s="14">
-        <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$G11*$BH11*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O11" s="14">
-        <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$J11*$BH11*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P11" s="15">
-        <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$J11*$BH11*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q11" s="15">
-        <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$AL11*$BH11*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R11" s="15">
@@ -6473,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="U11" s="12">
-        <f>MAX(0,$M11*Settings!$B$9)</f>
+        <f>MAX(0,$BI11*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V11" s="12">
@@ -6485,11 +7683,11 @@
         <v/>
       </c>
       <c r="X11" s="19">
-        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11-$AS$11,0),IF($S$11&gt;0,$S$11*0.5,0))</f>
+        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11*Settings!$B$6,0),IF($S$11&gt;0,$S$11*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y11" s="19">
-        <f>$Y10+$X11</f>
+        <f>IF(ROW()=2,$X11,$Y10+$X11)</f>
         <v/>
       </c>
       <c r="Z11" s="12">
@@ -6497,7 +7695,7 @@
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
+        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$S11-$AS11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
@@ -6625,6 +7823,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH11">
+        <f>IF($B11="BLOCKED",0,$BH10)</f>
+        <v/>
+      </c>
+      <c r="BI11">
+        <f>IF($B11="BLOCKED",0,$BI10)</f>
+        <v/>
+      </c>
+      <c r="BJ11">
+        <f>IF($B11="BIG_SIDE","BIG_HARVEST",IF($B11="SMALL_SIDE","SMALL_FLIP",IF($B11="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK11">
+        <f>IF($B11="BIG_SIDE",IF(ROW()=2,1,$BK10+1),IF(ROW()=2,0,$BK10))</f>
+        <v/>
+      </c>
+      <c r="BL11">
+        <f>IF($D11&gt;0,IFERROR($V11/$D11,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM11" t="b">
+        <f>IF($BN11&lt;=0,FALSE,$Y11&gt;=$BN11)</f>
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <f>MAX(0,$W11*$BI11*Settings!$B$9)</f>
+        <v>197.92</v>
+      </c>
+      <c r="BO11">
+        <f>$Y11-$BN11</f>
+        <v>-197.92</v>
       </c>
     </row>
   </sheetData>
@@ -6664,7 +7894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG11"/>
+  <dimension ref="A1:BO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6726,6 +7956,14 @@
     <col width="20" customWidth="1" min="57" max="57"/>
     <col width="20" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="15" customWidth="1" min="60" max="60"/>
+    <col width="19" customWidth="1" min="61" max="61"/>
+    <col width="14" customWidth="1" min="62" max="62"/>
+    <col width="14" customWidth="1" min="63" max="63"/>
+    <col width="17" customWidth="1" min="64" max="64"/>
+    <col width="17" customWidth="1" min="65" max="65"/>
+    <col width="15" customWidth="1" min="66" max="66"/>
+    <col width="14" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7024,15 +8262,56 @@
           <t>ManualAllowNewLevel</t>
         </is>
       </c>
+      <c r="BH1" s="38" t="inlineStr">
+        <is>
+          <t>BigMovePoints</t>
+        </is>
+      </c>
+      <c r="BI1" s="38" t="inlineStr">
+        <is>
+          <t>FarDistancePoints</t>
+        </is>
+      </c>
+      <c r="BJ1" s="38" t="inlineStr">
+        <is>
+          <t>HarvestMode</t>
+        </is>
+      </c>
+      <c r="BK1" s="38" t="inlineStr">
+        <is>
+          <t>HarvestCount</t>
+        </is>
+      </c>
+      <c r="BL1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarPercent</t>
+        </is>
+      </c>
+      <c r="BM1" s="38" t="inlineStr">
+        <is>
+          <t>CanFullCloseFar</t>
+        </is>
+      </c>
+      <c r="BN1" s="38" t="inlineStr">
+        <is>
+          <t>FarRemainLoss</t>
+        </is>
+      </c>
+      <c r="BO1" s="38" t="inlineStr">
+        <is>
+          <t>FinalClosePL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="13" t="str">
         <is>
           <t>BIG_SIDE</t>
         </is>
+        <v>BIG_SIDE</v>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
@@ -7041,7 +8320,7 @@
       </c>
       <c r="D2" s="13">
         <f>Settings!$B$2</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E2" s="12">
         <f>IF($B2="BLOCKED","",IF($C2="SELL","BUY","SELL"))</f>
@@ -7049,11 +8328,11 @@
       </c>
       <c r="F2" s="12">
         <f>IF($B2="BLOCKED",0,MAX(0,$D2*Settings!$B$3))</f>
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="G2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($F2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
+        <v>1.3</v>
       </c>
       <c r="H2" s="12">
         <f>IF($B2="BLOCKED","",$C2)</f>
@@ -7061,35 +8340,38 @@
       </c>
       <c r="I2" s="12">
         <f>IF($B2="BLOCKED",0,MAX(0,$G2*Settings!$B$4))</f>
-        <v/>
+        <v>0.468</v>
       </c>
       <c r="J2" s="12">
         <f>IF($B2="BLOCKED",0,IFERROR(MAX(0,ROUND($I2/Settings!$B$11,0)*Settings!$B$11),0))</f>
-        <v/>
-      </c>
-      <c r="K2" s="13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K2" s="13">
+        <f>$BH2</f>
         <v>100</v>
       </c>
-      <c r="L2" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M2" s="13" t="n">
-        <v>100</v>
+      <c r="L2" s="13">
+        <f>IF($B2="BLOCKED",0,-$BH2)</f>
+        <v>-100</v>
+      </c>
+      <c r="M2" s="13">
+        <f>$BI2</f>
+        <v>200</v>
       </c>
       <c r="N2" s="14">
-        <f>IF($B2="BIG_SIDE",$G2*MAX(0,$K2)*Settings!$B$9,0)</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",$G2*$BH2*Settings!$B$9,0)</f>
+        <v>130</v>
       </c>
       <c r="O2" s="14">
-        <f>IF($B2="SMALL_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$J2*$BH2*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P2" s="15">
-        <f>IF($B2="BIG_SIDE",$J2*ABS($L2)*Settings!$B$9,0)</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",$J2*$BH2*Settings!$B$9,0)</f>
+        <v>47</v>
       </c>
       <c r="Q2" s="15">
-        <f>IF($B2="SMALL_SIDE",$AL2*ABS($K2)*Settings!$B$9,0)</f>
+        <f>IF($B2="SMALL_SIDE",$AL2*$BH2*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R2" s="15">
@@ -7098,38 +8380,38 @@
       </c>
       <c r="S2" s="14">
         <f>IF($B2="BIG_SIDE",$N2-$P2-$R2,IF($B2="SMALL_SIDE",$O2-$Q2-$R2,0))</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="T2" s="12">
         <f>IF(AND($B2="BIG_SIDE",$AX2&gt;0),$AX2*Settings!$B$5,0)</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="U2" s="12">
-        <f>MAX(0,$M2*Settings!$B$9)</f>
-        <v/>
+        <f>MAX(0,$BI2*Settings!$B$9)</f>
+        <v>200</v>
       </c>
       <c r="V2" s="12">
         <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
-        <v/>
+        <v>0.3735</v>
       </c>
       <c r="W2" s="12">
         <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
-        <v/>
+        <v>0.6265</v>
       </c>
       <c r="X2" s="19">
-        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2-$AS$2,0),IF($S$2&gt;0,$S$2*0.5,0))</f>
-        <v/>
+        <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2*Settings!$B$6,0),IF($S$2&gt;0,$S$2*Settings!$B$6,0))</f>
+        <v>8.3</v>
       </c>
       <c r="Y2" s="19">
-        <f>X2</f>
-        <v/>
+        <f>IF(ROW()=2,$X2,$Y1+$X2)</f>
+        <v>8.3</v>
       </c>
       <c r="Z2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AA2" s="12">
-        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$AX2-$AS2-$AZ2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
-        <v/>
+        <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$S2-$AS2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
+        <v>8.3</v>
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
@@ -7201,7 +8483,7 @@
       </c>
       <c r="AS2" s="20">
         <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
-        <v/>
+        <v>74.7</v>
       </c>
       <c r="AT2" s="12">
         <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
@@ -7221,7 +8503,7 @@
       </c>
       <c r="AX2" s="12">
         <f>IF($B2="BIG_SIDE",$N2-$P2-$AY2,0)</f>
-        <v/>
+        <v>83</v>
       </c>
       <c r="AY2" s="12">
         <f>IF($B2="BIG_SIDE",($G2+$J2)*$AU2,0)</f>
@@ -7256,6 +8538,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH2">
+        <f>IF($B2="BLOCKED",0,100)</f>
+        <v>100</v>
+      </c>
+      <c r="BI2">
+        <f>IF($B2="BLOCKED",0,200)</f>
+        <v>200</v>
+      </c>
+      <c r="BJ2" t="str">
+        <f>IF($B2="BIG_SIDE","BIG_HARVEST",IF($B2="SMALL_SIDE","SMALL_FLIP",IF($B2="BLOCKED","BLOCKED","")))</f>
+        <v>BIG_HARVEST</v>
+      </c>
+      <c r="BK2">
+        <f>IF($B2="BIG_SIDE",IF(ROW()=2,1,$BK1+1),IF(ROW()=2,0,$BK1))</f>
+        <v>1</v>
+      </c>
+      <c r="BL2">
+        <f>IF($D2&gt;0,IFERROR($V2/$D2,0),0)</f>
+        <v>0.3735</v>
+      </c>
+      <c r="BM2" t="b">
+        <f>IF($BN2&lt;=0,FALSE,$Y2&gt;=$BN2)</f>
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <f>MAX(0,$W2*$BI2*Settings!$B$9)</f>
+        <v>125.3</v>
+      </c>
+      <c r="BO2">
+        <f>$Y2-$BN2</f>
+        <v>-117</v>
       </c>
     </row>
     <row r="3">
@@ -7298,29 +8612,32 @@
         <f>IF($B3="BLOCKED",0,IFERROR(MAX(0,ROUND($I3/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v/>
       </c>
-      <c r="K3" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="L3" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="M3" s="13" t="n">
-        <v>100</v>
+      <c r="K3" s="13">
+        <f>$BH3</f>
+        <v/>
+      </c>
+      <c r="L3" s="13">
+        <f>IF($B3="BLOCKED",0,-$BH3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="13">
+        <f>$BI3</f>
+        <v/>
       </c>
       <c r="N3" s="14">
-        <f>IF($B3="BIG_SIDE",$G3*MAX(0,$K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$G3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="O3" s="14">
-        <f>IF($B3="SMALL_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$J3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="P3" s="15">
-        <f>IF($B3="BIG_SIDE",$J3*ABS($L3)*Settings!$B$9,0)</f>
+        <f>IF($B3="BIG_SIDE",$J3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="Q3" s="15">
-        <f>IF($B3="SMALL_SIDE",$AL3*ABS($K3)*Settings!$B$9,0)</f>
+        <f>IF($B3="SMALL_SIDE",$AL3*$BH3*Settings!$B$9,0)</f>
         <v/>
       </c>
       <c r="R3" s="15">
@@ -7336,7 +8653,7 @@
         <v/>
       </c>
       <c r="U3" s="12">
-        <f>MAX(0,$M3*Settings!$B$9)</f>
+        <f>MAX(0,$BI3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V3" s="12">
@@ -7348,11 +8665,11 @@
         <v/>
       </c>
       <c r="X3" s="19">
-        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3-$AS$3,0),IF($S$3&gt;0,$S$3*0.5,0))</f>
+        <f>IF($B3="BIG_SIDE",IF($AX$3&gt;0,$AX$3*Settings!$B$6,0),IF($S$3&gt;0,$S$3*Settings!$B$6,0))</f>
         <v/>
       </c>
       <c r="Y3" s="19">
-        <f>$Y2+$X3</f>
+        <f>IF(ROW()=2,$X3,$Y2+$X3)</f>
         <v/>
       </c>
       <c r="Z3" s="12">
@@ -7360,7 +8677,7 @@
         <v/>
       </c>
       <c r="AA3" s="12">
-        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$AX3-$AS3-$AZ3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
+        <f>IF($B3="BLOCKED",$Z3+$BF3,IF($B3="BIG_SIDE",$Z3+$S3-$AS3,IF($B3="SMALL_SIDE",$Z3+$S3+$AI3,$Z3+$S3)))</f>
         <v/>
       </c>
       <c r="AB3" s="12">
@@ -7489,6 +8806,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH3">
+        <f>IF($B3="BLOCKED",0,$BH2)</f>
+        <v/>
+      </c>
+      <c r="BI3">
+        <f>IF($B3="BLOCKED",0,$BI2)</f>
+        <v/>
+      </c>
+      <c r="BJ3">
+        <f>IF($B3="BIG_SIDE","BIG_HARVEST",IF($B3="SMALL_SIDE","SMALL_FLIP",IF($B3="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK3">
+        <f>IF($B3="BIG_SIDE",IF(ROW()=2,1,$BK2+1),IF(ROW()=2,0,$BK2))</f>
+        <v/>
+      </c>
+      <c r="BL3">
+        <f>IF($D3&gt;0,IFERROR($V3/$D3,0),0)</f>
+        <v/>
+      </c>
+      <c r="BM3">
+        <f>IF($BN3&lt;=0,FALSE,$Y3&gt;=$BN3)</f>
+        <v/>
+      </c>
+      <c r="BN3">
+        <f>MAX(0,$W3*$BI3*Settings!$B$9)</f>
+        <v/>
+      </c>
+      <c r="BO3">
+        <f>$Y3-$BN3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="n">
@@ -7530,29 +8879,32 @@
         <f>IF($B4="BLOCKED",0,IFERROR(MAX(0,ROUND($I4/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L4" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M4" s="13" t="n">
-        <v>100</v>
+      <c r="K4" s="13">
+        <f>$BH4</f>
+        <v/>
+      </c>
+      <c r="L4" s="13">
+        <f>IF($B4="BLOCKED",0,-$BH4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="13">
+        <f>$BI4</f>
+        <v/>
       </c>
       <c r="N4" s="14">
-        <f>IF($B4="BIG_SIDE",$G4*MAX(0,$K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$G4*$BH4*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O4" s="14">
-        <f>IF($B4="SMALL_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$J4*$BH4*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P4" s="15">
-        <f>IF($B4="BIG_SIDE",$J4*ABS($L4)*Settings!$B$9,0)</f>
+        <f>IF($B4="BIG_SIDE",$J4*$BH4*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q4" s="15">
-        <f>IF($B4="SMALL_SIDE",$AL4*ABS($K4)*Settings!$B$9,0)</f>
+        <f>IF($B4="SMALL_SIDE",$AL4*$BH4*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R4" s="15">
@@ -7568,7 +8920,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="12">
-        <f>MAX(0,$M4*Settings!$B$9)</f>
+        <f>MAX(0,$BI4*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V4" s="12">
@@ -7580,11 +8932,11 @@
         <v/>
       </c>
       <c r="X4" s="19">
-        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4-$AS$4,0),IF($S$4&gt;0,$S$4*0.5,0))</f>
+        <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4*Settings!$B$6,0),IF($S$4&gt;0,$S$4*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y4" s="19">
-        <f>$Y3+$X4</f>
+        <f>IF(ROW()=2,$X4,$Y3+$X4)</f>
         <v/>
       </c>
       <c r="Z4" s="12">
@@ -7592,7 +8944,7 @@
         <v/>
       </c>
       <c r="AA4" s="12">
-        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$AX4-$AS4-$AZ4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
+        <f>IF($B4="BLOCKED",$Z4+$BF4,IF($B4="BIG_SIDE",$Z4+$S4-$AS4,IF($B4="SMALL_SIDE",$Z4+$S4+$AI4,$Z4+$S4)))</f>
         <v/>
       </c>
       <c r="AB4" s="12">
@@ -7721,6 +9073,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH4">
+        <f>IF($B4="BLOCKED",0,$BH3)</f>
+        <v/>
+      </c>
+      <c r="BI4">
+        <f>IF($B4="BLOCKED",0,$BI3)</f>
+        <v/>
+      </c>
+      <c r="BJ4">
+        <f>IF($B4="BIG_SIDE","BIG_HARVEST",IF($B4="SMALL_SIDE","SMALL_FLIP",IF($B4="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK4">
+        <f>IF($B4="BIG_SIDE",IF(ROW()=2,1,$BK3+1),IF(ROW()=2,0,$BK3))</f>
+        <v/>
+      </c>
+      <c r="BL4">
+        <f>IF($D4&gt;0,IFERROR($V4/$D4,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM4" t="b">
+        <f>IF($BN4&lt;=0,FALSE,$Y4&gt;=$BN4)</f>
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <f>MAX(0,$W4*$BI4*Settings!$B$9)</f>
+        <v>306.12</v>
+      </c>
+      <c r="BO4">
+        <f>$Y4-$BN4</f>
+        <v>-306.12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
@@ -7762,29 +9146,32 @@
         <f>IF($B5="BLOCKED",0,IFERROR(MAX(0,ROUND($I5/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K5" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M5" s="13" t="n">
-        <v>100</v>
+      <c r="K5" s="13">
+        <f>$BH5</f>
+        <v/>
+      </c>
+      <c r="L5" s="13">
+        <f>IF($B5="BLOCKED",0,-$BH5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="13">
+        <f>$BI5</f>
+        <v/>
       </c>
       <c r="N5" s="14">
-        <f>IF($B5="BIG_SIDE",$G5*MAX(0,$K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$G5*$BH5*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O5" s="14">
-        <f>IF($B5="SMALL_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$J5*$BH5*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P5" s="15">
-        <f>IF($B5="BIG_SIDE",$J5*ABS($L5)*Settings!$B$9,0)</f>
+        <f>IF($B5="BIG_SIDE",$J5*$BH5*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q5" s="15">
-        <f>IF($B5="SMALL_SIDE",$AL5*ABS($K5)*Settings!$B$9,0)</f>
+        <f>IF($B5="SMALL_SIDE",$AL5*$BH5*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R5" s="15">
@@ -7800,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="12">
-        <f>MAX(0,$M5*Settings!$B$9)</f>
+        <f>MAX(0,$BI5*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V5" s="12">
@@ -7812,11 +9199,11 @@
         <v/>
       </c>
       <c r="X5" s="19">
-        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5-$AS$5,0),IF($S$5&gt;0,$S$5*0.5,0))</f>
+        <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5*Settings!$B$6,0),IF($S$5&gt;0,$S$5*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y5" s="19">
-        <f>$Y4+$X5</f>
+        <f>IF(ROW()=2,$X5,$Y4+$X5)</f>
         <v/>
       </c>
       <c r="Z5" s="12">
@@ -7824,7 +9211,7 @@
         <v/>
       </c>
       <c r="AA5" s="12">
-        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$AX5-$AS5-$AZ5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
+        <f>IF($B5="BLOCKED",$Z5+$BF5,IF($B5="BIG_SIDE",$Z5+$S5-$AS5,IF($B5="SMALL_SIDE",$Z5+$S5+$AI5,$Z5+$S5)))</f>
         <v/>
       </c>
       <c r="AB5" s="12">
@@ -7953,6 +9340,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH5">
+        <f>IF($B5="BLOCKED",0,$BH4)</f>
+        <v/>
+      </c>
+      <c r="BI5">
+        <f>IF($B5="BLOCKED",0,$BI4)</f>
+        <v/>
+      </c>
+      <c r="BJ5">
+        <f>IF($B5="BIG_SIDE","BIG_HARVEST",IF($B5="SMALL_SIDE","SMALL_FLIP",IF($B5="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK5">
+        <f>IF($B5="BIG_SIDE",IF(ROW()=2,1,$BK4+1),IF(ROW()=2,0,$BK4))</f>
+        <v/>
+      </c>
+      <c r="BL5">
+        <f>IF($D5&gt;0,IFERROR($V5/$D5,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM5" t="b">
+        <f>IF($BN5&lt;=0,FALSE,$Y5&gt;=$BN5)</f>
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <f>MAX(0,$W5*$BI5*Settings!$B$9)</f>
+        <v>306.12</v>
+      </c>
+      <c r="BO5">
+        <f>$Y5-$BN5</f>
+        <v>-306.12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -7994,29 +9413,32 @@
         <f>IF($B6="BLOCKED",0,IFERROR(MAX(0,ROUND($I6/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M6" s="13" t="n">
-        <v>100</v>
+      <c r="K6" s="13">
+        <f>$BH6</f>
+        <v/>
+      </c>
+      <c r="L6" s="13">
+        <f>IF($B6="BLOCKED",0,-$BH6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="13">
+        <f>$BI6</f>
+        <v/>
       </c>
       <c r="N6" s="14">
-        <f>IF($B6="BIG_SIDE",$G6*MAX(0,$K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$G6*$BH6*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O6" s="14">
-        <f>IF($B6="SMALL_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$J6*$BH6*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P6" s="15">
-        <f>IF($B6="BIG_SIDE",$J6*ABS($L6)*Settings!$B$9,0)</f>
+        <f>IF($B6="BIG_SIDE",$J6*$BH6*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q6" s="15">
-        <f>IF($B6="SMALL_SIDE",$AL6*ABS($K6)*Settings!$B$9,0)</f>
+        <f>IF($B6="SMALL_SIDE",$AL6*$BH6*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R6" s="15">
@@ -8032,7 +9454,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="12">
-        <f>MAX(0,$M6*Settings!$B$9)</f>
+        <f>MAX(0,$BI6*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V6" s="12">
@@ -8044,11 +9466,11 @@
         <v/>
       </c>
       <c r="X6" s="19">
-        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6-$AS$6,0),IF($S$6&gt;0,$S$6*0.5,0))</f>
+        <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6*Settings!$B$6,0),IF($S$6&gt;0,$S$6*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y6" s="19">
-        <f>$Y5+$X6</f>
+        <f>IF(ROW()=2,$X6,$Y5+$X6)</f>
         <v/>
       </c>
       <c r="Z6" s="12">
@@ -8056,7 +9478,7 @@
         <v/>
       </c>
       <c r="AA6" s="12">
-        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$AX6-$AS6-$AZ6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
+        <f>IF($B6="BLOCKED",$Z6+$BF6,IF($B6="BIG_SIDE",$Z6+$S6-$AS6,IF($B6="SMALL_SIDE",$Z6+$S6+$AI6,$Z6+$S6)))</f>
         <v/>
       </c>
       <c r="AB6" s="12">
@@ -8185,6 +9607,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH6">
+        <f>IF($B6="BLOCKED",0,$BH5)</f>
+        <v/>
+      </c>
+      <c r="BI6">
+        <f>IF($B6="BLOCKED",0,$BI5)</f>
+        <v/>
+      </c>
+      <c r="BJ6">
+        <f>IF($B6="BIG_SIDE","BIG_HARVEST",IF($B6="SMALL_SIDE","SMALL_FLIP",IF($B6="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK6">
+        <f>IF($B6="BIG_SIDE",IF(ROW()=2,1,$BK5+1),IF(ROW()=2,0,$BK5))</f>
+        <v/>
+      </c>
+      <c r="BL6">
+        <f>IF($D6&gt;0,IFERROR($V6/$D6,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM6" t="b">
+        <f>IF($BN6&lt;=0,FALSE,$Y6&gt;=$BN6)</f>
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <f>MAX(0,$W6*$BI6*Settings!$B$9)</f>
+        <v>306.12</v>
+      </c>
+      <c r="BO6">
+        <f>$Y6-$BN6</f>
+        <v>-306.12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
@@ -8226,29 +9680,32 @@
         <f>IF($B7="BLOCKED",0,IFERROR(MAX(0,ROUND($I7/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>100</v>
+      <c r="K7" s="13">
+        <f>$BH7</f>
+        <v/>
+      </c>
+      <c r="L7" s="13">
+        <f>IF($B7="BLOCKED",0,-$BH7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="13">
+        <f>$BI7</f>
+        <v/>
       </c>
       <c r="N7" s="14">
-        <f>IF($B7="BIG_SIDE",$G7*MAX(0,$K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$G7*$BH7*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O7" s="14">
-        <f>IF($B7="SMALL_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$J7*$BH7*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P7" s="15">
-        <f>IF($B7="BIG_SIDE",$J7*ABS($L7)*Settings!$B$9,0)</f>
+        <f>IF($B7="BIG_SIDE",$J7*$BH7*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="15">
-        <f>IF($B7="SMALL_SIDE",$AL7*ABS($K7)*Settings!$B$9,0)</f>
+        <f>IF($B7="SMALL_SIDE",$AL7*$BH7*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R7" s="15">
@@ -8264,7 +9721,7 @@
         <v>0</v>
       </c>
       <c r="U7" s="12">
-        <f>MAX(0,$M7*Settings!$B$9)</f>
+        <f>MAX(0,$BI7*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V7" s="12">
@@ -8276,11 +9733,11 @@
         <v/>
       </c>
       <c r="X7" s="19">
-        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7-$AS$7,0),IF($S$7&gt;0,$S$7*0.5,0))</f>
+        <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7*Settings!$B$6,0),IF($S$7&gt;0,$S$7*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y7" s="19">
-        <f>$Y6+$X7</f>
+        <f>IF(ROW()=2,$X7,$Y6+$X7)</f>
         <v/>
       </c>
       <c r="Z7" s="12">
@@ -8288,7 +9745,7 @@
         <v/>
       </c>
       <c r="AA7" s="12">
-        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$AX7-$AS7-$AZ7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
+        <f>IF($B7="BLOCKED",$Z7+$BF7,IF($B7="BIG_SIDE",$Z7+$S7-$AS7,IF($B7="SMALL_SIDE",$Z7+$S7+$AI7,$Z7+$S7)))</f>
         <v/>
       </c>
       <c r="AB7" s="12">
@@ -8417,6 +9874,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH7">
+        <f>IF($B7="BLOCKED",0,$BH6)</f>
+        <v/>
+      </c>
+      <c r="BI7">
+        <f>IF($B7="BLOCKED",0,$BI6)</f>
+        <v/>
+      </c>
+      <c r="BJ7">
+        <f>IF($B7="BIG_SIDE","BIG_HARVEST",IF($B7="SMALL_SIDE","SMALL_FLIP",IF($B7="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK7">
+        <f>IF($B7="BIG_SIDE",IF(ROW()=2,1,$BK6+1),IF(ROW()=2,0,$BK6))</f>
+        <v/>
+      </c>
+      <c r="BL7">
+        <f>IF($D7&gt;0,IFERROR($V7/$D7,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM7" t="b">
+        <f>IF($BN7&lt;=0,FALSE,$Y7&gt;=$BN7)</f>
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <f>MAX(0,$W7*$BI7*Settings!$B$9)</f>
+        <v>306.12</v>
+      </c>
+      <c r="BO7">
+        <f>$Y7-$BN7</f>
+        <v>-306.12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
@@ -8458,29 +9947,32 @@
         <f>IF($B8="BLOCKED",0,IFERROR(MAX(0,ROUND($I8/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>100</v>
+      <c r="K8" s="13">
+        <f>$BH8</f>
+        <v/>
+      </c>
+      <c r="L8" s="13">
+        <f>IF($B8="BLOCKED",0,-$BH8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="13">
+        <f>$BI8</f>
+        <v/>
       </c>
       <c r="N8" s="14">
-        <f>IF($B8="BIG_SIDE",$G8*MAX(0,$K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$G8*$BH8*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O8" s="14">
-        <f>IF($B8="SMALL_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$J8*$BH8*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P8" s="15">
-        <f>IF($B8="BIG_SIDE",$J8*ABS($L8)*Settings!$B$9,0)</f>
+        <f>IF($B8="BIG_SIDE",$J8*$BH8*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="15">
-        <f>IF($B8="SMALL_SIDE",$AL8*ABS($K8)*Settings!$B$9,0)</f>
+        <f>IF($B8="SMALL_SIDE",$AL8*$BH8*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R8" s="15">
@@ -8496,7 +9988,7 @@
         <v>0</v>
       </c>
       <c r="U8" s="12">
-        <f>MAX(0,$M8*Settings!$B$9)</f>
+        <f>MAX(0,$BI8*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V8" s="12">
@@ -8508,11 +10000,11 @@
         <v/>
       </c>
       <c r="X8" s="19">
-        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8-$AS$8,0),IF($S$8&gt;0,$S$8*0.5,0))</f>
+        <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8*Settings!$B$6,0),IF($S$8&gt;0,$S$8*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y8" s="19">
-        <f>$Y7+$X8</f>
+        <f>IF(ROW()=2,$X8,$Y7+$X8)</f>
         <v/>
       </c>
       <c r="Z8" s="12">
@@ -8520,7 +10012,7 @@
         <v/>
       </c>
       <c r="AA8" s="12">
-        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$AX8-$AS8-$AZ8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
+        <f>IF($B8="BLOCKED",$Z8+$BF8,IF($B8="BIG_SIDE",$Z8+$S8-$AS8,IF($B8="SMALL_SIDE",$Z8+$S8+$AI8,$Z8+$S8)))</f>
         <v/>
       </c>
       <c r="AB8" s="12">
@@ -8649,6 +10141,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH8">
+        <f>IF($B8="BLOCKED",0,$BH7)</f>
+        <v/>
+      </c>
+      <c r="BI8">
+        <f>IF($B8="BLOCKED",0,$BI7)</f>
+        <v/>
+      </c>
+      <c r="BJ8">
+        <f>IF($B8="BIG_SIDE","BIG_HARVEST",IF($B8="SMALL_SIDE","SMALL_FLIP",IF($B8="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK8">
+        <f>IF($B8="BIG_SIDE",IF(ROW()=2,1,$BK7+1),IF(ROW()=2,0,$BK7))</f>
+        <v/>
+      </c>
+      <c r="BL8">
+        <f>IF($D8&gt;0,IFERROR($V8/$D8,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM8" t="b">
+        <f>IF($BN8&lt;=0,FALSE,$Y8&gt;=$BN8)</f>
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <f>MAX(0,$W8*$BI8*Settings!$B$9)</f>
+        <v>306.12</v>
+      </c>
+      <c r="BO8">
+        <f>$Y8-$BN8</f>
+        <v>-306.12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
@@ -8690,29 +10214,32 @@
         <f>IF($B9="BLOCKED",0,IFERROR(MAX(0,ROUND($I9/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>100</v>
+      <c r="K9" s="13">
+        <f>$BH9</f>
+        <v/>
+      </c>
+      <c r="L9" s="13">
+        <f>IF($B9="BLOCKED",0,-$BH9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="13">
+        <f>$BI9</f>
+        <v/>
       </c>
       <c r="N9" s="14">
-        <f>IF($B9="BIG_SIDE",$G9*MAX(0,$K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$G9*$BH9*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O9" s="14">
-        <f>IF($B9="SMALL_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$J9*$BH9*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P9" s="15">
-        <f>IF($B9="BIG_SIDE",$J9*ABS($L9)*Settings!$B$9,0)</f>
+        <f>IF($B9="BIG_SIDE",$J9*$BH9*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q9" s="15">
-        <f>IF($B9="SMALL_SIDE",$AL9*ABS($K9)*Settings!$B$9,0)</f>
+        <f>IF($B9="SMALL_SIDE",$AL9*$BH9*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R9" s="15">
@@ -8728,7 +10255,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="12">
-        <f>MAX(0,$M9*Settings!$B$9)</f>
+        <f>MAX(0,$BI9*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V9" s="12">
@@ -8740,11 +10267,11 @@
         <v/>
       </c>
       <c r="X9" s="19">
-        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9-$AS$9,0),IF($S$9&gt;0,$S$9*0.5,0))</f>
+        <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9*Settings!$B$6,0),IF($S$9&gt;0,$S$9*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y9" s="19">
-        <f>$Y8+$X9</f>
+        <f>IF(ROW()=2,$X9,$Y8+$X9)</f>
         <v/>
       </c>
       <c r="Z9" s="12">
@@ -8752,7 +10279,7 @@
         <v/>
       </c>
       <c r="AA9" s="12">
-        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$AX9-$AS9-$AZ9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
+        <f>IF($B9="BLOCKED",$Z9+$BF9,IF($B9="BIG_SIDE",$Z9+$S9-$AS9,IF($B9="SMALL_SIDE",$Z9+$S9+$AI9,$Z9+$S9)))</f>
         <v/>
       </c>
       <c r="AB9" s="12">
@@ -8881,6 +10408,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH9">
+        <f>IF($B9="BLOCKED",0,$BH8)</f>
+        <v/>
+      </c>
+      <c r="BI9">
+        <f>IF($B9="BLOCKED",0,$BI8)</f>
+        <v/>
+      </c>
+      <c r="BJ9">
+        <f>IF($B9="BIG_SIDE","BIG_HARVEST",IF($B9="SMALL_SIDE","SMALL_FLIP",IF($B9="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK9">
+        <f>IF($B9="BIG_SIDE",IF(ROW()=2,1,$BK8+1),IF(ROW()=2,0,$BK8))</f>
+        <v/>
+      </c>
+      <c r="BL9">
+        <f>IF($D9&gt;0,IFERROR($V9/$D9,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM9" t="b">
+        <f>IF($BN9&lt;=0,FALSE,$Y9&gt;=$BN9)</f>
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <f>MAX(0,$W9*$BI9*Settings!$B$9)</f>
+        <v>306.12</v>
+      </c>
+      <c r="BO9">
+        <f>$Y9-$BN9</f>
+        <v>-306.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
@@ -8922,29 +10481,32 @@
         <f>IF($B10="BLOCKED",0,IFERROR(MAX(0,ROUND($I10/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>100</v>
+      <c r="K10" s="13">
+        <f>$BH10</f>
+        <v/>
+      </c>
+      <c r="L10" s="13">
+        <f>IF($B10="BLOCKED",0,-$BH10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="13">
+        <f>$BI10</f>
+        <v/>
       </c>
       <c r="N10" s="14">
-        <f>IF($B10="BIG_SIDE",$G10*MAX(0,$K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$G10*$BH10*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O10" s="14">
-        <f>IF($B10="SMALL_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$J10*$BH10*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P10" s="15">
-        <f>IF($B10="BIG_SIDE",$J10*ABS($L10)*Settings!$B$9,0)</f>
+        <f>IF($B10="BIG_SIDE",$J10*$BH10*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q10" s="15">
-        <f>IF($B10="SMALL_SIDE",$AL10*ABS($K10)*Settings!$B$9,0)</f>
+        <f>IF($B10="SMALL_SIDE",$AL10*$BH10*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R10" s="15">
@@ -8960,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="U10" s="12">
-        <f>MAX(0,$M10*Settings!$B$9)</f>
+        <f>MAX(0,$BI10*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V10" s="12">
@@ -8972,11 +10534,11 @@
         <v/>
       </c>
       <c r="X10" s="19">
-        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10-$AS$10,0),IF($S$10&gt;0,$S$10*0.5,0))</f>
+        <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10*Settings!$B$6,0),IF($S$10&gt;0,$S$10*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y10" s="19">
-        <f>$Y9+$X10</f>
+        <f>IF(ROW()=2,$X10,$Y9+$X10)</f>
         <v/>
       </c>
       <c r="Z10" s="12">
@@ -8984,7 +10546,7 @@
         <v/>
       </c>
       <c r="AA10" s="12">
-        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$AX10-$AS10-$AZ10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
+        <f>IF($B10="BLOCKED",$Z10+$BF10,IF($B10="BIG_SIDE",$Z10+$S10-$AS10,IF($B10="SMALL_SIDE",$Z10+$S10+$AI10,$Z10+$S10)))</f>
         <v/>
       </c>
       <c r="AB10" s="12">
@@ -9113,6 +10675,38 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="BH10">
+        <f>IF($B10="BLOCKED",0,$BH9)</f>
+        <v/>
+      </c>
+      <c r="BI10">
+        <f>IF($B10="BLOCKED",0,$BI9)</f>
+        <v/>
+      </c>
+      <c r="BJ10">
+        <f>IF($B10="BIG_SIDE","BIG_HARVEST",IF($B10="SMALL_SIDE","SMALL_FLIP",IF($B10="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK10">
+        <f>IF($B10="BIG_SIDE",IF(ROW()=2,1,$BK9+1),IF(ROW()=2,0,$BK9))</f>
+        <v/>
+      </c>
+      <c r="BL10">
+        <f>IF($D10&gt;0,IFERROR($V10/$D10,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM10" t="b">
+        <f>IF($BN10&lt;=0,FALSE,$Y10&gt;=$BN10)</f>
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <f>MAX(0,$W10*$BI10*Settings!$B$9)</f>
+        <v>306.12</v>
+      </c>
+      <c r="BO10">
+        <f>$Y10-$BN10</f>
+        <v>-306.12</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
@@ -9154,29 +10748,32 @@
         <f>IF($B11="BLOCKED",0,IFERROR(MAX(0,ROUND($I11/Settings!$B$11,0)*Settings!$B$11),0))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>100</v>
+      <c r="K11" s="13">
+        <f>$BH11</f>
+        <v/>
+      </c>
+      <c r="L11" s="13">
+        <f>IF($B11="BLOCKED",0,-$BH11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="13">
+        <f>$BI11</f>
+        <v/>
       </c>
       <c r="N11" s="14">
-        <f>IF($B11="BIG_SIDE",$G11*MAX(0,$K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$G11*$BH11*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="O11" s="14">
-        <f>IF($B11="SMALL_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$J11*$BH11*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="P11" s="15">
-        <f>IF($B11="BIG_SIDE",$J11*ABS($L11)*Settings!$B$9,0)</f>
+        <f>IF($B11="BIG_SIDE",$J11*$BH11*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="Q11" s="15">
-        <f>IF($B11="SMALL_SIDE",$AL11*ABS($K11)*Settings!$B$9,0)</f>
+        <f>IF($B11="SMALL_SIDE",$AL11*$BH11*Settings!$B$9,0)</f>
         <v>0</v>
       </c>
       <c r="R11" s="15">
@@ -9192,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="U11" s="12">
-        <f>MAX(0,$M11*Settings!$B$9)</f>
+        <f>MAX(0,$BI11*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="V11" s="12">
@@ -9204,11 +10801,11 @@
         <v/>
       </c>
       <c r="X11" s="19">
-        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11-$AS$11,0),IF($S$11&gt;0,$S$11*0.5,0))</f>
+        <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11*Settings!$B$6,0),IF($S$11&gt;0,$S$11*Settings!$B$6,0))</f>
         <v>0</v>
       </c>
       <c r="Y11" s="19">
-        <f>$Y10+$X11</f>
+        <f>IF(ROW()=2,$X11,$Y10+$X11)</f>
         <v/>
       </c>
       <c r="Z11" s="12">
@@ -9216,7 +10813,7 @@
         <v/>
       </c>
       <c r="AA11" s="12">
-        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$AX11-$AS11-$AZ11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
+        <f>IF($B11="BLOCKED",$Z11+$BF11,IF($B11="BIG_SIDE",$Z11+$S11-$AS11,IF($B11="SMALL_SIDE",$Z11+$S11+$AI11,$Z11+$S11)))</f>
         <v/>
       </c>
       <c r="AB11" s="12">
@@ -9344,6 +10941,38 @@
         <is>
           <t>NO</t>
         </is>
+      </c>
+      <c r="BH11">
+        <f>IF($B11="BLOCKED",0,$BH10)</f>
+        <v/>
+      </c>
+      <c r="BI11">
+        <f>IF($B11="BLOCKED",0,$BI10)</f>
+        <v/>
+      </c>
+      <c r="BJ11">
+        <f>IF($B11="BIG_SIDE","BIG_HARVEST",IF($B11="SMALL_SIDE","SMALL_FLIP",IF($B11="BLOCKED","BLOCKED","")))</f>
+        <v/>
+      </c>
+      <c r="BK11">
+        <f>IF($B11="BIG_SIDE",IF(ROW()=2,1,$BK10+1),IF(ROW()=2,0,$BK10))</f>
+        <v/>
+      </c>
+      <c r="BL11">
+        <f>IF($D11&gt;0,IFERROR($V11/$D11,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM11" t="b">
+        <f>IF($BN11&lt;=0,FALSE,$Y11&gt;=$BN11)</f>
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <f>MAX(0,$W11*$BI11*Settings!$B$9)</f>
+        <v>306.12</v>
+      </c>
+      <c r="BO11">
+        <f>$Y11-$BN11</f>
+        <v>-306.12</v>
       </c>
     </row>
   </sheetData>
@@ -9383,7 +11012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10064,6 +11693,166 @@
       <c r="D35">
         <f>C35</f>
         <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Max FarDistancePoints</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Big Harvest Risk Checks</t>
+        </is>
+      </c>
+      <c r="C36">
+        <f>MAX(Calculator!BI2:BI11,Trend_UP!BI2:BI11,Trend_DOWN!BI2:BI11)</f>
+        <v>200</v>
+      </c>
+      <c r="D36">
+        <f>C36</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total CloseFarBudget</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Big Harvest Risk Checks</t>
+        </is>
+      </c>
+      <c r="C37">
+        <f>SUM(Calculator!T2:T11,Trend_UP!T2:T11,Trend_DOWN!T2:T11)</f>
+        <v>74.7</v>
+      </c>
+      <c r="D37">
+        <f>C37</f>
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total RealizedFarLoss</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Big Harvest Risk Checks</t>
+        </is>
+      </c>
+      <c r="C38">
+        <f>SUM(Calculator!AS2:AS11,Trend_UP!AS2:AS11,Trend_DOWN!AS2:AS11)</f>
+        <v>74.7</v>
+      </c>
+      <c r="D38">
+        <f>C38</f>
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total ReserveAdd</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Big Harvest Risk Checks</t>
+        </is>
+      </c>
+      <c r="C39">
+        <f>SUM(Calculator!X2:X11,Trend_UP!X2:X11,Trend_DOWN!X2:X11)</f>
+        <v>8.3</v>
+      </c>
+      <c r="D39">
+        <f>C39</f>
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Final FarRemainLot</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Big Harvest Risk Checks</t>
+        </is>
+      </c>
+      <c r="C40">
+        <f>LOOKUP(2,1/(Calculator!W2:W11&lt;&gt;""),Calculator!W2:W11)</f>
+        <v>0.6265</v>
+      </c>
+      <c r="D40">
+        <f>C40</f>
+        <v>0.6265</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Final FarRemainLoss</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Big Harvest Risk Checks</t>
+        </is>
+      </c>
+      <c r="C41">
+        <f>LOOKUP(2,1/(Calculator!BN2:BN11&lt;&gt;""),Calculator!BN2:BN11)</f>
+        <v>125.3</v>
+      </c>
+      <c r="D41">
+        <f>C41</f>
+        <v>125.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CanFullCloseFar Count</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Big Harvest Risk Checks</t>
+        </is>
+      </c>
+      <c r="C42">
+        <f>COUNTIF(Calculator!BM2:BM11,TRUE)+COUNTIF(Trend_UP!BM2:BM11,TRUE)+COUNTIF(Trend_DOWN!BM2:BM11,TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <f>C42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FinalClosePL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Big Harvest Risk Checks</t>
+        </is>
+      </c>
+      <c r="C43">
+        <f>LOOKUP(2,1/(Calculator!BO2:BO11&lt;&gt;""),Calculator!BO2:BO11)</f>
+        <v>-117</v>
+      </c>
+      <c r="D43">
+        <f>C43</f>
+        <v>-117</v>
       </c>
     </row>
   </sheetData>
@@ -10077,7 +11866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14117,6 +15906,258 @@
       <c r="H96" t="inlineStr">
         <is>
           <t>Close-N is not used in Calculator formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BH-01</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CloseFarShare is money budget, not lot percent</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Far=1, BigMove=100, FarDistance=200</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CloseFarLot≈0.3735; FarRemain≈0.6265; not 0.90/0.10</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Calculator data-only row 2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CloseFarLot = CloseFarBudget / LossPerLotToClose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BH-02</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ReserveAdd 10%</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NetProfit≈83</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ReserveAdd = NetProfit × 0.10</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Calculator row 2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Reserve share follows Settings!ReserveShare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>BH-03</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CloseFarBudget 90%</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NetProfit≈83</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CloseFarBudget = NetProfit × 0.90</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Calculator row 2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CloseFarShare is applied to money NetProfit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BH-04</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Small scenario positive</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Big=1.30 Small=0.468 CloseBig=0.39</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetSmall=+7.8; NewFar=0.91</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Numeric model</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Small side remains profitable under new parameters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>BH-05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Realized loss not above budget</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Calculator row 2</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RealizedFarLoss &lt;= CloseFarBudget</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Calculator row 2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Cannot close Far beyond available budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>BH-06</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>No cycles after Big-harvest update</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Workbook formulas</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0 direct self refs and 0 dependency cycles</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>openpyxl graph scan</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Formula graph remains acyclic.</t>
         </is>
       </c>
     </row>

--- a/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
+++ b/work/MinusLock_SelfCompressing_BigSmall_v2/MinusLock_SelfCompressing_BigSmall_v2.xlsx
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -260,6 +260,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -673,9 +676,16 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,7 +998,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Big Harvest Geometry — денежное закрытие Far через CloseFarBudget</t>
+          <t>Big Harvest Geometry — LotStep rounding and final-close validation</t>
         </is>
       </c>
     </row>
@@ -1050,17 +1060,52 @@
       </c>
       <c r="L21" s="31" t="inlineStr">
         <is>
-          <t>CloseFarLot</t>
-        </is>
-      </c>
-      <c r="M21" s="29" t="inlineStr">
-        <is>
-          <t>FarRemain</t>
-        </is>
-      </c>
-      <c r="N21" s="31" t="inlineStr">
+          <t>CloseFarLotRaw</t>
+        </is>
+      </c>
+      <c r="M21" s="31" t="inlineStr">
+        <is>
+          <t>CloseFarLotRounded</t>
+        </is>
+      </c>
+      <c r="N21" s="29" t="inlineStr">
+        <is>
+          <t>FarRemainAfterRounded</t>
+        </is>
+      </c>
+      <c r="O21" s="31" t="inlineStr">
         <is>
           <t>CloseFarPercent</t>
+        </is>
+      </c>
+      <c r="P21" s="36" t="inlineStr">
+        <is>
+          <t>CannotCloseBelowLotStep</t>
+        </is>
+      </c>
+      <c r="Q21" s="36" t="inlineStr">
+        <is>
+          <t>FarRemainLoss</t>
+        </is>
+      </c>
+      <c r="R21" s="37" t="inlineStr">
+        <is>
+          <t>TotalReserve</t>
+        </is>
+      </c>
+      <c r="S21" s="28" t="inlineStr">
+        <is>
+          <t>FinalCloseAllowed</t>
+        </is>
+      </c>
+      <c r="T21" s="36" t="inlineStr">
+        <is>
+          <t>FinalClosePL</t>
+        </is>
+      </c>
+      <c r="U21" s="31" t="inlineStr">
+        <is>
+          <t>LostToRounding</t>
         </is>
       </c>
     </row>
@@ -1110,16 +1155,44 @@
         <v>8.3</v>
       </c>
       <c r="L22" s="33">
-        <f>IF($A22="","",MIN($B22,IFERROR($J22/($D22*Settings!$B$9),0)))</f>
+        <f>IF($A22="","",IFERROR($J22/($D22*Settings!$B$9),0))</f>
         <v>0.3735</v>
       </c>
       <c r="M22" s="33">
-        <f>IF($A22="","",MAX(0,$B22-$L22))</f>
-        <v>0.6265</v>
+        <f>IF($A22="","",MIN($B22,FLOOR(MAX(0,$L22),Settings!$B$11)))</f>
+        <v>0.37</v>
       </c>
       <c r="N22" s="33">
-        <f>IF($A22="","",IFERROR($L22/$B22,0))</f>
-        <v>0.3735</v>
+        <f>IF($A22="","",MAX(0,$B22-$M22))</f>
+        <v>0.63</v>
+      </c>
+      <c r="O22" s="33">
+        <f>IF($A22="","",IFERROR($M22/$B22,0))</f>
+        <v>0.37</v>
+      </c>
+      <c r="P22" s="39" t="str">
+        <f>IF($A22="","",IF(AND($L22&gt;0,$L22&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q22" s="33">
+        <f>IF($A22="","",$N22*$D22*Settings!$B$9)</f>
+        <v>126</v>
+      </c>
+      <c r="R22" s="33">
+        <f>IF($A22="","",SUM($K$22:$K22))</f>
+        <v>8.3</v>
+      </c>
+      <c r="S22" s="39" t="str">
+        <f>IF($A22="","",IF($R22&gt;=$Q22,"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="T22" s="33">
+        <f>IF($A22="","",$R22-$Q22)</f>
+        <v>-117.7</v>
+      </c>
+      <c r="U22" s="33">
+        <f>IF($A22="","",MAX(0,$L22-$M22))</f>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="23">
@@ -1128,8 +1201,8 @@
         <v>2</v>
       </c>
       <c r="B23" s="33">
-        <f>IF($A23="","",$M22)</f>
-        <v>0.6265</v>
+        <f>IF($A23="","",$N22)</f>
+        <v>0.63</v>
       </c>
       <c r="C23" s="32">
         <f>IF($A23="","",100)</f>
@@ -1141,19 +1214,19 @@
       </c>
       <c r="E23" s="33">
         <f>IF($A23="","",ROUND(($B23*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="F23" s="33">
         <f>IF($A23="","",ROUND(($E23*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="G23" s="33">
         <f>IF($A23="","",$E23*$C23*Settings!$B$9)</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" s="33">
         <f>IF($A23="","",$F23*$C23*Settings!$B$9)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I23" s="33">
         <f>IF($A23="","",$G23-$H23)</f>
@@ -1168,16 +1241,44 @@
         <v>5.2</v>
       </c>
       <c r="L23" s="33">
-        <f>IF($A23="","",MIN($B23,IFERROR($J23/($D23*Settings!$B$9),0)))</f>
+        <f>IF($A23="","",IFERROR($J23/($D23*Settings!$B$9),0))</f>
         <v>0.234</v>
       </c>
       <c r="M23" s="33">
-        <f>IF($A23="","",MAX(0,$B23-$L23))</f>
-        <v>0.3925</v>
+        <f>IF($A23="","",MIN($B23,FLOOR(MAX(0,$L23),Settings!$B$11)))</f>
+        <v>0.23</v>
       </c>
       <c r="N23" s="33">
-        <f>IF($A23="","",IFERROR($L23/$B23,0))</f>
-        <v>0.373503591381</v>
+        <f>IF($A23="","",MAX(0,$B23-$M23))</f>
+        <v>0.4</v>
+      </c>
+      <c r="O23" s="33">
+        <f>IF($A23="","",IFERROR($M23/$B23,0))</f>
+        <v>0.365079365079</v>
+      </c>
+      <c r="P23" s="39" t="str">
+        <f>IF($A23="","",IF(AND($L23&gt;0,$L23&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q23" s="33">
+        <f>IF($A23="","",$N23*$D23*Settings!$B$9)</f>
+        <v>80</v>
+      </c>
+      <c r="R23" s="33">
+        <f>IF($A23="","",SUM($K$22:$K23))</f>
+        <v>13.5</v>
+      </c>
+      <c r="S23" s="39" t="str">
+        <f>IF($A23="","",IF($R23&gt;=$Q23,"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="T23" s="33">
+        <f>IF($A23="","",$R23-$Q23)</f>
+        <v>-66.5</v>
+      </c>
+      <c r="U23" s="33">
+        <f>IF($A23="","",MAX(0,$L23-$M23))</f>
+        <v>0.004</v>
       </c>
     </row>
     <row r="24">
@@ -1186,8 +1287,8 @@
         <v>3</v>
       </c>
       <c r="B24" s="33">
-        <f>IF($A24="","",$M23)</f>
-        <v>0.3925</v>
+        <f>IF($A24="","",$N23)</f>
+        <v>0.4</v>
       </c>
       <c r="C24" s="32">
         <f>IF($A24="","",100)</f>
@@ -1199,19 +1300,19 @@
       </c>
       <c r="E24" s="33">
         <f>IF($A24="","",ROUND(($B24*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="F24" s="33">
         <f>IF($A24="","",ROUND(($E24*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G24" s="33">
         <f>IF($A24="","",$E24*$C24*Settings!$B$9)</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H24" s="33">
         <f>IF($A24="","",$F24*$C24*Settings!$B$9)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I24" s="33">
         <f>IF($A24="","",$G24-$H24)</f>
@@ -1226,16 +1327,44 @@
         <v>3.3</v>
       </c>
       <c r="L24" s="33">
-        <f>IF($A24="","",MIN($B24,IFERROR($J24/($D24*Settings!$B$9),0)))</f>
+        <f>IF($A24="","",IFERROR($J24/($D24*Settings!$B$9),0))</f>
         <v>0.1485</v>
       </c>
       <c r="M24" s="33">
-        <f>IF($A24="","",MAX(0,$B24-$L24))</f>
-        <v>0.244</v>
+        <f>IF($A24="","",MIN($B24,FLOOR(MAX(0,$L24),Settings!$B$11)))</f>
+        <v>0.14</v>
       </c>
       <c r="N24" s="33">
-        <f>IF($A24="","",IFERROR($L24/$B24,0))</f>
-        <v>0.378343949045</v>
+        <f>IF($A24="","",MAX(0,$B24-$M24))</f>
+        <v>0.26</v>
+      </c>
+      <c r="O24" s="33">
+        <f>IF($A24="","",IFERROR($M24/$B24,0))</f>
+        <v>0.35</v>
+      </c>
+      <c r="P24" s="39" t="str">
+        <f>IF($A24="","",IF(AND($L24&gt;0,$L24&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q24" s="33">
+        <f>IF($A24="","",$N24*$D24*Settings!$B$9)</f>
+        <v>52</v>
+      </c>
+      <c r="R24" s="33">
+        <f>IF($A24="","",SUM($K$22:$K24))</f>
+        <v>16.8</v>
+      </c>
+      <c r="S24" s="39" t="str">
+        <f>IF($A24="","",IF($R24&gt;=$Q24,"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="T24" s="33">
+        <f>IF($A24="","",$R24-$Q24)</f>
+        <v>-35.2</v>
+      </c>
+      <c r="U24" s="33">
+        <f>IF($A24="","",MAX(0,$L24-$M24))</f>
+        <v>0.0085</v>
       </c>
     </row>
     <row r="25">
@@ -1244,8 +1373,8 @@
         <v>4</v>
       </c>
       <c r="B25" s="33">
-        <f>IF($A25="","",$M24)</f>
-        <v>0.244</v>
+        <f>IF($A25="","",$N24)</f>
+        <v>0.26</v>
       </c>
       <c r="C25" s="32">
         <f>IF($A25="","",100)</f>
@@ -1257,7 +1386,7 @@
       </c>
       <c r="E25" s="33">
         <f>IF($A25="","",ROUND(($B25*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="F25" s="33">
         <f>IF($A25="","",ROUND(($E25*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
@@ -1265,7 +1394,7 @@
       </c>
       <c r="G25" s="33">
         <f>IF($A25="","",$E25*$C25*Settings!$B$9)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H25" s="33">
         <f>IF($A25="","",$F25*$C25*Settings!$B$9)</f>
@@ -1273,27 +1402,55 @@
       </c>
       <c r="I25" s="33">
         <f>IF($A25="","",$G25-$H25)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J25" s="33">
         <f>IF($A25="","",MAX(0,$I25*Settings!$B$5))</f>
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="K25" s="33">
         <f>IF($A25="","",MAX(0,$I25*Settings!$B$6))</f>
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="L25" s="33">
-        <f>IF($A25="","",MIN($B25,IFERROR($J25/($D25*Settings!$B$9),0)))</f>
+        <f>IF($A25="","",IFERROR($J25/($D25*Settings!$B$9),0))</f>
+        <v>0.099</v>
+      </c>
+      <c r="M25" s="33">
+        <f>IF($A25="","",MIN($B25,FLOOR(MAX(0,$L25),Settings!$B$11)))</f>
         <v>0.09</v>
       </c>
-      <c r="M25" s="33">
-        <f>IF($A25="","",MAX(0,$B25-$L25))</f>
-        <v>0.154</v>
-      </c>
       <c r="N25" s="33">
-        <f>IF($A25="","",IFERROR($L25/$B25,0))</f>
-        <v>0.368852459016</v>
+        <f>IF($A25="","",MAX(0,$B25-$M25))</f>
+        <v>0.17</v>
+      </c>
+      <c r="O25" s="33">
+        <f>IF($A25="","",IFERROR($M25/$B25,0))</f>
+        <v>0.346153846154</v>
+      </c>
+      <c r="P25" s="39" t="str">
+        <f>IF($A25="","",IF(AND($L25&gt;0,$L25&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q25" s="33">
+        <f>IF($A25="","",$N25*$D25*Settings!$B$9)</f>
+        <v>34</v>
+      </c>
+      <c r="R25" s="33">
+        <f>IF($A25="","",SUM($K$22:$K25))</f>
+        <v>19</v>
+      </c>
+      <c r="S25" s="39" t="str">
+        <f>IF($A25="","",IF($R25&gt;=$Q25,"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="T25" s="33">
+        <f>IF($A25="","",$R25-$Q25)</f>
+        <v>-15</v>
+      </c>
+      <c r="U25" s="33">
+        <f>IF($A25="","",MAX(0,$L25-$M25))</f>
+        <v>0.009</v>
       </c>
     </row>
     <row r="26">
@@ -1302,8 +1459,8 @@
         <v>5</v>
       </c>
       <c r="B26" s="33">
-        <f>IF($A26="","",$M25)</f>
-        <v>0.154</v>
+        <f>IF($A26="","",$N25)</f>
+        <v>0.17</v>
       </c>
       <c r="C26" s="32">
         <f>IF($A26="","",100)</f>
@@ -1315,43 +1472,71 @@
       </c>
       <c r="E26" s="33">
         <f>IF($A26="","",ROUND(($B26*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="F26" s="33">
         <f>IF($A26="","",ROUND(($E26*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="G26" s="33">
         <f>IF($A26="","",$E26*$C26*Settings!$B$9)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H26" s="33">
         <f>IF($A26="","",$F26*$C26*Settings!$B$9)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="33">
         <f>IF($A26="","",$G26-$H26)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="33">
         <f>IF($A26="","",MAX(0,$I26*Settings!$B$5))</f>
-        <v>11.7</v>
+        <v>12.6</v>
       </c>
       <c r="K26" s="33">
         <f>IF($A26="","",MAX(0,$I26*Settings!$B$6))</f>
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="L26" s="33">
-        <f>IF($A26="","",MIN($B26,IFERROR($J26/($D26*Settings!$B$9),0)))</f>
-        <v>0.0585</v>
+        <f>IF($A26="","",IFERROR($J26/($D26*Settings!$B$9),0))</f>
+        <v>0.063</v>
       </c>
       <c r="M26" s="33">
-        <f>IF($A26="","",MAX(0,$B26-$L26))</f>
-        <v>0.0955</v>
+        <f>IF($A26="","",MIN($B26,FLOOR(MAX(0,$L26),Settings!$B$11)))</f>
+        <v>0.06</v>
       </c>
       <c r="N26" s="33">
-        <f>IF($A26="","",IFERROR($L26/$B26,0))</f>
-        <v>0.37987012987</v>
+        <f>IF($A26="","",MAX(0,$B26-$M26))</f>
+        <v>0.11</v>
+      </c>
+      <c r="O26" s="33">
+        <f>IF($A26="","",IFERROR($M26/$B26,0))</f>
+        <v>0.352941176471</v>
+      </c>
+      <c r="P26" s="39" t="str">
+        <f>IF($A26="","",IF(AND($L26&gt;0,$L26&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q26" s="33">
+        <f>IF($A26="","",$N26*$D26*Settings!$B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="R26" s="33">
+        <f>IF($A26="","",SUM($K$22:$K26))</f>
+        <v>20.4</v>
+      </c>
+      <c r="S26" s="39" t="str">
+        <f>IF($A26="","",IF($R26&gt;=$Q26,"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="T26" s="33">
+        <f>IF($A26="","",$R26-$Q26)</f>
+        <v>-1.6</v>
+      </c>
+      <c r="U26" s="33">
+        <f>IF($A26="","",MAX(0,$L26-$M26))</f>
+        <v>0.003</v>
       </c>
     </row>
     <row r="27">
@@ -1360,8 +1545,8 @@
         <v>6</v>
       </c>
       <c r="B27" s="33">
-        <f>IF($A27="","",$M26)</f>
-        <v>0.0955</v>
+        <f>IF($A27="","",$N26)</f>
+        <v>0.11</v>
       </c>
       <c r="C27" s="32">
         <f>IF($A27="","",100)</f>
@@ -1373,43 +1558,71 @@
       </c>
       <c r="E27" s="33">
         <f>IF($A27="","",ROUND(($B27*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F27" s="33">
         <f>IF($A27="","",ROUND(($E27*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G27" s="33">
         <f>IF($A27="","",$E27*$C27*Settings!$B$9)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H27" s="33">
         <f>IF($A27="","",$F27*$C27*Settings!$B$9)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="33">
         <f>IF($A27="","",$G27-$H27)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="33">
         <f>IF($A27="","",MAX(0,$I27*Settings!$B$5))</f>
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="K27" s="33">
         <f>IF($A27="","",MAX(0,$I27*Settings!$B$6))</f>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L27" s="33">
-        <f>IF($A27="","",MIN($B27,IFERROR($J27/($D27*Settings!$B$9),0)))</f>
-        <v>0.036</v>
+        <f>IF($A27="","",IFERROR($J27/($D27*Settings!$B$9),0))</f>
+        <v>0.0405</v>
       </c>
       <c r="M27" s="33">
-        <f>IF($A27="","",MAX(0,$B27-$L27))</f>
-        <v>0.0595</v>
+        <f>IF($A27="","",MIN($B27,FLOOR(MAX(0,$L27),Settings!$B$11)))</f>
+        <v>0.04</v>
       </c>
       <c r="N27" s="33">
-        <f>IF($A27="","",IFERROR($L27/$B27,0))</f>
-        <v>0.376963350785</v>
+        <f>IF($A27="","",MAX(0,$B27-$M27))</f>
+        <v>0.07</v>
+      </c>
+      <c r="O27" s="33">
+        <f>IF($A27="","",IFERROR($M27/$B27,0))</f>
+        <v>0.363636363636</v>
+      </c>
+      <c r="P27" s="39" t="str">
+        <f>IF($A27="","",IF(AND($L27&gt;0,$L27&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q27" s="33">
+        <f>IF($A27="","",$N27*$D27*Settings!$B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="R27" s="33">
+        <f>IF($A27="","",SUM($K$22:$K27))</f>
+        <v>21.3</v>
+      </c>
+      <c r="S27" s="39" t="str">
+        <f>IF($A27="","",IF($R27&gt;=$Q27,"YES","NO"))</f>
+        <v>YES</v>
+      </c>
+      <c r="T27" s="33">
+        <f>IF($A27="","",$R27-$Q27)</f>
+        <v>7.3</v>
+      </c>
+      <c r="U27" s="33">
+        <f>IF($A27="","",MAX(0,$L27-$M27))</f>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="28">
@@ -1418,8 +1631,8 @@
         <v>7</v>
       </c>
       <c r="B28" s="33">
-        <f>IF($A28="","",$M27)</f>
-        <v>0.0595</v>
+        <f>IF($A28="","",$N27)</f>
+        <v>0.07</v>
       </c>
       <c r="C28" s="32">
         <f>IF($A28="","",100)</f>
@@ -1431,7 +1644,7 @@
       </c>
       <c r="E28" s="33">
         <f>IF($A28="","",ROUND(($B28*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F28" s="33">
         <f>IF($A28="","",ROUND(($E28*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
@@ -1439,7 +1652,7 @@
       </c>
       <c r="G28" s="33">
         <f>IF($A28="","",$E28*$C28*Settings!$B$9)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="33">
         <f>IF($A28="","",$F28*$C28*Settings!$B$9)</f>
@@ -1447,27 +1660,55 @@
       </c>
       <c r="I28" s="33">
         <f>IF($A28="","",$G28-$H28)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="33">
         <f>IF($A28="","",MAX(0,$I28*Settings!$B$5))</f>
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="K28" s="33">
         <f>IF($A28="","",MAX(0,$I28*Settings!$B$6))</f>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L28" s="33">
-        <f>IF($A28="","",MIN($B28,IFERROR($J28/($D28*Settings!$B$9),0)))</f>
-        <v>0.0225</v>
+        <f>IF($A28="","",IFERROR($J28/($D28*Settings!$B$9),0))</f>
+        <v>0.027</v>
       </c>
       <c r="M28" s="33">
-        <f>IF($A28="","",MAX(0,$B28-$L28))</f>
-        <v>0.037</v>
+        <f>IF($A28="","",MIN($B28,FLOOR(MAX(0,$L28),Settings!$B$11)))</f>
+        <v>0.02</v>
       </c>
       <c r="N28" s="33">
-        <f>IF($A28="","",IFERROR($L28/$B28,0))</f>
-        <v>0.378151260504</v>
+        <f>IF($A28="","",MAX(0,$B28-$M28))</f>
+        <v>0.05</v>
+      </c>
+      <c r="O28" s="33">
+        <f>IF($A28="","",IFERROR($M28/$B28,0))</f>
+        <v>0.285714285714</v>
+      </c>
+      <c r="P28" s="39" t="str">
+        <f>IF($A28="","",IF(AND($L28&gt;0,$L28&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q28" s="33">
+        <f>IF($A28="","",$N28*$D28*Settings!$B$9)</f>
+        <v>10</v>
+      </c>
+      <c r="R28" s="33">
+        <f>IF($A28="","",SUM($K$22:$K28))</f>
+        <v>21.9</v>
+      </c>
+      <c r="S28" s="39" t="str">
+        <f>IF($A28="","",IF($R28&gt;=$Q28,"YES","NO"))</f>
+        <v>YES</v>
+      </c>
+      <c r="T28" s="33">
+        <f>IF($A28="","",$R28-$Q28)</f>
+        <v>11.9</v>
+      </c>
+      <c r="U28" s="33">
+        <f>IF($A28="","",MAX(0,$L28-$M28))</f>
+        <v>0.007</v>
       </c>
     </row>
     <row r="29">
@@ -1476,8 +1717,8 @@
         <v>8</v>
       </c>
       <c r="B29" s="33">
-        <f>IF($A29="","",$M28)</f>
-        <v>0.037</v>
+        <f>IF($A29="","",$N28)</f>
+        <v>0.05</v>
       </c>
       <c r="C29" s="32">
         <f>IF($A29="","",100)</f>
@@ -1489,7 +1730,7 @@
       </c>
       <c r="E29" s="33">
         <f>IF($A29="","",ROUND(($B29*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F29" s="33">
         <f>IF($A29="","",ROUND(($E29*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
@@ -1497,7 +1738,7 @@
       </c>
       <c r="G29" s="33">
         <f>IF($A29="","",$E29*$C29*Settings!$B$9)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" s="33">
         <f>IF($A29="","",$F29*$C29*Settings!$B$9)</f>
@@ -1505,27 +1746,55 @@
       </c>
       <c r="I29" s="33">
         <f>IF($A29="","",$G29-$H29)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="33">
         <f>IF($A29="","",MAX(0,$I29*Settings!$B$5))</f>
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="K29" s="33">
         <f>IF($A29="","",MAX(0,$I29*Settings!$B$6))</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L29" s="33">
-        <f>IF($A29="","",MIN($B29,IFERROR($J29/($D29*Settings!$B$9),0)))</f>
-        <v>0.0135</v>
+        <f>IF($A29="","",IFERROR($J29/($D29*Settings!$B$9),0))</f>
+        <v>0.018</v>
       </c>
       <c r="M29" s="33">
-        <f>IF($A29="","",MAX(0,$B29-$L29))</f>
-        <v>0.0235</v>
+        <f>IF($A29="","",MIN($B29,FLOOR(MAX(0,$L29),Settings!$B$11)))</f>
+        <v>0.01</v>
       </c>
       <c r="N29" s="33">
-        <f>IF($A29="","",IFERROR($L29/$B29,0))</f>
-        <v>0.364864864865</v>
+        <f>IF($A29="","",MAX(0,$B29-$M29))</f>
+        <v>0.04</v>
+      </c>
+      <c r="O29" s="33">
+        <f>IF($A29="","",IFERROR($M29/$B29,0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="P29" s="39" t="str">
+        <f>IF($A29="","",IF(AND($L29&gt;0,$L29&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q29" s="33">
+        <f>IF($A29="","",$N29*$D29*Settings!$B$9)</f>
+        <v>8</v>
+      </c>
+      <c r="R29" s="33">
+        <f>IF($A29="","",SUM($K$22:$K29))</f>
+        <v>22.3</v>
+      </c>
+      <c r="S29" s="39" t="str">
+        <f>IF($A29="","",IF($R29&gt;=$Q29,"YES","NO"))</f>
+        <v>YES</v>
+      </c>
+      <c r="T29" s="33">
+        <f>IF($A29="","",$R29-$Q29)</f>
+        <v>14.3</v>
+      </c>
+      <c r="U29" s="33">
+        <f>IF($A29="","",MAX(0,$L29-$M29))</f>
+        <v>0.008</v>
       </c>
     </row>
     <row r="30">
@@ -1534,8 +1803,8 @@
         <v>9</v>
       </c>
       <c r="B30" s="33">
-        <f>IF($A30="","",$M29)</f>
-        <v>0.0235</v>
+        <f>IF($A30="","",$N29)</f>
+        <v>0.04</v>
       </c>
       <c r="C30" s="32">
         <f>IF($A30="","",100)</f>
@@ -1547,43 +1816,71 @@
       </c>
       <c r="E30" s="33">
         <f>IF($A30="","",ROUND(($B30*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F30" s="33">
         <f>IF($A30="","",ROUND(($E30*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G30" s="33">
         <f>IF($A30="","",$E30*$C30*Settings!$B$9)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H30" s="33">
         <f>IF($A30="","",$F30*$C30*Settings!$B$9)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="33">
         <f>IF($A30="","",$G30-$H30)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="33">
         <f>IF($A30="","",MAX(0,$I30*Settings!$B$5))</f>
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="K30" s="33">
         <f>IF($A30="","",MAX(0,$I30*Settings!$B$6))</f>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L30" s="33">
-        <f>IF($A30="","",MIN($B30,IFERROR($J30/($D30*Settings!$B$9),0)))</f>
-        <v>0.009</v>
+        <f>IF($A30="","",IFERROR($J30/($D30*Settings!$B$9),0))</f>
+        <v>0.0135</v>
       </c>
       <c r="M30" s="33">
-        <f>IF($A30="","",MAX(0,$B30-$L30))</f>
-        <v>0.0145</v>
+        <f>IF($A30="","",MIN($B30,FLOOR(MAX(0,$L30),Settings!$B$11)))</f>
+        <v>0.01</v>
       </c>
       <c r="N30" s="33">
-        <f>IF($A30="","",IFERROR($L30/$B30,0))</f>
-        <v>0.382978723404</v>
+        <f>IF($A30="","",MAX(0,$B30-$M30))</f>
+        <v>0.03</v>
+      </c>
+      <c r="O30" s="33">
+        <f>IF($A30="","",IFERROR($M30/$B30,0))</f>
+        <v>0.25</v>
+      </c>
+      <c r="P30" s="39" t="str">
+        <f>IF($A30="","",IF(AND($L30&gt;0,$L30&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q30" s="33">
+        <f>IF($A30="","",$N30*$D30*Settings!$B$9)</f>
+        <v>6</v>
+      </c>
+      <c r="R30" s="33">
+        <f>IF($A30="","",SUM($K$22:$K30))</f>
+        <v>22.6</v>
+      </c>
+      <c r="S30" s="39" t="str">
+        <f>IF($A30="","",IF($R30&gt;=$Q30,"YES","NO"))</f>
+        <v>YES</v>
+      </c>
+      <c r="T30" s="33">
+        <f>IF($A30="","",$R30-$Q30)</f>
+        <v>16.6</v>
+      </c>
+      <c r="U30" s="33">
+        <f>IF($A30="","",MAX(0,$L30-$M30))</f>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="31">
@@ -1592,8 +1889,8 @@
         <v>10</v>
       </c>
       <c r="B31" s="33">
-        <f>IF($A31="","",$M30)</f>
-        <v>0.0145</v>
+        <f>IF($A31="","",$N30)</f>
+        <v>0.03</v>
       </c>
       <c r="C31" s="32">
         <f>IF($A31="","",100)</f>
@@ -1605,7 +1902,7 @@
       </c>
       <c r="E31" s="33">
         <f>IF($A31="","",ROUND(($B31*Settings!$B$3)/Settings!$B$11,0)*Settings!$B$11)</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F31" s="33">
         <f>IF($A31="","",ROUND(($E31*Settings!$B$4)/Settings!$B$11,0)*Settings!$B$11)</f>
@@ -1613,7 +1910,7 @@
       </c>
       <c r="G31" s="33">
         <f>IF($A31="","",$E31*$C31*Settings!$B$9)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" s="33">
         <f>IF($A31="","",$F31*$C31*Settings!$B$9)</f>
@@ -1621,32 +1918,60 @@
       </c>
       <c r="I31" s="33">
         <f>IF($A31="","",$G31-$H31)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" s="33">
         <f>IF($A31="","",MAX(0,$I31*Settings!$B$5))</f>
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="K31" s="33">
         <f>IF($A31="","",MAX(0,$I31*Settings!$B$6))</f>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L31" s="33">
-        <f>IF($A31="","",MIN($B31,IFERROR($J31/($D31*Settings!$B$9),0)))</f>
-        <v>0.0045</v>
+        <f>IF($A31="","",IFERROR($J31/($D31*Settings!$B$9),0))</f>
+        <v>0.0135</v>
       </c>
       <c r="M31" s="33">
-        <f>IF($A31="","",MAX(0,$B31-$L31))</f>
+        <f>IF($A31="","",MIN($B31,FLOOR(MAX(0,$L31),Settings!$B$11)))</f>
         <v>0.01</v>
       </c>
       <c r="N31" s="33">
-        <f>IF($A31="","",IFERROR($L31/$B31,0))</f>
-        <v>0.310344827586</v>
+        <f>IF($A31="","",MAX(0,$B31-$M31))</f>
+        <v>0.02</v>
+      </c>
+      <c r="O31" s="33">
+        <f>IF($A31="","",IFERROR($M31/$B31,0))</f>
+        <v>0.333333333333</v>
+      </c>
+      <c r="P31" s="39" t="str">
+        <f>IF($A31="","",IF(AND($L31&gt;0,$L31&lt;Settings!$B$11),"YES","NO"))</f>
+        <v>NO</v>
+      </c>
+      <c r="Q31" s="33">
+        <f>IF($A31="","",$N31*$D31*Settings!$B$9)</f>
+        <v>4</v>
+      </c>
+      <c r="R31" s="33">
+        <f>IF($A31="","",SUM($K$22:$K31))</f>
+        <v>22.9</v>
+      </c>
+      <c r="S31" s="39" t="str">
+        <f>IF($A31="","",IF($R31&gt;=$Q31,"YES","NO"))</f>
+        <v>YES</v>
+      </c>
+      <c r="T31" s="33">
+        <f>IF($A31="","",$R31-$Q31)</f>
+        <v>18.9</v>
+      </c>
+      <c r="U31" s="33">
+        <f>IF($A31="","",MAX(0,$L31-$M31))</f>
+        <v>0.0035</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A20:U20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1658,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO11"/>
+  <dimension ref="A1:BU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1728,6 +2053,12 @@
     <col width="17" customWidth="1" min="65" max="65"/>
     <col width="15" customWidth="1" min="66" max="66"/>
     <col width="14" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="20" customWidth="1" min="69" max="69"/>
+    <col width="23" customWidth="1" min="70" max="70"/>
+    <col width="25" customWidth="1" min="71" max="71"/>
+    <col width="19" customWidth="1" min="72" max="72"/>
+    <col width="16" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2066,6 +2397,36 @@
           <t>FinalClosePL</t>
         </is>
       </c>
+      <c r="BP1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarLotRaw</t>
+        </is>
+      </c>
+      <c r="BQ1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarLotRounded</t>
+        </is>
+      </c>
+      <c r="BR1" s="38" t="inlineStr">
+        <is>
+          <t>FarRemainAfterRounded</t>
+        </is>
+      </c>
+      <c r="BS1" s="38" t="inlineStr">
+        <is>
+          <t>CannotCloseBelowLotStep</t>
+        </is>
+      </c>
+      <c r="BT1" s="38" t="inlineStr">
+        <is>
+          <t>FinalCloseAllowed</t>
+        </is>
+      </c>
+      <c r="BU1" s="38" t="inlineStr">
+        <is>
+          <t>LostToRounding</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -2155,12 +2516,12 @@
         <v>200</v>
       </c>
       <c r="V2" s="12">
-        <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
-        <v>0.3735</v>
+        <f>$BQ2</f>
+        <v>0.37</v>
       </c>
       <c r="W2" s="12">
-        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
-        <v>0.6265</v>
+        <f>IF($B2="BIG_SIDE",$BR2,$AJ2)</f>
+        <v>0.63</v>
       </c>
       <c r="X2" s="19">
         <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2*Settings!$B$6,0),IF($S$2&gt;0,$S$2*Settings!$B$6,0))</f>
@@ -2175,7 +2536,7 @@
       </c>
       <c r="AA2" s="12">
         <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$S2-$AS2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
-        <v>8.3</v>
+        <v>9</v>
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
@@ -2246,11 +2607,11 @@
         <v/>
       </c>
       <c r="AS2" s="20">
-        <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
-        <v>74.7</v>
+        <f>IF($B2="BIG_SIDE",$BQ2*$U2,0)</f>
+        <v>74</v>
       </c>
       <c r="AT2" s="12">
-        <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
+        <f>IF($B2="BIG_SIDE",$G2+$J2+$BQ2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
         <v/>
       </c>
       <c r="AU2" s="12">
@@ -2320,20 +2681,44 @@
         <v>1</v>
       </c>
       <c r="BL2">
-        <f>IF($D2&gt;0,IFERROR($V2/$D2,0),0)</f>
-        <v>0.3735</v>
+        <f>IF($D2&gt;0,IFERROR($BQ2/$D2,0),0)</f>
+        <v>0.37</v>
       </c>
       <c r="BM2" t="b">
-        <f>IF($BN2&lt;=0,FALSE,$Y2&gt;=$BN2)</f>
+        <f>$BT2</f>
         <v>0</v>
       </c>
       <c r="BN2">
-        <f>MAX(0,$W2*$BI2*Settings!$B$9)</f>
-        <v>125.3</v>
+        <f>MAX(0,$BR2*$BI2*Settings!$B$9)</f>
+        <v>126</v>
       </c>
       <c r="BO2">
         <f>$Y2-$BN2</f>
-        <v>-117</v>
+        <v>-117.7</v>
+      </c>
+      <c r="BP2">
+        <f>IF($B2="BIG_SIDE",IFERROR($T2/$U2,0),0)</f>
+        <v>0.3735</v>
+      </c>
+      <c r="BQ2">
+        <f>IF($B2="BIG_SIDE",MIN($D2,FLOOR(MAX(0,$BP2),Settings!$B$11)),0)</f>
+        <v>0.37</v>
+      </c>
+      <c r="BR2">
+        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$BQ2),$AJ2)</f>
+        <v>0.63</v>
+      </c>
+      <c r="BS2" t="str">
+        <f>IF(AND($BP2&gt;0,$BP2&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT2" t="str">
+        <f>IF($Y2&gt;=$BN2,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU2">
+        <f>MAX(0,$BP2-$BQ2)</f>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="3">
@@ -2421,11 +2806,11 @@
         <v/>
       </c>
       <c r="V3" s="12">
-        <f>IF($B3="BIG_SIDE",IFERROR(MIN($D3,MAX(0,$T3/$U3)),0),0)</f>
+        <f>$BQ3</f>
         <v/>
       </c>
       <c r="W3" s="12">
-        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$V3),$AJ3)</f>
+        <f>IF($B3="BIG_SIDE",$BR3,$AJ3)</f>
         <v/>
       </c>
       <c r="X3" s="19">
@@ -2513,11 +2898,11 @@
         <v/>
       </c>
       <c r="AS3" s="20">
-        <f>IF($B3="BIG_SIDE",$V3*$U3,0)</f>
+        <f>IF($B3="BIG_SIDE",$BQ3*$U3,0)</f>
         <v/>
       </c>
       <c r="AT3" s="12">
-        <f>IF($B3="BIG_SIDE",$G3+$J3+$V3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
+        <f>IF($B3="BIG_SIDE",$G3+$J3+$BQ3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
         <v/>
       </c>
       <c r="AU3" s="12">
@@ -2587,19 +2972,43 @@
         <v/>
       </c>
       <c r="BL3">
-        <f>IF($D3&gt;0,IFERROR($V3/$D3,0),0)</f>
+        <f>IF($D3&gt;0,IFERROR($BQ3/$D3,0),0)</f>
         <v/>
       </c>
       <c r="BM3">
-        <f>IF($BN3&lt;=0,FALSE,$Y3&gt;=$BN3)</f>
+        <f>$BT3</f>
         <v/>
       </c>
       <c r="BN3">
-        <f>MAX(0,$W3*$BI3*Settings!$B$9)</f>
+        <f>MAX(0,$BR3*$BI3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO3">
         <f>$Y3-$BN3</f>
+        <v/>
+      </c>
+      <c r="BP3">
+        <f>IF($B3="BIG_SIDE",IFERROR($T3/$U3,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ3">
+        <f>IF($B3="BIG_SIDE",MIN($D3,FLOOR(MAX(0,$BP3),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR3">
+        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$BQ3),$AJ3)</f>
+        <v/>
+      </c>
+      <c r="BS3">
+        <f>IF(AND($BP3&gt;0,$BP3&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT3">
+        <f>IF($Y3&gt;=$BN3,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU3">
+        <f>MAX(0,$BP3-$BQ3)</f>
         <v/>
       </c>
     </row>
@@ -2688,11 +3097,11 @@
         <v/>
       </c>
       <c r="V4" s="12">
-        <f>IF($B4="BIG_SIDE",IFERROR(MIN($D4,MAX(0,$T4/$U4)),0),0)</f>
+        <f>$BQ4</f>
         <v/>
       </c>
       <c r="W4" s="12">
-        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$V4),$AJ4)</f>
+        <f>IF($B4="BIG_SIDE",$BR4,$AJ4)</f>
         <v/>
       </c>
       <c r="X4" s="19">
@@ -2780,11 +3189,11 @@
         <v/>
       </c>
       <c r="AS4" s="20">
-        <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
+        <f>IF($B4="BIG_SIDE",$BQ4*$U4,0)</f>
         <v/>
       </c>
       <c r="AT4" s="12">
-        <f>IF($B4="BIG_SIDE",$G4+$J4+$V4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
+        <f>IF($B4="BIG_SIDE",$G4+$J4+$BQ4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
         <v/>
       </c>
       <c r="AU4" s="12">
@@ -2854,19 +3263,43 @@
         <v/>
       </c>
       <c r="BL4">
-        <f>IF($D4&gt;0,IFERROR($V4/$D4,0),0)</f>
+        <f>IF($D4&gt;0,IFERROR($BQ4/$D4,0),0)</f>
         <v/>
       </c>
       <c r="BM4">
-        <f>IF($BN4&lt;=0,FALSE,$Y4&gt;=$BN4)</f>
+        <f>$BT4</f>
         <v/>
       </c>
       <c r="BN4">
-        <f>MAX(0,$W4*$BI4*Settings!$B$9)</f>
+        <f>MAX(0,$BR4*$BI4*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO4">
         <f>$Y4-$BN4</f>
+        <v/>
+      </c>
+      <c r="BP4">
+        <f>IF($B4="BIG_SIDE",IFERROR($T4/$U4,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ4">
+        <f>IF($B4="BIG_SIDE",MIN($D4,FLOOR(MAX(0,$BP4),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR4">
+        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$BQ4),$AJ4)</f>
+        <v/>
+      </c>
+      <c r="BS4">
+        <f>IF(AND($BP4&gt;0,$BP4&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT4">
+        <f>IF($Y4&gt;=$BN4,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU4">
+        <f>MAX(0,$BP4-$BQ4)</f>
         <v/>
       </c>
     </row>
@@ -2955,11 +3388,11 @@
         <v/>
       </c>
       <c r="V5" s="12">
-        <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
+        <f>$BQ5</f>
         <v/>
       </c>
       <c r="W5" s="12">
-        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
+        <f>IF($B5="BIG_SIDE",$BR5,$AJ5)</f>
         <v/>
       </c>
       <c r="X5" s="19">
@@ -3047,11 +3480,11 @@
         <v/>
       </c>
       <c r="AS5" s="20">
-        <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
+        <f>IF($B5="BIG_SIDE",$BQ5*$U5,0)</f>
         <v/>
       </c>
       <c r="AT5" s="12">
-        <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
+        <f>IF($B5="BIG_SIDE",$G5+$J5+$BQ5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
         <v/>
       </c>
       <c r="AU5" s="12">
@@ -3121,19 +3554,43 @@
         <v/>
       </c>
       <c r="BL5">
-        <f>IF($D5&gt;0,IFERROR($V5/$D5,0),0)</f>
+        <f>IF($D5&gt;0,IFERROR($BQ5/$D5,0),0)</f>
         <v/>
       </c>
       <c r="BM5">
-        <f>IF($BN5&lt;=0,FALSE,$Y5&gt;=$BN5)</f>
+        <f>$BT5</f>
         <v/>
       </c>
       <c r="BN5">
-        <f>MAX(0,$W5*$BI5*Settings!$B$9)</f>
+        <f>MAX(0,$BR5*$BI5*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO5">
         <f>$Y5-$BN5</f>
+        <v/>
+      </c>
+      <c r="BP5">
+        <f>IF($B5="BIG_SIDE",IFERROR($T5/$U5,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ5">
+        <f>IF($B5="BIG_SIDE",MIN($D5,FLOOR(MAX(0,$BP5),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR5">
+        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$BQ5),$AJ5)</f>
+        <v/>
+      </c>
+      <c r="BS5">
+        <f>IF(AND($BP5&gt;0,$BP5&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT5">
+        <f>IF($Y5&gt;=$BN5,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU5">
+        <f>MAX(0,$BP5-$BQ5)</f>
         <v/>
       </c>
     </row>
@@ -3222,11 +3679,11 @@
         <v/>
       </c>
       <c r="V6" s="12">
-        <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
+        <f>$BQ6</f>
         <v/>
       </c>
       <c r="W6" s="12">
-        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
+        <f>IF($B6="BIG_SIDE",$BR6,$AJ6)</f>
         <v/>
       </c>
       <c r="X6" s="19">
@@ -3314,11 +3771,11 @@
         <v/>
       </c>
       <c r="AS6" s="20">
-        <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
+        <f>IF($B6="BIG_SIDE",$BQ6*$U6,0)</f>
         <v/>
       </c>
       <c r="AT6" s="12">
-        <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
+        <f>IF($B6="BIG_SIDE",$G6+$J6+$BQ6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
         <v/>
       </c>
       <c r="AU6" s="12">
@@ -3388,19 +3845,43 @@
         <v/>
       </c>
       <c r="BL6">
-        <f>IF($D6&gt;0,IFERROR($V6/$D6,0),0)</f>
+        <f>IF($D6&gt;0,IFERROR($BQ6/$D6,0),0)</f>
         <v/>
       </c>
       <c r="BM6">
-        <f>IF($BN6&lt;=0,FALSE,$Y6&gt;=$BN6)</f>
+        <f>$BT6</f>
         <v/>
       </c>
       <c r="BN6">
-        <f>MAX(0,$W6*$BI6*Settings!$B$9)</f>
+        <f>MAX(0,$BR6*$BI6*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO6">
         <f>$Y6-$BN6</f>
+        <v/>
+      </c>
+      <c r="BP6">
+        <f>IF($B6="BIG_SIDE",IFERROR($T6/$U6,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ6">
+        <f>IF($B6="BIG_SIDE",MIN($D6,FLOOR(MAX(0,$BP6),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR6">
+        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$BQ6),$AJ6)</f>
+        <v/>
+      </c>
+      <c r="BS6">
+        <f>IF(AND($BP6&gt;0,$BP6&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT6">
+        <f>IF($Y6&gt;=$BN6,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU6">
+        <f>MAX(0,$BP6-$BQ6)</f>
         <v/>
       </c>
     </row>
@@ -3489,11 +3970,11 @@
         <v/>
       </c>
       <c r="V7" s="12">
-        <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
+        <f>$BQ7</f>
         <v/>
       </c>
       <c r="W7" s="12">
-        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
+        <f>IF($B7="BIG_SIDE",$BR7,$AJ7)</f>
         <v/>
       </c>
       <c r="X7" s="19">
@@ -3581,11 +4062,11 @@
         <v/>
       </c>
       <c r="AS7" s="20">
-        <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
+        <f>IF($B7="BIG_SIDE",$BQ7*$U7,0)</f>
         <v/>
       </c>
       <c r="AT7" s="12">
-        <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
+        <f>IF($B7="BIG_SIDE",$G7+$J7+$BQ7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
         <v/>
       </c>
       <c r="AU7" s="12">
@@ -3655,19 +4136,43 @@
         <v/>
       </c>
       <c r="BL7">
-        <f>IF($D7&gt;0,IFERROR($V7/$D7,0),0)</f>
+        <f>IF($D7&gt;0,IFERROR($BQ7/$D7,0),0)</f>
         <v/>
       </c>
       <c r="BM7">
-        <f>IF($BN7&lt;=0,FALSE,$Y7&gt;=$BN7)</f>
+        <f>$BT7</f>
         <v/>
       </c>
       <c r="BN7">
-        <f>MAX(0,$W7*$BI7*Settings!$B$9)</f>
+        <f>MAX(0,$BR7*$BI7*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO7">
         <f>$Y7-$BN7</f>
+        <v/>
+      </c>
+      <c r="BP7">
+        <f>IF($B7="BIG_SIDE",IFERROR($T7/$U7,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ7">
+        <f>IF($B7="BIG_SIDE",MIN($D7,FLOOR(MAX(0,$BP7),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR7">
+        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$BQ7),$AJ7)</f>
+        <v/>
+      </c>
+      <c r="BS7">
+        <f>IF(AND($BP7&gt;0,$BP7&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT7">
+        <f>IF($Y7&gt;=$BN7,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU7">
+        <f>MAX(0,$BP7-$BQ7)</f>
         <v/>
       </c>
     </row>
@@ -3756,11 +4261,11 @@
         <v/>
       </c>
       <c r="V8" s="12">
-        <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
+        <f>$BQ8</f>
         <v/>
       </c>
       <c r="W8" s="12">
-        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
+        <f>IF($B8="BIG_SIDE",$BR8,$AJ8)</f>
         <v/>
       </c>
       <c r="X8" s="19">
@@ -3848,11 +4353,11 @@
         <v/>
       </c>
       <c r="AS8" s="20">
-        <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
+        <f>IF($B8="BIG_SIDE",$BQ8*$U8,0)</f>
         <v/>
       </c>
       <c r="AT8" s="12">
-        <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
+        <f>IF($B8="BIG_SIDE",$G8+$J8+$BQ8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
         <v/>
       </c>
       <c r="AU8" s="12">
@@ -3922,19 +4427,43 @@
         <v/>
       </c>
       <c r="BL8">
-        <f>IF($D8&gt;0,IFERROR($V8/$D8,0),0)</f>
+        <f>IF($D8&gt;0,IFERROR($BQ8/$D8,0),0)</f>
         <v/>
       </c>
       <c r="BM8">
-        <f>IF($BN8&lt;=0,FALSE,$Y8&gt;=$BN8)</f>
+        <f>$BT8</f>
         <v/>
       </c>
       <c r="BN8">
-        <f>MAX(0,$W8*$BI8*Settings!$B$9)</f>
+        <f>MAX(0,$BR8*$BI8*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO8">
         <f>$Y8-$BN8</f>
+        <v/>
+      </c>
+      <c r="BP8">
+        <f>IF($B8="BIG_SIDE",IFERROR($T8/$U8,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ8">
+        <f>IF($B8="BIG_SIDE",MIN($D8,FLOOR(MAX(0,$BP8),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR8">
+        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$BQ8),$AJ8)</f>
+        <v/>
+      </c>
+      <c r="BS8">
+        <f>IF(AND($BP8&gt;0,$BP8&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT8">
+        <f>IF($Y8&gt;=$BN8,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU8">
+        <f>MAX(0,$BP8-$BQ8)</f>
         <v/>
       </c>
     </row>
@@ -4023,11 +4552,11 @@
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
+        <f>$BQ9</f>
         <v/>
       </c>
       <c r="W9" s="12">
-        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
+        <f>IF($B9="BIG_SIDE",$BR9,$AJ9)</f>
         <v/>
       </c>
       <c r="X9" s="19">
@@ -4115,11 +4644,11 @@
         <v/>
       </c>
       <c r="AS9" s="20">
-        <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
+        <f>IF($B9="BIG_SIDE",$BQ9*$U9,0)</f>
         <v/>
       </c>
       <c r="AT9" s="12">
-        <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
+        <f>IF($B9="BIG_SIDE",$G9+$J9+$BQ9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
         <v/>
       </c>
       <c r="AU9" s="12">
@@ -4189,19 +4718,43 @@
         <v/>
       </c>
       <c r="BL9">
-        <f>IF($D9&gt;0,IFERROR($V9/$D9,0),0)</f>
+        <f>IF($D9&gt;0,IFERROR($BQ9/$D9,0),0)</f>
         <v/>
       </c>
       <c r="BM9">
-        <f>IF($BN9&lt;=0,FALSE,$Y9&gt;=$BN9)</f>
+        <f>$BT9</f>
         <v/>
       </c>
       <c r="BN9">
-        <f>MAX(0,$W9*$BI9*Settings!$B$9)</f>
+        <f>MAX(0,$BR9*$BI9*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO9">
         <f>$Y9-$BN9</f>
+        <v/>
+      </c>
+      <c r="BP9">
+        <f>IF($B9="BIG_SIDE",IFERROR($T9/$U9,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ9">
+        <f>IF($B9="BIG_SIDE",MIN($D9,FLOOR(MAX(0,$BP9),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR9">
+        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$BQ9),$AJ9)</f>
+        <v/>
+      </c>
+      <c r="BS9">
+        <f>IF(AND($BP9&gt;0,$BP9&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT9">
+        <f>IF($Y9&gt;=$BN9,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU9">
+        <f>MAX(0,$BP9-$BQ9)</f>
         <v/>
       </c>
     </row>
@@ -4209,9 +4762,9 @@
       <c r="A10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="13" t="str">
         <f>IF(AND($AQ9="MANUAL_READY",$BG9="YES"),"BIG_SIDE",IF(OR($AP9="NO",$AQ9="DUAL_TAIL",$AQ9="DANGER",$AQ9="STOP",$AQ9="MANUAL_READY",$AQ9="STOP_CLEARED"),"BLOCKED","BIG_SIDE"))</f>
-        <v/>
+        <v>BIG_SIDE</v>
       </c>
       <c r="C10" s="13">
         <f>IF($B10="BLOCKED",$AF9,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),$AF9,IF($AP9="YES",$AF9,$C9)))</f>
@@ -4219,7 +4772,7 @@
       </c>
       <c r="D10" s="13">
         <f>IF($B10="BLOCKED",0,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),MAX($BA9,$BB9),IF($AP9="YES",MAX(0,$AG9),$D9)))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="E10" s="12">
         <f>IF($B10="BLOCKED","",IF($C10="SELL","BUY","SELL"))</f>
@@ -4290,11 +4843,11 @@
         <v/>
       </c>
       <c r="V10" s="12">
-        <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
-        <v/>
+        <f>$BQ10</f>
+        <v>0</v>
       </c>
       <c r="W10" s="12">
-        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
+        <f>IF($B10="BIG_SIDE",$BR10,$AJ10)</f>
         <v/>
       </c>
       <c r="X10" s="19">
@@ -4382,11 +4935,11 @@
         <v/>
       </c>
       <c r="AS10" s="20">
-        <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
+        <f>IF($B10="BIG_SIDE",$BQ10*$U10,0)</f>
         <v/>
       </c>
       <c r="AT10" s="12">
-        <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
+        <f>IF($B10="BIG_SIDE",$G10+$J10+$BQ10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
         <v/>
       </c>
       <c r="AU10" s="12">
@@ -4456,20 +5009,44 @@
         <v/>
       </c>
       <c r="BL10">
-        <f>IF($D10&gt;0,IFERROR($V10/$D10,0),0)</f>
+        <f>IF($D10&gt;0,IFERROR($BQ10/$D10,0),0)</f>
         <v/>
       </c>
       <c r="BM10">
-        <f>IF($BN10&lt;=0,FALSE,$Y10&gt;=$BN10)</f>
+        <f>$BT10</f>
         <v/>
       </c>
       <c r="BN10">
-        <f>MAX(0,$W10*$BI10*Settings!$B$9)</f>
-        <v/>
+        <f>MAX(0,$BR10*$BI10*Settings!$B$9)</f>
+        <v>20</v>
       </c>
       <c r="BO10">
         <f>$Y10-$BN10</f>
-        <v/>
+        <v>-20</v>
+      </c>
+      <c r="BP10">
+        <f>IF($B10="BIG_SIDE",IFERROR($T10/$U10,0),0)</f>
+        <v>0.009</v>
+      </c>
+      <c r="BQ10">
+        <f>IF($B10="BIG_SIDE",MIN($D10,FLOOR(MAX(0,$BP10),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$BQ10),$AJ10)</f>
+        <v>0.1</v>
+      </c>
+      <c r="BS10" t="str">
+        <f>IF(AND($BP10&gt;0,$BP10&lt;Settings!$B$11),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="BT10" t="str">
+        <f>IF($Y10&gt;=$BN10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU10">
+        <f>MAX(0,$BP10-$BQ10)</f>
+        <v>0.009</v>
       </c>
     </row>
     <row r="11">
@@ -4557,11 +5134,11 @@
         <v/>
       </c>
       <c r="V11" s="12">
-        <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
+        <f>$BQ11</f>
         <v/>
       </c>
       <c r="W11" s="12">
-        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
+        <f>IF($B11="BIG_SIDE",$BR11,$AJ11)</f>
         <v/>
       </c>
       <c r="X11" s="19">
@@ -4649,11 +5226,11 @@
         <v/>
       </c>
       <c r="AS11" s="20">
-        <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
+        <f>IF($B11="BIG_SIDE",$BQ11*$U11,0)</f>
         <v/>
       </c>
       <c r="AT11" s="12">
-        <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
+        <f>IF($B11="BIG_SIDE",$G11+$J11+$BQ11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
         <v/>
       </c>
       <c r="AU11" s="12">
@@ -4723,19 +5300,43 @@
         <v/>
       </c>
       <c r="BL11">
-        <f>IF($D11&gt;0,IFERROR($V11/$D11,0),0)</f>
+        <f>IF($D11&gt;0,IFERROR($BQ11/$D11,0),0)</f>
         <v/>
       </c>
       <c r="BM11">
-        <f>IF($BN11&lt;=0,FALSE,$Y11&gt;=$BN11)</f>
+        <f>$BT11</f>
         <v/>
       </c>
       <c r="BN11">
-        <f>MAX(0,$W11*$BI11*Settings!$B$9)</f>
+        <f>MAX(0,$BR11*$BI11*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO11">
         <f>$Y11-$BN11</f>
+        <v/>
+      </c>
+      <c r="BP11">
+        <f>IF($B11="BIG_SIDE",IFERROR($T11/$U11,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ11">
+        <f>IF($B11="BIG_SIDE",MIN($D11,FLOOR(MAX(0,$BP11),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR11">
+        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$BQ11),$AJ11)</f>
+        <v/>
+      </c>
+      <c r="BS11">
+        <f>IF(AND($BP11&gt;0,$BP11&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT11">
+        <f>IF($Y11&gt;=$BN11,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU11">
+        <f>MAX(0,$BP11-$BQ11)</f>
         <v/>
       </c>
     </row>
@@ -4776,7 +5377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO11"/>
+  <dimension ref="A1:BU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4846,6 +5447,12 @@
     <col width="17" customWidth="1" min="65" max="65"/>
     <col width="15" customWidth="1" min="66" max="66"/>
     <col width="14" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="20" customWidth="1" min="69" max="69"/>
+    <col width="23" customWidth="1" min="70" max="70"/>
+    <col width="25" customWidth="1" min="71" max="71"/>
+    <col width="19" customWidth="1" min="72" max="72"/>
+    <col width="16" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5184,6 +5791,36 @@
           <t>FinalClosePL</t>
         </is>
       </c>
+      <c r="BP1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarLotRaw</t>
+        </is>
+      </c>
+      <c r="BQ1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarLotRounded</t>
+        </is>
+      </c>
+      <c r="BR1" s="38" t="inlineStr">
+        <is>
+          <t>FarRemainAfterRounded</t>
+        </is>
+      </c>
+      <c r="BS1" s="38" t="inlineStr">
+        <is>
+          <t>CannotCloseBelowLotStep</t>
+        </is>
+      </c>
+      <c r="BT1" s="38" t="inlineStr">
+        <is>
+          <t>FinalCloseAllowed</t>
+        </is>
+      </c>
+      <c r="BU1" s="38" t="inlineStr">
+        <is>
+          <t>LostToRounding</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -5273,12 +5910,12 @@
         <v>200</v>
       </c>
       <c r="V2" s="12">
-        <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
-        <v>0.3735</v>
+        <f>$BQ2</f>
+        <v>0.37</v>
       </c>
       <c r="W2" s="12">
-        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
-        <v>0.6265</v>
+        <f>IF($B2="BIG_SIDE",$BR2,$AJ2)</f>
+        <v>0.63</v>
       </c>
       <c r="X2" s="19">
         <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2*Settings!$B$6,0),IF($S$2&gt;0,$S$2*Settings!$B$6,0))</f>
@@ -5293,7 +5930,7 @@
       </c>
       <c r="AA2" s="12">
         <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$S2-$AS2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
-        <v>8.3</v>
+        <v>9</v>
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
@@ -5364,11 +6001,11 @@
         <v/>
       </c>
       <c r="AS2" s="20">
-        <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
-        <v>74.7</v>
+        <f>IF($B2="BIG_SIDE",$BQ2*$U2,0)</f>
+        <v>74</v>
       </c>
       <c r="AT2" s="12">
-        <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
+        <f>IF($B2="BIG_SIDE",$G2+$J2+$BQ2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
         <v/>
       </c>
       <c r="AU2" s="12">
@@ -5438,20 +6075,44 @@
         <v>1</v>
       </c>
       <c r="BL2">
-        <f>IF($D2&gt;0,IFERROR($V2/$D2,0),0)</f>
-        <v>0.3735</v>
+        <f>IF($D2&gt;0,IFERROR($BQ2/$D2,0),0)</f>
+        <v>0.37</v>
       </c>
       <c r="BM2" t="b">
-        <f>IF($BN2&lt;=0,FALSE,$Y2&gt;=$BN2)</f>
+        <f>$BT2</f>
         <v>0</v>
       </c>
       <c r="BN2">
-        <f>MAX(0,$W2*$BI2*Settings!$B$9)</f>
-        <v>125.3</v>
+        <f>MAX(0,$BR2*$BI2*Settings!$B$9)</f>
+        <v>126</v>
       </c>
       <c r="BO2">
         <f>$Y2-$BN2</f>
-        <v>-117</v>
+        <v>-117.7</v>
+      </c>
+      <c r="BP2">
+        <f>IF($B2="BIG_SIDE",IFERROR($T2/$U2,0),0)</f>
+        <v>0.3735</v>
+      </c>
+      <c r="BQ2">
+        <f>IF($B2="BIG_SIDE",MIN($D2,FLOOR(MAX(0,$BP2),Settings!$B$11)),0)</f>
+        <v>0.37</v>
+      </c>
+      <c r="BR2">
+        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$BQ2),$AJ2)</f>
+        <v>0.63</v>
+      </c>
+      <c r="BS2" t="str">
+        <f>IF(AND($BP2&gt;0,$BP2&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT2" t="str">
+        <f>IF($Y2&gt;=$BN2,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU2">
+        <f>MAX(0,$BP2-$BQ2)</f>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="3">
@@ -5539,11 +6200,11 @@
         <v/>
       </c>
       <c r="V3" s="12">
-        <f>IF($B3="BIG_SIDE",IFERROR(MIN($D3,MAX(0,$T3/$U3)),0),0)</f>
+        <f>$BQ3</f>
         <v/>
       </c>
       <c r="W3" s="12">
-        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$V3),$AJ3)</f>
+        <f>IF($B3="BIG_SIDE",$BR3,$AJ3)</f>
         <v/>
       </c>
       <c r="X3" s="19">
@@ -5631,11 +6292,11 @@
         <v/>
       </c>
       <c r="AS3" s="20">
-        <f>IF($B3="BIG_SIDE",$V3*$U3,0)</f>
+        <f>IF($B3="BIG_SIDE",$BQ3*$U3,0)</f>
         <v/>
       </c>
       <c r="AT3" s="12">
-        <f>IF($B3="BIG_SIDE",$G3+$J3+$V3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
+        <f>IF($B3="BIG_SIDE",$G3+$J3+$BQ3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
         <v/>
       </c>
       <c r="AU3" s="12">
@@ -5705,19 +6366,43 @@
         <v/>
       </c>
       <c r="BL3">
-        <f>IF($D3&gt;0,IFERROR($V3/$D3,0),0)</f>
+        <f>IF($D3&gt;0,IFERROR($BQ3/$D3,0),0)</f>
         <v/>
       </c>
       <c r="BM3">
-        <f>IF($BN3&lt;=0,FALSE,$Y3&gt;=$BN3)</f>
+        <f>$BT3</f>
         <v/>
       </c>
       <c r="BN3">
-        <f>MAX(0,$W3*$BI3*Settings!$B$9)</f>
+        <f>MAX(0,$BR3*$BI3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO3">
         <f>$Y3-$BN3</f>
+        <v/>
+      </c>
+      <c r="BP3">
+        <f>IF($B3="BIG_SIDE",IFERROR($T3/$U3,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ3">
+        <f>IF($B3="BIG_SIDE",MIN($D3,FLOOR(MAX(0,$BP3),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR3">
+        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$BQ3),$AJ3)</f>
+        <v/>
+      </c>
+      <c r="BS3">
+        <f>IF(AND($BP3&gt;0,$BP3&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT3">
+        <f>IF($Y3&gt;=$BN3,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU3">
+        <f>MAX(0,$BP3-$BQ3)</f>
         <v/>
       </c>
     </row>
@@ -5806,11 +6491,11 @@
         <v/>
       </c>
       <c r="V4" s="12">
-        <f>IF($B4="BIG_SIDE",IFERROR(MIN($D4,MAX(0,$T4/$U4)),0),0)</f>
+        <f>$BQ4</f>
         <v/>
       </c>
       <c r="W4" s="12">
-        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$V4),$AJ4)</f>
+        <f>IF($B4="BIG_SIDE",$BR4,$AJ4)</f>
         <v/>
       </c>
       <c r="X4" s="19">
@@ -5898,11 +6583,11 @@
         <v/>
       </c>
       <c r="AS4" s="20">
-        <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
+        <f>IF($B4="BIG_SIDE",$BQ4*$U4,0)</f>
         <v/>
       </c>
       <c r="AT4" s="12">
-        <f>IF($B4="BIG_SIDE",$G4+$J4+$V4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
+        <f>IF($B4="BIG_SIDE",$G4+$J4+$BQ4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
         <v/>
       </c>
       <c r="AU4" s="12">
@@ -5972,19 +6657,43 @@
         <v/>
       </c>
       <c r="BL4">
-        <f>IF($D4&gt;0,IFERROR($V4/$D4,0),0)</f>
+        <f>IF($D4&gt;0,IFERROR($BQ4/$D4,0),0)</f>
         <v/>
       </c>
       <c r="BM4">
-        <f>IF($BN4&lt;=0,FALSE,$Y4&gt;=$BN4)</f>
+        <f>$BT4</f>
         <v/>
       </c>
       <c r="BN4">
-        <f>MAX(0,$W4*$BI4*Settings!$B$9)</f>
+        <f>MAX(0,$BR4*$BI4*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO4">
         <f>$Y4-$BN4</f>
+        <v/>
+      </c>
+      <c r="BP4">
+        <f>IF($B4="BIG_SIDE",IFERROR($T4/$U4,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ4">
+        <f>IF($B4="BIG_SIDE",MIN($D4,FLOOR(MAX(0,$BP4),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR4">
+        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$BQ4),$AJ4)</f>
+        <v/>
+      </c>
+      <c r="BS4">
+        <f>IF(AND($BP4&gt;0,$BP4&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT4">
+        <f>IF($Y4&gt;=$BN4,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU4">
+        <f>MAX(0,$BP4-$BQ4)</f>
         <v/>
       </c>
     </row>
@@ -6073,11 +6782,11 @@
         <v/>
       </c>
       <c r="V5" s="12">
-        <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
+        <f>$BQ5</f>
         <v/>
       </c>
       <c r="W5" s="12">
-        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
+        <f>IF($B5="BIG_SIDE",$BR5,$AJ5)</f>
         <v/>
       </c>
       <c r="X5" s="19">
@@ -6165,11 +6874,11 @@
         <v>DUAL_TAIL: старый и новый хвост сохранены</v>
       </c>
       <c r="AS5" s="20">
-        <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
+        <f>IF($B5="BIG_SIDE",$BQ5*$U5,0)</f>
         <v/>
       </c>
       <c r="AT5" s="12">
-        <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
+        <f>IF($B5="BIG_SIDE",$G5+$J5+$BQ5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
         <v/>
       </c>
       <c r="AU5" s="12">
@@ -6239,19 +6948,43 @@
         <v/>
       </c>
       <c r="BL5">
-        <f>IF($D5&gt;0,IFERROR($V5/$D5,0),0)</f>
+        <f>IF($D5&gt;0,IFERROR($BQ5/$D5,0),0)</f>
         <v/>
       </c>
       <c r="BM5">
-        <f>IF($BN5&lt;=0,FALSE,$Y5&gt;=$BN5)</f>
+        <f>$BT5</f>
         <v/>
       </c>
       <c r="BN5">
-        <f>MAX(0,$W5*$BI5*Settings!$B$9)</f>
+        <f>MAX(0,$BR5*$BI5*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO5">
         <f>$Y5-$BN5</f>
+        <v/>
+      </c>
+      <c r="BP5">
+        <f>IF($B5="BIG_SIDE",IFERROR($T5/$U5,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ5">
+        <f>IF($B5="BIG_SIDE",MIN($D5,FLOOR(MAX(0,$BP5),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR5">
+        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$BQ5),$AJ5)</f>
+        <v/>
+      </c>
+      <c r="BS5">
+        <f>IF(AND($BP5&gt;0,$BP5&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT5">
+        <f>IF($Y5&gt;=$BN5,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU5">
+        <f>MAX(0,$BP5-$BQ5)</f>
         <v/>
       </c>
     </row>
@@ -6340,16 +7073,16 @@
         <v/>
       </c>
       <c r="V6" s="12">
-        <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
+        <f>$BQ6</f>
         <v>0</v>
       </c>
       <c r="W6" s="12">
-        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
+        <f>IF($B6="BIG_SIDE",$BR6,$AJ6)</f>
         <v/>
       </c>
       <c r="X6" s="19">
         <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6*Settings!$B$6,0),IF($S$6&gt;0,$S$6*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y6" s="19">
         <f>IF(ROW()=2,$X6,$Y5+$X6)</f>
@@ -6432,11 +7165,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS6" s="20">
-        <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
+        <f>IF($B6="BIG_SIDE",$BQ6*$U6,0)</f>
         <v>0</v>
       </c>
       <c r="AT6" s="12">
-        <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
+        <f>IF($B6="BIG_SIDE",$G6+$J6+$BQ6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
         <v/>
       </c>
       <c r="AU6" s="12">
@@ -6506,21 +7239,45 @@
         <v/>
       </c>
       <c r="BL6">
-        <f>IF($D6&gt;0,IFERROR($V6/$D6,0),0)</f>
+        <f>IF($D6&gt;0,IFERROR($BQ6/$D6,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM6" t="b">
-        <f>IF($BN6&lt;=0,FALSE,$Y6&gt;=$BN6)</f>
+        <f>$BT6</f>
         <v>0</v>
       </c>
       <c r="BN6">
-        <f>MAX(0,$W6*$BI6*Settings!$B$9)</f>
+        <f>MAX(0,$BR6*$BI6*Settings!$B$9)</f>
         <v>197.92</v>
       </c>
       <c r="BO6">
         <f>$Y6-$BN6</f>
         <v>-197.92</v>
       </c>
+      <c r="BP6">
+        <f>IF($B6="BIG_SIDE",IFERROR($T6/$U6,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <f>IF($B6="BIG_SIDE",MIN($D6,FLOOR(MAX(0,$BP6),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$BQ6),$AJ6)</f>
+        <v>0.9896</v>
+      </c>
+      <c r="BS6" t="str">
+        <f>IF(AND($BP6&gt;0,$BP6&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT6" t="str">
+        <f>IF($Y6&gt;=$BN6,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU6">
+        <f>MAX(0,$BP6-$BQ6)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
@@ -6607,16 +7364,16 @@
         <v/>
       </c>
       <c r="V7" s="12">
-        <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
+        <f>$BQ7</f>
         <v>0</v>
       </c>
       <c r="W7" s="12">
-        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
+        <f>IF($B7="BIG_SIDE",$BR7,$AJ7)</f>
         <v/>
       </c>
       <c r="X7" s="19">
         <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7*Settings!$B$6,0),IF($S$7&gt;0,$S$7*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y7" s="19">
         <f>IF(ROW()=2,$X7,$Y6+$X7)</f>
@@ -6699,11 +7456,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS7" s="20">
-        <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
+        <f>IF($B7="BIG_SIDE",$BQ7*$U7,0)</f>
         <v>0</v>
       </c>
       <c r="AT7" s="12">
-        <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
+        <f>IF($B7="BIG_SIDE",$G7+$J7+$BQ7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
         <v/>
       </c>
       <c r="AU7" s="12">
@@ -6773,21 +7530,45 @@
         <v/>
       </c>
       <c r="BL7">
-        <f>IF($D7&gt;0,IFERROR($V7/$D7,0),0)</f>
+        <f>IF($D7&gt;0,IFERROR($BQ7/$D7,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM7" t="b">
-        <f>IF($BN7&lt;=0,FALSE,$Y7&gt;=$BN7)</f>
+        <f>$BT7</f>
         <v>0</v>
       </c>
       <c r="BN7">
-        <f>MAX(0,$W7*$BI7*Settings!$B$9)</f>
+        <f>MAX(0,$BR7*$BI7*Settings!$B$9)</f>
         <v>197.92</v>
       </c>
       <c r="BO7">
         <f>$Y7-$BN7</f>
         <v>-197.92</v>
       </c>
+      <c r="BP7">
+        <f>IF($B7="BIG_SIDE",IFERROR($T7/$U7,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <f>IF($B7="BIG_SIDE",MIN($D7,FLOOR(MAX(0,$BP7),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$BQ7),$AJ7)</f>
+        <v>0.9896</v>
+      </c>
+      <c r="BS7" t="str">
+        <f>IF(AND($BP7&gt;0,$BP7&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT7" t="str">
+        <f>IF($Y7&gt;=$BN7,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU7">
+        <f>MAX(0,$BP7-$BQ7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
@@ -6874,16 +7655,16 @@
         <v/>
       </c>
       <c r="V8" s="12">
-        <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
+        <f>$BQ8</f>
         <v>0</v>
       </c>
       <c r="W8" s="12">
-        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
+        <f>IF($B8="BIG_SIDE",$BR8,$AJ8)</f>
         <v/>
       </c>
       <c r="X8" s="19">
         <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8*Settings!$B$6,0),IF($S$8&gt;0,$S$8*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y8" s="19">
         <f>IF(ROW()=2,$X8,$Y7+$X8)</f>
@@ -6966,11 +7747,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS8" s="20">
-        <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
+        <f>IF($B8="BIG_SIDE",$BQ8*$U8,0)</f>
         <v>0</v>
       </c>
       <c r="AT8" s="12">
-        <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
+        <f>IF($B8="BIG_SIDE",$G8+$J8+$BQ8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
         <v/>
       </c>
       <c r="AU8" s="12">
@@ -7040,21 +7821,45 @@
         <v/>
       </c>
       <c r="BL8">
-        <f>IF($D8&gt;0,IFERROR($V8/$D8,0),0)</f>
+        <f>IF($D8&gt;0,IFERROR($BQ8/$D8,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM8" t="b">
-        <f>IF($BN8&lt;=0,FALSE,$Y8&gt;=$BN8)</f>
+        <f>$BT8</f>
         <v>0</v>
       </c>
       <c r="BN8">
-        <f>MAX(0,$W8*$BI8*Settings!$B$9)</f>
+        <f>MAX(0,$BR8*$BI8*Settings!$B$9)</f>
         <v>197.92</v>
       </c>
       <c r="BO8">
         <f>$Y8-$BN8</f>
         <v>-197.92</v>
       </c>
+      <c r="BP8">
+        <f>IF($B8="BIG_SIDE",IFERROR($T8/$U8,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <f>IF($B8="BIG_SIDE",MIN($D8,FLOOR(MAX(0,$BP8),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$BQ8),$AJ8)</f>
+        <v>0.9896</v>
+      </c>
+      <c r="BS8" t="str">
+        <f>IF(AND($BP8&gt;0,$BP8&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT8" t="str">
+        <f>IF($Y8&gt;=$BN8,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU8">
+        <f>MAX(0,$BP8-$BQ8)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
@@ -7141,16 +7946,16 @@
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
+        <f>$BQ9</f>
         <v>0</v>
       </c>
       <c r="W9" s="12">
-        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
+        <f>IF($B9="BIG_SIDE",$BR9,$AJ9)</f>
         <v/>
       </c>
       <c r="X9" s="19">
         <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9*Settings!$B$6,0),IF($S$9&gt;0,$S$9*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y9" s="19">
         <f>IF(ROW()=2,$X9,$Y8+$X9)</f>
@@ -7233,11 +8038,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS9" s="20">
-        <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
+        <f>IF($B9="BIG_SIDE",$BQ9*$U9,0)</f>
         <v>0</v>
       </c>
       <c r="AT9" s="12">
-        <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
+        <f>IF($B9="BIG_SIDE",$G9+$J9+$BQ9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
         <v/>
       </c>
       <c r="AU9" s="12">
@@ -7307,21 +8112,45 @@
         <v/>
       </c>
       <c r="BL9">
-        <f>IF($D9&gt;0,IFERROR($V9/$D9,0),0)</f>
+        <f>IF($D9&gt;0,IFERROR($BQ9/$D9,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM9" t="b">
-        <f>IF($BN9&lt;=0,FALSE,$Y9&gt;=$BN9)</f>
+        <f>$BT9</f>
         <v>0</v>
       </c>
       <c r="BN9">
-        <f>MAX(0,$W9*$BI9*Settings!$B$9)</f>
+        <f>MAX(0,$BR9*$BI9*Settings!$B$9)</f>
         <v>197.92</v>
       </c>
       <c r="BO9">
         <f>$Y9-$BN9</f>
         <v>-197.92</v>
       </c>
+      <c r="BP9">
+        <f>IF($B9="BIG_SIDE",IFERROR($T9/$U9,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <f>IF($B9="BIG_SIDE",MIN($D9,FLOOR(MAX(0,$BP9),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$BQ9),$AJ9)</f>
+        <v>0.9896</v>
+      </c>
+      <c r="BS9" t="str">
+        <f>IF(AND($BP9&gt;0,$BP9&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT9" t="str">
+        <f>IF($Y9&gt;=$BN9,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU9">
+        <f>MAX(0,$BP9-$BQ9)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
@@ -7337,7 +8166,7 @@
       </c>
       <c r="D10" s="13">
         <f>IF($B10="BLOCKED",0,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),MAX($BA9,$BB9),IF($AP9="YES",MAX(0,$AG9),$D9)))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="E10" s="12">
         <f>IF($B10="BLOCKED","",IF($C10="SELL","BUY","SELL"))</f>
@@ -7408,16 +8237,16 @@
         <v/>
       </c>
       <c r="V10" s="12">
-        <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
+        <f>$BQ10</f>
         <v>0</v>
       </c>
       <c r="W10" s="12">
-        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
+        <f>IF($B10="BIG_SIDE",$BR10,$AJ10)</f>
         <v/>
       </c>
       <c r="X10" s="19">
         <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10*Settings!$B$6,0),IF($S$10&gt;0,$S$10*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y10" s="19">
         <f>IF(ROW()=2,$X10,$Y9+$X10)</f>
@@ -7500,11 +8329,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS10" s="20">
-        <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
+        <f>IF($B10="BIG_SIDE",$BQ10*$U10,0)</f>
         <v>0</v>
       </c>
       <c r="AT10" s="12">
-        <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
+        <f>IF($B10="BIG_SIDE",$G10+$J10+$BQ10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
         <v/>
       </c>
       <c r="AU10" s="12">
@@ -7574,21 +8403,45 @@
         <v/>
       </c>
       <c r="BL10">
-        <f>IF($D10&gt;0,IFERROR($V10/$D10,0),0)</f>
+        <f>IF($D10&gt;0,IFERROR($BQ10/$D10,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM10" t="b">
-        <f>IF($BN10&lt;=0,FALSE,$Y10&gt;=$BN10)</f>
+        <f>$BT10</f>
         <v>0</v>
       </c>
       <c r="BN10">
-        <f>MAX(0,$W10*$BI10*Settings!$B$9)</f>
+        <f>MAX(0,$BR10*$BI10*Settings!$B$9)</f>
         <v>197.92</v>
       </c>
       <c r="BO10">
         <f>$Y10-$BN10</f>
         <v>-197.92</v>
       </c>
+      <c r="BP10">
+        <f>IF($B10="BIG_SIDE",IFERROR($T10/$U10,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <f>IF($B10="BIG_SIDE",MIN($D10,FLOOR(MAX(0,$BP10),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$BQ10),$AJ10)</f>
+        <v>0.9896</v>
+      </c>
+      <c r="BS10" t="str">
+        <f>IF(AND($BP10&gt;0,$BP10&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT10" t="str">
+        <f>IF($Y10&gt;=$BN10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU10">
+        <f>MAX(0,$BP10-$BQ10)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
@@ -7675,16 +8528,16 @@
         <v/>
       </c>
       <c r="V11" s="12">
-        <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
+        <f>$BQ11</f>
         <v>0</v>
       </c>
       <c r="W11" s="12">
-        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
+        <f>IF($B11="BIG_SIDE",$BR11,$AJ11)</f>
         <v/>
       </c>
       <c r="X11" s="19">
         <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11*Settings!$B$6,0),IF($S$11&gt;0,$S$11*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y11" s="19">
         <f>IF(ROW()=2,$X11,$Y10+$X11)</f>
@@ -7767,11 +8620,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS11" s="20">
-        <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
+        <f>IF($B11="BIG_SIDE",$BQ11*$U11,0)</f>
         <v>0</v>
       </c>
       <c r="AT11" s="12">
-        <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
+        <f>IF($B11="BIG_SIDE",$G11+$J11+$BQ11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
         <v/>
       </c>
       <c r="AU11" s="12">
@@ -7841,20 +8694,44 @@
         <v/>
       </c>
       <c r="BL11">
-        <f>IF($D11&gt;0,IFERROR($V11/$D11,0),0)</f>
+        <f>IF($D11&gt;0,IFERROR($BQ11/$D11,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM11" t="b">
-        <f>IF($BN11&lt;=0,FALSE,$Y11&gt;=$BN11)</f>
+        <f>$BT11</f>
         <v>0</v>
       </c>
       <c r="BN11">
-        <f>MAX(0,$W11*$BI11*Settings!$B$9)</f>
+        <f>MAX(0,$BR11*$BI11*Settings!$B$9)</f>
         <v>197.92</v>
       </c>
       <c r="BO11">
         <f>$Y11-$BN11</f>
         <v>-197.92</v>
+      </c>
+      <c r="BP11">
+        <f>IF($B11="BIG_SIDE",IFERROR($T11/$U11,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <f>IF($B11="BIG_SIDE",MIN($D11,FLOOR(MAX(0,$BP11),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$BQ11),$AJ11)</f>
+        <v>0.9896</v>
+      </c>
+      <c r="BS11" t="str">
+        <f>IF(AND($BP11&gt;0,$BP11&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT11" t="str">
+        <f>IF($Y11&gt;=$BN11,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU11">
+        <f>MAX(0,$BP11-$BQ11)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7894,7 +8771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO11"/>
+  <dimension ref="A1:BU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7964,6 +8841,12 @@
     <col width="17" customWidth="1" min="65" max="65"/>
     <col width="15" customWidth="1" min="66" max="66"/>
     <col width="14" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="20" customWidth="1" min="69" max="69"/>
+    <col width="23" customWidth="1" min="70" max="70"/>
+    <col width="25" customWidth="1" min="71" max="71"/>
+    <col width="19" customWidth="1" min="72" max="72"/>
+    <col width="16" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8302,6 +9185,36 @@
           <t>FinalClosePL</t>
         </is>
       </c>
+      <c r="BP1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarLotRaw</t>
+        </is>
+      </c>
+      <c r="BQ1" s="38" t="inlineStr">
+        <is>
+          <t>CloseFarLotRounded</t>
+        </is>
+      </c>
+      <c r="BR1" s="38" t="inlineStr">
+        <is>
+          <t>FarRemainAfterRounded</t>
+        </is>
+      </c>
+      <c r="BS1" s="38" t="inlineStr">
+        <is>
+          <t>CannotCloseBelowLotStep</t>
+        </is>
+      </c>
+      <c r="BT1" s="38" t="inlineStr">
+        <is>
+          <t>FinalCloseAllowed</t>
+        </is>
+      </c>
+      <c r="BU1" s="38" t="inlineStr">
+        <is>
+          <t>LostToRounding</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -8391,12 +9304,12 @@
         <v>200</v>
       </c>
       <c r="V2" s="12">
-        <f>IF($B2="BIG_SIDE",IFERROR(MIN($D2,MAX(0,$T2/$U2)),0),0)</f>
-        <v>0.3735</v>
+        <f>$BQ2</f>
+        <v>0.37</v>
       </c>
       <c r="W2" s="12">
-        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$V2),$AJ2)</f>
-        <v>0.6265</v>
+        <f>IF($B2="BIG_SIDE",$BR2,$AJ2)</f>
+        <v>0.63</v>
       </c>
       <c r="X2" s="19">
         <f>IF($B2="BIG_SIDE",IF($AX$2&gt;0,$AX$2*Settings!$B$6,0),IF($S$2&gt;0,$S$2*Settings!$B$6,0))</f>
@@ -8411,7 +9324,7 @@
       </c>
       <c r="AA2" s="12">
         <f>IF($B2="BLOCKED",$Z2+$BF2,IF($B2="BIG_SIDE",$Z2+$S2-$AS2,IF($B2="SMALL_SIDE",$Z2+$S2+$AI2,$Z2+$S2)))</f>
-        <v>8.3</v>
+        <v>9</v>
       </c>
       <c r="AB2" s="12">
         <f>IF($B2="BLOCKED",$BC2,$D2+$G2+$J2)</f>
@@ -8482,11 +9395,11 @@
         <v/>
       </c>
       <c r="AS2" s="20">
-        <f>IF($B2="BIG_SIDE",$V2*$U2,0)</f>
-        <v>74.7</v>
+        <f>IF($B2="BIG_SIDE",$BQ2*$U2,0)</f>
+        <v>74</v>
       </c>
       <c r="AT2" s="12">
-        <f>IF($B2="BIG_SIDE",$G2+$J2+$V2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
+        <f>IF($B2="BIG_SIDE",$G2+$J2+$BQ2,IF($B2="SMALL_SIDE",$J2+$AL2+$AV2,0))</f>
         <v/>
       </c>
       <c r="AU2" s="12">
@@ -8556,20 +9469,44 @@
         <v>1</v>
       </c>
       <c r="BL2">
-        <f>IF($D2&gt;0,IFERROR($V2/$D2,0),0)</f>
-        <v>0.3735</v>
+        <f>IF($D2&gt;0,IFERROR($BQ2/$D2,0),0)</f>
+        <v>0.37</v>
       </c>
       <c r="BM2" t="b">
-        <f>IF($BN2&lt;=0,FALSE,$Y2&gt;=$BN2)</f>
+        <f>$BT2</f>
         <v>0</v>
       </c>
       <c r="BN2">
-        <f>MAX(0,$W2*$BI2*Settings!$B$9)</f>
-        <v>125.3</v>
+        <f>MAX(0,$BR2*$BI2*Settings!$B$9)</f>
+        <v>126</v>
       </c>
       <c r="BO2">
         <f>$Y2-$BN2</f>
-        <v>-117</v>
+        <v>-117.7</v>
+      </c>
+      <c r="BP2">
+        <f>IF($B2="BIG_SIDE",IFERROR($T2/$U2,0),0)</f>
+        <v>0.3735</v>
+      </c>
+      <c r="BQ2">
+        <f>IF($B2="BIG_SIDE",MIN($D2,FLOOR(MAX(0,$BP2),Settings!$B$11)),0)</f>
+        <v>0.37</v>
+      </c>
+      <c r="BR2">
+        <f>IF($B2="BIG_SIDE",MAX(0,$D2-$BQ2),$AJ2)</f>
+        <v>0.63</v>
+      </c>
+      <c r="BS2" t="str">
+        <f>IF(AND($BP2&gt;0,$BP2&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT2" t="str">
+        <f>IF($Y2&gt;=$BN2,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU2">
+        <f>MAX(0,$BP2-$BQ2)</f>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="3">
@@ -8657,11 +9594,11 @@
         <v/>
       </c>
       <c r="V3" s="12">
-        <f>IF($B3="BIG_SIDE",IFERROR(MIN($D3,MAX(0,$T3/$U3)),0),0)</f>
+        <f>$BQ3</f>
         <v/>
       </c>
       <c r="W3" s="12">
-        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$V3),$AJ3)</f>
+        <f>IF($B3="BIG_SIDE",$BR3,$AJ3)</f>
         <v/>
       </c>
       <c r="X3" s="19">
@@ -8749,11 +9686,11 @@
         <v>DUAL_TAIL: старый и новый хвост сохранены</v>
       </c>
       <c r="AS3" s="20">
-        <f>IF($B3="BIG_SIDE",$V3*$U3,0)</f>
+        <f>IF($B3="BIG_SIDE",$BQ3*$U3,0)</f>
         <v/>
       </c>
       <c r="AT3" s="12">
-        <f>IF($B3="BIG_SIDE",$G3+$J3+$V3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
+        <f>IF($B3="BIG_SIDE",$G3+$J3+$BQ3,IF($B3="SMALL_SIDE",$J3+$AL3+$AV3,0))</f>
         <v/>
       </c>
       <c r="AU3" s="12">
@@ -8823,19 +9760,43 @@
         <v/>
       </c>
       <c r="BL3">
-        <f>IF($D3&gt;0,IFERROR($V3/$D3,0),0)</f>
+        <f>IF($D3&gt;0,IFERROR($BQ3/$D3,0),0)</f>
         <v/>
       </c>
       <c r="BM3">
-        <f>IF($BN3&lt;=0,FALSE,$Y3&gt;=$BN3)</f>
+        <f>$BT3</f>
         <v/>
       </c>
       <c r="BN3">
-        <f>MAX(0,$W3*$BI3*Settings!$B$9)</f>
+        <f>MAX(0,$BR3*$BI3*Settings!$B$9)</f>
         <v/>
       </c>
       <c r="BO3">
         <f>$Y3-$BN3</f>
+        <v/>
+      </c>
+      <c r="BP3">
+        <f>IF($B3="BIG_SIDE",IFERROR($T3/$U3,0),0)</f>
+        <v/>
+      </c>
+      <c r="BQ3">
+        <f>IF($B3="BIG_SIDE",MIN($D3,FLOOR(MAX(0,$BP3),Settings!$B$11)),0)</f>
+        <v/>
+      </c>
+      <c r="BR3">
+        <f>IF($B3="BIG_SIDE",MAX(0,$D3-$BQ3),$AJ3)</f>
+        <v/>
+      </c>
+      <c r="BS3">
+        <f>IF(AND($BP3&gt;0,$BP3&lt;Settings!$B$11),"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BT3">
+        <f>IF($Y3&gt;=$BN3,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="BU3">
+        <f>MAX(0,$BP3-$BQ3)</f>
         <v/>
       </c>
     </row>
@@ -8924,16 +9885,16 @@
         <v/>
       </c>
       <c r="V4" s="12">
-        <f>IF($B4="BIG_SIDE",IFERROR(MIN($D4,MAX(0,$T4/$U4)),0),0)</f>
+        <f>$BQ4</f>
         <v>0</v>
       </c>
       <c r="W4" s="12">
-        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$V4),$AJ4)</f>
+        <f>IF($B4="BIG_SIDE",$BR4,$AJ4)</f>
         <v/>
       </c>
       <c r="X4" s="19">
         <f>IF($B4="BIG_SIDE",IF($AX$4&gt;0,$AX$4*Settings!$B$6,0),IF($S$4&gt;0,$S$4*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y4" s="19">
         <f>IF(ROW()=2,$X4,$Y3+$X4)</f>
@@ -9016,11 +9977,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS4" s="20">
-        <f>IF($B4="BIG_SIDE",$V4*$U4,0)</f>
+        <f>IF($B4="BIG_SIDE",$BQ4*$U4,0)</f>
         <v>0</v>
       </c>
       <c r="AT4" s="12">
-        <f>IF($B4="BIG_SIDE",$G4+$J4+$V4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
+        <f>IF($B4="BIG_SIDE",$G4+$J4+$BQ4,IF($B4="SMALL_SIDE",$J4+$AL4+$AV4,0))</f>
         <v/>
       </c>
       <c r="AU4" s="12">
@@ -9090,21 +10051,45 @@
         <v/>
       </c>
       <c r="BL4">
-        <f>IF($D4&gt;0,IFERROR($V4/$D4,0),0)</f>
+        <f>IF($D4&gt;0,IFERROR($BQ4/$D4,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM4" t="b">
-        <f>IF($BN4&lt;=0,FALSE,$Y4&gt;=$BN4)</f>
+        <f>$BT4</f>
         <v>0</v>
       </c>
       <c r="BN4">
-        <f>MAX(0,$W4*$BI4*Settings!$B$9)</f>
+        <f>MAX(0,$BR4*$BI4*Settings!$B$9)</f>
         <v>306.12</v>
       </c>
       <c r="BO4">
         <f>$Y4-$BN4</f>
         <v>-306.12</v>
       </c>
+      <c r="BP4">
+        <f>IF($B4="BIG_SIDE",IFERROR($T4/$U4,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <f>IF($B4="BIG_SIDE",MIN($D4,FLOOR(MAX(0,$BP4),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <f>IF($B4="BIG_SIDE",MAX(0,$D4-$BQ4),$AJ4)</f>
+        <v>1.5306</v>
+      </c>
+      <c r="BS4" t="str">
+        <f>IF(AND($BP4&gt;0,$BP4&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT4" t="str">
+        <f>IF($Y4&gt;=$BN4,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU4">
+        <f>MAX(0,$BP4-$BQ4)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
@@ -9191,16 +10176,16 @@
         <v/>
       </c>
       <c r="V5" s="12">
-        <f>IF($B5="BIG_SIDE",IFERROR(MIN($D5,MAX(0,$T5/$U5)),0),0)</f>
+        <f>$BQ5</f>
         <v>0</v>
       </c>
       <c r="W5" s="12">
-        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$V5),$AJ5)</f>
+        <f>IF($B5="BIG_SIDE",$BR5,$AJ5)</f>
         <v/>
       </c>
       <c r="X5" s="19">
         <f>IF($B5="BIG_SIDE",IF($AX$5&gt;0,$AX$5*Settings!$B$6,0),IF($S$5&gt;0,$S$5*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y5" s="19">
         <f>IF(ROW()=2,$X5,$Y4+$X5)</f>
@@ -9283,11 +10268,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS5" s="20">
-        <f>IF($B5="BIG_SIDE",$V5*$U5,0)</f>
+        <f>IF($B5="BIG_SIDE",$BQ5*$U5,0)</f>
         <v>0</v>
       </c>
       <c r="AT5" s="12">
-        <f>IF($B5="BIG_SIDE",$G5+$J5+$V5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
+        <f>IF($B5="BIG_SIDE",$G5+$J5+$BQ5,IF($B5="SMALL_SIDE",$J5+$AL5+$AV5,0))</f>
         <v/>
       </c>
       <c r="AU5" s="12">
@@ -9357,21 +10342,45 @@
         <v/>
       </c>
       <c r="BL5">
-        <f>IF($D5&gt;0,IFERROR($V5/$D5,0),0)</f>
+        <f>IF($D5&gt;0,IFERROR($BQ5/$D5,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM5" t="b">
-        <f>IF($BN5&lt;=0,FALSE,$Y5&gt;=$BN5)</f>
+        <f>$BT5</f>
         <v>0</v>
       </c>
       <c r="BN5">
-        <f>MAX(0,$W5*$BI5*Settings!$B$9)</f>
+        <f>MAX(0,$BR5*$BI5*Settings!$B$9)</f>
         <v>306.12</v>
       </c>
       <c r="BO5">
         <f>$Y5-$BN5</f>
         <v>-306.12</v>
       </c>
+      <c r="BP5">
+        <f>IF($B5="BIG_SIDE",IFERROR($T5/$U5,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <f>IF($B5="BIG_SIDE",MIN($D5,FLOOR(MAX(0,$BP5),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <f>IF($B5="BIG_SIDE",MAX(0,$D5-$BQ5),$AJ5)</f>
+        <v>1.5306</v>
+      </c>
+      <c r="BS5" t="str">
+        <f>IF(AND($BP5&gt;0,$BP5&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT5" t="str">
+        <f>IF($Y5&gt;=$BN5,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU5">
+        <f>MAX(0,$BP5-$BQ5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -9458,16 +10467,16 @@
         <v/>
       </c>
       <c r="V6" s="12">
-        <f>IF($B6="BIG_SIDE",IFERROR(MIN($D6,MAX(0,$T6/$U6)),0),0)</f>
+        <f>$BQ6</f>
         <v>0</v>
       </c>
       <c r="W6" s="12">
-        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$V6),$AJ6)</f>
+        <f>IF($B6="BIG_SIDE",$BR6,$AJ6)</f>
         <v/>
       </c>
       <c r="X6" s="19">
         <f>IF($B6="BIG_SIDE",IF($AX$6&gt;0,$AX$6*Settings!$B$6,0),IF($S$6&gt;0,$S$6*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y6" s="19">
         <f>IF(ROW()=2,$X6,$Y5+$X6)</f>
@@ -9550,11 +10559,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS6" s="20">
-        <f>IF($B6="BIG_SIDE",$V6*$U6,0)</f>
+        <f>IF($B6="BIG_SIDE",$BQ6*$U6,0)</f>
         <v>0</v>
       </c>
       <c r="AT6" s="12">
-        <f>IF($B6="BIG_SIDE",$G6+$J6+$V6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
+        <f>IF($B6="BIG_SIDE",$G6+$J6+$BQ6,IF($B6="SMALL_SIDE",$J6+$AL6+$AV6,0))</f>
         <v/>
       </c>
       <c r="AU6" s="12">
@@ -9624,21 +10633,45 @@
         <v/>
       </c>
       <c r="BL6">
-        <f>IF($D6&gt;0,IFERROR($V6/$D6,0),0)</f>
+        <f>IF($D6&gt;0,IFERROR($BQ6/$D6,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM6" t="b">
-        <f>IF($BN6&lt;=0,FALSE,$Y6&gt;=$BN6)</f>
+        <f>$BT6</f>
         <v>0</v>
       </c>
       <c r="BN6">
-        <f>MAX(0,$W6*$BI6*Settings!$B$9)</f>
+        <f>MAX(0,$BR6*$BI6*Settings!$B$9)</f>
         <v>306.12</v>
       </c>
       <c r="BO6">
         <f>$Y6-$BN6</f>
         <v>-306.12</v>
       </c>
+      <c r="BP6">
+        <f>IF($B6="BIG_SIDE",IFERROR($T6/$U6,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <f>IF($B6="BIG_SIDE",MIN($D6,FLOOR(MAX(0,$BP6),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <f>IF($B6="BIG_SIDE",MAX(0,$D6-$BQ6),$AJ6)</f>
+        <v>1.5306</v>
+      </c>
+      <c r="BS6" t="str">
+        <f>IF(AND($BP6&gt;0,$BP6&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT6" t="str">
+        <f>IF($Y6&gt;=$BN6,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU6">
+        <f>MAX(0,$BP6-$BQ6)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
@@ -9725,16 +10758,16 @@
         <v/>
       </c>
       <c r="V7" s="12">
-        <f>IF($B7="BIG_SIDE",IFERROR(MIN($D7,MAX(0,$T7/$U7)),0),0)</f>
+        <f>$BQ7</f>
         <v>0</v>
       </c>
       <c r="W7" s="12">
-        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$V7),$AJ7)</f>
+        <f>IF($B7="BIG_SIDE",$BR7,$AJ7)</f>
         <v/>
       </c>
       <c r="X7" s="19">
         <f>IF($B7="BIG_SIDE",IF($AX$7&gt;0,$AX$7*Settings!$B$6,0),IF($S$7&gt;0,$S$7*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y7" s="19">
         <f>IF(ROW()=2,$X7,$Y6+$X7)</f>
@@ -9817,11 +10850,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS7" s="20">
-        <f>IF($B7="BIG_SIDE",$V7*$U7,0)</f>
+        <f>IF($B7="BIG_SIDE",$BQ7*$U7,0)</f>
         <v>0</v>
       </c>
       <c r="AT7" s="12">
-        <f>IF($B7="BIG_SIDE",$G7+$J7+$V7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
+        <f>IF($B7="BIG_SIDE",$G7+$J7+$BQ7,IF($B7="SMALL_SIDE",$J7+$AL7+$AV7,0))</f>
         <v/>
       </c>
       <c r="AU7" s="12">
@@ -9891,21 +10924,45 @@
         <v/>
       </c>
       <c r="BL7">
-        <f>IF($D7&gt;0,IFERROR($V7/$D7,0),0)</f>
+        <f>IF($D7&gt;0,IFERROR($BQ7/$D7,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM7" t="b">
-        <f>IF($BN7&lt;=0,FALSE,$Y7&gt;=$BN7)</f>
+        <f>$BT7</f>
         <v>0</v>
       </c>
       <c r="BN7">
-        <f>MAX(0,$W7*$BI7*Settings!$B$9)</f>
+        <f>MAX(0,$BR7*$BI7*Settings!$B$9)</f>
         <v>306.12</v>
       </c>
       <c r="BO7">
         <f>$Y7-$BN7</f>
         <v>-306.12</v>
       </c>
+      <c r="BP7">
+        <f>IF($B7="BIG_SIDE",IFERROR($T7/$U7,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <f>IF($B7="BIG_SIDE",MIN($D7,FLOOR(MAX(0,$BP7),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <f>IF($B7="BIG_SIDE",MAX(0,$D7-$BQ7),$AJ7)</f>
+        <v>1.5306</v>
+      </c>
+      <c r="BS7" t="str">
+        <f>IF(AND($BP7&gt;0,$BP7&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT7" t="str">
+        <f>IF($Y7&gt;=$BN7,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU7">
+        <f>MAX(0,$BP7-$BQ7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
@@ -9992,16 +11049,16 @@
         <v/>
       </c>
       <c r="V8" s="12">
-        <f>IF($B8="BIG_SIDE",IFERROR(MIN($D8,MAX(0,$T8/$U8)),0),0)</f>
+        <f>$BQ8</f>
         <v>0</v>
       </c>
       <c r="W8" s="12">
-        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$V8),$AJ8)</f>
+        <f>IF($B8="BIG_SIDE",$BR8,$AJ8)</f>
         <v/>
       </c>
       <c r="X8" s="19">
         <f>IF($B8="BIG_SIDE",IF($AX$8&gt;0,$AX$8*Settings!$B$6,0),IF($S$8&gt;0,$S$8*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y8" s="19">
         <f>IF(ROW()=2,$X8,$Y7+$X8)</f>
@@ -10084,11 +11141,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS8" s="20">
-        <f>IF($B8="BIG_SIDE",$V8*$U8,0)</f>
+        <f>IF($B8="BIG_SIDE",$BQ8*$U8,0)</f>
         <v>0</v>
       </c>
       <c r="AT8" s="12">
-        <f>IF($B8="BIG_SIDE",$G8+$J8+$V8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
+        <f>IF($B8="BIG_SIDE",$G8+$J8+$BQ8,IF($B8="SMALL_SIDE",$J8+$AL8+$AV8,0))</f>
         <v/>
       </c>
       <c r="AU8" s="12">
@@ -10158,21 +11215,45 @@
         <v/>
       </c>
       <c r="BL8">
-        <f>IF($D8&gt;0,IFERROR($V8/$D8,0),0)</f>
+        <f>IF($D8&gt;0,IFERROR($BQ8/$D8,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM8" t="b">
-        <f>IF($BN8&lt;=0,FALSE,$Y8&gt;=$BN8)</f>
+        <f>$BT8</f>
         <v>0</v>
       </c>
       <c r="BN8">
-        <f>MAX(0,$W8*$BI8*Settings!$B$9)</f>
+        <f>MAX(0,$BR8*$BI8*Settings!$B$9)</f>
         <v>306.12</v>
       </c>
       <c r="BO8">
         <f>$Y8-$BN8</f>
         <v>-306.12</v>
       </c>
+      <c r="BP8">
+        <f>IF($B8="BIG_SIDE",IFERROR($T8/$U8,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <f>IF($B8="BIG_SIDE",MIN($D8,FLOOR(MAX(0,$BP8),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <f>IF($B8="BIG_SIDE",MAX(0,$D8-$BQ8),$AJ8)</f>
+        <v>1.5306</v>
+      </c>
+      <c r="BS8" t="str">
+        <f>IF(AND($BP8&gt;0,$BP8&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT8" t="str">
+        <f>IF($Y8&gt;=$BN8,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU8">
+        <f>MAX(0,$BP8-$BQ8)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
@@ -10259,16 +11340,16 @@
         <v/>
       </c>
       <c r="V9" s="12">
-        <f>IF($B9="BIG_SIDE",IFERROR(MIN($D9,MAX(0,$T9/$U9)),0),0)</f>
+        <f>$BQ9</f>
         <v>0</v>
       </c>
       <c r="W9" s="12">
-        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$V9),$AJ9)</f>
+        <f>IF($B9="BIG_SIDE",$BR9,$AJ9)</f>
         <v/>
       </c>
       <c r="X9" s="19">
         <f>IF($B9="BIG_SIDE",IF($AX$9&gt;0,$AX$9*Settings!$B$6,0),IF($S$9&gt;0,$S$9*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y9" s="19">
         <f>IF(ROW()=2,$X9,$Y8+$X9)</f>
@@ -10351,11 +11432,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS9" s="20">
-        <f>IF($B9="BIG_SIDE",$V9*$U9,0)</f>
+        <f>IF($B9="BIG_SIDE",$BQ9*$U9,0)</f>
         <v>0</v>
       </c>
       <c r="AT9" s="12">
-        <f>IF($B9="BIG_SIDE",$G9+$J9+$V9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
+        <f>IF($B9="BIG_SIDE",$G9+$J9+$BQ9,IF($B9="SMALL_SIDE",$J9+$AL9+$AV9,0))</f>
         <v/>
       </c>
       <c r="AU9" s="12">
@@ -10425,21 +11506,45 @@
         <v/>
       </c>
       <c r="BL9">
-        <f>IF($D9&gt;0,IFERROR($V9/$D9,0),0)</f>
+        <f>IF($D9&gt;0,IFERROR($BQ9/$D9,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM9" t="b">
-        <f>IF($BN9&lt;=0,FALSE,$Y9&gt;=$BN9)</f>
+        <f>$BT9</f>
         <v>0</v>
       </c>
       <c r="BN9">
-        <f>MAX(0,$W9*$BI9*Settings!$B$9)</f>
+        <f>MAX(0,$BR9*$BI9*Settings!$B$9)</f>
         <v>306.12</v>
       </c>
       <c r="BO9">
         <f>$Y9-$BN9</f>
         <v>-306.12</v>
       </c>
+      <c r="BP9">
+        <f>IF($B9="BIG_SIDE",IFERROR($T9/$U9,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <f>IF($B9="BIG_SIDE",MIN($D9,FLOOR(MAX(0,$BP9),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <f>IF($B9="BIG_SIDE",MAX(0,$D9-$BQ9),$AJ9)</f>
+        <v>1.5306</v>
+      </c>
+      <c r="BS9" t="str">
+        <f>IF(AND($BP9&gt;0,$BP9&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT9" t="str">
+        <f>IF($Y9&gt;=$BN9,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU9">
+        <f>MAX(0,$BP9-$BQ9)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
@@ -10455,7 +11560,7 @@
       </c>
       <c r="D10" s="13">
         <f>IF($B10="BLOCKED",0,IF(AND($AQ9="MANUAL_READY",$BG9="YES"),MAX($BA9,$BB9),IF($AP9="YES",MAX(0,$AG9),$D9)))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="E10" s="12">
         <f>IF($B10="BLOCKED","",IF($C10="SELL","BUY","SELL"))</f>
@@ -10526,16 +11631,16 @@
         <v/>
       </c>
       <c r="V10" s="12">
-        <f>IF($B10="BIG_SIDE",IFERROR(MIN($D10,MAX(0,$T10/$U10)),0),0)</f>
+        <f>$BQ10</f>
         <v>0</v>
       </c>
       <c r="W10" s="12">
-        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$V10),$AJ10)</f>
+        <f>IF($B10="BIG_SIDE",$BR10,$AJ10)</f>
         <v/>
       </c>
       <c r="X10" s="19">
         <f>IF($B10="BIG_SIDE",IF($AX$10&gt;0,$AX$10*Settings!$B$6,0),IF($S$10&gt;0,$S$10*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y10" s="19">
         <f>IF(ROW()=2,$X10,$Y9+$X10)</f>
@@ -10618,11 +11723,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS10" s="20">
-        <f>IF($B10="BIG_SIDE",$V10*$U10,0)</f>
+        <f>IF($B10="BIG_SIDE",$BQ10*$U10,0)</f>
         <v>0</v>
       </c>
       <c r="AT10" s="12">
-        <f>IF($B10="BIG_SIDE",$G10+$J10+$V10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
+        <f>IF($B10="BIG_SIDE",$G10+$J10+$BQ10,IF($B10="SMALL_SIDE",$J10+$AL10+$AV10,0))</f>
         <v/>
       </c>
       <c r="AU10" s="12">
@@ -10692,21 +11797,45 @@
         <v/>
       </c>
       <c r="BL10">
-        <f>IF($D10&gt;0,IFERROR($V10/$D10,0),0)</f>
+        <f>IF($D10&gt;0,IFERROR($BQ10/$D10,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM10" t="b">
-        <f>IF($BN10&lt;=0,FALSE,$Y10&gt;=$BN10)</f>
+        <f>$BT10</f>
         <v>0</v>
       </c>
       <c r="BN10">
-        <f>MAX(0,$W10*$BI10*Settings!$B$9)</f>
+        <f>MAX(0,$BR10*$BI10*Settings!$B$9)</f>
         <v>306.12</v>
       </c>
       <c r="BO10">
         <f>$Y10-$BN10</f>
         <v>-306.12</v>
       </c>
+      <c r="BP10">
+        <f>IF($B10="BIG_SIDE",IFERROR($T10/$U10,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <f>IF($B10="BIG_SIDE",MIN($D10,FLOOR(MAX(0,$BP10),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <f>IF($B10="BIG_SIDE",MAX(0,$D10-$BQ10),$AJ10)</f>
+        <v>1.5306</v>
+      </c>
+      <c r="BS10" t="str">
+        <f>IF(AND($BP10&gt;0,$BP10&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT10" t="str">
+        <f>IF($Y10&gt;=$BN10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU10">
+        <f>MAX(0,$BP10-$BQ10)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
@@ -10793,16 +11922,16 @@
         <v/>
       </c>
       <c r="V11" s="12">
-        <f>IF($B11="BIG_SIDE",IFERROR(MIN($D11,MAX(0,$T11/$U11)),0),0)</f>
+        <f>$BQ11</f>
         <v>0</v>
       </c>
       <c r="W11" s="12">
-        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$V11),$AJ11)</f>
+        <f>IF($B11="BIG_SIDE",$BR11,$AJ11)</f>
         <v/>
       </c>
       <c r="X11" s="19">
         <f>IF($B11="BIG_SIDE",IF($AX$11&gt;0,$AX$11*Settings!$B$6,0),IF($S$11&gt;0,$S$11*Settings!$B$6,0))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y11" s="19">
         <f>IF(ROW()=2,$X11,$Y10+$X11)</f>
@@ -10885,11 +12014,11 @@
         <v>Заблокировано: DUAL_TAIL сохраняет оба хвоста до ручного закрытия</v>
       </c>
       <c r="AS11" s="20">
-        <f>IF($B11="BIG_SIDE",$V11*$U11,0)</f>
+        <f>IF($B11="BIG_SIDE",$BQ11*$U11,0)</f>
         <v>0</v>
       </c>
       <c r="AT11" s="12">
-        <f>IF($B11="BIG_SIDE",$G11+$J11+$V11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
+        <f>IF($B11="BIG_SIDE",$G11+$J11+$BQ11,IF($B11="SMALL_SIDE",$J11+$AL11+$AV11,0))</f>
         <v/>
       </c>
       <c r="AU11" s="12">
@@ -10959,20 +12088,44 @@
         <v/>
       </c>
       <c r="BL11">
-        <f>IF($D11&gt;0,IFERROR($V11/$D11,0),0)</f>
+        <f>IF($D11&gt;0,IFERROR($BQ11/$D11,0),0)</f>
         <v>0</v>
       </c>
       <c r="BM11" t="b">
-        <f>IF($BN11&lt;=0,FALSE,$Y11&gt;=$BN11)</f>
+        <f>$BT11</f>
         <v>0</v>
       </c>
       <c r="BN11">
-        <f>MAX(0,$W11*$BI11*Settings!$B$9)</f>
+        <f>MAX(0,$BR11*$BI11*Settings!$B$9)</f>
         <v>306.12</v>
       </c>
       <c r="BO11">
         <f>$Y11-$BN11</f>
         <v>-306.12</v>
+      </c>
+      <c r="BP11">
+        <f>IF($B11="BIG_SIDE",IFERROR($T11/$U11,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <f>IF($B11="BIG_SIDE",MIN($D11,FLOOR(MAX(0,$BP11),Settings!$B$11)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <f>IF($B11="BIG_SIDE",MAX(0,$D11-$BQ11),$AJ11)</f>
+        <v>1.5306</v>
+      </c>
+      <c r="BS11" t="str">
+        <f>IF(AND($BP11&gt;0,$BP11&lt;Settings!$B$11),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BT11" t="str">
+        <f>IF($Y11&gt;=$BN11,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="BU11">
+        <f>MAX(0,$BP11-$BQ11)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11012,7 +12165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11748,11 +12901,11 @@
       </c>
       <c r="C38">
         <f>SUM(Calculator!AS2:AS11,Trend_UP!AS2:AS11,Trend_DOWN!AS2:AS11)</f>
-        <v>74.7</v>
+        <v>74</v>
       </c>
       <c r="D38">
         <f>C38</f>
-        <v>74.7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39">
@@ -11788,11 +12941,11 @@
       </c>
       <c r="C40">
         <f>LOOKUP(2,1/(Calculator!W2:W11&lt;&gt;""),Calculator!W2:W11)</f>
-        <v>0.6265</v>
+        <v>0.63</v>
       </c>
       <c r="D40">
         <f>C40</f>
-        <v>0.6265</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="41">
@@ -11808,11 +12961,11 @@
       </c>
       <c r="C41">
         <f>LOOKUP(2,1/(Calculator!BN2:BN11&lt;&gt;""),Calculator!BN2:BN11)</f>
-        <v>125.3</v>
+        <v>126</v>
       </c>
       <c r="D41">
         <f>C41</f>
-        <v>125.3</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42">
@@ -11848,11 +13001,131 @@
       </c>
       <c r="C43">
         <f>LOOKUP(2,1/(Calculator!BO2:BO11&lt;&gt;""),Calculator!BO2:BO11)</f>
-        <v>-117</v>
+        <v>-117.7</v>
       </c>
       <c r="D43">
         <f>C43</f>
-        <v>-117</v>
+        <v>-117.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total CloseFarLotRaw</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LotStep Rounding Risk Checks</t>
+        </is>
+      </c>
+      <c r="C44">
+        <f>SUM(Calculator!BP2:BP11,Trend_UP!BP2:BP11,Trend_DOWN!BP2:BP11)</f>
+        <v>0.3735</v>
+      </c>
+      <c r="D44">
+        <f>C44</f>
+        <v>0.3735</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total CloseFarLotRounded</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LotStep Rounding Risk Checks</t>
+        </is>
+      </c>
+      <c r="C45">
+        <f>SUM(Calculator!BQ2:BQ11,Trend_UP!BQ2:BQ11,Trend_DOWN!BQ2:BQ11)</f>
+        <v>0.37</v>
+      </c>
+      <c r="D45">
+        <f>C45</f>
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total LostToRounding</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LotStep Rounding Risk Checks</t>
+        </is>
+      </c>
+      <c r="C46">
+        <f>SUM(Calculator!BU2:BU11,Trend_UP!BU2:BU11,Trend_DOWN!BU2:BU11)</f>
+        <v>0.0035</v>
+      </c>
+      <c r="D46">
+        <f>C46</f>
+        <v>0.0035</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Final FarRemainAfterRounded</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LotStep Rounding Risk Checks</t>
+        </is>
+      </c>
+      <c r="C47">
+        <f>LOOKUP(2,1/(Calculator!BR2:BR11&lt;&gt;""),Calculator!BR2:BR11)</f>
+        <v>0.63</v>
+      </c>
+      <c r="D47">
+        <f>C47</f>
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CannotCloseBelowLotStep Count</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LotStep Rounding Risk Checks</t>
+        </is>
+      </c>
+      <c r="C48">
+        <f>COUNTIF(Calculator!BS2:BS11,"YES")+COUNTIF(Trend_UP!BS2:BS11,"YES")+COUNTIF(Trend_DOWN!BS2:BS11,"YES")</f>
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <f>C48</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FinalCloseAllowed Count</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LotStep Rounding Risk Checks</t>
+        </is>
+      </c>
+      <c r="C49">
+        <f>COUNTIF(Calculator!BT2:BT11,"YES")+COUNTIF(Trend_UP!BT2:BT11,"YES")+COUNTIF(Trend_DOWN!BT2:BT11,"YES")</f>
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <f>C49</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
